--- a/data/50001533 - GESVIAL.xlsx
+++ b/data/50001533 - GESVIAL.xlsx
@@ -1592,13 +1592,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46118.495183391206</v>
+        <v>46118.66185005787</v>
       </c>
       <c r="C4" s="5">
-        <v>46129.394169652776</v>
+        <v>46129.56083631945</v>
       </c>
       <c r="D4" s="5">
-        <v>46147.847120624996</v>
+        <v>46148.01378729167</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1641,13 +1641,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46118.49534550926</v>
+        <v>46118.662012175926</v>
       </c>
       <c r="C5" s="8">
-        <v>46129.393189814815</v>
+        <v>46129.559856481486</v>
       </c>
       <c r="D5" s="8">
-        <v>46133.710560625</v>
+        <v>46133.87722729167</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1706,13 +1706,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46118.49534890046</v>
+        <v>46118.662015567126</v>
       </c>
       <c r="C6" s="5">
-        <v>46129.39325076389</v>
+        <v>46129.55991743055</v>
       </c>
       <c r="D6" s="5">
-        <v>46129.393267453706</v>
+        <v>46129.55993412037</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -1771,13 +1771,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="8">
-        <v>46118.49535210648</v>
+        <v>46118.662018773146</v>
       </c>
       <c r="C7" s="8">
-        <v>46129.39360674769</v>
+        <v>46129.56027341435</v>
       </c>
       <c r="D7" s="8">
-        <v>46129.39362375</v>
+        <v>46129.560290416666</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>38</v>
@@ -1836,13 +1836,13 @@
         <v>40</v>
       </c>
       <c r="B8" s="5">
-        <v>46118.49535528936</v>
+        <v>46118.66202195601</v>
       </c>
       <c r="C8" s="5">
-        <v>46129.39401967592</v>
+        <v>46129.56068634259</v>
       </c>
       <c r="D8" s="5">
-        <v>46129.39403539352</v>
+        <v>46129.56070206019</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>41</v>
@@ -1901,13 +1901,13 @@
         <v>44</v>
       </c>
       <c r="B9" s="8">
-        <v>46118.495359479166</v>
+        <v>46118.66202614583</v>
       </c>
       <c r="C9" s="8">
-        <v>46129.39415508102</v>
+        <v>46129.560821747684</v>
       </c>
       <c r="D9" s="8">
-        <v>46156.67195390046</v>
+        <v>46156.83862056713</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>45</v>
@@ -1966,11 +1966,11 @@
         <v>47</v>
       </c>
       <c r="B10" s="5">
-        <v>46118.49518951389</v>
+        <v>46118.66185618055</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46129.40463821759</v>
+        <v>46129.57130488426</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>48</v>
@@ -2013,13 +2013,13 @@
         <v>50</v>
       </c>
       <c r="B11" s="8">
-        <v>46118.495363379625</v>
+        <v>46118.6620300463</v>
       </c>
       <c r="C11" s="8">
-        <v>46129.40463276621</v>
+        <v>46129.57129943287</v>
       </c>
       <c r="D11" s="8">
-        <v>46129.40464815972</v>
+        <v>46129.57131482639</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>51</v>
@@ -2078,11 +2078,11 @@
         <v>56</v>
       </c>
       <c r="B12" s="5">
-        <v>46118.49536912037</v>
+        <v>46118.66203578704</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46133.734291967594</v>
+        <v>46133.90095863426</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>57</v>
@@ -2141,11 +2141,11 @@
         <v>61</v>
       </c>
       <c r="B13" s="8">
-        <v>46118.495194097224</v>
+        <v>46118.66186076389</v>
       </c>
       <c r="C13" s="9"/>
       <c r="D13" s="8">
-        <v>46129.40046122685</v>
+        <v>46129.56712789352</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>62</v>
@@ -2188,13 +2188,13 @@
         <v>64</v>
       </c>
       <c r="B14" s="5">
-        <v>46118.49537506944</v>
+        <v>46118.66204173611</v>
       </c>
       <c r="C14" s="5">
-        <v>46129.395261620375</v>
+        <v>46129.56192828703</v>
       </c>
       <c r="D14" s="5">
-        <v>46129.39527554398</v>
+        <v>46129.56194221065</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>65</v>
@@ -2253,13 +2253,13 @@
         <v>68</v>
       </c>
       <c r="B15" s="8">
-        <v>46118.49538085648</v>
+        <v>46118.66204752315</v>
       </c>
       <c r="C15" s="8">
-        <v>46129.39527212963</v>
+        <v>46129.561938796294</v>
       </c>
       <c r="D15" s="8">
-        <v>46129.39528736111</v>
+        <v>46129.56195402778</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>69</v>
@@ -2318,13 +2318,13 @@
         <v>72</v>
       </c>
       <c r="B16" s="5">
-        <v>46118.49538628472</v>
+        <v>46118.66205295139</v>
       </c>
       <c r="C16" s="5">
-        <v>46129.40045137731</v>
+        <v>46129.56711804398</v>
       </c>
       <c r="D16" s="5">
-        <v>46141.71619153935</v>
+        <v>46141.88285820602</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>73</v>
@@ -2383,11 +2383,11 @@
         <v>76</v>
       </c>
       <c r="B17" s="8">
-        <v>46118.49539210648</v>
+        <v>46118.662058773145</v>
       </c>
       <c r="C17" s="9"/>
       <c r="D17" s="8">
-        <v>46129.40046981482</v>
+        <v>46129.56713648148</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>77</v>
@@ -2446,13 +2446,13 @@
         <v>81</v>
       </c>
       <c r="B18" s="5">
-        <v>46118.495199490746</v>
+        <v>46118.6618661574</v>
       </c>
       <c r="C18" s="5">
-        <v>46184.563075972226</v>
+        <v>46184.72974263889</v>
       </c>
       <c r="D18" s="5">
-        <v>46184.563077349536</v>
+        <v>46184.72974401621</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>82</v>
@@ -2495,13 +2495,13 @@
         <v>84</v>
       </c>
       <c r="B19" s="8">
-        <v>46118.495399872685</v>
+        <v>46118.66206653936</v>
       </c>
       <c r="C19" s="8">
-        <v>46129.395672175924</v>
+        <v>46129.56233884259</v>
       </c>
       <c r="D19" s="8">
-        <v>46129.3956940625</v>
+        <v>46129.56236072916</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>85</v>
@@ -2560,13 +2560,13 @@
         <v>88</v>
       </c>
       <c r="B20" s="5">
-        <v>46118.49540508102</v>
+        <v>46118.66207174768</v>
       </c>
       <c r="C20" s="5">
-        <v>46129.39567921296</v>
+        <v>46129.56234587963</v>
       </c>
       <c r="D20" s="5">
-        <v>46129.39570070602</v>
+        <v>46129.56236737268</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>89</v>
@@ -2625,13 +2625,13 @@
         <v>91</v>
       </c>
       <c r="B21" s="8">
-        <v>46118.49541042824</v>
+        <v>46118.66207709491</v>
       </c>
       <c r="C21" s="8">
-        <v>46129.40467122685</v>
+        <v>46129.57133789352</v>
       </c>
       <c r="D21" s="8">
-        <v>46129.40468762731</v>
+        <v>46129.57135429398</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>92</v>
@@ -2690,13 +2690,13 @@
         <v>95</v>
       </c>
       <c r="B22" s="5">
-        <v>46118.49541564815</v>
+        <v>46118.66208231481</v>
       </c>
       <c r="C22" s="5">
-        <v>46183.71343438658</v>
+        <v>46183.88010105324</v>
       </c>
       <c r="D22" s="5">
-        <v>46183.71343625</v>
+        <v>46183.880102916664</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>96</v>
@@ -2755,13 +2755,13 @@
         <v>99</v>
       </c>
       <c r="B23" s="8">
-        <v>46118.49542085648</v>
+        <v>46118.662087523146</v>
       </c>
       <c r="C23" s="8">
-        <v>46183.72138519676</v>
+        <v>46183.888051863425</v>
       </c>
       <c r="D23" s="8">
-        <v>46183.721584768515</v>
+        <v>46183.888251435186</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>100</v>
@@ -2820,13 +2820,13 @@
         <v>105</v>
       </c>
       <c r="B24" s="5">
-        <v>46118.49520528935</v>
+        <v>46118.66187195602</v>
       </c>
       <c r="C24" s="5">
-        <v>46184.5195800463</v>
+        <v>46184.68624671296</v>
       </c>
       <c r="D24" s="5">
-        <v>46184.51958140046</v>
+        <v>46184.686248067126</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>106</v>
@@ -2869,13 +2869,13 @@
         <v>108</v>
       </c>
       <c r="B25" s="8">
-        <v>46118.49542702547</v>
+        <v>46118.662093692124</v>
       </c>
       <c r="C25" s="8">
-        <v>46182.509780231485</v>
+        <v>46182.67644689815</v>
       </c>
       <c r="D25" s="8">
-        <v>46182.50978262731</v>
+        <v>46182.676449293984</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>109</v>
@@ -2934,13 +2934,13 @@
         <v>113</v>
       </c>
       <c r="B26" s="5">
-        <v>46118.495431793985</v>
+        <v>46118.66209846065</v>
       </c>
       <c r="C26" s="5">
-        <v>46174.4590187037</v>
+        <v>46174.62568537037</v>
       </c>
       <c r="D26" s="5">
-        <v>46174.45902023149</v>
+        <v>46174.62568689814</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>114</v>
@@ -2989,13 +2989,13 @@
         <v>116</v>
       </c>
       <c r="B27" s="8">
-        <v>46118.49543604167</v>
+        <v>46118.66210270833</v>
       </c>
       <c r="C27" s="8">
-        <v>46182.476623263894</v>
+        <v>46182.64328993055</v>
       </c>
       <c r="D27" s="8">
-        <v>46182.47662475695</v>
+        <v>46182.64329142361</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>117</v>
@@ -3044,13 +3044,13 @@
         <v>119</v>
       </c>
       <c r="B28" s="5">
-        <v>46118.4954403125</v>
+        <v>46118.662106979165</v>
       </c>
       <c r="C28" s="5">
-        <v>46182.47440028936</v>
+        <v>46182.641066956014</v>
       </c>
       <c r="D28" s="5">
-        <v>46182.47440253472</v>
+        <v>46182.64106920139</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>120</v>
@@ -3109,13 +3109,13 @@
         <v>122</v>
       </c>
       <c r="B29" s="8">
-        <v>46118.49544542824</v>
+        <v>46118.662112094906</v>
       </c>
       <c r="C29" s="8">
-        <v>46174.459855</v>
+        <v>46174.626521666665</v>
       </c>
       <c r="D29" s="8">
-        <v>46174.45985648148</v>
+        <v>46174.62652314815</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>123</v>
@@ -3170,13 +3170,13 @@
         <v>125</v>
       </c>
       <c r="B30" s="5">
-        <v>46118.4954502662</v>
+        <v>46118.66211693287</v>
       </c>
       <c r="C30" s="5">
-        <v>46174.45996375</v>
+        <v>46174.626630416664</v>
       </c>
       <c r="D30" s="5">
-        <v>46174.45996519676</v>
+        <v>46174.62663186343</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>126</v>
@@ -3231,13 +3231,13 @@
         <v>128</v>
       </c>
       <c r="B31" s="8">
-        <v>46118.495455358796</v>
+        <v>46118.66212202546</v>
       </c>
       <c r="C31" s="8">
-        <v>46184.519414780094</v>
+        <v>46184.68608144676</v>
       </c>
       <c r="D31" s="8">
-        <v>46184.519416574076</v>
+        <v>46184.68608324074</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>129</v>
@@ -3296,13 +3296,13 @@
         <v>131</v>
       </c>
       <c r="B32" s="5">
-        <v>46118.495460011574</v>
+        <v>46118.662126678246</v>
       </c>
       <c r="C32" s="5">
-        <v>46184.519052372685</v>
+        <v>46184.68571903935</v>
       </c>
       <c r="D32" s="5">
-        <v>46184.519054143515</v>
+        <v>46184.68572081019</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>132</v>
@@ -3357,13 +3357,13 @@
         <v>134</v>
       </c>
       <c r="B33" s="8">
-        <v>46118.495464594904</v>
+        <v>46118.662131261575</v>
       </c>
       <c r="C33" s="8">
-        <v>46184.519122233796</v>
+        <v>46184.68578890046</v>
       </c>
       <c r="D33" s="8">
-        <v>46184.51912386574</v>
+        <v>46184.68579053241</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>135</v>
@@ -3418,13 +3418,13 @@
         <v>137</v>
       </c>
       <c r="B34" s="5">
-        <v>46118.49551706019</v>
+        <v>46118.66218372685</v>
       </c>
       <c r="C34" s="5">
-        <v>46156.654673321755</v>
+        <v>46156.821339988426</v>
       </c>
       <c r="D34" s="5">
-        <v>46169.657316111116</v>
+        <v>46169.82398277777</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>138</v>
@@ -3483,13 +3483,13 @@
         <v>140</v>
       </c>
       <c r="B35" s="8">
-        <v>46118.4955234375</v>
+        <v>46118.662190104165</v>
       </c>
       <c r="C35" s="8">
-        <v>46134.624486030094</v>
+        <v>46134.79115269676</v>
       </c>
       <c r="D35" s="8">
-        <v>46169.65732769676</v>
+        <v>46169.823994363425</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>141</v>
@@ -3544,13 +3544,13 @@
         <v>143</v>
       </c>
       <c r="B36" s="5">
-        <v>46118.49552902778</v>
+        <v>46118.662195694444</v>
       </c>
       <c r="C36" s="5">
-        <v>46155.736021006946</v>
+        <v>46155.90268767361</v>
       </c>
       <c r="D36" s="5">
-        <v>46169.657349201385</v>
+        <v>46169.82401586806</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>144</v>
@@ -3605,13 +3605,13 @@
         <v>146</v>
       </c>
       <c r="B37" s="8">
-        <v>46118.495534155096</v>
+        <v>46118.66220082176</v>
       </c>
       <c r="C37" s="8">
-        <v>46134.624528726854</v>
+        <v>46134.79119539352</v>
       </c>
       <c r="D37" s="8">
-        <v>46169.65736949074</v>
+        <v>46169.824036157406</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>147</v>
@@ -3666,13 +3666,13 @@
         <v>149</v>
       </c>
       <c r="B38" s="5">
-        <v>46118.495539675925</v>
+        <v>46118.66220634259</v>
       </c>
       <c r="C38" s="5">
-        <v>46184.51943712963</v>
+        <v>46184.686103796295</v>
       </c>
       <c r="D38" s="5">
-        <v>46184.519438564814</v>
+        <v>46184.68610523148</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>150</v>
@@ -3731,13 +3731,13 @@
         <v>153</v>
       </c>
       <c r="B39" s="8">
-        <v>46118.495545682876</v>
+        <v>46118.66221234953</v>
       </c>
       <c r="C39" s="8">
-        <v>46184.36428194444</v>
+        <v>46184.53094861111</v>
       </c>
       <c r="D39" s="8">
-        <v>46184.36428409722</v>
+        <v>46184.53095076389</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>154</v>
@@ -3792,13 +3792,13 @@
         <v>156</v>
       </c>
       <c r="B40" s="5">
-        <v>46118.495549907406</v>
+        <v>46118.66221657407</v>
       </c>
       <c r="C40" s="5">
-        <v>46184.36495873843</v>
+        <v>46184.53162540509</v>
       </c>
       <c r="D40" s="5">
-        <v>46184.36496005787</v>
+        <v>46184.531626724536</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>155</v>
@@ -3853,11 +3853,11 @@
         <v>158</v>
       </c>
       <c r="B41" s="8">
-        <v>46118.495554305555</v>
+        <v>46118.662220972226</v>
       </c>
       <c r="C41" s="9"/>
       <c r="D41" s="8">
-        <v>46134.63373538194</v>
+        <v>46134.80040204861</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>159</v>
@@ -3900,13 +3900,13 @@
         <v>161</v>
       </c>
       <c r="B42" s="5">
-        <v>46118.495558553244</v>
+        <v>46118.66222521991</v>
       </c>
       <c r="C42" s="5">
-        <v>46129.40051568287</v>
+        <v>46129.567182349536</v>
       </c>
       <c r="D42" s="5">
-        <v>46129.40751229167</v>
+        <v>46129.57417895833</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>162</v>
@@ -3965,13 +3965,13 @@
         <v>166</v>
       </c>
       <c r="B43" s="8">
-        <v>46118.495565034726</v>
+        <v>46118.66223170139</v>
       </c>
       <c r="C43" s="8">
-        <v>46134.633600057874</v>
+        <v>46134.80026672454</v>
       </c>
       <c r="D43" s="8">
-        <v>46134.63361603009</v>
+        <v>46134.80028269676</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>167</v>
@@ -4030,13 +4030,13 @@
         <v>172</v>
       </c>
       <c r="B44" s="5">
-        <v>46118.49557270833</v>
+        <v>46118.662239375</v>
       </c>
       <c r="C44" s="5">
-        <v>46134.63372706018</v>
+        <v>46134.80039372685</v>
       </c>
       <c r="D44" s="5">
-        <v>46134.633741701386</v>
+        <v>46134.80040836806</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>103</v>
@@ -4093,11 +4093,11 @@
         <v>174</v>
       </c>
       <c r="B45" s="8">
-        <v>46118.49557863426</v>
+        <v>46118.662245300926</v>
       </c>
       <c r="C45" s="9"/>
       <c r="D45" s="8">
-        <v>46118.60057776621</v>
+        <v>46118.76724443287</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>175</v>
@@ -4156,13 +4156,13 @@
         <v>180</v>
       </c>
       <c r="B46" s="5">
-        <v>46118.49558318287</v>
+        <v>46118.66224984954</v>
       </c>
       <c r="C46" s="5">
-        <v>46184.520520185186</v>
+        <v>46184.68718685185</v>
       </c>
       <c r="D46" s="5">
-        <v>46184.520521620376</v>
+        <v>46184.68718828703</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>181</v>
@@ -4205,13 +4205,13 @@
         <v>183</v>
       </c>
       <c r="B47" s="8">
-        <v>46118.495586840276</v>
+        <v>46118.66225350695</v>
       </c>
       <c r="C47" s="8">
-        <v>46184.52003991898</v>
+        <v>46184.68670658565</v>
       </c>
       <c r="D47" s="8">
-        <v>46184.52025868055</v>
+        <v>46184.686925347225</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>157</v>
@@ -4270,13 +4270,13 @@
         <v>187</v>
       </c>
       <c r="B48" s="5">
-        <v>46118.49559196759</v>
+        <v>46118.66225863426</v>
       </c>
       <c r="C48" s="5">
-        <v>46184.520299317126</v>
+        <v>46184.6869659838</v>
       </c>
       <c r="D48" s="5">
-        <v>46184.52047996528</v>
+        <v>46184.68714663194</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>188</v>
@@ -4335,11 +4335,11 @@
         <v>192</v>
       </c>
       <c r="B49" s="8">
-        <v>46118.49559715278</v>
+        <v>46118.662263819446</v>
       </c>
       <c r="C49" s="9"/>
       <c r="D49" s="8">
-        <v>46184.523562476854</v>
+        <v>46184.69022914352</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>193</v>
@@ -4382,13 +4382,13 @@
         <v>195</v>
       </c>
       <c r="B50" s="5">
-        <v>46118.49560084491</v>
+        <v>46118.66226751157</v>
       </c>
       <c r="C50" s="5">
-        <v>46184.52128453704</v>
+        <v>46184.687951203705</v>
       </c>
       <c r="D50" s="5">
-        <v>46184.52128605324</v>
+        <v>46184.687952719905</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>196</v>
@@ -4447,11 +4447,11 @@
         <v>200</v>
       </c>
       <c r="B51" s="8">
-        <v>46118.49560603009</v>
+        <v>46118.66227269676</v>
       </c>
       <c r="C51" s="9"/>
       <c r="D51" s="8">
-        <v>46185.535224004634</v>
+        <v>46185.70189067129</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>201</v>
@@ -4510,13 +4510,13 @@
         <v>204</v>
       </c>
       <c r="B52" s="5">
-        <v>46184.52131372685</v>
+        <v>46184.687980393515</v>
       </c>
       <c r="C52" s="5">
-        <v>46184.52255061343</v>
+        <v>46184.68921728009</v>
       </c>
       <c r="D52" s="5">
-        <v>46184.52279166666</v>
+        <v>46184.689458333334</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>205</v>
@@ -4563,11 +4563,11 @@
         <v>206</v>
       </c>
       <c r="B53" s="8">
-        <v>46184.52142638889</v>
+        <v>46184.688093055556</v>
       </c>
       <c r="C53" s="9"/>
       <c r="D53" s="8">
-        <v>46185.536183449076</v>
+        <v>46185.70285011574</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>207</v>
@@ -4614,13 +4614,13 @@
         <v>208</v>
       </c>
       <c r="B54" s="5">
-        <v>46184.52150136574</v>
+        <v>46184.68816803241</v>
       </c>
       <c r="C54" s="5">
-        <v>46184.523340844906</v>
+        <v>46184.69000751157</v>
       </c>
       <c r="D54" s="5">
-        <v>46184.52334186343</v>
+        <v>46184.69000853009</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>209</v>
@@ -4667,13 +4667,13 @@
         <v>210</v>
       </c>
       <c r="B55" s="8">
-        <v>46184.52160033565</v>
+        <v>46184.68826700232</v>
       </c>
       <c r="C55" s="8">
-        <v>46184.52365296296</v>
+        <v>46184.69031962963</v>
       </c>
       <c r="D55" s="8">
-        <v>46184.523654502314</v>
+        <v>46184.69032116898</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>211</v>
@@ -4720,11 +4720,11 @@
         <v>212</v>
       </c>
       <c r="B56" s="5">
-        <v>46118.49561196759</v>
+        <v>46118.66227863426</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46184.52356325231</v>
+        <v>46184.69022991898</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>213</v>
@@ -4783,11 +4783,11 @@
         <v>216</v>
       </c>
       <c r="B57" s="8">
-        <v>46118.495618217596</v>
+        <v>46118.66228488426</v>
       </c>
       <c r="C57" s="9"/>
       <c r="D57" s="8">
-        <v>46118.59150753472</v>
+        <v>46118.758174201386</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>181</v>
@@ -4830,11 +4830,11 @@
         <v>218</v>
       </c>
       <c r="B58" s="5">
-        <v>46118.49562136574</v>
+        <v>46118.66228803241</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46184.5191285301</v>
+        <v>46184.685795196754</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>219</v>
@@ -4893,11 +4893,11 @@
         <v>221</v>
       </c>
       <c r="B59" s="8">
-        <v>46118.49562685185</v>
+        <v>46118.662293518515</v>
       </c>
       <c r="C59" s="9"/>
       <c r="D59" s="8">
-        <v>46174.459972557874</v>
+        <v>46174.62663922454</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>58</v>
@@ -4956,11 +4956,11 @@
         <v>223</v>
       </c>
       <c r="B60" s="5">
-        <v>46118.49563322916</v>
+        <v>46118.662299895834</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46182.47662865741</v>
+        <v>46182.64329532407</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>224</v>
@@ -5019,11 +5019,11 @@
         <v>226</v>
       </c>
       <c r="B61" s="8">
-        <v>46118.495688842595</v>
+        <v>46118.66235550926</v>
       </c>
       <c r="C61" s="9"/>
       <c r="D61" s="8">
-        <v>46155.736030659726</v>
+        <v>46155.90269732639</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>227</v>
@@ -5082,11 +5082,11 @@
         <v>229</v>
       </c>
       <c r="B62" s="5">
-        <v>46118.49569628472</v>
+        <v>46118.66236295139</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46184.71634863426</v>
+        <v>46184.883015300926</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>230</v>
@@ -5129,11 +5129,11 @@
         <v>232</v>
       </c>
       <c r="B63" s="8">
-        <v>46118.495702071756</v>
+        <v>46118.66236873843</v>
       </c>
       <c r="C63" s="9"/>
       <c r="D63" s="8">
-        <v>46183.72433546296</v>
+        <v>46183.89100212963</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>233</v>
@@ -5192,11 +5192,11 @@
         <v>235</v>
       </c>
       <c r="B64" s="5">
-        <v>46118.49570939815</v>
+        <v>46118.662376064814</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46134.63374116898</v>
+        <v>46134.800407835646</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>228</v>
@@ -5255,11 +5255,11 @@
         <v>238</v>
       </c>
       <c r="B65" s="8">
-        <v>46118.4957208912</v>
+        <v>46118.662387557866</v>
       </c>
       <c r="C65" s="9"/>
       <c r="D65" s="8">
-        <v>46134.63373446759</v>
+        <v>46134.80040113426</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>239</v>
@@ -5318,11 +5318,11 @@
         <v>241</v>
       </c>
       <c r="B66" s="5">
-        <v>46118.495732129624</v>
+        <v>46118.662398796296</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46134.63374045139</v>
+        <v>46134.800407118055</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>242</v>
@@ -5381,11 +5381,11 @@
         <v>244</v>
       </c>
       <c r="B67" s="8">
-        <v>46118.495743182866</v>
+        <v>46118.66240984954</v>
       </c>
       <c r="C67" s="9"/>
       <c r="D67" s="8">
-        <v>46118.6011034375</v>
+        <v>46118.76777010417</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>178</v>
@@ -5442,11 +5442,11 @@
         <v>247</v>
       </c>
       <c r="B68" s="5">
-        <v>46118.49575346065</v>
+        <v>46118.662420127315</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46118.601098784726</v>
+        <v>46118.76776545139</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>248</v>
@@ -5505,11 +5505,11 @@
         <v>250</v>
       </c>
       <c r="B69" s="8">
-        <v>46118.49576103009</v>
+        <v>46118.66242769676</v>
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46118.59566493056</v>
+        <v>46118.76233159722</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>251</v>
@@ -5552,11 +5552,11 @@
         <v>253</v>
       </c>
       <c r="B70" s="5">
-        <v>46118.49576510416</v>
+        <v>46118.662431770834</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46118.60123006944</v>
+        <v>46118.76789673611</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>254</v>
@@ -5613,11 +5613,11 @@
         <v>258</v>
       </c>
       <c r="B71" s="8">
-        <v>46118.49577158564</v>
+        <v>46118.662438252315</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46118.60127770834</v>
+        <v>46118.767944374995</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>259</v>
@@ -5674,11 +5674,11 @@
         <v>262</v>
       </c>
       <c r="B72" s="5">
-        <v>46118.49578482639</v>
+        <v>46118.66245149306</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46118.60132649305</v>
+        <v>46118.76799315972</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>263</v>
@@ -5735,11 +5735,11 @@
         <v>267</v>
       </c>
       <c r="B73" s="8">
-        <v>46118.49579103009</v>
+        <v>46118.66245769676</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46118.601365995375</v>
+        <v>46118.76803266203</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>268</v>
@@ -5796,11 +5796,11 @@
         <v>270</v>
       </c>
       <c r="B74" s="5">
-        <v>46118.49579800926</v>
+        <v>46118.66246467593</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46118.5961819213</v>
+        <v>46118.76284858796</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>271</v>
@@ -5843,11 +5843,11 @@
         <v>273</v>
       </c>
       <c r="B75" s="8">
-        <v>46118.495801296296</v>
+        <v>46118.66246796296</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46118.60144140046</v>
+        <v>46118.76810806713</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>274</v>
@@ -5906,11 +5906,11 @@
         <v>277</v>
       </c>
       <c r="B76" s="5">
-        <v>46118.49584592592</v>
+        <v>46118.66251259259</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46118.601438576385</v>
+        <v>46118.768105243056</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>278</v>
@@ -5969,11 +5969,11 @@
         <v>280</v>
       </c>
       <c r="B77" s="8">
-        <v>46118.49585471065</v>
+        <v>46118.662521377315</v>
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46118.59695680556</v>
+        <v>46118.76362347222</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>281</v>
@@ -6016,11 +6016,11 @@
         <v>283</v>
       </c>
       <c r="B78" s="5">
-        <v>46118.495858993054</v>
+        <v>46118.66252565972</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46118.60159583333</v>
+        <v>46118.7682625</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>284</v>
@@ -6079,11 +6079,11 @@
         <v>286</v>
       </c>
       <c r="B79" s="8">
-        <v>46118.49586534723</v>
+        <v>46118.662532013885</v>
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="8">
-        <v>46118.601592962965</v>
+        <v>46118.76825962963</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>287</v>

--- a/data/50001533 - GESVIAL.xlsx
+++ b/data/50001533 - GESVIAL.xlsx
@@ -4897,7 +4897,7 @@
       </c>
       <c r="C59" s="9"/>
       <c r="D59" s="8">
-        <v>46174.62663922454</v>
+        <v>46190.16815429398</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>58</v>

--- a/data/50001533 - GESVIAL.xlsx
+++ b/data/50001533 - GESVIAL.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="956" uniqueCount="288">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="960" uniqueCount="288">
   <si>
     <t xml:space="preserve"> 50001533 - GESVIAL</t>
   </si>
@@ -4516,7 +4516,7 @@
         <v>46184.68921728009</v>
       </c>
       <c r="D52" s="5">
-        <v>46184.689458333334</v>
+        <v>46191.68718039352</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>205</v>
@@ -4525,9 +4525,11 @@
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H52" s="6"/>
+        <v>197</v>
+      </c>
+      <c r="H52" s="6" t="s">
+        <v>198</v>
+      </c>
       <c r="I52" s="5">
         <v>46188</v>
       </c>
@@ -4567,7 +4569,7 @@
       </c>
       <c r="C53" s="9"/>
       <c r="D53" s="8">
-        <v>46185.70285011574</v>
+        <v>46191.687177245374</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>207</v>
@@ -4576,9 +4578,11 @@
         <v>26</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H53" s="9"/>
+        <v>197</v>
+      </c>
+      <c r="H53" s="9" t="s">
+        <v>198</v>
+      </c>
       <c r="I53" s="8">
         <v>46188</v>
       </c>
@@ -4620,7 +4624,7 @@
         <v>46184.69000751157</v>
       </c>
       <c r="D54" s="5">
-        <v>46184.69000853009</v>
+        <v>46191.6871738426</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>209</v>
@@ -4629,9 +4633,11 @@
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H54" s="6"/>
+        <v>197</v>
+      </c>
+      <c r="H54" s="6" t="s">
+        <v>198</v>
+      </c>
       <c r="I54" s="5">
         <v>46188</v>
       </c>
@@ -4673,7 +4679,7 @@
         <v>46184.69031962963</v>
       </c>
       <c r="D55" s="8">
-        <v>46184.69032116898</v>
+        <v>46191.687168993056</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>211</v>
@@ -4682,9 +4688,11 @@
         <v>26</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H55" s="9"/>
+        <v>197</v>
+      </c>
+      <c r="H55" s="9" t="s">
+        <v>198</v>
+      </c>
       <c r="I55" s="8">
         <v>46188</v>
       </c>

--- a/data/50001533 - GESVIAL.xlsx
+++ b/data/50001533 - GESVIAL.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="960" uniqueCount="288">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="947" uniqueCount="283">
   <si>
     <t xml:space="preserve"> 50001533 - GESVIAL</t>
   </si>
@@ -260,7 +260,7 @@
     <t>Ingenieria Jefe de proyecto:</t>
   </si>
   <si>
-    <t>Analisis de costeo,Ingenieria Basica Motor,Ingenieria basica Rodete,Ingenieria Detalle</t>
+    <t>Ingenieria Basica Motor,Ingenieria basica Rodete,Ingenieria Detalle</t>
   </si>
   <si>
     <t>1213962383646351</t>
@@ -275,7 +275,7 @@
 </t>
   </si>
   <si>
-    <t>Analisis de costeo,Planos definitivo,Ingenieria Jefe de proyecto:,propuesta motor</t>
+    <t>Planos definitivo,Ingenieria Jefe de proyecto:,propuesta motor</t>
   </si>
   <si>
     <t>1213962383646371</t>
@@ -293,7 +293,7 @@
 </t>
   </si>
   <si>
-    <t>Analisis de costeo,propuesta nucleo rodete,Ingenieria Jefe de proyecto:,propuesta alabes</t>
+    <t>propuesta nucleo rodete,Ingenieria Jefe de proyecto:,propuesta alabes</t>
   </si>
   <si>
     <t>1213963540621437</t>
@@ -309,22 +309,7 @@
 PLANO MONTAJE Y CIMENTACION.</t>
   </si>
   <si>
-    <t>Analisis de costeo,Ingenieria Jefe de proyecto:,Planos Preliminar</t>
-  </si>
-  <si>
-    <t>1213955269696090</t>
-  </si>
-  <si>
-    <t>Analisis de costeo</t>
-  </si>
-  <si>
-    <t>Ingenieria Basica Motor,Ingenieria Detalle,Ingenieria basica Rodete</t>
-  </si>
-  <si>
-    <t>Ingenieria Jefe de proyecto:,Costos</t>
-  </si>
-  <si>
-    <t>Tarea en curso</t>
+    <t>Ingenieria Jefe de proyecto:,Planos Preliminar</t>
   </si>
   <si>
     <t>1213955236952401</t>
@@ -401,6 +386,9 @@
     <t>Propuesta compras:,Generación OC Rodete - OT4285</t>
   </si>
   <si>
+    <t>Tarea en curso</t>
+  </si>
+  <si>
     <t>1213955269699705</t>
   </si>
   <si>
@@ -939,9 +927,6 @@
   </si>
   <si>
     <t>Costos</t>
-  </si>
-  <si>
-    <t>Despacho,Analisis de costeo</t>
   </si>
   <si>
     <t>1213962383736711</t>
@@ -1489,7 +1474,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:U79"/>
+  <dimension ref="A1:U78"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10.4" customWidth="1"/>
@@ -2145,7 +2130,7 @@
       </c>
       <c r="C13" s="9"/>
       <c r="D13" s="8">
-        <v>46129.56712789352</v>
+        <v>46191.77226840278</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>62</v>
@@ -2194,7 +2179,7 @@
         <v>46129.56192828703</v>
       </c>
       <c r="D14" s="5">
-        <v>46129.56194221065</v>
+        <v>46191.77226219907</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>65</v>
@@ -2259,7 +2244,7 @@
         <v>46129.561938796294</v>
       </c>
       <c r="D15" s="8">
-        <v>46129.56195402778</v>
+        <v>46191.77226225694</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>69</v>
@@ -2324,7 +2309,7 @@
         <v>46129.56711804398</v>
       </c>
       <c r="D16" s="5">
-        <v>46141.88285820602</v>
+        <v>46191.7722621412</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>73</v>
@@ -2383,30 +2368,26 @@
         <v>76</v>
       </c>
       <c r="B17" s="8">
-        <v>46118.662058773145</v>
-      </c>
-      <c r="C17" s="9"/>
+        <v>46118.6618661574</v>
+      </c>
+      <c r="C17" s="8">
+        <v>46184.72974263889</v>
+      </c>
       <c r="D17" s="8">
-        <v>46129.56713648148</v>
+        <v>46184.72974401621</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>77</v>
       </c>
       <c r="F17" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G17" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="H17" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="I17" s="8">
-        <v>46106</v>
-      </c>
-      <c r="J17" s="8">
-        <v>46114</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H17" s="9"/>
+      <c r="I17" s="9"/>
+      <c r="J17" s="9"/>
       <c r="K17" s="9" t="s">
         <v>26</v>
       </c>
@@ -2414,97 +2395,103 @@
         <v>26</v>
       </c>
       <c r="M17" s="9" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N17" s="9" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="O17" s="9" t="s">
         <v>78</v>
       </c>
       <c r="P17" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q17" s="8">
-        <v>46114</v>
-      </c>
-      <c r="R17" s="8">
-        <v>46106</v>
-      </c>
-      <c r="S17" s="9">
-        <v>0</v>
-      </c>
-      <c r="T17" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="U17" s="12" t="s">
-        <v>80</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="Q17" s="9"/>
+      <c r="R17" s="9"/>
+      <c r="S17" s="9"/>
+      <c r="T17" s="9"/>
+      <c r="U17" s="9"/>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="B18" s="5">
+        <v>46118.66206653936</v>
+      </c>
+      <c r="C18" s="5">
+        <v>46129.56233884259</v>
+      </c>
+      <c r="D18" s="5">
+        <v>46129.56236072916</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="H18" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="I18" s="5">
+        <v>46115</v>
+      </c>
+      <c r="J18" s="5">
+        <v>46118</v>
+      </c>
+      <c r="K18" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L18" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="B18" s="5">
-        <v>46118.6618661574</v>
-      </c>
-      <c r="C18" s="5">
-        <v>46184.72974263889</v>
-      </c>
-      <c r="D18" s="5">
-        <v>46184.72974401621</v>
-      </c>
-      <c r="E18" s="6" t="s">
+      <c r="M18" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N18" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="O18" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="P18" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="F18" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G18" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H18" s="6"/>
-      <c r="I18" s="6"/>
-      <c r="J18" s="6"/>
-      <c r="K18" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L18" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M18" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="N18" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="O18" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="P18" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q18" s="6"/>
-      <c r="R18" s="6"/>
-      <c r="S18" s="6"/>
-      <c r="T18" s="6"/>
-      <c r="U18" s="6"/>
+      <c r="Q18" s="5">
+        <v>46118</v>
+      </c>
+      <c r="R18" s="5">
+        <v>46115</v>
+      </c>
+      <c r="S18" s="6">
+        <v>1</v>
+      </c>
+      <c r="T18" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="U18" s="10" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="B19" s="8">
+        <v>46118.66207174768</v>
+      </c>
+      <c r="C19" s="8">
+        <v>46129.56234587963</v>
+      </c>
+      <c r="D19" s="8">
+        <v>46129.56236737268</v>
+      </c>
+      <c r="E19" s="9" t="s">
         <v>84</v>
-      </c>
-      <c r="B19" s="8">
-        <v>46118.66206653936</v>
-      </c>
-      <c r="C19" s="8">
-        <v>46129.56233884259</v>
-      </c>
-      <c r="D19" s="8">
-        <v>46129.56236072916</v>
-      </c>
-      <c r="E19" s="9" t="s">
-        <v>85</v>
       </c>
       <c r="F19" s="9" t="s">
         <v>26</v>
@@ -2516,34 +2503,34 @@
         <v>30</v>
       </c>
       <c r="I19" s="8">
-        <v>46115</v>
+        <v>46108</v>
       </c>
       <c r="J19" s="8">
-        <v>46118</v>
+        <v>46111</v>
       </c>
       <c r="K19" s="9" t="s">
         <v>26</v>
       </c>
       <c r="L19" s="9" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="M19" s="9" t="s">
         <v>26</v>
       </c>
       <c r="N19" s="9" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="O19" s="9" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="P19" s="9" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="Q19" s="8">
-        <v>46118</v>
+        <v>46111</v>
       </c>
       <c r="R19" s="8">
-        <v>46115</v>
+        <v>46108</v>
       </c>
       <c r="S19" s="9">
         <v>1</v>
@@ -2557,19 +2544,19 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B20" s="5">
-        <v>46118.66207174768</v>
+        <v>46118.66207709491</v>
       </c>
       <c r="C20" s="5">
-        <v>46129.56234587963</v>
+        <v>46129.57133789352</v>
       </c>
       <c r="D20" s="5">
-        <v>46129.56236737268</v>
+        <v>46129.57135429398</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
@@ -2581,34 +2568,34 @@
         <v>30</v>
       </c>
       <c r="I20" s="5">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="J20" s="5">
+        <v>46112</v>
+      </c>
+      <c r="K20" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L20" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="M20" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N20" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="O20" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="P20" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q20" s="5">
+        <v>46112</v>
+      </c>
+      <c r="R20" s="5">
         <v>46111</v>
-      </c>
-      <c r="K20" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L20" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="M20" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N20" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="O20" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="P20" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="Q20" s="5">
-        <v>46111</v>
-      </c>
-      <c r="R20" s="5">
-        <v>46108</v>
       </c>
       <c r="S20" s="6">
         <v>1</v>
@@ -2622,67 +2609,67 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="B21" s="8">
+        <v>46118.66208231481</v>
+      </c>
+      <c r="C21" s="8">
+        <v>46183.88010105324</v>
+      </c>
+      <c r="D21" s="8">
+        <v>46183.880102916664</v>
+      </c>
+      <c r="E21" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="B21" s="8">
-        <v>46118.66207709491</v>
-      </c>
-      <c r="C21" s="8">
-        <v>46129.57133789352</v>
-      </c>
-      <c r="D21" s="8">
-        <v>46129.57135429398</v>
-      </c>
-      <c r="E21" s="9" t="s">
+      <c r="F21" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G21" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="F21" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G21" s="9" t="s">
-        <v>29</v>
-      </c>
       <c r="H21" s="9" t="s">
-        <v>30</v>
+        <v>92</v>
       </c>
       <c r="I21" s="8">
-        <v>46111</v>
+        <v>46115</v>
       </c>
       <c r="J21" s="8">
-        <v>46112</v>
+        <v>46118</v>
       </c>
       <c r="K21" s="9" t="s">
         <v>26</v>
       </c>
       <c r="L21" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M21" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N21" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="O21" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="P21" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="M21" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N21" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="O21" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="P21" s="9" t="s">
-        <v>94</v>
-      </c>
       <c r="Q21" s="8">
-        <v>46112</v>
+        <v>46118</v>
       </c>
       <c r="R21" s="8">
-        <v>46111</v>
+        <v>46115</v>
       </c>
       <c r="S21" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T21" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="U21" s="10" t="s">
-        <v>33</v>
+      <c r="U21" s="12" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
@@ -2690,13 +2677,13 @@
         <v>95</v>
       </c>
       <c r="B22" s="5">
-        <v>46118.66208231481</v>
+        <v>46118.662087523146</v>
       </c>
       <c r="C22" s="5">
-        <v>46183.88010105324</v>
+        <v>46183.888051863425</v>
       </c>
       <c r="D22" s="5">
-        <v>46183.880102916664</v>
+        <v>46183.888251435186</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>96</v>
@@ -2708,13 +2695,13 @@
         <v>97</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I22" s="5">
-        <v>46115</v>
+        <v>46150</v>
       </c>
       <c r="J22" s="5">
-        <v>46118</v>
+        <v>46153</v>
       </c>
       <c r="K22" s="6" t="s">
         <v>26</v>
@@ -2726,61 +2713,55 @@
         <v>26</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="Q22" s="5">
-        <v>46118</v>
+        <v>46153</v>
       </c>
       <c r="R22" s="5">
-        <v>46115</v>
+        <v>46150</v>
       </c>
       <c r="S22" s="6">
         <v>0</v>
       </c>
-      <c r="T22" s="11" t="s">
-        <v>55</v>
+      <c r="T22" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="U22" s="12" t="s">
-        <v>80</v>
+        <v>94</v>
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B23" s="8">
-        <v>46118.662087523146</v>
+        <v>46118.66187195602</v>
       </c>
       <c r="C23" s="8">
-        <v>46183.888051863425</v>
+        <v>46184.68624671296</v>
       </c>
       <c r="D23" s="8">
-        <v>46183.888251435186</v>
+        <v>46184.686248067126</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F23" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="H23" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="I23" s="8">
-        <v>46150</v>
-      </c>
-      <c r="J23" s="8">
-        <v>46153</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H23" s="9"/>
+      <c r="I23" s="9"/>
+      <c r="J23" s="9"/>
       <c r="K23" s="9" t="s">
         <v>26</v>
       </c>
@@ -2788,58 +2769,54 @@
         <v>26</v>
       </c>
       <c r="M23" s="9" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N23" s="9" t="s">
-        <v>82</v>
+        <v>26</v>
       </c>
       <c r="O23" s="9" t="s">
         <v>103</v>
       </c>
       <c r="P23" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q23" s="8">
-        <v>46153</v>
-      </c>
-      <c r="R23" s="8">
-        <v>46150</v>
-      </c>
-      <c r="S23" s="9">
-        <v>0</v>
-      </c>
-      <c r="T23" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="U23" s="12" t="s">
-        <v>80</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="Q23" s="9"/>
+      <c r="R23" s="9"/>
+      <c r="S23" s="9"/>
+      <c r="T23" s="9"/>
+      <c r="U23" s="9"/>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="B24" s="5">
+        <v>46118.662093692124</v>
+      </c>
+      <c r="C24" s="5">
+        <v>46182.67644689815</v>
+      </c>
+      <c r="D24" s="5">
+        <v>46182.676449293984</v>
+      </c>
+      <c r="E24" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="B24" s="5">
-        <v>46118.66187195602</v>
-      </c>
-      <c r="C24" s="5">
-        <v>46184.68624671296</v>
-      </c>
-      <c r="D24" s="5">
-        <v>46184.686248067126</v>
-      </c>
-      <c r="E24" s="6" t="s">
+      <c r="F24" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G24" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="F24" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G24" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H24" s="6"/>
-      <c r="I24" s="6"/>
-      <c r="J24" s="6"/>
+      <c r="H24" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="I24" s="5">
+        <v>46119</v>
+      </c>
+      <c r="J24" s="5">
+        <v>46232</v>
+      </c>
       <c r="K24" s="6" t="s">
         <v>26</v>
       </c>
@@ -2847,53 +2824,63 @@
         <v>26</v>
       </c>
       <c r="M24" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N24" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="O24" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="P24" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q24" s="5">
+        <v>46232</v>
+      </c>
+      <c r="R24" s="5">
+        <v>46119</v>
+      </c>
+      <c r="S24" s="6">
         <v>0</v>
       </c>
-      <c r="N24" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="O24" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="P24" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q24" s="6"/>
-      <c r="R24" s="6"/>
-      <c r="S24" s="6"/>
-      <c r="T24" s="6"/>
-      <c r="U24" s="6"/>
+      <c r="T24" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="U24" s="11" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B25" s="8">
-        <v>46118.662093692124</v>
+        <v>46118.66209846065</v>
       </c>
       <c r="C25" s="8">
-        <v>46182.67644689815</v>
+        <v>46174.62568537037</v>
       </c>
       <c r="D25" s="8">
-        <v>46182.676449293984</v>
+        <v>46174.62568689814</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="I25" s="8">
         <v>46119</v>
       </c>
       <c r="J25" s="8">
-        <v>46232</v>
+        <v>46120</v>
       </c>
       <c r="K25" s="9" t="s">
         <v>26</v>
@@ -2905,78 +2892,68 @@
         <v>26</v>
       </c>
       <c r="N25" s="9" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="O25" s="9" t="s">
-        <v>112</v>
+        <v>80</v>
       </c>
       <c r="P25" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="Q25" s="8">
-        <v>46232</v>
-      </c>
-      <c r="R25" s="8">
-        <v>46119</v>
-      </c>
-      <c r="S25" s="9">
-        <v>0</v>
-      </c>
-      <c r="T25" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="U25" s="11" t="s">
-        <v>60</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="Q25" s="9"/>
+      <c r="R25" s="9"/>
+      <c r="S25" s="9"/>
+      <c r="T25" s="9"/>
+      <c r="U25" s="9"/>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B26" s="5">
+        <v>46118.66210270833</v>
+      </c>
+      <c r="C26" s="5">
+        <v>46182.64328993055</v>
+      </c>
+      <c r="D26" s="5">
+        <v>46182.64329142361</v>
+      </c>
+      <c r="E26" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="B26" s="5">
-        <v>46118.66209846065</v>
-      </c>
-      <c r="C26" s="5">
-        <v>46174.62568537037</v>
-      </c>
-      <c r="D26" s="5">
-        <v>46174.62568689814</v>
-      </c>
-      <c r="E26" s="6" t="s">
+      <c r="F26" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G26" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="H26" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="I26" s="5">
+        <v>46121</v>
+      </c>
+      <c r="J26" s="5">
+        <v>46232</v>
+      </c>
+      <c r="K26" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L26" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M26" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N26" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="O26" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="P26" s="6" t="s">
         <v>114</v>
-      </c>
-      <c r="F26" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G26" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="H26" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="I26" s="5">
-        <v>46119</v>
-      </c>
-      <c r="J26" s="5">
-        <v>46120</v>
-      </c>
-      <c r="K26" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L26" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M26" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N26" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="O26" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="P26" s="6" t="s">
-        <v>115</v>
       </c>
       <c r="Q26" s="6"/>
       <c r="R26" s="6"/>
@@ -2986,89 +2963,99 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="B27" s="8">
+        <v>46118.662106979165</v>
+      </c>
+      <c r="C27" s="8">
+        <v>46182.641066956014</v>
+      </c>
+      <c r="D27" s="8">
+        <v>46182.64106920139</v>
+      </c>
+      <c r="E27" s="9" t="s">
         <v>116</v>
       </c>
-      <c r="B27" s="8">
-        <v>46118.66210270833</v>
-      </c>
-      <c r="C27" s="8">
-        <v>46182.64328993055</v>
-      </c>
-      <c r="D27" s="8">
-        <v>46182.64329142361</v>
-      </c>
-      <c r="E27" s="9" t="s">
+      <c r="F27" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G27" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="H27" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="I27" s="8">
+        <v>46111</v>
+      </c>
+      <c r="J27" s="8">
+        <v>46188</v>
+      </c>
+      <c r="K27" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L27" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M27" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N27" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="O27" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="F27" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G27" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="H27" s="9" t="s">
-        <v>111</v>
-      </c>
-      <c r="I27" s="8">
-        <v>46121</v>
-      </c>
-      <c r="J27" s="8">
-        <v>46232</v>
-      </c>
-      <c r="K27" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L27" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M27" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N27" s="9" t="s">
-        <v>109</v>
-      </c>
-      <c r="O27" s="9" t="s">
-        <v>114</v>
-      </c>
       <c r="P27" s="9" t="s">
-        <v>118</v>
-      </c>
-      <c r="Q27" s="9"/>
-      <c r="R27" s="9"/>
-      <c r="S27" s="9"/>
-      <c r="T27" s="9"/>
-      <c r="U27" s="9"/>
+        <v>102</v>
+      </c>
+      <c r="Q27" s="8">
+        <v>46188</v>
+      </c>
+      <c r="R27" s="8">
+        <v>46111</v>
+      </c>
+      <c r="S27" s="9">
+        <v>0</v>
+      </c>
+      <c r="T27" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="U27" s="11" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="B28" s="5">
+        <v>46118.662112094906</v>
+      </c>
+      <c r="C28" s="5">
+        <v>46174.626521666665</v>
+      </c>
+      <c r="D28" s="5">
+        <v>46174.62652314815</v>
+      </c>
+      <c r="E28" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="B28" s="5">
-        <v>46118.662106979165</v>
-      </c>
-      <c r="C28" s="5">
-        <v>46182.641066956014</v>
-      </c>
-      <c r="D28" s="5">
-        <v>46182.64106920139</v>
-      </c>
-      <c r="E28" s="6" t="s">
-        <v>120</v>
-      </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="I28" s="5">
         <v>46111</v>
       </c>
       <c r="J28" s="5">
-        <v>46188</v>
+        <v>46119</v>
       </c>
       <c r="K28" s="6" t="s">
         <v>26</v>
@@ -3080,20 +3067,16 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>121</v>
+        <v>87</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="Q28" s="5">
-        <v>46188</v>
-      </c>
-      <c r="R28" s="5">
-        <v>46111</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="Q28" s="6"/>
+      <c r="R28" s="6"/>
       <c r="S28" s="6">
         <v>0</v>
       </c>
@@ -3106,52 +3089,52 @@
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="B29" s="8">
+        <v>46118.66211693287</v>
+      </c>
+      <c r="C29" s="8">
+        <v>46174.626630416664</v>
+      </c>
+      <c r="D29" s="8">
+        <v>46174.62663186343</v>
+      </c>
+      <c r="E29" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="B29" s="8">
-        <v>46118.662112094906</v>
-      </c>
-      <c r="C29" s="8">
-        <v>46174.626521666665</v>
-      </c>
-      <c r="D29" s="8">
-        <v>46174.62652314815</v>
-      </c>
-      <c r="E29" s="9" t="s">
+      <c r="F29" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G29" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="H29" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="I29" s="8">
+        <v>46120</v>
+      </c>
+      <c r="J29" s="8">
+        <v>46188</v>
+      </c>
+      <c r="K29" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L29" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M29" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N29" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="O29" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="P29" s="9" t="s">
         <v>123</v>
-      </c>
-      <c r="F29" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G29" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="H29" s="9" t="s">
-        <v>111</v>
-      </c>
-      <c r="I29" s="8">
-        <v>46111</v>
-      </c>
-      <c r="J29" s="8">
-        <v>46119</v>
-      </c>
-      <c r="K29" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L29" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M29" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N29" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="O29" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="P29" s="9" t="s">
-        <v>124</v>
       </c>
       <c r="Q29" s="9"/>
       <c r="R29" s="9"/>
@@ -3167,55 +3150,59 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="B30" s="5">
+        <v>46118.66212202546</v>
+      </c>
+      <c r="C30" s="5">
+        <v>46184.68608144676</v>
+      </c>
+      <c r="D30" s="5">
+        <v>46184.68608324074</v>
+      </c>
+      <c r="E30" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="B30" s="5">
-        <v>46118.66211693287</v>
-      </c>
-      <c r="C30" s="5">
-        <v>46174.626630416664</v>
-      </c>
-      <c r="D30" s="5">
-        <v>46174.62663186343</v>
-      </c>
-      <c r="E30" s="6" t="s">
+      <c r="F30" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G30" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="H30" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="I30" s="5">
+        <v>46119</v>
+      </c>
+      <c r="J30" s="5">
+        <v>46167</v>
+      </c>
+      <c r="K30" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L30" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M30" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N30" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="O30" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="F30" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G30" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="H30" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="I30" s="5">
-        <v>46120</v>
-      </c>
-      <c r="J30" s="5">
-        <v>46188</v>
-      </c>
-      <c r="K30" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L30" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M30" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N30" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="O30" s="6" t="s">
-        <v>123</v>
-      </c>
       <c r="P30" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="Q30" s="6"/>
-      <c r="R30" s="6"/>
+        <v>102</v>
+      </c>
+      <c r="Q30" s="5">
+        <v>46167</v>
+      </c>
+      <c r="R30" s="5">
+        <v>46119</v>
+      </c>
       <c r="S30" s="6">
         <v>0</v>
       </c>
@@ -3228,34 +3215,34 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="B31" s="8">
+        <v>46118.662126678246</v>
+      </c>
+      <c r="C31" s="8">
+        <v>46184.68571903935</v>
+      </c>
+      <c r="D31" s="8">
+        <v>46184.68572081019</v>
+      </c>
+      <c r="E31" s="9" t="s">
         <v>128</v>
       </c>
-      <c r="B31" s="8">
-        <v>46118.66212202546</v>
-      </c>
-      <c r="C31" s="8">
-        <v>46184.68608144676</v>
-      </c>
-      <c r="D31" s="8">
-        <v>46184.68608324074</v>
-      </c>
-      <c r="E31" s="9" t="s">
-        <v>129</v>
-      </c>
       <c r="F31" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="I31" s="8">
         <v>46119</v>
       </c>
       <c r="J31" s="8">
-        <v>46167</v>
+        <v>46120</v>
       </c>
       <c r="K31" s="9" t="s">
         <v>26</v>
@@ -3267,20 +3254,16 @@
         <v>26</v>
       </c>
       <c r="N31" s="9" t="s">
-        <v>106</v>
+        <v>125</v>
       </c>
       <c r="O31" s="9" t="s">
-        <v>130</v>
+        <v>91</v>
       </c>
       <c r="P31" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="Q31" s="8">
-        <v>46167</v>
-      </c>
-      <c r="R31" s="8">
-        <v>46119</v>
-      </c>
+        <v>129</v>
+      </c>
+      <c r="Q31" s="9"/>
+      <c r="R31" s="9"/>
       <c r="S31" s="9">
         <v>0</v>
       </c>
@@ -3293,52 +3276,52 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="B32" s="5">
+        <v>46118.662131261575</v>
+      </c>
+      <c r="C32" s="5">
+        <v>46184.68578890046</v>
+      </c>
+      <c r="D32" s="5">
+        <v>46184.68579053241</v>
+      </c>
+      <c r="E32" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="B32" s="5">
-        <v>46118.662126678246</v>
-      </c>
-      <c r="C32" s="5">
-        <v>46184.68571903935</v>
-      </c>
-      <c r="D32" s="5">
-        <v>46184.68572081019</v>
-      </c>
-      <c r="E32" s="6" t="s">
+      <c r="F32" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G32" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="H32" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="I32" s="5">
+        <v>46121</v>
+      </c>
+      <c r="J32" s="5">
+        <v>46167</v>
+      </c>
+      <c r="K32" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L32" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M32" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N32" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="O32" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="P32" s="6" t="s">
         <v>132</v>
-      </c>
-      <c r="F32" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G32" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="H32" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="I32" s="5">
-        <v>46119</v>
-      </c>
-      <c r="J32" s="5">
-        <v>46120</v>
-      </c>
-      <c r="K32" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L32" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M32" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N32" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="O32" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="P32" s="6" t="s">
-        <v>133</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
@@ -3354,57 +3337,61 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="B33" s="8">
+        <v>46118.66218372685</v>
+      </c>
+      <c r="C33" s="8">
+        <v>46156.821339988426</v>
+      </c>
+      <c r="D33" s="8">
+        <v>46169.82398277777</v>
+      </c>
+      <c r="E33" s="9" t="s">
         <v>134</v>
       </c>
-      <c r="B33" s="8">
-        <v>46118.662131261575</v>
-      </c>
-      <c r="C33" s="8">
-        <v>46184.68578890046</v>
-      </c>
-      <c r="D33" s="8">
-        <v>46184.68579053241</v>
-      </c>
-      <c r="E33" s="9" t="s">
+      <c r="F33" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G33" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="H33" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="I33" s="8">
+        <v>46112</v>
+      </c>
+      <c r="J33" s="8">
+        <v>46254</v>
+      </c>
+      <c r="K33" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L33" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M33" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N33" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="O33" s="9" t="s">
         <v>135</v>
       </c>
-      <c r="F33" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G33" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="H33" s="9" t="s">
-        <v>111</v>
-      </c>
-      <c r="I33" s="8">
-        <v>46121</v>
-      </c>
-      <c r="J33" s="8">
-        <v>46167</v>
-      </c>
-      <c r="K33" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L33" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M33" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N33" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="O33" s="9" t="s">
-        <v>132</v>
-      </c>
       <c r="P33" s="9" t="s">
-        <v>136</v>
-      </c>
-      <c r="Q33" s="9"/>
-      <c r="R33" s="9"/>
+        <v>102</v>
+      </c>
+      <c r="Q33" s="8">
+        <v>46254</v>
+      </c>
+      <c r="R33" s="8">
+        <v>46112</v>
+      </c>
       <c r="S33" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T33" s="10" t="s">
         <v>32</v>
@@ -3415,34 +3402,34 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="B34" s="5">
+        <v>46118.662190104165</v>
+      </c>
+      <c r="C34" s="5">
+        <v>46134.79115269676</v>
+      </c>
+      <c r="D34" s="5">
+        <v>46169.823994363425</v>
+      </c>
+      <c r="E34" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="B34" s="5">
-        <v>46118.66218372685</v>
-      </c>
-      <c r="C34" s="5">
-        <v>46156.821339988426</v>
-      </c>
-      <c r="D34" s="5">
-        <v>46169.82398277777</v>
-      </c>
-      <c r="E34" s="6" t="s">
-        <v>138</v>
-      </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="I34" s="5">
         <v>46112</v>
       </c>
       <c r="J34" s="5">
-        <v>46254</v>
+        <v>46132</v>
       </c>
       <c r="K34" s="6" t="s">
         <v>26</v>
@@ -3454,22 +3441,18 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>106</v>
+        <v>134</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>139</v>
+        <v>84</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="Q34" s="5">
-        <v>46254</v>
-      </c>
-      <c r="R34" s="5">
-        <v>46112</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="Q34" s="6"/>
+      <c r="R34" s="6"/>
       <c r="S34" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T34" s="10" t="s">
         <v>32</v>
@@ -3480,52 +3463,52 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="B35" s="8">
+        <v>46118.662195694444</v>
+      </c>
+      <c r="C35" s="8">
+        <v>46155.90268767361</v>
+      </c>
+      <c r="D35" s="8">
+        <v>46169.82401586806</v>
+      </c>
+      <c r="E35" s="9" t="s">
         <v>140</v>
       </c>
-      <c r="B35" s="8">
-        <v>46118.662190104165</v>
-      </c>
-      <c r="C35" s="8">
-        <v>46134.79115269676</v>
-      </c>
-      <c r="D35" s="8">
-        <v>46169.823994363425</v>
-      </c>
-      <c r="E35" s="9" t="s">
+      <c r="F35" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G35" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="H35" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="I35" s="8">
+        <v>46133</v>
+      </c>
+      <c r="J35" s="8">
+        <v>46254</v>
+      </c>
+      <c r="K35" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L35" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M35" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N35" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="O35" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="P35" s="9" t="s">
         <v>141</v>
-      </c>
-      <c r="F35" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G35" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="H35" s="9" t="s">
-        <v>111</v>
-      </c>
-      <c r="I35" s="8">
-        <v>46112</v>
-      </c>
-      <c r="J35" s="8">
-        <v>46132</v>
-      </c>
-      <c r="K35" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L35" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M35" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N35" s="9" t="s">
-        <v>138</v>
-      </c>
-      <c r="O35" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="P35" s="9" t="s">
-        <v>142</v>
       </c>
       <c r="Q35" s="9"/>
       <c r="R35" s="9"/>
@@ -3541,34 +3524,34 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="B36" s="5">
+        <v>46118.66220082176</v>
+      </c>
+      <c r="C36" s="5">
+        <v>46134.79119539352</v>
+      </c>
+      <c r="D36" s="5">
+        <v>46169.824036157406</v>
+      </c>
+      <c r="E36" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="B36" s="5">
-        <v>46118.662195694444</v>
-      </c>
-      <c r="C36" s="5">
-        <v>46155.90268767361</v>
-      </c>
-      <c r="D36" s="5">
-        <v>46169.82401586806</v>
-      </c>
-      <c r="E36" s="6" t="s">
-        <v>144</v>
-      </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="I36" s="5">
         <v>46133</v>
       </c>
       <c r="J36" s="5">
-        <v>46254</v>
+        <v>46141</v>
       </c>
       <c r="K36" s="6" t="s">
         <v>26</v>
@@ -3580,13 +3563,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
@@ -3602,34 +3585,34 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="B37" s="8">
+        <v>46118.66220634259</v>
+      </c>
+      <c r="C37" s="8">
+        <v>46184.686103796295</v>
+      </c>
+      <c r="D37" s="8">
+        <v>46184.68610523148</v>
+      </c>
+      <c r="E37" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="B37" s="8">
-        <v>46118.66220082176</v>
-      </c>
-      <c r="C37" s="8">
-        <v>46134.79119539352</v>
-      </c>
-      <c r="D37" s="8">
-        <v>46169.824036157406</v>
-      </c>
-      <c r="E37" s="9" t="s">
+      <c r="F37" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G37" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="F37" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G37" s="9" t="s">
-        <v>110</v>
-      </c>
       <c r="H37" s="9" t="s">
-        <v>111</v>
+        <v>148</v>
       </c>
       <c r="I37" s="8">
-        <v>46133</v>
+        <v>46154</v>
       </c>
       <c r="J37" s="8">
-        <v>46141</v>
+        <v>46170</v>
       </c>
       <c r="K37" s="9" t="s">
         <v>26</v>
@@ -3641,16 +3624,20 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>138</v>
+        <v>102</v>
       </c>
       <c r="O37" s="9" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>148</v>
-      </c>
-      <c r="Q37" s="9"/>
-      <c r="R37" s="9"/>
+        <v>102</v>
+      </c>
+      <c r="Q37" s="8">
+        <v>46170</v>
+      </c>
+      <c r="R37" s="8">
+        <v>46154</v>
+      </c>
       <c r="S37" s="9">
         <v>0</v>
       </c>
@@ -3666,13 +3653,13 @@
         <v>149</v>
       </c>
       <c r="B38" s="5">
-        <v>46118.66220634259</v>
+        <v>46118.66221234953</v>
       </c>
       <c r="C38" s="5">
-        <v>46184.686103796295</v>
+        <v>46184.53094861111</v>
       </c>
       <c r="D38" s="5">
-        <v>46184.68610523148</v>
+        <v>46184.53095076389</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>150</v>
@@ -3681,16 +3668,16 @@
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="I38" s="5">
         <v>46154</v>
       </c>
       <c r="J38" s="5">
-        <v>46170</v>
+        <v>46160</v>
       </c>
       <c r="K38" s="6" t="s">
         <v>26</v>
@@ -3702,20 +3689,16 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>106</v>
+        <v>146</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>135</v>
+        <v>96</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="Q38" s="5">
-        <v>46170</v>
-      </c>
-      <c r="R38" s="5">
-        <v>46154</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="Q38" s="6"/>
+      <c r="R38" s="6"/>
       <c r="S38" s="6">
         <v>0</v>
       </c>
@@ -3728,52 +3711,52 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="B39" s="8">
+        <v>46118.66221657407</v>
+      </c>
+      <c r="C39" s="8">
+        <v>46184.53162540509</v>
+      </c>
+      <c r="D39" s="8">
+        <v>46184.531626724536</v>
+      </c>
+      <c r="E39" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="F39" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G39" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="H39" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="I39" s="8">
+        <v>46162</v>
+      </c>
+      <c r="J39" s="8">
+        <v>46170</v>
+      </c>
+      <c r="K39" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L39" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M39" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N39" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="O39" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="P39" s="9" t="s">
         <v>153</v>
-      </c>
-      <c r="B39" s="8">
-        <v>46118.66221234953</v>
-      </c>
-      <c r="C39" s="8">
-        <v>46184.53094861111</v>
-      </c>
-      <c r="D39" s="8">
-        <v>46184.53095076389</v>
-      </c>
-      <c r="E39" s="9" t="s">
-        <v>154</v>
-      </c>
-      <c r="F39" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G39" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="H39" s="9" t="s">
-        <v>152</v>
-      </c>
-      <c r="I39" s="8">
-        <v>46154</v>
-      </c>
-      <c r="J39" s="8">
-        <v>46160</v>
-      </c>
-      <c r="K39" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L39" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M39" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N39" s="9" t="s">
-        <v>150</v>
-      </c>
-      <c r="O39" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="P39" s="9" t="s">
-        <v>155</v>
       </c>
       <c r="Q39" s="9"/>
       <c r="R39" s="9"/>
@@ -3789,35 +3772,27 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B40" s="5">
-        <v>46118.66221657407</v>
-      </c>
-      <c r="C40" s="5">
-        <v>46184.53162540509</v>
-      </c>
+        <v>46118.662220972226</v>
+      </c>
+      <c r="C40" s="6"/>
       <c r="D40" s="5">
-        <v>46184.531626724536</v>
+        <v>46134.80040204861</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>155</v>
       </c>
       <c r="F40" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="H40" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="I40" s="5">
-        <v>46162</v>
-      </c>
-      <c r="J40" s="5">
-        <v>46170</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H40" s="6"/>
+      <c r="I40" s="6"/>
+      <c r="J40" s="6"/>
       <c r="K40" s="6" t="s">
         <v>26</v>
       </c>
@@ -3825,52 +3800,54 @@
         <v>26</v>
       </c>
       <c r="M40" s="6" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>150</v>
+        <v>26</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>157</v>
+        <v>26</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
-      <c r="S40" s="6">
-        <v>0</v>
-      </c>
-      <c r="T40" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="U40" s="11" t="s">
-        <v>60</v>
-      </c>
+      <c r="S40" s="6"/>
+      <c r="T40" s="6"/>
+      <c r="U40" s="6"/>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="B41" s="8">
+        <v>46118.66222521991</v>
+      </c>
+      <c r="C41" s="8">
+        <v>46129.567182349536</v>
+      </c>
+      <c r="D41" s="8">
+        <v>46129.57417895833</v>
+      </c>
+      <c r="E41" s="9" t="s">
         <v>158</v>
       </c>
-      <c r="B41" s="8">
-        <v>46118.662220972226</v>
-      </c>
-      <c r="C41" s="9"/>
-      <c r="D41" s="8">
-        <v>46134.80040204861</v>
-      </c>
-      <c r="E41" s="9" t="s">
+      <c r="F41" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G41" s="9" t="s">
         <v>159</v>
       </c>
-      <c r="F41" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="G41" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H41" s="9"/>
-      <c r="I41" s="9"/>
-      <c r="J41" s="9"/>
+      <c r="H41" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="I41" s="8">
+        <v>46115</v>
+      </c>
+      <c r="J41" s="8">
+        <v>46121</v>
+      </c>
       <c r="K41" s="9" t="s">
         <v>26</v>
       </c>
@@ -3878,53 +3855,63 @@
         <v>26</v>
       </c>
       <c r="M41" s="9" t="s">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>26</v>
+        <v>155</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>160</v>
+        <v>73</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q41" s="9"/>
-      <c r="R41" s="9"/>
-      <c r="S41" s="9"/>
-      <c r="T41" s="9"/>
-      <c r="U41" s="9"/>
+        <v>161</v>
+      </c>
+      <c r="Q41" s="8">
+        <v>46121</v>
+      </c>
+      <c r="R41" s="8">
+        <v>46115</v>
+      </c>
+      <c r="S41" s="9">
+        <v>1</v>
+      </c>
+      <c r="T41" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="U41" s="10" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B42" s="5">
-        <v>46118.66222521991</v>
+        <v>46118.66223170139</v>
       </c>
       <c r="C42" s="5">
-        <v>46129.567182349536</v>
+        <v>46134.80026672454</v>
       </c>
       <c r="D42" s="5">
-        <v>46129.57417895833</v>
+        <v>46134.80028269676</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I42" s="5">
-        <v>46115</v>
+        <v>46142</v>
       </c>
       <c r="J42" s="5">
-        <v>46121</v>
+        <v>46148</v>
       </c>
       <c r="K42" s="6" t="s">
         <v>26</v>
@@ -3936,25 +3923,25 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>73</v>
+        <v>166</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="Q42" s="5">
-        <v>46121</v>
+        <v>46148</v>
       </c>
       <c r="R42" s="5">
-        <v>46115</v>
+        <v>46142</v>
       </c>
       <c r="S42" s="6">
         <v>1</v>
       </c>
-      <c r="T42" s="11" t="s">
-        <v>55</v>
+      <c r="T42" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="U42" s="10" t="s">
         <v>33</v>
@@ -3962,58 +3949,56 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B43" s="8">
-        <v>46118.66223170139</v>
+        <v>46118.662239375</v>
       </c>
       <c r="C43" s="8">
-        <v>46134.80026672454</v>
+        <v>46134.80039372685</v>
       </c>
       <c r="D43" s="8">
-        <v>46134.80028269676</v>
+        <v>46134.80040836806</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>167</v>
+        <v>99</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="H43" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="I43" s="9"/>
+      <c r="J43" s="8">
+        <v>46149</v>
+      </c>
+      <c r="K43" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L43" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M43" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N43" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="O43" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="P43" s="9" t="s">
         <v>169</v>
       </c>
-      <c r="I43" s="8">
-        <v>46142</v>
-      </c>
-      <c r="J43" s="8">
-        <v>46148</v>
-      </c>
-      <c r="K43" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L43" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M43" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N43" s="9" t="s">
-        <v>159</v>
-      </c>
-      <c r="O43" s="9" t="s">
-        <v>170</v>
-      </c>
-      <c r="P43" s="9" t="s">
-        <v>171</v>
-      </c>
       <c r="Q43" s="8">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="R43" s="8">
-        <v>46142</v>
+        <v>46149</v>
       </c>
       <c r="S43" s="9">
         <v>1</v>
@@ -4027,32 +4012,32 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="B44" s="5">
+        <v>46118.662245300926</v>
+      </c>
+      <c r="C44" s="6"/>
+      <c r="D44" s="5">
+        <v>46118.76724443287</v>
+      </c>
+      <c r="E44" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="F44" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G44" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="B44" s="5">
-        <v>46118.662239375</v>
-      </c>
-      <c r="C44" s="5">
-        <v>46134.80039372685</v>
-      </c>
-      <c r="D44" s="5">
-        <v>46134.80040836806</v>
-      </c>
-      <c r="E44" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="F44" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G44" s="6" t="s">
-        <v>168</v>
-      </c>
       <c r="H44" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="I44" s="6"/>
+        <v>173</v>
+      </c>
+      <c r="I44" s="5">
+        <v>46268</v>
+      </c>
       <c r="J44" s="5">
-        <v>46149</v>
+        <v>46268</v>
       </c>
       <c r="K44" s="6" t="s">
         <v>26</v>
@@ -4064,59 +4049,55 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="Q44" s="5">
-        <v>46149</v>
+        <v>46268</v>
       </c>
       <c r="R44" s="5">
-        <v>46149</v>
+        <v>46268</v>
       </c>
       <c r="S44" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T44" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="U44" s="10" t="s">
-        <v>33</v>
+      <c r="U44" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B45" s="8">
-        <v>46118.662245300926</v>
-      </c>
-      <c r="C45" s="9"/>
+        <v>46118.66224984954</v>
+      </c>
+      <c r="C45" s="8">
+        <v>46184.68718685185</v>
+      </c>
       <c r="D45" s="8">
-        <v>46118.76724443287</v>
+        <v>46184.68718828703</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="F45" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>176</v>
-      </c>
-      <c r="H45" s="9" t="s">
-        <v>177</v>
-      </c>
-      <c r="I45" s="8">
-        <v>46268</v>
-      </c>
-      <c r="J45" s="8">
-        <v>46268</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H45" s="9"/>
+      <c r="I45" s="9"/>
+      <c r="J45" s="9"/>
       <c r="K45" s="9" t="s">
         <v>26</v>
       </c>
@@ -4124,58 +4105,54 @@
         <v>26</v>
       </c>
       <c r="M45" s="9" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N45" s="9" t="s">
-        <v>159</v>
+        <v>26</v>
       </c>
       <c r="O45" s="9" t="s">
         <v>178</v>
       </c>
       <c r="P45" s="9" t="s">
-        <v>179</v>
-      </c>
-      <c r="Q45" s="8">
-        <v>46268</v>
-      </c>
-      <c r="R45" s="8">
-        <v>46268</v>
-      </c>
-      <c r="S45" s="9">
-        <v>0</v>
-      </c>
-      <c r="T45" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="U45" s="11" t="s">
-        <v>60</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="Q45" s="9"/>
+      <c r="R45" s="9"/>
+      <c r="S45" s="9"/>
+      <c r="T45" s="9"/>
+      <c r="U45" s="9"/>
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="B46" s="5">
+        <v>46118.66225350695</v>
+      </c>
+      <c r="C46" s="5">
+        <v>46184.68670658565</v>
+      </c>
+      <c r="D46" s="5">
+        <v>46184.686925347225</v>
+      </c>
+      <c r="E46" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="F46" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G46" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="B46" s="5">
-        <v>46118.66224984954</v>
-      </c>
-      <c r="C46" s="5">
-        <v>46184.68718685185</v>
-      </c>
-      <c r="D46" s="5">
-        <v>46184.68718828703</v>
-      </c>
-      <c r="E46" s="6" t="s">
+      <c r="H46" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="F46" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G46" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H46" s="6"/>
-      <c r="I46" s="6"/>
-      <c r="J46" s="6"/>
+      <c r="I46" s="5">
+        <v>46171</v>
+      </c>
+      <c r="J46" s="5">
+        <v>46174</v>
+      </c>
       <c r="K46" s="6" t="s">
         <v>26</v>
       </c>
@@ -4183,53 +4160,63 @@
         <v>26</v>
       </c>
       <c r="M46" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N46" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="O46" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="P46" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="Q46" s="5">
+        <v>46174</v>
+      </c>
+      <c r="R46" s="5">
+        <v>46171</v>
+      </c>
+      <c r="S46" s="6">
         <v>0</v>
       </c>
-      <c r="N46" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="O46" s="6" t="s">
-        <v>182</v>
-      </c>
-      <c r="P46" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q46" s="6"/>
-      <c r="R46" s="6"/>
-      <c r="S46" s="6"/>
-      <c r="T46" s="6"/>
-      <c r="U46" s="6"/>
+      <c r="T46" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="U46" s="11" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
         <v>183</v>
       </c>
       <c r="B47" s="8">
-        <v>46118.66225350695</v>
+        <v>46118.66225863426</v>
       </c>
       <c r="C47" s="8">
-        <v>46184.68670658565</v>
+        <v>46184.6869659838</v>
       </c>
       <c r="D47" s="8">
-        <v>46184.686925347225</v>
+        <v>46184.68714663194</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>157</v>
+        <v>184</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I47" s="8">
-        <v>46171</v>
+        <v>46175</v>
       </c>
       <c r="J47" s="8">
-        <v>46174</v>
+        <v>46176</v>
       </c>
       <c r="K47" s="9" t="s">
         <v>26</v>
@@ -4241,19 +4228,19 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q47" s="8">
-        <v>46174</v>
+        <v>46176</v>
       </c>
       <c r="R47" s="8">
-        <v>46171</v>
+        <v>46175</v>
       </c>
       <c r="S47" s="9">
         <v>0</v>
@@ -4267,92 +4254,82 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B48" s="5">
-        <v>46118.66225863426</v>
-      </c>
-      <c r="C48" s="5">
-        <v>46184.6869659838</v>
-      </c>
+        <v>46118.662263819446</v>
+      </c>
+      <c r="C48" s="6"/>
       <c r="D48" s="5">
-        <v>46184.68714663194</v>
+        <v>46184.69022914352</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F48" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>189</v>
-      </c>
-      <c r="H48" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="H48" s="6"/>
+      <c r="I48" s="6"/>
+      <c r="J48" s="6"/>
+      <c r="K48" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L48" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M48" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="N48" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="O48" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="I48" s="5">
-        <v>46175</v>
-      </c>
-      <c r="J48" s="5">
-        <v>46176</v>
-      </c>
-      <c r="K48" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L48" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M48" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N48" s="6" t="s">
-        <v>181</v>
-      </c>
-      <c r="O48" s="6" t="s">
-        <v>157</v>
-      </c>
       <c r="P48" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="Q48" s="5">
-        <v>46176</v>
-      </c>
-      <c r="R48" s="5">
-        <v>46175</v>
-      </c>
-      <c r="S48" s="6">
-        <v>0</v>
-      </c>
-      <c r="T48" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="U48" s="11" t="s">
-        <v>60</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="Q48" s="6"/>
+      <c r="R48" s="6"/>
+      <c r="S48" s="6"/>
+      <c r="T48" s="6"/>
+      <c r="U48" s="6"/>
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="B49" s="8">
+        <v>46118.66226751157</v>
+      </c>
+      <c r="C49" s="8">
+        <v>46184.687951203705</v>
+      </c>
+      <c r="D49" s="8">
+        <v>46184.687952719905</v>
+      </c>
+      <c r="E49" s="9" t="s">
         <v>192</v>
       </c>
-      <c r="B49" s="8">
-        <v>46118.662263819446</v>
-      </c>
-      <c r="C49" s="9"/>
-      <c r="D49" s="8">
-        <v>46184.69022914352</v>
-      </c>
-      <c r="E49" s="9" t="s">
+      <c r="F49" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G49" s="9" t="s">
         <v>193</v>
       </c>
-      <c r="F49" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="G49" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H49" s="9"/>
-      <c r="I49" s="9"/>
-      <c r="J49" s="9"/>
+      <c r="H49" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="I49" s="8">
+        <v>46177</v>
+      </c>
+      <c r="J49" s="8">
+        <v>46185</v>
+      </c>
       <c r="K49" s="9" t="s">
         <v>26</v>
       </c>
@@ -4360,77 +4337,85 @@
         <v>26</v>
       </c>
       <c r="M49" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N49" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="O49" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="P49" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="Q49" s="8">
+        <v>46185</v>
+      </c>
+      <c r="R49" s="8">
+        <v>46177</v>
+      </c>
+      <c r="S49" s="9">
         <v>0</v>
       </c>
-      <c r="N49" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="O49" s="9" t="s">
-        <v>194</v>
-      </c>
-      <c r="P49" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q49" s="9"/>
-      <c r="R49" s="9"/>
-      <c r="S49" s="9"/>
-      <c r="T49" s="9"/>
-      <c r="U49" s="9"/>
+      <c r="T49" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="U49" s="11" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B50" s="5">
-        <v>46118.66226751157</v>
-      </c>
-      <c r="C50" s="5">
-        <v>46184.687951203705</v>
-      </c>
+        <v>46118.66227269676</v>
+      </c>
+      <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46184.687952719905</v>
+        <v>46185.70189067129</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="H50" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="I50" s="5">
+        <v>46188</v>
+      </c>
+      <c r="J50" s="5">
+        <v>46205</v>
+      </c>
+      <c r="K50" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L50" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M50" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N50" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="O50" s="6" t="s">
         <v>198</v>
-      </c>
-      <c r="I50" s="5">
-        <v>46177</v>
-      </c>
-      <c r="J50" s="5">
-        <v>46185</v>
-      </c>
-      <c r="K50" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L50" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M50" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N50" s="6" t="s">
-        <v>193</v>
-      </c>
-      <c r="O50" s="6" t="s">
-        <v>188</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>199</v>
       </c>
       <c r="Q50" s="5">
-        <v>46185</v>
+        <v>46205</v>
       </c>
       <c r="R50" s="5">
-        <v>46177</v>
+        <v>46188</v>
       </c>
       <c r="S50" s="6">
         <v>0</v>
@@ -4447,11 +4432,13 @@
         <v>200</v>
       </c>
       <c r="B51" s="8">
-        <v>46118.66227269676</v>
-      </c>
-      <c r="C51" s="9"/>
+        <v>46184.687980393515</v>
+      </c>
+      <c r="C51" s="8">
+        <v>46184.68921728009</v>
+      </c>
       <c r="D51" s="8">
-        <v>46185.70189067129</v>
+        <v>46191.68718039352</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>201</v>
@@ -4460,10 +4447,10 @@
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="I51" s="8">
         <v>46188</v>
@@ -4481,54 +4468,42 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>202</v>
+        <v>26</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="Q51" s="8">
-        <v>46205</v>
-      </c>
-      <c r="R51" s="8">
-        <v>46188</v>
-      </c>
-      <c r="S51" s="9">
-        <v>0</v>
-      </c>
-      <c r="T51" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="U51" s="11" t="s">
-        <v>60</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="Q51" s="9"/>
+      <c r="R51" s="9"/>
+      <c r="S51" s="9"/>
+      <c r="T51" s="9"/>
+      <c r="U51" s="9"/>
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B52" s="5">
-        <v>46184.687980393515</v>
-      </c>
-      <c r="C52" s="5">
-        <v>46184.68921728009</v>
-      </c>
+        <v>46184.688093055556</v>
+      </c>
+      <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46191.68718039352</v>
+        <v>46191.687177245374</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="I52" s="5">
         <v>46188</v>
@@ -4546,7 +4521,7 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="O52" s="6" t="s">
         <v>26</v>
@@ -4562,26 +4537,28 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B53" s="8">
-        <v>46184.688093055556</v>
-      </c>
-      <c r="C53" s="9"/>
+        <v>46184.68816803241</v>
+      </c>
+      <c r="C53" s="8">
+        <v>46184.69000751157</v>
+      </c>
       <c r="D53" s="8">
-        <v>46191.687177245374</v>
+        <v>46191.6871738426</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="H53" s="9" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="I53" s="8">
         <v>46188</v>
@@ -4599,7 +4576,7 @@
         <v>26</v>
       </c>
       <c r="N53" s="9" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="O53" s="9" t="s">
         <v>26</v>
@@ -4615,28 +4592,28 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B54" s="5">
-        <v>46184.68816803241</v>
+        <v>46184.68826700232</v>
       </c>
       <c r="C54" s="5">
-        <v>46184.69000751157</v>
+        <v>46184.69031962963</v>
       </c>
       <c r="D54" s="5">
-        <v>46191.6871738426</v>
+        <v>46191.687168993056</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="I54" s="5">
         <v>46188</v>
@@ -4654,7 +4631,7 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="O54" s="6" t="s">
         <v>26</v>
@@ -4670,145 +4647,143 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="B55" s="8">
+        <v>46118.66227863426</v>
+      </c>
+      <c r="C55" s="9"/>
+      <c r="D55" s="8">
+        <v>46184.69022991898</v>
+      </c>
+      <c r="E55" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="F55" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G55" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="H55" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="I55" s="8">
+        <v>46206</v>
+      </c>
+      <c r="J55" s="8">
+        <v>46209</v>
+      </c>
+      <c r="K55" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L55" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M55" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N55" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="O55" s="9" t="s">
         <v>210</v>
       </c>
-      <c r="B55" s="8">
-        <v>46184.68826700232</v>
-      </c>
-      <c r="C55" s="8">
-        <v>46184.69031962963</v>
-      </c>
-      <c r="D55" s="8">
-        <v>46191.687168993056</v>
-      </c>
-      <c r="E55" s="9" t="s">
+      <c r="P55" s="9" t="s">
         <v>211</v>
       </c>
-      <c r="F55" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G55" s="9" t="s">
-        <v>197</v>
-      </c>
-      <c r="H55" s="9" t="s">
-        <v>198</v>
-      </c>
-      <c r="I55" s="8">
-        <v>46188</v>
-      </c>
-      <c r="J55" s="8">
-        <v>46205</v>
-      </c>
-      <c r="K55" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L55" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M55" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N55" s="9" t="s">
-        <v>201</v>
-      </c>
-      <c r="O55" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="P55" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q55" s="9"/>
-      <c r="R55" s="9"/>
-      <c r="S55" s="9"/>
-      <c r="T55" s="9"/>
-      <c r="U55" s="9"/>
+      <c r="Q55" s="8">
+        <v>46209</v>
+      </c>
+      <c r="R55" s="8">
+        <v>46206</v>
+      </c>
+      <c r="S55" s="9">
+        <v>0</v>
+      </c>
+      <c r="T55" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="U55" s="11" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
         <v>212</v>
       </c>
       <c r="B56" s="5">
-        <v>46118.66227863426</v>
+        <v>46118.66228488426</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46184.69022991898</v>
+        <v>46118.758174201386</v>
       </c>
       <c r="E56" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="F56" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="G56" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="H56" s="6"/>
+      <c r="I56" s="6"/>
+      <c r="J56" s="6"/>
+      <c r="K56" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L56" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M56" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="N56" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="O56" s="6" t="s">
         <v>213</v>
       </c>
-      <c r="F56" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G56" s="6" t="s">
-        <v>189</v>
-      </c>
-      <c r="H56" s="6" t="s">
-        <v>190</v>
-      </c>
-      <c r="I56" s="5">
-        <v>46206</v>
-      </c>
-      <c r="J56" s="5">
-        <v>46209</v>
-      </c>
-      <c r="K56" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L56" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M56" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N56" s="6" t="s">
-        <v>193</v>
-      </c>
-      <c r="O56" s="6" t="s">
-        <v>214</v>
-      </c>
       <c r="P56" s="6" t="s">
-        <v>215</v>
-      </c>
-      <c r="Q56" s="5">
-        <v>46209</v>
-      </c>
-      <c r="R56" s="5">
-        <v>46206</v>
-      </c>
-      <c r="S56" s="6">
-        <v>0</v>
-      </c>
-      <c r="T56" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="U56" s="11" t="s">
-        <v>60</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="Q56" s="6"/>
+      <c r="R56" s="6"/>
+      <c r="S56" s="6"/>
+      <c r="T56" s="6"/>
+      <c r="U56" s="6"/>
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B57" s="8">
-        <v>46118.66228488426</v>
+        <v>46118.66228803241</v>
       </c>
       <c r="C57" s="9"/>
       <c r="D57" s="8">
-        <v>46118.758174201386</v>
+        <v>46184.685795196754</v>
       </c>
       <c r="E57" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="F57" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G57" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="H57" s="9" t="s">
         <v>181</v>
       </c>
-      <c r="F57" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="G57" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H57" s="9"/>
-      <c r="I57" s="9"/>
-      <c r="J57" s="9"/>
+      <c r="I57" s="8">
+        <v>46168</v>
+      </c>
+      <c r="J57" s="8">
+        <v>46169</v>
+      </c>
       <c r="K57" s="9" t="s">
         <v>26</v>
       </c>
@@ -4816,51 +4791,61 @@
         <v>26</v>
       </c>
       <c r="M57" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N57" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="O57" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="P57" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="Q57" s="8">
+        <v>46169</v>
+      </c>
+      <c r="R57" s="8">
+        <v>46168</v>
+      </c>
+      <c r="S57" s="9">
         <v>0</v>
       </c>
-      <c r="N57" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="O57" s="9" t="s">
-        <v>217</v>
-      </c>
-      <c r="P57" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q57" s="9"/>
-      <c r="R57" s="9"/>
-      <c r="S57" s="9"/>
-      <c r="T57" s="9"/>
-      <c r="U57" s="9"/>
+      <c r="T57" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="U57" s="11" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B58" s="5">
-        <v>46118.66228803241</v>
+        <v>46118.662293518515</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46184.685795196754</v>
+        <v>46190.16815429398</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>219</v>
+        <v>58</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="I58" s="5">
-        <v>46168</v>
+        <v>46189</v>
       </c>
       <c r="J58" s="5">
-        <v>46169</v>
+        <v>46190</v>
       </c>
       <c r="K58" s="6" t="s">
         <v>26</v>
@@ -4872,19 +4857,19 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="Q58" s="5">
-        <v>46169</v>
+        <v>46190</v>
       </c>
       <c r="R58" s="5">
-        <v>46168</v>
+        <v>46189</v>
       </c>
       <c r="S58" s="6">
         <v>0</v>
@@ -4898,32 +4883,32 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B59" s="8">
-        <v>46118.662293518515</v>
+        <v>46118.662299895834</v>
       </c>
       <c r="C59" s="9"/>
       <c r="D59" s="8">
-        <v>46190.16815429398</v>
+        <v>46182.64329532407</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>58</v>
+        <v>220</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="I59" s="8">
-        <v>46189</v>
+        <v>46233</v>
       </c>
       <c r="J59" s="8">
-        <v>46190</v>
+        <v>46234</v>
       </c>
       <c r="K59" s="9" t="s">
         <v>26</v>
@@ -4935,19 +4920,19 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="Q59" s="8">
-        <v>46190</v>
+        <v>46234</v>
       </c>
       <c r="R59" s="8">
-        <v>46189</v>
+        <v>46233</v>
       </c>
       <c r="S59" s="9">
         <v>0</v>
@@ -4961,56 +4946,56 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B60" s="5">
-        <v>46118.662299895834</v>
+        <v>46118.66235550926</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46182.64329532407</v>
+        <v>46155.90269732639</v>
       </c>
       <c r="E60" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="F60" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G60" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="H60" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="I60" s="5">
+        <v>46255</v>
+      </c>
+      <c r="J60" s="5">
+        <v>46258</v>
+      </c>
+      <c r="K60" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L60" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M60" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N60" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="O60" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="P60" s="6" t="s">
         <v>224</v>
       </c>
-      <c r="F60" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G60" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="H60" s="6" t="s">
-        <v>185</v>
-      </c>
-      <c r="I60" s="5">
-        <v>46233</v>
-      </c>
-      <c r="J60" s="5">
-        <v>46234</v>
-      </c>
-      <c r="K60" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L60" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M60" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N60" s="6" t="s">
-        <v>181</v>
-      </c>
-      <c r="O60" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="P60" s="6" t="s">
-        <v>225</v>
-      </c>
       <c r="Q60" s="5">
-        <v>46234</v>
+        <v>46258</v>
       </c>
       <c r="R60" s="5">
-        <v>46233</v>
+        <v>46255</v>
       </c>
       <c r="S60" s="6">
         <v>0</v>
@@ -5024,166 +5009,166 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B61" s="8">
-        <v>46118.66235550926</v>
+        <v>46118.66236295139</v>
       </c>
       <c r="C61" s="9"/>
       <c r="D61" s="8">
-        <v>46155.90269732639</v>
+        <v>46184.883015300926</v>
       </c>
       <c r="E61" s="9" t="s">
+        <v>226</v>
+      </c>
+      <c r="F61" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="G61" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="H61" s="9"/>
+      <c r="I61" s="9"/>
+      <c r="J61" s="9"/>
+      <c r="K61" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L61" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M61" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="N61" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="O61" s="9" t="s">
         <v>227</v>
       </c>
-      <c r="F61" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G61" s="9" t="s">
-        <v>184</v>
-      </c>
-      <c r="H61" s="9" t="s">
-        <v>185</v>
-      </c>
-      <c r="I61" s="8">
-        <v>46255</v>
-      </c>
-      <c r="J61" s="8">
-        <v>46258</v>
-      </c>
-      <c r="K61" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L61" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M61" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N61" s="9" t="s">
-        <v>181</v>
-      </c>
-      <c r="O61" s="9" t="s">
-        <v>144</v>
-      </c>
       <c r="P61" s="9" t="s">
-        <v>228</v>
-      </c>
-      <c r="Q61" s="8">
-        <v>46258</v>
-      </c>
-      <c r="R61" s="8">
-        <v>46255</v>
-      </c>
-      <c r="S61" s="9">
-        <v>0</v>
-      </c>
-      <c r="T61" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="U61" s="11" t="s">
-        <v>60</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="Q61" s="9"/>
+      <c r="R61" s="9"/>
+      <c r="S61" s="9"/>
+      <c r="T61" s="9"/>
+      <c r="U61" s="9"/>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B62" s="5">
-        <v>46118.66236295139</v>
+        <v>46118.66236873843</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46184.883015300926</v>
+        <v>46183.89100212963</v>
       </c>
       <c r="E62" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="F62" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G62" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="H62" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="I62" s="5">
+        <v>46210</v>
+      </c>
+      <c r="J62" s="5">
+        <v>46227</v>
+      </c>
+      <c r="K62" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L62" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M62" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N62" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="O62" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="P62" s="6" t="s">
         <v>230</v>
       </c>
-      <c r="F62" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G62" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H62" s="6"/>
-      <c r="I62" s="6"/>
-      <c r="J62" s="6"/>
-      <c r="K62" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L62" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M62" s="6" t="s">
+      <c r="Q62" s="5">
+        <v>46227</v>
+      </c>
+      <c r="R62" s="5">
+        <v>46210</v>
+      </c>
+      <c r="S62" s="6">
         <v>0</v>
       </c>
-      <c r="N62" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="O62" s="6" t="s">
-        <v>231</v>
-      </c>
-      <c r="P62" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q62" s="6"/>
-      <c r="R62" s="6"/>
-      <c r="S62" s="6"/>
-      <c r="T62" s="6"/>
-      <c r="U62" s="6"/>
+      <c r="T62" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="U62" s="11" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B63" s="8">
-        <v>46118.66236873843</v>
+        <v>46118.662376064814</v>
       </c>
       <c r="C63" s="9"/>
       <c r="D63" s="8">
-        <v>46183.89100212963</v>
+        <v>46134.800407835646</v>
       </c>
       <c r="E63" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="F63" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G63" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="H63" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="I63" s="8">
+        <v>46259</v>
+      </c>
+      <c r="J63" s="8">
+        <v>46260</v>
+      </c>
+      <c r="K63" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L63" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M63" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N63" s="9" t="s">
+        <v>226</v>
+      </c>
+      <c r="O63" s="9" t="s">
+        <v>232</v>
+      </c>
+      <c r="P63" s="9" t="s">
         <v>233</v>
       </c>
-      <c r="F63" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G63" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="H63" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="I63" s="8">
-        <v>46210</v>
-      </c>
-      <c r="J63" s="8">
-        <v>46227</v>
-      </c>
-      <c r="K63" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L63" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M63" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N63" s="9" t="s">
-        <v>230</v>
-      </c>
-      <c r="O63" s="9" t="s">
-        <v>213</v>
-      </c>
-      <c r="P63" s="9" t="s">
-        <v>234</v>
-      </c>
       <c r="Q63" s="8">
-        <v>46227</v>
+        <v>46260</v>
       </c>
       <c r="R63" s="8">
-        <v>46210</v>
+        <v>46259</v>
       </c>
       <c r="S63" s="9">
         <v>0</v>
@@ -5197,32 +5182,32 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B64" s="5">
-        <v>46118.662376064814</v>
+        <v>46118.662387557866</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46134.800407835646</v>
+        <v>46134.80040113426</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="I64" s="5">
-        <v>46259</v>
+        <v>46261</v>
       </c>
       <c r="J64" s="5">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="K64" s="6" t="s">
         <v>26</v>
@@ -5234,19 +5219,19 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="O64" s="6" t="s">
         <v>236</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="Q64" s="5">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="R64" s="5">
-        <v>46259</v>
+        <v>46261</v>
       </c>
       <c r="S64" s="6">
         <v>0</v>
@@ -5260,56 +5245,56 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B65" s="8">
-        <v>46118.662387557866</v>
+        <v>46118.662398796296</v>
       </c>
       <c r="C65" s="9"/>
       <c r="D65" s="8">
-        <v>46134.80040113426</v>
+        <v>46134.800407118055</v>
       </c>
       <c r="E65" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="F65" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G65" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="H65" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="I65" s="8">
+        <v>46265</v>
+      </c>
+      <c r="J65" s="8">
+        <v>46266</v>
+      </c>
+      <c r="K65" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L65" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M65" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N65" s="9" t="s">
+        <v>226</v>
+      </c>
+      <c r="O65" s="9" t="s">
         <v>239</v>
       </c>
-      <c r="F65" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G65" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="H65" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="I65" s="8">
-        <v>46261</v>
-      </c>
-      <c r="J65" s="8">
-        <v>46262</v>
-      </c>
-      <c r="K65" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L65" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M65" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N65" s="9" t="s">
-        <v>230</v>
-      </c>
-      <c r="O65" s="9" t="s">
-        <v>240</v>
-      </c>
       <c r="P65" s="9" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="Q65" s="8">
-        <v>46262</v>
+        <v>46266</v>
       </c>
       <c r="R65" s="8">
-        <v>46261</v>
+        <v>46265</v>
       </c>
       <c r="S65" s="9">
         <v>0</v>
@@ -5323,56 +5308,54 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B66" s="5">
-        <v>46118.662398796296</v>
+        <v>46118.66240984954</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46134.800407118055</v>
+        <v>46118.76777010417</v>
       </c>
       <c r="E66" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="F66" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G66" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="H66" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="I66" s="6"/>
+      <c r="J66" s="5">
+        <v>46267</v>
+      </c>
+      <c r="K66" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L66" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M66" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N66" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="O66" s="6" t="s">
+        <v>241</v>
+      </c>
+      <c r="P66" s="6" t="s">
         <v>242</v>
       </c>
-      <c r="F66" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G66" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="H66" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="I66" s="5">
-        <v>46265</v>
-      </c>
-      <c r="J66" s="5">
-        <v>46266</v>
-      </c>
-      <c r="K66" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L66" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M66" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N66" s="6" t="s">
-        <v>230</v>
-      </c>
-      <c r="O66" s="6" t="s">
-        <v>243</v>
-      </c>
-      <c r="P66" s="6" t="s">
-        <v>237</v>
-      </c>
       <c r="Q66" s="5">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="R66" s="5">
-        <v>46265</v>
+        <v>46267</v>
       </c>
       <c r="S66" s="6">
         <v>0</v>
@@ -5386,30 +5369,32 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B67" s="8">
-        <v>46118.66240984954</v>
+        <v>46118.662420127315</v>
       </c>
       <c r="C67" s="9"/>
       <c r="D67" s="8">
-        <v>46118.76777010417</v>
+        <v>46118.76776545139</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>178</v>
+        <v>244</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="H67" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="I67" s="9"/>
+        <v>92</v>
+      </c>
+      <c r="I67" s="8">
+        <v>46269</v>
+      </c>
       <c r="J67" s="8">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="K67" s="9" t="s">
         <v>26</v>
@@ -5421,19 +5406,19 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="O67" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="P67" s="9" t="s">
         <v>245</v>
       </c>
-      <c r="P67" s="9" t="s">
-        <v>246</v>
-      </c>
       <c r="Q67" s="8">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="R67" s="8">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="S67" s="9">
         <v>0</v>
@@ -5447,90 +5432,78 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B68" s="5">
-        <v>46118.662420127315</v>
+        <v>46118.66242769676</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46118.76776545139</v>
+        <v>46118.76233159722</v>
       </c>
       <c r="E68" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="F68" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="G68" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="H68" s="6"/>
+      <c r="I68" s="6"/>
+      <c r="J68" s="6"/>
+      <c r="K68" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L68" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M68" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="N68" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="O68" s="6" t="s">
         <v>248</v>
       </c>
-      <c r="F68" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G68" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="H68" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="I68" s="5">
-        <v>46269</v>
-      </c>
-      <c r="J68" s="5">
-        <v>46269</v>
-      </c>
-      <c r="K68" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L68" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M68" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N68" s="6" t="s">
-        <v>230</v>
-      </c>
-      <c r="O68" s="6" t="s">
-        <v>175</v>
-      </c>
       <c r="P68" s="6" t="s">
-        <v>249</v>
-      </c>
-      <c r="Q68" s="5">
-        <v>46269</v>
-      </c>
-      <c r="R68" s="5">
-        <v>46269</v>
-      </c>
-      <c r="S68" s="6">
-        <v>0</v>
-      </c>
-      <c r="T68" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="U68" s="11" t="s">
-        <v>60</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="Q68" s="6"/>
+      <c r="R68" s="6"/>
+      <c r="S68" s="6"/>
+      <c r="T68" s="6"/>
+      <c r="U68" s="6"/>
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B69" s="8">
-        <v>46118.66242769676</v>
+        <v>46118.662431770834</v>
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46118.76233159722</v>
+        <v>46118.76789673611</v>
       </c>
       <c r="E69" s="9" t="s">
+        <v>250</v>
+      </c>
+      <c r="F69" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G69" s="9" t="s">
         <v>251</v>
       </c>
-      <c r="F69" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="G69" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H69" s="9"/>
+      <c r="H69" s="9" t="s">
+        <v>252</v>
+      </c>
       <c r="I69" s="9"/>
-      <c r="J69" s="9"/>
+      <c r="J69" s="8">
+        <v>46272</v>
+      </c>
       <c r="K69" s="9" t="s">
         <v>26</v>
       </c>
@@ -5538,49 +5511,59 @@
         <v>26</v>
       </c>
       <c r="M69" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N69" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="O69" s="9" t="s">
+        <v>244</v>
+      </c>
+      <c r="P69" s="9" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q69" s="8">
+        <v>46272</v>
+      </c>
+      <c r="R69" s="8">
+        <v>46272</v>
+      </c>
+      <c r="S69" s="9">
         <v>0</v>
       </c>
-      <c r="N69" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="O69" s="9" t="s">
-        <v>252</v>
-      </c>
-      <c r="P69" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q69" s="9"/>
-      <c r="R69" s="9"/>
-      <c r="S69" s="9"/>
-      <c r="T69" s="9"/>
-      <c r="U69" s="9"/>
+      <c r="T69" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="U69" s="11" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B70" s="5">
-        <v>46118.662431770834</v>
+        <v>46118.662438252315</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46118.76789673611</v>
+        <v>46118.767944374995</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>255</v>
+        <v>92</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>256</v>
+        <v>92</v>
       </c>
       <c r="I70" s="6"/>
       <c r="J70" s="5">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="K70" s="6" t="s">
         <v>26</v>
@@ -5592,19 +5575,19 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>257</v>
       </c>
       <c r="Q70" s="5">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="R70" s="5">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="S70" s="6">
         <v>0</v>
@@ -5621,11 +5604,11 @@
         <v>258</v>
       </c>
       <c r="B71" s="8">
-        <v>46118.662438252315</v>
+        <v>46118.66245149306</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46118.767944374995</v>
+        <v>46118.76799315972</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>259</v>
@@ -5634,14 +5617,14 @@
         <v>26</v>
       </c>
       <c r="G71" s="9" t="s">
-        <v>97</v>
+        <v>260</v>
       </c>
       <c r="H71" s="9" t="s">
-        <v>97</v>
+        <v>261</v>
       </c>
       <c r="I71" s="9"/>
       <c r="J71" s="8">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="K71" s="9" t="s">
         <v>26</v>
@@ -5653,19 +5636,19 @@
         <v>26</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="P71" s="9" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q71" s="8">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="R71" s="8">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="S71" s="9">
         <v>0</v>
@@ -5679,30 +5662,30 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B72" s="5">
-        <v>46118.66245149306</v>
+        <v>46118.66245769676</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46118.76799315972</v>
+        <v>46118.76803266203</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="I72" s="6"/>
       <c r="J72" s="5">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="K72" s="6" t="s">
         <v>26</v>
@@ -5714,19 +5697,19 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="O72" s="6" t="s">
         <v>259</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="Q72" s="5">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="R72" s="5">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="S72" s="6">
         <v>0</v>
@@ -5740,88 +5723,80 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B73" s="8">
-        <v>46118.66245769676</v>
+        <v>46118.66246467593</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46118.76803266203</v>
+        <v>46118.76284858796</v>
       </c>
       <c r="E73" s="9" t="s">
+        <v>267</v>
+      </c>
+      <c r="F73" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="G73" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="H73" s="9"/>
+      <c r="I73" s="9"/>
+      <c r="J73" s="9"/>
+      <c r="K73" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L73" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M73" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="N73" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="O73" s="9" t="s">
         <v>268</v>
       </c>
-      <c r="F73" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G73" s="9" t="s">
-        <v>264</v>
-      </c>
-      <c r="H73" s="9" t="s">
-        <v>265</v>
-      </c>
-      <c r="I73" s="9"/>
-      <c r="J73" s="8">
-        <v>46275</v>
-      </c>
-      <c r="K73" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L73" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M73" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N73" s="9" t="s">
-        <v>251</v>
-      </c>
-      <c r="O73" s="9" t="s">
-        <v>263</v>
-      </c>
       <c r="P73" s="9" t="s">
-        <v>269</v>
-      </c>
-      <c r="Q73" s="8">
-        <v>46275</v>
-      </c>
-      <c r="R73" s="8">
-        <v>46275</v>
-      </c>
-      <c r="S73" s="9">
-        <v>0</v>
-      </c>
-      <c r="T73" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="U73" s="11" t="s">
-        <v>60</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="Q73" s="9"/>
+      <c r="R73" s="9"/>
+      <c r="S73" s="9"/>
+      <c r="T73" s="9"/>
+      <c r="U73" s="9"/>
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B74" s="5">
-        <v>46118.66246467593</v>
+        <v>46118.66246796296</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46118.76284858796</v>
+        <v>46118.76810806713</v>
       </c>
       <c r="E74" s="6" t="s">
+        <v>270</v>
+      </c>
+      <c r="F74" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G74" s="6" t="s">
         <v>271</v>
       </c>
-      <c r="F74" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G74" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H74" s="6"/>
-      <c r="I74" s="6"/>
-      <c r="J74" s="6"/>
+      <c r="H74" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="I74" s="5">
+        <v>46276</v>
+      </c>
+      <c r="J74" s="5">
+        <v>46286</v>
+      </c>
       <c r="K74" s="6" t="s">
         <v>26</v>
       </c>
@@ -5829,33 +5804,43 @@
         <v>26</v>
       </c>
       <c r="M74" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N74" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="O74" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="P74" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="Q74" s="5">
+        <v>46286</v>
+      </c>
+      <c r="R74" s="5">
+        <v>46276</v>
+      </c>
+      <c r="S74" s="6">
         <v>0</v>
       </c>
-      <c r="N74" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="O74" s="6" t="s">
-        <v>272</v>
-      </c>
-      <c r="P74" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q74" s="6"/>
-      <c r="R74" s="6"/>
-      <c r="S74" s="6"/>
-      <c r="T74" s="6"/>
-      <c r="U74" s="6"/>
+      <c r="T74" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="U74" s="11" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
         <v>273</v>
       </c>
       <c r="B75" s="8">
-        <v>46118.66246796296</v>
+        <v>46118.66251259259</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46118.76810806713</v>
+        <v>46191.7722621412</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>274</v>
@@ -5864,10 +5849,10 @@
         <v>26</v>
       </c>
       <c r="G75" s="9" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="H75" s="9" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="I75" s="8">
         <v>46276</v>
@@ -5885,13 +5870,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="Q75" s="8">
         <v>46286</v>
@@ -5911,33 +5896,27 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B76" s="5">
-        <v>46118.66251259259</v>
+        <v>46118.662521377315</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46118.768105243056</v>
+        <v>46118.76362347222</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="F76" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>275</v>
-      </c>
-      <c r="H76" s="6" t="s">
-        <v>276</v>
-      </c>
-      <c r="I76" s="5">
-        <v>46276</v>
-      </c>
-      <c r="J76" s="5">
-        <v>46286</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H76" s="6"/>
+      <c r="I76" s="6"/>
+      <c r="J76" s="6"/>
       <c r="K76" s="6" t="s">
         <v>26</v>
       </c>
@@ -5945,56 +5924,52 @@
         <v>26</v>
       </c>
       <c r="M76" s="6" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>271</v>
+        <v>26</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="Q76" s="5">
-        <v>46286</v>
-      </c>
-      <c r="R76" s="5">
-        <v>46276</v>
-      </c>
-      <c r="S76" s="6">
-        <v>0</v>
-      </c>
-      <c r="T76" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="U76" s="11" t="s">
-        <v>60</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="Q76" s="6"/>
+      <c r="R76" s="6"/>
+      <c r="S76" s="6"/>
+      <c r="T76" s="6"/>
+      <c r="U76" s="6"/>
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B77" s="8">
-        <v>46118.662521377315</v>
+        <v>46118.66252565972</v>
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46118.76362347222</v>
+        <v>46118.7682625</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="F77" s="9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G77" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H77" s="9"/>
-      <c r="I77" s="9"/>
-      <c r="J77" s="9"/>
+        <v>52</v>
+      </c>
+      <c r="H77" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="I77" s="8">
+        <v>46276</v>
+      </c>
+      <c r="J77" s="8">
+        <v>46286</v>
+      </c>
       <c r="K77" s="9" t="s">
         <v>26</v>
       </c>
@@ -6002,36 +5977,46 @@
         <v>26</v>
       </c>
       <c r="M77" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N77" s="9" t="s">
+        <v>276</v>
+      </c>
+      <c r="O77" s="9" t="s">
+        <v>264</v>
+      </c>
+      <c r="P77" s="9" t="s">
+        <v>280</v>
+      </c>
+      <c r="Q77" s="8">
+        <v>46286</v>
+      </c>
+      <c r="R77" s="8">
+        <v>46276</v>
+      </c>
+      <c r="S77" s="9">
         <v>0</v>
       </c>
-      <c r="N77" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="O77" s="9" t="s">
-        <v>282</v>
-      </c>
-      <c r="P77" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q77" s="9"/>
-      <c r="R77" s="9"/>
-      <c r="S77" s="9"/>
-      <c r="T77" s="9"/>
-      <c r="U77" s="9"/>
+      <c r="T77" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="U77" s="11" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B78" s="5">
-        <v>46118.66252565972</v>
+        <v>46118.662532013885</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46118.7682625</v>
+        <v>46118.76825962963</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
@@ -6043,10 +6028,10 @@
         <v>53</v>
       </c>
       <c r="I78" s="5">
-        <v>46276</v>
+        <v>46287</v>
       </c>
       <c r="J78" s="5">
-        <v>46286</v>
+        <v>46295</v>
       </c>
       <c r="K78" s="6" t="s">
         <v>26</v>
@@ -6058,19 +6043,19 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>268</v>
+        <v>279</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>285</v>
+        <v>276</v>
       </c>
       <c r="Q78" s="5">
-        <v>46286</v>
+        <v>46295</v>
       </c>
       <c r="R78" s="5">
-        <v>46276</v>
+        <v>46287</v>
       </c>
       <c r="S78" s="6">
         <v>0</v>
@@ -6079,69 +6064,6 @@
         <v>32</v>
       </c>
       <c r="U78" s="11" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="79" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A79" s="7" t="s">
-        <v>286</v>
-      </c>
-      <c r="B79" s="8">
-        <v>46118.662532013885</v>
-      </c>
-      <c r="C79" s="9"/>
-      <c r="D79" s="8">
-        <v>46118.76825962963</v>
-      </c>
-      <c r="E79" s="9" t="s">
-        <v>287</v>
-      </c>
-      <c r="F79" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G79" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="H79" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="I79" s="8">
-        <v>46287</v>
-      </c>
-      <c r="J79" s="8">
-        <v>46295</v>
-      </c>
-      <c r="K79" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L79" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M79" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N79" s="9" t="s">
-        <v>281</v>
-      </c>
-      <c r="O79" s="9" t="s">
-        <v>284</v>
-      </c>
-      <c r="P79" s="9" t="s">
-        <v>281</v>
-      </c>
-      <c r="Q79" s="8">
-        <v>46295</v>
-      </c>
-      <c r="R79" s="8">
-        <v>46287</v>
-      </c>
-      <c r="S79" s="9">
-        <v>0</v>
-      </c>
-      <c r="T79" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="U79" s="11" t="s">
         <v>60</v>
       </c>
     </row>

--- a/data/50001533 - GESVIAL.xlsx
+++ b/data/50001533 - GESVIAL.xlsx
@@ -2067,7 +2067,7 @@
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46133.90095863426</v>
+        <v>46192.52082222222</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>57</v>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46183.89100212963</v>
+        <v>46192.52234210648</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>229</v>

--- a/data/50001533 - GESVIAL.xlsx
+++ b/data/50001533 - GESVIAL.xlsx
@@ -5063,7 +5063,7 @@
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46192.52234210648</v>
+        <v>46192.891900636576</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>229</v>

--- a/data/50001533 - GESVIAL.xlsx
+++ b/data/50001533 - GESVIAL.xlsx
@@ -2067,7 +2067,7 @@
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46192.52082222222</v>
+        <v>46193.56198241898</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>57</v>
@@ -2128,9 +2128,11 @@
       <c r="B13" s="8">
         <v>46118.66186076389</v>
       </c>
-      <c r="C13" s="9"/>
+      <c r="C13" s="8">
+        <v>46193.56179229167</v>
+      </c>
       <c r="D13" s="8">
-        <v>46191.77226840278</v>
+        <v>46193.561794629626</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>62</v>
@@ -4019,7 +4021,7 @@
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="5">
-        <v>46118.76724443287</v>
+        <v>46193.765527129624</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>171</v>
@@ -4261,7 +4263,7 @@
       </c>
       <c r="C48" s="6"/>
       <c r="D48" s="5">
-        <v>46184.69022914352</v>
+        <v>46193.56241145833</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>189</v>
@@ -4371,9 +4373,11 @@
       <c r="B50" s="5">
         <v>46118.66227269676</v>
       </c>
-      <c r="C50" s="6"/>
+      <c r="C50" s="5">
+        <v>46193.56191304398</v>
+      </c>
       <c r="D50" s="5">
-        <v>46185.70189067129</v>
+        <v>46193.561914942125</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>197</v>
@@ -4652,9 +4656,11 @@
       <c r="B55" s="8">
         <v>46118.66227863426</v>
       </c>
-      <c r="C55" s="9"/>
+      <c r="C55" s="8">
+        <v>46193.56240042824</v>
+      </c>
       <c r="D55" s="8">
-        <v>46184.69022991898</v>
+        <v>46193.562405625</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>209</v>
@@ -4717,7 +4723,7 @@
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46118.758174201386</v>
+        <v>46193.56235371528</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>177</v>
@@ -4762,9 +4768,11 @@
       <c r="B57" s="8">
         <v>46118.66228803241</v>
       </c>
-      <c r="C57" s="9"/>
+      <c r="C57" s="8">
+        <v>46193.562345370374</v>
+      </c>
       <c r="D57" s="8">
-        <v>46184.685795196754</v>
+        <v>46193.56234733797</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>215</v>
@@ -4825,9 +4833,11 @@
       <c r="B58" s="5">
         <v>46118.662293518515</v>
       </c>
-      <c r="C58" s="6"/>
+      <c r="C58" s="5">
+        <v>46193.56197458333</v>
+      </c>
       <c r="D58" s="5">
-        <v>46190.16815429398</v>
+        <v>46193.56197650463</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>58</v>
@@ -4888,9 +4898,11 @@
       <c r="B59" s="8">
         <v>46118.662299895834</v>
       </c>
-      <c r="C59" s="9"/>
+      <c r="C59" s="8">
+        <v>46193.561984872686</v>
+      </c>
       <c r="D59" s="8">
-        <v>46182.64329532407</v>
+        <v>46193.561986678236</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>220</v>
@@ -4951,9 +4963,11 @@
       <c r="B60" s="5">
         <v>46118.66235550926</v>
       </c>
-      <c r="C60" s="6"/>
+      <c r="C60" s="5">
+        <v>46193.56199724537</v>
+      </c>
       <c r="D60" s="5">
-        <v>46155.90269732639</v>
+        <v>46193.56199886574</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>223</v>
@@ -5014,9 +5028,11 @@
       <c r="B61" s="8">
         <v>46118.66236295139</v>
       </c>
-      <c r="C61" s="9"/>
+      <c r="C61" s="8">
+        <v>46193.765035358796</v>
+      </c>
       <c r="D61" s="8">
-        <v>46184.883015300926</v>
+        <v>46193.765528379634</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>226</v>
@@ -5061,9 +5077,11 @@
       <c r="B62" s="5">
         <v>46118.66236873843</v>
       </c>
-      <c r="C62" s="6"/>
+      <c r="C62" s="5">
+        <v>46193.61261344908</v>
+      </c>
       <c r="D62" s="5">
-        <v>46192.891900636576</v>
+        <v>46193.61261581018</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>229</v>
@@ -5124,9 +5142,11 @@
       <c r="B63" s="8">
         <v>46118.662376064814</v>
       </c>
-      <c r="C63" s="9"/>
+      <c r="C63" s="8">
+        <v>46193.6126587037</v>
+      </c>
       <c r="D63" s="8">
-        <v>46134.800407835646</v>
+        <v>46193.61266056713</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>224</v>
@@ -5187,9 +5207,11 @@
       <c r="B64" s="5">
         <v>46118.662387557866</v>
       </c>
-      <c r="C64" s="6"/>
+      <c r="C64" s="5">
+        <v>46193.61267944444</v>
+      </c>
       <c r="D64" s="5">
-        <v>46134.80040113426</v>
+        <v>46193.61268100694</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>235</v>
@@ -5250,9 +5272,11 @@
       <c r="B65" s="8">
         <v>46118.662398796296</v>
       </c>
-      <c r="C65" s="9"/>
+      <c r="C65" s="8">
+        <v>46193.61273716435</v>
+      </c>
       <c r="D65" s="8">
-        <v>46134.800407118055</v>
+        <v>46193.61273954861</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>238</v>
@@ -5313,9 +5337,11 @@
       <c r="B66" s="5">
         <v>46118.66240984954</v>
       </c>
-      <c r="C66" s="6"/>
+      <c r="C66" s="5">
+        <v>46193.765511875</v>
+      </c>
       <c r="D66" s="5">
-        <v>46118.76777010417</v>
+        <v>46193.765518935186</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>174</v>
@@ -5376,7 +5402,7 @@
       </c>
       <c r="C67" s="9"/>
       <c r="D67" s="8">
-        <v>46118.76776545139</v>
+        <v>46193.56286064815</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>244</v>

--- a/data/50001533 - GESVIAL.xlsx
+++ b/data/50001533 - GESVIAL.xlsx
@@ -4261,9 +4261,11 @@
       <c r="B48" s="5">
         <v>46118.662263819446</v>
       </c>
-      <c r="C48" s="6"/>
+      <c r="C48" s="5">
+        <v>46194.056337268514</v>
+      </c>
       <c r="D48" s="5">
-        <v>46193.56241145833</v>
+        <v>46194.05633912037</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>189</v>
@@ -4721,9 +4723,11 @@
       <c r="B56" s="5">
         <v>46118.66228488426</v>
       </c>
-      <c r="C56" s="6"/>
+      <c r="C56" s="5">
+        <v>46194.05632121528</v>
+      </c>
       <c r="D56" s="5">
-        <v>46193.56235371528</v>
+        <v>46194.05632325231</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>177</v>

--- a/data/50001533 - GESVIAL.xlsx
+++ b/data/50001533 - GESVIAL.xlsx
@@ -2067,7 +2067,7 @@
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46193.56198241898</v>
+        <v>46195.52671909722</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>57</v>

--- a/data/50001533 - GESVIAL.xlsx
+++ b/data/50001533 - GESVIAL.xlsx
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C67" s="9"/>
       <c r="D67" s="8">
-        <v>46193.56286064815</v>
+        <v>46195.56277597223</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>244</v>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46118.76789673611</v>
+        <v>46195.56384930556</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>250</v>
@@ -5577,7 +5577,7 @@
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46118.767944374995</v>
+        <v>46195.563925752314</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>255</v>
@@ -5638,7 +5638,7 @@
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46118.76799315972</v>
+        <v>46195.56435059028</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>259</v>
@@ -5699,7 +5699,7 @@
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46118.76803266203</v>
+        <v>46195.56406409723</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>264</v>

--- a/data/50001533 - GESVIAL.xlsx
+++ b/data/50001533 - GESVIAL.xlsx
@@ -4495,9 +4495,11 @@
       <c r="B52" s="5">
         <v>46184.688093055556</v>
       </c>
-      <c r="C52" s="6"/>
+      <c r="C52" s="5">
+        <v>46195.7025405787</v>
+      </c>
       <c r="D52" s="5">
-        <v>46191.687177245374</v>
+        <v>46195.70254238426</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>203</v>

--- a/data/50001533 - GESVIAL.xlsx
+++ b/data/50001533 - GESVIAL.xlsx
@@ -5640,7 +5640,7 @@
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46195.56435059028</v>
+        <v>46196.567130752315</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>259</v>
@@ -5701,7 +5701,7 @@
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46195.56406409723</v>
+        <v>46196.57031530092</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>264</v>

--- a/data/50001533 - GESVIAL.xlsx
+++ b/data/50001533 - GESVIAL.xlsx
@@ -5518,7 +5518,7 @@
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46195.56384930556</v>
+        <v>46196.576254618056</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>250</v>
@@ -5579,7 +5579,7 @@
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46195.563925752314</v>
+        <v>46196.57543765046</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>255</v>

--- a/data/50001533 - GESVIAL.xlsx
+++ b/data/50001533 - GESVIAL.xlsx
@@ -251,9 +251,6 @@
     <t>Ingenieria Servicios:,Embalaje</t>
   </si>
   <si>
-    <t>Tarea sin iniciar</t>
-  </si>
-  <si>
     <t>1213955236952399</t>
   </si>
   <si>
@@ -429,6 +426,9 @@
   </si>
   <si>
     <t>Fabricación Alabe - OT4285,Generación OC Alabe - OT4285</t>
+  </si>
+  <si>
+    <t>Tarea sin iniciar</t>
   </si>
   <si>
     <t>1213973327836153</t>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46129.57130488426</v>
+        <v>46196.895724664355</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>48</v>
@@ -2065,9 +2065,11 @@
       <c r="B12" s="5">
         <v>46118.66203578704</v>
       </c>
-      <c r="C12" s="6"/>
+      <c r="C12" s="5">
+        <v>46196.89571644676</v>
+      </c>
       <c r="D12" s="5">
-        <v>46195.52671909722</v>
+        <v>46196.89571872685</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>57</v>
@@ -2112,18 +2114,18 @@
         <v>46191</v>
       </c>
       <c r="S12" s="6">
-        <v>0</v>
-      </c>
-      <c r="T12" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="U12" s="11" t="s">
-        <v>60</v>
+        <v>1</v>
+      </c>
+      <c r="T12" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="U12" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B13" s="8">
         <v>46118.66186076389</v>
@@ -2135,7 +2137,7 @@
         <v>46193.561794629626</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F13" s="9" t="s">
         <v>25</v>
@@ -2159,7 +2161,7 @@
         <v>26</v>
       </c>
       <c r="O13" s="9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="P13" s="9" t="s">
         <v>26</v>
@@ -2172,7 +2174,7 @@
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B14" s="5">
         <v>46118.66204173611</v>
@@ -2184,7 +2186,7 @@
         <v>46191.77226219907</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>26</v>
@@ -2205,19 +2207,19 @@
         <v>26</v>
       </c>
       <c r="L14" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="M14" s="6" t="s">
         <v>26</v>
       </c>
       <c r="N14" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="O14" s="6" t="s">
         <v>41</v>
       </c>
       <c r="P14" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="Q14" s="5">
         <v>46107</v>
@@ -2237,7 +2239,7 @@
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B15" s="8">
         <v>46118.66204752315</v>
@@ -2249,7 +2251,7 @@
         <v>46191.77226225694</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F15" s="9" t="s">
         <v>26</v>
@@ -2270,19 +2272,19 @@
         <v>26</v>
       </c>
       <c r="L15" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="M15" s="9" t="s">
         <v>26</v>
       </c>
       <c r="N15" s="9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="O15" s="9" t="s">
         <v>41</v>
       </c>
       <c r="P15" s="9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="Q15" s="8">
         <v>46114</v>
@@ -2302,7 +2304,7 @@
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B16" s="5">
         <v>46118.66205295139</v>
@@ -2314,7 +2316,7 @@
         <v>46191.7722621412</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>26</v>
@@ -2335,19 +2337,19 @@
         <v>26</v>
       </c>
       <c r="L16" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="M16" s="6" t="s">
         <v>26</v>
       </c>
       <c r="N16" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="O16" s="6" t="s">
         <v>41</v>
       </c>
       <c r="P16" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="Q16" s="5">
         <v>46114</v>
@@ -2367,7 +2369,7 @@
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B17" s="8">
         <v>46118.6618661574</v>
@@ -2379,7 +2381,7 @@
         <v>46184.72974401621</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F17" s="9" t="s">
         <v>25</v>
@@ -2403,7 +2405,7 @@
         <v>26</v>
       </c>
       <c r="O17" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="P17" s="9" t="s">
         <v>26</v>
@@ -2416,7 +2418,7 @@
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B18" s="5">
         <v>46118.66206653936</v>
@@ -2428,7 +2430,7 @@
         <v>46129.56236072916</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>26</v>
@@ -2449,19 +2451,19 @@
         <v>26</v>
       </c>
       <c r="L18" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="M18" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N18" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="O18" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="P18" s="6" t="s">
         <v>81</v>
-      </c>
-      <c r="M18" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N18" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="O18" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="P18" s="6" t="s">
-        <v>82</v>
       </c>
       <c r="Q18" s="5">
         <v>46118</v>
@@ -2481,7 +2483,7 @@
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B19" s="8">
         <v>46118.66207174768</v>
@@ -2493,7 +2495,7 @@
         <v>46129.56236737268</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F19" s="9" t="s">
         <v>26</v>
@@ -2514,19 +2516,19 @@
         <v>26</v>
       </c>
       <c r="L19" s="9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="M19" s="9" t="s">
         <v>26</v>
       </c>
       <c r="N19" s="9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="O19" s="9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="P19" s="9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q19" s="8">
         <v>46111</v>
@@ -2546,7 +2548,7 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B20" s="5">
         <v>46118.66207709491</v>
@@ -2558,7 +2560,7 @@
         <v>46129.57135429398</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
@@ -2579,19 +2581,19 @@
         <v>26</v>
       </c>
       <c r="L20" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="M20" s="6" t="s">
         <v>26</v>
       </c>
       <c r="N20" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="O20" s="6" t="s">
         <v>51</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="Q20" s="5">
         <v>46112</v>
@@ -2611,7 +2613,7 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B21" s="8">
         <v>46118.66208231481</v>
@@ -2623,16 +2625,16 @@
         <v>46183.880102916664</v>
       </c>
       <c r="E21" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="F21" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G21" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="F21" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G21" s="9" t="s">
-        <v>92</v>
-      </c>
       <c r="H21" s="9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I21" s="8">
         <v>46115</v>
@@ -2650,13 +2652,13 @@
         <v>26</v>
       </c>
       <c r="N21" s="9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="O21" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="P21" s="9" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Q21" s="8">
         <v>46118</v>
@@ -2671,12 +2673,12 @@
         <v>55</v>
       </c>
       <c r="U21" s="12" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B22" s="5">
         <v>46118.662087523146</v>
@@ -2688,16 +2690,16 @@
         <v>46183.888251435186</v>
       </c>
       <c r="E22" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G22" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="F22" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G22" s="6" t="s">
+      <c r="H22" s="6" t="s">
         <v>97</v>
-      </c>
-      <c r="H22" s="6" t="s">
-        <v>98</v>
       </c>
       <c r="I22" s="5">
         <v>46150</v>
@@ -2715,13 +2717,13 @@
         <v>26</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="O22" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="P22" s="6" t="s">
         <v>99</v>
-      </c>
-      <c r="P22" s="6" t="s">
-        <v>100</v>
       </c>
       <c r="Q22" s="5">
         <v>46153</v>
@@ -2736,12 +2738,12 @@
         <v>32</v>
       </c>
       <c r="U22" s="12" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B23" s="8">
         <v>46118.66187195602</v>
@@ -2753,7 +2755,7 @@
         <v>46184.686248067126</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>25</v>
@@ -2777,7 +2779,7 @@
         <v>26</v>
       </c>
       <c r="O23" s="9" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="P23" s="9" t="s">
         <v>26</v>
@@ -2790,7 +2792,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B24" s="5">
         <v>46118.662093692124</v>
@@ -2802,16 +2804,16 @@
         <v>46182.676449293984</v>
       </c>
       <c r="E24" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G24" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="F24" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G24" s="6" t="s">
+      <c r="H24" s="6" t="s">
         <v>106</v>
-      </c>
-      <c r="H24" s="6" t="s">
-        <v>107</v>
       </c>
       <c r="I24" s="5">
         <v>46119</v>
@@ -2829,13 +2831,13 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="Q24" s="5">
         <v>46232</v>
@@ -2850,7 +2852,7 @@
         <v>32</v>
       </c>
       <c r="U24" s="11" t="s">
-        <v>60</v>
+        <v>108</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
@@ -2873,10 +2875,10 @@
         <v>26</v>
       </c>
       <c r="G25" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="H25" s="9" t="s">
         <v>106</v>
-      </c>
-      <c r="H25" s="9" t="s">
-        <v>107</v>
       </c>
       <c r="I25" s="8">
         <v>46119</v>
@@ -2894,10 +2896,10 @@
         <v>26</v>
       </c>
       <c r="N25" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="O25" s="9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="P25" s="9" t="s">
         <v>111</v>
@@ -2928,10 +2930,10 @@
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="H26" s="6" t="s">
         <v>106</v>
-      </c>
-      <c r="H26" s="6" t="s">
-        <v>107</v>
       </c>
       <c r="I26" s="5">
         <v>46121</v>
@@ -2949,7 +2951,7 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="O26" s="6" t="s">
         <v>110</v>
@@ -2983,10 +2985,10 @@
         <v>26</v>
       </c>
       <c r="G27" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="H27" s="9" t="s">
         <v>106</v>
-      </c>
-      <c r="H27" s="9" t="s">
-        <v>107</v>
       </c>
       <c r="I27" s="8">
         <v>46111</v>
@@ -3004,13 +3006,13 @@
         <v>26</v>
       </c>
       <c r="N27" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="O27" s="9" t="s">
         <v>117</v>
       </c>
       <c r="P27" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="Q27" s="8">
         <v>46188</v>
@@ -3025,7 +3027,7 @@
         <v>32</v>
       </c>
       <c r="U27" s="11" t="s">
-        <v>60</v>
+        <v>108</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
@@ -3048,10 +3050,10 @@
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="H28" s="6" t="s">
         <v>106</v>
-      </c>
-      <c r="H28" s="6" t="s">
-        <v>107</v>
       </c>
       <c r="I28" s="5">
         <v>46111</v>
@@ -3072,7 +3074,7 @@
         <v>116</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="P28" s="6" t="s">
         <v>120</v>
@@ -3086,7 +3088,7 @@
         <v>32</v>
       </c>
       <c r="U28" s="11" t="s">
-        <v>60</v>
+        <v>108</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
@@ -3109,10 +3111,10 @@
         <v>26</v>
       </c>
       <c r="G29" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="H29" s="9" t="s">
         <v>106</v>
-      </c>
-      <c r="H29" s="9" t="s">
-        <v>107</v>
       </c>
       <c r="I29" s="8">
         <v>46120</v>
@@ -3147,7 +3149,7 @@
         <v>32</v>
       </c>
       <c r="U29" s="11" t="s">
-        <v>60</v>
+        <v>108</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
@@ -3170,10 +3172,10 @@
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="H30" s="6" t="s">
         <v>106</v>
-      </c>
-      <c r="H30" s="6" t="s">
-        <v>107</v>
       </c>
       <c r="I30" s="5">
         <v>46119</v>
@@ -3191,13 +3193,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="O30" s="6" t="s">
         <v>126</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="Q30" s="5">
         <v>46167</v>
@@ -3212,7 +3214,7 @@
         <v>32</v>
       </c>
       <c r="U30" s="11" t="s">
-        <v>60</v>
+        <v>108</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
@@ -3235,10 +3237,10 @@
         <v>26</v>
       </c>
       <c r="G31" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="H31" s="9" t="s">
         <v>106</v>
-      </c>
-      <c r="H31" s="9" t="s">
-        <v>107</v>
       </c>
       <c r="I31" s="8">
         <v>46119</v>
@@ -3259,7 +3261,7 @@
         <v>125</v>
       </c>
       <c r="O31" s="9" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="P31" s="9" t="s">
         <v>129</v>
@@ -3273,7 +3275,7 @@
         <v>32</v>
       </c>
       <c r="U31" s="11" t="s">
-        <v>60</v>
+        <v>108</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
@@ -3296,10 +3298,10 @@
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="H32" s="6" t="s">
         <v>106</v>
-      </c>
-      <c r="H32" s="6" t="s">
-        <v>107</v>
       </c>
       <c r="I32" s="5">
         <v>46121</v>
@@ -3334,7 +3336,7 @@
         <v>32</v>
       </c>
       <c r="U32" s="11" t="s">
-        <v>60</v>
+        <v>108</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
@@ -3357,10 +3359,10 @@
         <v>26</v>
       </c>
       <c r="G33" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="H33" s="9" t="s">
         <v>106</v>
-      </c>
-      <c r="H33" s="9" t="s">
-        <v>107</v>
       </c>
       <c r="I33" s="8">
         <v>46112</v>
@@ -3378,13 +3380,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="O33" s="9" t="s">
         <v>135</v>
       </c>
       <c r="P33" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="Q33" s="8">
         <v>46254</v>
@@ -3399,7 +3401,7 @@
         <v>32</v>
       </c>
       <c r="U33" s="11" t="s">
-        <v>60</v>
+        <v>108</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
@@ -3422,10 +3424,10 @@
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="H34" s="6" t="s">
         <v>106</v>
-      </c>
-      <c r="H34" s="6" t="s">
-        <v>107</v>
       </c>
       <c r="I34" s="5">
         <v>46112</v>
@@ -3446,7 +3448,7 @@
         <v>134</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="P34" s="6" t="s">
         <v>138</v>
@@ -3460,7 +3462,7 @@
         <v>32</v>
       </c>
       <c r="U34" s="11" t="s">
-        <v>60</v>
+        <v>108</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
@@ -3483,10 +3485,10 @@
         <v>26</v>
       </c>
       <c r="G35" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="H35" s="9" t="s">
         <v>106</v>
-      </c>
-      <c r="H35" s="9" t="s">
-        <v>107</v>
       </c>
       <c r="I35" s="8">
         <v>46133</v>
@@ -3521,7 +3523,7 @@
         <v>32</v>
       </c>
       <c r="U35" s="11" t="s">
-        <v>60</v>
+        <v>108</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
@@ -3544,10 +3546,10 @@
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="H36" s="6" t="s">
         <v>106</v>
-      </c>
-      <c r="H36" s="6" t="s">
-        <v>107</v>
       </c>
       <c r="I36" s="5">
         <v>46133</v>
@@ -3582,7 +3584,7 @@
         <v>32</v>
       </c>
       <c r="U36" s="11" t="s">
-        <v>60</v>
+        <v>108</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
@@ -3626,13 +3628,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="O37" s="9" t="s">
         <v>131</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="Q37" s="8">
         <v>46170</v>
@@ -3647,7 +3649,7 @@
         <v>32</v>
       </c>
       <c r="U37" s="11" t="s">
-        <v>60</v>
+        <v>108</v>
       </c>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
@@ -3694,7 +3696,7 @@
         <v>146</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="P38" s="6" t="s">
         <v>151</v>
@@ -3708,7 +3710,7 @@
         <v>32</v>
       </c>
       <c r="U38" s="11" t="s">
-        <v>60</v>
+        <v>108</v>
       </c>
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
@@ -3769,7 +3771,7 @@
         <v>32</v>
       </c>
       <c r="U39" s="11" t="s">
-        <v>60</v>
+        <v>108</v>
       </c>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
@@ -3863,7 +3865,7 @@
         <v>155</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="P41" s="9" t="s">
         <v>161</v>
@@ -3963,7 +3965,7 @@
         <v>46134.80040836806</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
@@ -4072,7 +4074,7 @@
         <v>32</v>
       </c>
       <c r="U44" s="11" t="s">
-        <v>60</v>
+        <v>108</v>
       </c>
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
@@ -4186,7 +4188,7 @@
         <v>32</v>
       </c>
       <c r="U46" s="11" t="s">
-        <v>60</v>
+        <v>108</v>
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
@@ -4251,7 +4253,7 @@
         <v>32</v>
       </c>
       <c r="U47" s="11" t="s">
-        <v>60</v>
+        <v>108</v>
       </c>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
@@ -4365,7 +4367,7 @@
         <v>32</v>
       </c>
       <c r="U49" s="11" t="s">
-        <v>60</v>
+        <v>108</v>
       </c>
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
@@ -4430,7 +4432,7 @@
         <v>32</v>
       </c>
       <c r="U50" s="11" t="s">
-        <v>60</v>
+        <v>108</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
@@ -4715,7 +4717,7 @@
         <v>32</v>
       </c>
       <c r="U55" s="11" t="s">
-        <v>60</v>
+        <v>108</v>
       </c>
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
@@ -4829,7 +4831,7 @@
         <v>32</v>
       </c>
       <c r="U57" s="11" t="s">
-        <v>60</v>
+        <v>108</v>
       </c>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
@@ -4894,7 +4896,7 @@
         <v>32</v>
       </c>
       <c r="U58" s="11" t="s">
-        <v>60</v>
+        <v>108</v>
       </c>
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
@@ -4959,7 +4961,7 @@
         <v>32</v>
       </c>
       <c r="U59" s="11" t="s">
-        <v>60</v>
+        <v>108</v>
       </c>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
@@ -5024,7 +5026,7 @@
         <v>32</v>
       </c>
       <c r="U60" s="11" t="s">
-        <v>60</v>
+        <v>108</v>
       </c>
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
@@ -5096,10 +5098,10 @@
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I62" s="5">
         <v>46210</v>
@@ -5138,7 +5140,7 @@
         <v>32</v>
       </c>
       <c r="U62" s="11" t="s">
-        <v>60</v>
+        <v>108</v>
       </c>
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
@@ -5161,10 +5163,10 @@
         <v>26</v>
       </c>
       <c r="G63" s="9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H63" s="9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I63" s="8">
         <v>46259</v>
@@ -5203,7 +5205,7 @@
         <v>32</v>
       </c>
       <c r="U63" s="11" t="s">
-        <v>60</v>
+        <v>108</v>
       </c>
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
@@ -5226,10 +5228,10 @@
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I64" s="5">
         <v>46261</v>
@@ -5268,7 +5270,7 @@
         <v>32</v>
       </c>
       <c r="U64" s="11" t="s">
-        <v>60</v>
+        <v>108</v>
       </c>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
@@ -5291,10 +5293,10 @@
         <v>26</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H65" s="9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I65" s="8">
         <v>46265</v>
@@ -5333,7 +5335,7 @@
         <v>32</v>
       </c>
       <c r="U65" s="11" t="s">
-        <v>60</v>
+        <v>108</v>
       </c>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
@@ -5356,10 +5358,10 @@
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I66" s="6"/>
       <c r="J66" s="5">
@@ -5396,7 +5398,7 @@
         <v>32</v>
       </c>
       <c r="U66" s="11" t="s">
-        <v>60</v>
+        <v>108</v>
       </c>
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
@@ -5417,10 +5419,10 @@
         <v>26</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H67" s="9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I67" s="8">
         <v>46269</v>
@@ -5459,7 +5461,7 @@
         <v>32</v>
       </c>
       <c r="U67" s="11" t="s">
-        <v>60</v>
+        <v>108</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
@@ -5567,7 +5569,7 @@
         <v>32</v>
       </c>
       <c r="U69" s="11" t="s">
-        <v>60</v>
+        <v>108</v>
       </c>
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
@@ -5579,7 +5581,7 @@
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46196.57543765046</v>
+        <v>46196.89572584491</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>255</v>
@@ -5588,10 +5590,10 @@
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I70" s="6"/>
       <c r="J70" s="5">
@@ -5628,7 +5630,7 @@
         <v>32</v>
       </c>
       <c r="U70" s="11" t="s">
-        <v>60</v>
+        <v>108</v>
       </c>
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
@@ -5689,7 +5691,7 @@
         <v>32</v>
       </c>
       <c r="U71" s="11" t="s">
-        <v>60</v>
+        <v>108</v>
       </c>
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
@@ -5750,7 +5752,7 @@
         <v>32</v>
       </c>
       <c r="U72" s="11" t="s">
-        <v>60</v>
+        <v>108</v>
       </c>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
@@ -5860,7 +5862,7 @@
         <v>32</v>
       </c>
       <c r="U74" s="11" t="s">
-        <v>60</v>
+        <v>108</v>
       </c>
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
@@ -5923,7 +5925,7 @@
         <v>32</v>
       </c>
       <c r="U75" s="11" t="s">
-        <v>60</v>
+        <v>108</v>
       </c>
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
@@ -6033,7 +6035,7 @@
         <v>32</v>
       </c>
       <c r="U77" s="11" t="s">
-        <v>60</v>
+        <v>108</v>
       </c>
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
@@ -6096,7 +6098,7 @@
         <v>32</v>
       </c>
       <c r="U78" s="11" t="s">
-        <v>60</v>
+        <v>108</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001533 - GESVIAL.xlsx
+++ b/data/50001533 - GESVIAL.xlsx
@@ -5089,7 +5089,7 @@
         <v>46193.61261344908</v>
       </c>
       <c r="D62" s="5">
-        <v>46193.61261581018</v>
+        <v>46196.921998854166</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>229</v>

--- a/data/50001533 - GESVIAL.xlsx
+++ b/data/50001533 - GESVIAL.xlsx
@@ -5040,7 +5040,7 @@
         <v>46193.765035358796</v>
       </c>
       <c r="D61" s="8">
-        <v>46193.765528379634</v>
+        <v>46196.92347159723</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>226</v>
@@ -5408,9 +5408,11 @@
       <c r="B67" s="8">
         <v>46118.662420127315</v>
       </c>
-      <c r="C67" s="9"/>
+      <c r="C67" s="8">
+        <v>46196.92346424768</v>
+      </c>
       <c r="D67" s="8">
-        <v>46195.56277597223</v>
+        <v>46196.92346578704</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>244</v>
@@ -5473,7 +5475,7 @@
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46118.76233159722</v>
+        <v>46196.92306695602</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>247</v>
@@ -5520,7 +5522,7 @@
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46196.576254618056</v>
+        <v>46196.92347351852</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>250</v>
@@ -5640,9 +5642,11 @@
       <c r="B71" s="8">
         <v>46118.66245149306</v>
       </c>
-      <c r="C71" s="9"/>
+      <c r="C71" s="8">
+        <v>46196.9230577662</v>
+      </c>
       <c r="D71" s="8">
-        <v>46196.567130752315</v>
+        <v>46196.92306033565</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>259</v>
@@ -5703,7 +5707,7 @@
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46196.57031530092</v>
+        <v>46196.92306840278</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>264</v>

--- a/data/50001533 - GESVIAL.xlsx
+++ b/data/50001533 - GESVIAL.xlsx
@@ -1577,13 +1577,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46118.66185005787</v>
+        <v>46118.495183391206</v>
       </c>
       <c r="C4" s="5">
-        <v>46129.56083631945</v>
+        <v>46129.394169652776</v>
       </c>
       <c r="D4" s="5">
-        <v>46148.01378729167</v>
+        <v>46147.847120624996</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1626,13 +1626,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46118.662012175926</v>
+        <v>46118.49534550926</v>
       </c>
       <c r="C5" s="8">
-        <v>46129.559856481486</v>
+        <v>46129.393189814815</v>
       </c>
       <c r="D5" s="8">
-        <v>46133.87722729167</v>
+        <v>46133.710560625</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1691,13 +1691,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46118.662015567126</v>
+        <v>46118.49534890046</v>
       </c>
       <c r="C6" s="5">
-        <v>46129.55991743055</v>
+        <v>46129.39325076389</v>
       </c>
       <c r="D6" s="5">
-        <v>46129.55993412037</v>
+        <v>46129.393267453706</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -1756,13 +1756,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="8">
-        <v>46118.662018773146</v>
+        <v>46118.49535210648</v>
       </c>
       <c r="C7" s="8">
-        <v>46129.56027341435</v>
+        <v>46129.39360674769</v>
       </c>
       <c r="D7" s="8">
-        <v>46129.560290416666</v>
+        <v>46129.39362375</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>38</v>
@@ -1821,13 +1821,13 @@
         <v>40</v>
       </c>
       <c r="B8" s="5">
-        <v>46118.66202195601</v>
+        <v>46118.49535528936</v>
       </c>
       <c r="C8" s="5">
-        <v>46129.56068634259</v>
+        <v>46129.39401967592</v>
       </c>
       <c r="D8" s="5">
-        <v>46129.56070206019</v>
+        <v>46129.39403539352</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>41</v>
@@ -1886,13 +1886,13 @@
         <v>44</v>
       </c>
       <c r="B9" s="8">
-        <v>46118.66202614583</v>
+        <v>46118.495359479166</v>
       </c>
       <c r="C9" s="8">
-        <v>46129.560821747684</v>
+        <v>46129.39415508102</v>
       </c>
       <c r="D9" s="8">
-        <v>46156.83862056713</v>
+        <v>46156.67195390046</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>45</v>
@@ -1951,11 +1951,11 @@
         <v>47</v>
       </c>
       <c r="B10" s="5">
-        <v>46118.66185618055</v>
+        <v>46118.49518951389</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46196.895724664355</v>
+        <v>46196.72905799768</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>48</v>
@@ -1998,13 +1998,13 @@
         <v>50</v>
       </c>
       <c r="B11" s="8">
-        <v>46118.6620300463</v>
+        <v>46118.495363379625</v>
       </c>
       <c r="C11" s="8">
-        <v>46129.57129943287</v>
+        <v>46129.40463276621</v>
       </c>
       <c r="D11" s="8">
-        <v>46129.57131482639</v>
+        <v>46129.40464815972</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>51</v>
@@ -2063,13 +2063,13 @@
         <v>56</v>
       </c>
       <c r="B12" s="5">
-        <v>46118.66203578704</v>
+        <v>46118.49536912037</v>
       </c>
       <c r="C12" s="5">
-        <v>46196.89571644676</v>
+        <v>46196.72904978009</v>
       </c>
       <c r="D12" s="5">
-        <v>46196.89571872685</v>
+        <v>46196.72905206018</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>57</v>
@@ -2128,13 +2128,13 @@
         <v>60</v>
       </c>
       <c r="B13" s="8">
-        <v>46118.66186076389</v>
+        <v>46118.495194097224</v>
       </c>
       <c r="C13" s="8">
-        <v>46193.56179229167</v>
+        <v>46193.395125625</v>
       </c>
       <c r="D13" s="8">
-        <v>46193.561794629626</v>
+        <v>46193.39512796296</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>61</v>
@@ -2177,13 +2177,13 @@
         <v>63</v>
       </c>
       <c r="B14" s="5">
-        <v>46118.66204173611</v>
+        <v>46118.49537506944</v>
       </c>
       <c r="C14" s="5">
-        <v>46129.56192828703</v>
+        <v>46129.395261620375</v>
       </c>
       <c r="D14" s="5">
-        <v>46191.77226219907</v>
+        <v>46191.60559553241</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>64</v>
@@ -2242,13 +2242,13 @@
         <v>67</v>
       </c>
       <c r="B15" s="8">
-        <v>46118.66204752315</v>
+        <v>46118.49538085648</v>
       </c>
       <c r="C15" s="8">
-        <v>46129.561938796294</v>
+        <v>46129.39527212963</v>
       </c>
       <c r="D15" s="8">
-        <v>46191.77226225694</v>
+        <v>46191.60559559028</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>68</v>
@@ -2307,13 +2307,13 @@
         <v>71</v>
       </c>
       <c r="B16" s="5">
-        <v>46118.66205295139</v>
+        <v>46118.49538628472</v>
       </c>
       <c r="C16" s="5">
-        <v>46129.56711804398</v>
+        <v>46129.40045137731</v>
       </c>
       <c r="D16" s="5">
-        <v>46191.7722621412</v>
+        <v>46191.60559547454</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>72</v>
@@ -2372,13 +2372,13 @@
         <v>75</v>
       </c>
       <c r="B17" s="8">
-        <v>46118.6618661574</v>
+        <v>46118.495199490746</v>
       </c>
       <c r="C17" s="8">
-        <v>46184.72974263889</v>
+        <v>46184.563075972226</v>
       </c>
       <c r="D17" s="8">
-        <v>46184.72974401621</v>
+        <v>46184.563077349536</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>76</v>
@@ -2421,13 +2421,13 @@
         <v>78</v>
       </c>
       <c r="B18" s="5">
-        <v>46118.66206653936</v>
+        <v>46118.495399872685</v>
       </c>
       <c r="C18" s="5">
-        <v>46129.56233884259</v>
+        <v>46129.395672175924</v>
       </c>
       <c r="D18" s="5">
-        <v>46129.56236072916</v>
+        <v>46129.3956940625</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>79</v>
@@ -2486,13 +2486,13 @@
         <v>82</v>
       </c>
       <c r="B19" s="8">
-        <v>46118.66207174768</v>
+        <v>46118.49540508102</v>
       </c>
       <c r="C19" s="8">
-        <v>46129.56234587963</v>
+        <v>46129.39567921296</v>
       </c>
       <c r="D19" s="8">
-        <v>46129.56236737268</v>
+        <v>46129.39570070602</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>83</v>
@@ -2551,13 +2551,13 @@
         <v>85</v>
       </c>
       <c r="B20" s="5">
-        <v>46118.66207709491</v>
+        <v>46118.49541042824</v>
       </c>
       <c r="C20" s="5">
-        <v>46129.57133789352</v>
+        <v>46129.40467122685</v>
       </c>
       <c r="D20" s="5">
-        <v>46129.57135429398</v>
+        <v>46129.40468762731</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>86</v>
@@ -2616,13 +2616,13 @@
         <v>89</v>
       </c>
       <c r="B21" s="8">
-        <v>46118.66208231481</v>
+        <v>46118.49541564815</v>
       </c>
       <c r="C21" s="8">
-        <v>46183.88010105324</v>
+        <v>46183.71343438658</v>
       </c>
       <c r="D21" s="8">
-        <v>46183.880102916664</v>
+        <v>46183.71343625</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>90</v>
@@ -2681,13 +2681,13 @@
         <v>94</v>
       </c>
       <c r="B22" s="5">
-        <v>46118.662087523146</v>
+        <v>46118.49542085648</v>
       </c>
       <c r="C22" s="5">
-        <v>46183.888051863425</v>
+        <v>46183.72138519676</v>
       </c>
       <c r="D22" s="5">
-        <v>46183.888251435186</v>
+        <v>46183.721584768515</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>95</v>
@@ -2746,13 +2746,13 @@
         <v>100</v>
       </c>
       <c r="B23" s="8">
-        <v>46118.66187195602</v>
+        <v>46118.49520528935</v>
       </c>
       <c r="C23" s="8">
-        <v>46184.68624671296</v>
+        <v>46184.5195800463</v>
       </c>
       <c r="D23" s="8">
-        <v>46184.686248067126</v>
+        <v>46184.51958140046</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>101</v>
@@ -2795,13 +2795,13 @@
         <v>103</v>
       </c>
       <c r="B24" s="5">
-        <v>46118.662093692124</v>
+        <v>46118.49542702547</v>
       </c>
       <c r="C24" s="5">
-        <v>46182.67644689815</v>
+        <v>46182.509780231485</v>
       </c>
       <c r="D24" s="5">
-        <v>46182.676449293984</v>
+        <v>46182.50978262731</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>104</v>
@@ -2860,13 +2860,13 @@
         <v>109</v>
       </c>
       <c r="B25" s="8">
-        <v>46118.66209846065</v>
+        <v>46118.495431793985</v>
       </c>
       <c r="C25" s="8">
-        <v>46174.62568537037</v>
+        <v>46174.4590187037</v>
       </c>
       <c r="D25" s="8">
-        <v>46174.62568689814</v>
+        <v>46174.45902023149</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>110</v>
@@ -2915,13 +2915,13 @@
         <v>112</v>
       </c>
       <c r="B26" s="5">
-        <v>46118.66210270833</v>
+        <v>46118.49543604167</v>
       </c>
       <c r="C26" s="5">
-        <v>46182.64328993055</v>
+        <v>46182.476623263894</v>
       </c>
       <c r="D26" s="5">
-        <v>46182.64329142361</v>
+        <v>46182.47662475695</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>113</v>
@@ -2970,13 +2970,13 @@
         <v>115</v>
       </c>
       <c r="B27" s="8">
-        <v>46118.662106979165</v>
+        <v>46118.4954403125</v>
       </c>
       <c r="C27" s="8">
-        <v>46182.641066956014</v>
+        <v>46182.47440028936</v>
       </c>
       <c r="D27" s="8">
-        <v>46182.64106920139</v>
+        <v>46182.47440253472</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>116</v>
@@ -3035,13 +3035,13 @@
         <v>118</v>
       </c>
       <c r="B28" s="5">
-        <v>46118.662112094906</v>
+        <v>46118.49544542824</v>
       </c>
       <c r="C28" s="5">
-        <v>46174.626521666665</v>
+        <v>46174.459855</v>
       </c>
       <c r="D28" s="5">
-        <v>46174.62652314815</v>
+        <v>46174.45985648148</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>119</v>
@@ -3096,13 +3096,13 @@
         <v>121</v>
       </c>
       <c r="B29" s="8">
-        <v>46118.66211693287</v>
+        <v>46118.4954502662</v>
       </c>
       <c r="C29" s="8">
-        <v>46174.626630416664</v>
+        <v>46174.45996375</v>
       </c>
       <c r="D29" s="8">
-        <v>46174.62663186343</v>
+        <v>46174.45996519676</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>122</v>
@@ -3157,13 +3157,13 @@
         <v>124</v>
       </c>
       <c r="B30" s="5">
-        <v>46118.66212202546</v>
+        <v>46118.495455358796</v>
       </c>
       <c r="C30" s="5">
-        <v>46184.68608144676</v>
+        <v>46184.519414780094</v>
       </c>
       <c r="D30" s="5">
-        <v>46184.68608324074</v>
+        <v>46184.519416574076</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>125</v>
@@ -3222,13 +3222,13 @@
         <v>127</v>
       </c>
       <c r="B31" s="8">
-        <v>46118.662126678246</v>
+        <v>46118.495460011574</v>
       </c>
       <c r="C31" s="8">
-        <v>46184.68571903935</v>
+        <v>46184.519052372685</v>
       </c>
       <c r="D31" s="8">
-        <v>46184.68572081019</v>
+        <v>46184.519054143515</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>128</v>
@@ -3283,13 +3283,13 @@
         <v>130</v>
       </c>
       <c r="B32" s="5">
-        <v>46118.662131261575</v>
+        <v>46118.495464594904</v>
       </c>
       <c r="C32" s="5">
-        <v>46184.68578890046</v>
+        <v>46184.519122233796</v>
       </c>
       <c r="D32" s="5">
-        <v>46184.68579053241</v>
+        <v>46184.51912386574</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>131</v>
@@ -3344,13 +3344,13 @@
         <v>133</v>
       </c>
       <c r="B33" s="8">
-        <v>46118.66218372685</v>
+        <v>46118.49551706019</v>
       </c>
       <c r="C33" s="8">
-        <v>46156.821339988426</v>
+        <v>46156.654673321755</v>
       </c>
       <c r="D33" s="8">
-        <v>46169.82398277777</v>
+        <v>46169.657316111116</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>134</v>
@@ -3409,13 +3409,13 @@
         <v>136</v>
       </c>
       <c r="B34" s="5">
-        <v>46118.662190104165</v>
+        <v>46118.4955234375</v>
       </c>
       <c r="C34" s="5">
-        <v>46134.79115269676</v>
+        <v>46134.624486030094</v>
       </c>
       <c r="D34" s="5">
-        <v>46169.823994363425</v>
+        <v>46169.65732769676</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>137</v>
@@ -3470,13 +3470,13 @@
         <v>139</v>
       </c>
       <c r="B35" s="8">
-        <v>46118.662195694444</v>
+        <v>46118.49552902778</v>
       </c>
       <c r="C35" s="8">
-        <v>46155.90268767361</v>
+        <v>46155.736021006946</v>
       </c>
       <c r="D35" s="8">
-        <v>46169.82401586806</v>
+        <v>46169.657349201385</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>140</v>
@@ -3531,13 +3531,13 @@
         <v>142</v>
       </c>
       <c r="B36" s="5">
-        <v>46118.66220082176</v>
+        <v>46118.495534155096</v>
       </c>
       <c r="C36" s="5">
-        <v>46134.79119539352</v>
+        <v>46134.624528726854</v>
       </c>
       <c r="D36" s="5">
-        <v>46169.824036157406</v>
+        <v>46169.65736949074</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>143</v>
@@ -3592,13 +3592,13 @@
         <v>145</v>
       </c>
       <c r="B37" s="8">
-        <v>46118.66220634259</v>
+        <v>46118.495539675925</v>
       </c>
       <c r="C37" s="8">
-        <v>46184.686103796295</v>
+        <v>46184.51943712963</v>
       </c>
       <c r="D37" s="8">
-        <v>46184.68610523148</v>
+        <v>46184.519438564814</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>146</v>
@@ -3657,13 +3657,13 @@
         <v>149</v>
       </c>
       <c r="B38" s="5">
-        <v>46118.66221234953</v>
+        <v>46118.495545682876</v>
       </c>
       <c r="C38" s="5">
-        <v>46184.53094861111</v>
+        <v>46184.36428194444</v>
       </c>
       <c r="D38" s="5">
-        <v>46184.53095076389</v>
+        <v>46184.36428409722</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>150</v>
@@ -3718,13 +3718,13 @@
         <v>152</v>
       </c>
       <c r="B39" s="8">
-        <v>46118.66221657407</v>
+        <v>46118.495549907406</v>
       </c>
       <c r="C39" s="8">
-        <v>46184.53162540509</v>
+        <v>46184.36495873843</v>
       </c>
       <c r="D39" s="8">
-        <v>46184.531626724536</v>
+        <v>46184.36496005787</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>151</v>
@@ -3779,11 +3779,11 @@
         <v>154</v>
       </c>
       <c r="B40" s="5">
-        <v>46118.662220972226</v>
+        <v>46118.495554305555</v>
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="5">
-        <v>46134.80040204861</v>
+        <v>46134.63373538194</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>155</v>
@@ -3826,13 +3826,13 @@
         <v>157</v>
       </c>
       <c r="B41" s="8">
-        <v>46118.66222521991</v>
+        <v>46118.495558553244</v>
       </c>
       <c r="C41" s="8">
-        <v>46129.567182349536</v>
+        <v>46129.40051568287</v>
       </c>
       <c r="D41" s="8">
-        <v>46129.57417895833</v>
+        <v>46129.40751229167</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>158</v>
@@ -3891,13 +3891,13 @@
         <v>162</v>
       </c>
       <c r="B42" s="5">
-        <v>46118.66223170139</v>
+        <v>46118.495565034726</v>
       </c>
       <c r="C42" s="5">
-        <v>46134.80026672454</v>
+        <v>46134.633600057874</v>
       </c>
       <c r="D42" s="5">
-        <v>46134.80028269676</v>
+        <v>46134.63361603009</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>163</v>
@@ -3956,13 +3956,13 @@
         <v>168</v>
       </c>
       <c r="B43" s="8">
-        <v>46118.662239375</v>
+        <v>46118.49557270833</v>
       </c>
       <c r="C43" s="8">
-        <v>46134.80039372685</v>
+        <v>46134.63372706018</v>
       </c>
       <c r="D43" s="8">
-        <v>46134.80040836806</v>
+        <v>46134.633741701386</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>98</v>
@@ -4019,11 +4019,11 @@
         <v>170</v>
       </c>
       <c r="B44" s="5">
-        <v>46118.662245300926</v>
+        <v>46118.49557863426</v>
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="5">
-        <v>46193.765527129624</v>
+        <v>46193.59886046297</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>171</v>
@@ -4082,13 +4082,13 @@
         <v>176</v>
       </c>
       <c r="B45" s="8">
-        <v>46118.66224984954</v>
+        <v>46118.49558318287</v>
       </c>
       <c r="C45" s="8">
-        <v>46184.68718685185</v>
+        <v>46184.520520185186</v>
       </c>
       <c r="D45" s="8">
-        <v>46184.68718828703</v>
+        <v>46184.520521620376</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>177</v>
@@ -4131,13 +4131,13 @@
         <v>179</v>
       </c>
       <c r="B46" s="5">
-        <v>46118.66225350695</v>
+        <v>46118.495586840276</v>
       </c>
       <c r="C46" s="5">
-        <v>46184.68670658565</v>
+        <v>46184.52003991898</v>
       </c>
       <c r="D46" s="5">
-        <v>46184.686925347225</v>
+        <v>46184.52025868055</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>153</v>
@@ -4196,13 +4196,13 @@
         <v>183</v>
       </c>
       <c r="B47" s="8">
-        <v>46118.66225863426</v>
+        <v>46118.49559196759</v>
       </c>
       <c r="C47" s="8">
-        <v>46184.6869659838</v>
+        <v>46184.520299317126</v>
       </c>
       <c r="D47" s="8">
-        <v>46184.68714663194</v>
+        <v>46184.52047996528</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>184</v>
@@ -4261,13 +4261,13 @@
         <v>188</v>
       </c>
       <c r="B48" s="5">
-        <v>46118.662263819446</v>
+        <v>46118.49559715278</v>
       </c>
       <c r="C48" s="5">
-        <v>46194.056337268514</v>
+        <v>46193.88967060186</v>
       </c>
       <c r="D48" s="5">
-        <v>46194.05633912037</v>
+        <v>46193.889672453704</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>189</v>
@@ -4310,13 +4310,13 @@
         <v>191</v>
       </c>
       <c r="B49" s="8">
-        <v>46118.66226751157</v>
+        <v>46118.49560084491</v>
       </c>
       <c r="C49" s="8">
-        <v>46184.687951203705</v>
+        <v>46184.52128453704</v>
       </c>
       <c r="D49" s="8">
-        <v>46184.687952719905</v>
+        <v>46184.52128605324</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>192</v>
@@ -4375,13 +4375,13 @@
         <v>196</v>
       </c>
       <c r="B50" s="5">
-        <v>46118.66227269676</v>
+        <v>46118.49560603009</v>
       </c>
       <c r="C50" s="5">
-        <v>46193.56191304398</v>
+        <v>46193.39524637732</v>
       </c>
       <c r="D50" s="5">
-        <v>46193.561914942125</v>
+        <v>46193.39524827546</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>197</v>
@@ -4440,13 +4440,13 @@
         <v>200</v>
       </c>
       <c r="B51" s="8">
-        <v>46184.687980393515</v>
+        <v>46184.52131372685</v>
       </c>
       <c r="C51" s="8">
-        <v>46184.68921728009</v>
+        <v>46184.52255061343</v>
       </c>
       <c r="D51" s="8">
-        <v>46191.68718039352</v>
+        <v>46191.52051372685</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>201</v>
@@ -4495,13 +4495,13 @@
         <v>202</v>
       </c>
       <c r="B52" s="5">
-        <v>46184.688093055556</v>
+        <v>46184.52142638889</v>
       </c>
       <c r="C52" s="5">
-        <v>46195.7025405787</v>
+        <v>46195.53587391204</v>
       </c>
       <c r="D52" s="5">
-        <v>46195.70254238426</v>
+        <v>46195.53587571759</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>203</v>
@@ -4550,13 +4550,13 @@
         <v>204</v>
       </c>
       <c r="B53" s="8">
-        <v>46184.68816803241</v>
+        <v>46184.52150136574</v>
       </c>
       <c r="C53" s="8">
-        <v>46184.69000751157</v>
+        <v>46184.523340844906</v>
       </c>
       <c r="D53" s="8">
-        <v>46191.6871738426</v>
+        <v>46191.52050717593</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>205</v>
@@ -4605,13 +4605,13 @@
         <v>206</v>
       </c>
       <c r="B54" s="5">
-        <v>46184.68826700232</v>
+        <v>46184.52160033565</v>
       </c>
       <c r="C54" s="5">
-        <v>46184.69031962963</v>
+        <v>46184.52365296296</v>
       </c>
       <c r="D54" s="5">
-        <v>46191.687168993056</v>
+        <v>46191.520502326384</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>207</v>
@@ -4660,13 +4660,13 @@
         <v>208</v>
       </c>
       <c r="B55" s="8">
-        <v>46118.66227863426</v>
+        <v>46118.49561196759</v>
       </c>
       <c r="C55" s="8">
-        <v>46193.56240042824</v>
+        <v>46193.39573376157</v>
       </c>
       <c r="D55" s="8">
-        <v>46193.562405625</v>
+        <v>46193.39573895834</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>209</v>
@@ -4725,13 +4725,13 @@
         <v>212</v>
       </c>
       <c r="B56" s="5">
-        <v>46118.66228488426</v>
+        <v>46118.495618217596</v>
       </c>
       <c r="C56" s="5">
-        <v>46194.05632121528</v>
+        <v>46193.889654548606</v>
       </c>
       <c r="D56" s="5">
-        <v>46194.05632325231</v>
+        <v>46193.88965658565</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>177</v>
@@ -4774,13 +4774,13 @@
         <v>214</v>
       </c>
       <c r="B57" s="8">
-        <v>46118.66228803241</v>
+        <v>46118.49562136574</v>
       </c>
       <c r="C57" s="8">
-        <v>46193.562345370374</v>
+        <v>46193.3956787037</v>
       </c>
       <c r="D57" s="8">
-        <v>46193.56234733797</v>
+        <v>46193.395680671296</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>215</v>
@@ -4839,13 +4839,13 @@
         <v>217</v>
       </c>
       <c r="B58" s="5">
-        <v>46118.662293518515</v>
+        <v>46118.49562685185</v>
       </c>
       <c r="C58" s="5">
-        <v>46193.56197458333</v>
+        <v>46193.39530791667</v>
       </c>
       <c r="D58" s="5">
-        <v>46193.56197650463</v>
+        <v>46193.395309837964</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>58</v>
@@ -4904,13 +4904,13 @@
         <v>219</v>
       </c>
       <c r="B59" s="8">
-        <v>46118.662299895834</v>
+        <v>46118.49563322916</v>
       </c>
       <c r="C59" s="8">
-        <v>46193.561984872686</v>
+        <v>46193.39531820602</v>
       </c>
       <c r="D59" s="8">
-        <v>46193.561986678236</v>
+        <v>46193.39532001158</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>220</v>
@@ -4969,13 +4969,13 @@
         <v>222</v>
       </c>
       <c r="B60" s="5">
-        <v>46118.66235550926</v>
+        <v>46118.495688842595</v>
       </c>
       <c r="C60" s="5">
-        <v>46193.56199724537</v>
+        <v>46193.3953305787</v>
       </c>
       <c r="D60" s="5">
-        <v>46193.56199886574</v>
+        <v>46193.39533219907</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>223</v>
@@ -5034,13 +5034,13 @@
         <v>225</v>
       </c>
       <c r="B61" s="8">
-        <v>46118.66236295139</v>
+        <v>46118.49569628472</v>
       </c>
       <c r="C61" s="8">
-        <v>46193.765035358796</v>
+        <v>46193.598368692124</v>
       </c>
       <c r="D61" s="8">
-        <v>46196.92347159723</v>
+        <v>46196.756804930556</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>226</v>
@@ -5083,13 +5083,13 @@
         <v>228</v>
       </c>
       <c r="B62" s="5">
-        <v>46118.66236873843</v>
+        <v>46118.495702071756</v>
       </c>
       <c r="C62" s="5">
-        <v>46193.61261344908</v>
+        <v>46193.445946782405</v>
       </c>
       <c r="D62" s="5">
-        <v>46196.921998854166</v>
+        <v>46196.7553321875</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>229</v>
@@ -5148,13 +5148,13 @@
         <v>231</v>
       </c>
       <c r="B63" s="8">
-        <v>46118.662376064814</v>
+        <v>46118.49570939815</v>
       </c>
       <c r="C63" s="8">
-        <v>46193.6126587037</v>
+        <v>46193.445992037035</v>
       </c>
       <c r="D63" s="8">
-        <v>46193.61266056713</v>
+        <v>46193.44599390046</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>224</v>
@@ -5213,13 +5213,13 @@
         <v>234</v>
       </c>
       <c r="B64" s="5">
-        <v>46118.662387557866</v>
+        <v>46118.4957208912</v>
       </c>
       <c r="C64" s="5">
-        <v>46193.61267944444</v>
+        <v>46193.44601277778</v>
       </c>
       <c r="D64" s="5">
-        <v>46193.61268100694</v>
+        <v>46193.44601434028</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>235</v>
@@ -5278,13 +5278,13 @@
         <v>237</v>
       </c>
       <c r="B65" s="8">
-        <v>46118.662398796296</v>
+        <v>46118.495732129624</v>
       </c>
       <c r="C65" s="8">
-        <v>46193.61273716435</v>
+        <v>46193.44607049768</v>
       </c>
       <c r="D65" s="8">
-        <v>46193.61273954861</v>
+        <v>46193.44607288194</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>238</v>
@@ -5343,13 +5343,13 @@
         <v>240</v>
       </c>
       <c r="B66" s="5">
-        <v>46118.66240984954</v>
+        <v>46118.495743182866</v>
       </c>
       <c r="C66" s="5">
-        <v>46193.765511875</v>
+        <v>46193.59884520833</v>
       </c>
       <c r="D66" s="5">
-        <v>46193.765518935186</v>
+        <v>46193.59885226852</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>174</v>
@@ -5406,13 +5406,13 @@
         <v>243</v>
       </c>
       <c r="B67" s="8">
-        <v>46118.662420127315</v>
+        <v>46118.49575346065</v>
       </c>
       <c r="C67" s="8">
-        <v>46196.92346424768</v>
+        <v>46196.75679758102</v>
       </c>
       <c r="D67" s="8">
-        <v>46196.92346578704</v>
+        <v>46196.75679912037</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>244</v>
@@ -5471,11 +5471,11 @@
         <v>246</v>
       </c>
       <c r="B68" s="5">
-        <v>46118.66242769676</v>
+        <v>46118.49576103009</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46196.92306695602</v>
+        <v>46196.75640028935</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>247</v>
@@ -5518,11 +5518,11 @@
         <v>249</v>
       </c>
       <c r="B69" s="8">
-        <v>46118.662431770834</v>
+        <v>46118.49576510416</v>
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46196.92347351852</v>
+        <v>46196.75680685185</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>250</v>
@@ -5579,11 +5579,11 @@
         <v>254</v>
       </c>
       <c r="B70" s="5">
-        <v>46118.662438252315</v>
+        <v>46118.49577158564</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46196.89572584491</v>
+        <v>46196.72905917824</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>255</v>
@@ -5640,13 +5640,13 @@
         <v>258</v>
       </c>
       <c r="B71" s="8">
-        <v>46118.66245149306</v>
+        <v>46118.49578482639</v>
       </c>
       <c r="C71" s="8">
-        <v>46196.9230577662</v>
+        <v>46196.75639109954</v>
       </c>
       <c r="D71" s="8">
-        <v>46196.92306033565</v>
+        <v>46196.756393668984</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>259</v>
@@ -5703,11 +5703,11 @@
         <v>263</v>
       </c>
       <c r="B72" s="5">
-        <v>46118.66245769676</v>
+        <v>46118.49579103009</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46196.92306840278</v>
+        <v>46196.756401736115</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>264</v>
@@ -5764,11 +5764,11 @@
         <v>266</v>
       </c>
       <c r="B73" s="8">
-        <v>46118.66246467593</v>
+        <v>46118.49579800926</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46118.76284858796</v>
+        <v>46118.5961819213</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>267</v>
@@ -5811,11 +5811,11 @@
         <v>269</v>
       </c>
       <c r="B74" s="5">
-        <v>46118.66246796296</v>
+        <v>46118.495801296296</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46118.76810806713</v>
+        <v>46118.60144140046</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>270</v>
@@ -5874,11 +5874,11 @@
         <v>273</v>
       </c>
       <c r="B75" s="8">
-        <v>46118.66251259259</v>
+        <v>46118.49584592592</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46191.7722621412</v>
+        <v>46191.60559547454</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>274</v>
@@ -5937,11 +5937,11 @@
         <v>275</v>
       </c>
       <c r="B76" s="5">
-        <v>46118.662521377315</v>
+        <v>46118.49585471065</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46118.76362347222</v>
+        <v>46118.59695680556</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>276</v>
@@ -5984,11 +5984,11 @@
         <v>278</v>
       </c>
       <c r="B77" s="8">
-        <v>46118.66252565972</v>
+        <v>46118.495858993054</v>
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46118.7682625</v>
+        <v>46118.60159583333</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>279</v>
@@ -6047,11 +6047,11 @@
         <v>281</v>
       </c>
       <c r="B78" s="5">
-        <v>46118.662532013885</v>
+        <v>46118.49586534723</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46118.76825962963</v>
+        <v>46118.601592962965</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>282</v>

--- a/data/50001533 - GESVIAL.xlsx
+++ b/data/50001533 - GESVIAL.xlsx
@@ -1577,13 +1577,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46118.495183391206</v>
+        <v>46118.66185005787</v>
       </c>
       <c r="C4" s="5">
-        <v>46129.394169652776</v>
+        <v>46129.56083631945</v>
       </c>
       <c r="D4" s="5">
-        <v>46147.847120624996</v>
+        <v>46148.01378729167</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1626,13 +1626,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46118.49534550926</v>
+        <v>46118.662012175926</v>
       </c>
       <c r="C5" s="8">
-        <v>46129.393189814815</v>
+        <v>46129.559856481486</v>
       </c>
       <c r="D5" s="8">
-        <v>46133.710560625</v>
+        <v>46133.87722729167</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1691,13 +1691,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46118.49534890046</v>
+        <v>46118.662015567126</v>
       </c>
       <c r="C6" s="5">
-        <v>46129.39325076389</v>
+        <v>46129.55991743055</v>
       </c>
       <c r="D6" s="5">
-        <v>46129.393267453706</v>
+        <v>46129.55993412037</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -1756,13 +1756,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="8">
-        <v>46118.49535210648</v>
+        <v>46118.662018773146</v>
       </c>
       <c r="C7" s="8">
-        <v>46129.39360674769</v>
+        <v>46129.56027341435</v>
       </c>
       <c r="D7" s="8">
-        <v>46129.39362375</v>
+        <v>46129.560290416666</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>38</v>
@@ -1821,13 +1821,13 @@
         <v>40</v>
       </c>
       <c r="B8" s="5">
-        <v>46118.49535528936</v>
+        <v>46118.66202195601</v>
       </c>
       <c r="C8" s="5">
-        <v>46129.39401967592</v>
+        <v>46129.56068634259</v>
       </c>
       <c r="D8" s="5">
-        <v>46129.39403539352</v>
+        <v>46129.56070206019</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>41</v>
@@ -1886,13 +1886,13 @@
         <v>44</v>
       </c>
       <c r="B9" s="8">
-        <v>46118.495359479166</v>
+        <v>46118.66202614583</v>
       </c>
       <c r="C9" s="8">
-        <v>46129.39415508102</v>
+        <v>46129.560821747684</v>
       </c>
       <c r="D9" s="8">
-        <v>46156.67195390046</v>
+        <v>46156.83862056713</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>45</v>
@@ -1951,11 +1951,11 @@
         <v>47</v>
       </c>
       <c r="B10" s="5">
-        <v>46118.49518951389</v>
+        <v>46118.66185618055</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46196.72905799768</v>
+        <v>46196.895724664355</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>48</v>
@@ -1998,13 +1998,13 @@
         <v>50</v>
       </c>
       <c r="B11" s="8">
-        <v>46118.495363379625</v>
+        <v>46118.6620300463</v>
       </c>
       <c r="C11" s="8">
-        <v>46129.40463276621</v>
+        <v>46129.57129943287</v>
       </c>
       <c r="D11" s="8">
-        <v>46129.40464815972</v>
+        <v>46129.57131482639</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>51</v>
@@ -2063,13 +2063,13 @@
         <v>56</v>
       </c>
       <c r="B12" s="5">
-        <v>46118.49536912037</v>
+        <v>46118.66203578704</v>
       </c>
       <c r="C12" s="5">
-        <v>46196.72904978009</v>
+        <v>46196.89571644676</v>
       </c>
       <c r="D12" s="5">
-        <v>46196.72905206018</v>
+        <v>46196.89571872685</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>57</v>
@@ -2128,13 +2128,13 @@
         <v>60</v>
       </c>
       <c r="B13" s="8">
-        <v>46118.495194097224</v>
+        <v>46118.66186076389</v>
       </c>
       <c r="C13" s="8">
-        <v>46193.395125625</v>
+        <v>46193.56179229167</v>
       </c>
       <c r="D13" s="8">
-        <v>46193.39512796296</v>
+        <v>46193.561794629626</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>61</v>
@@ -2177,13 +2177,13 @@
         <v>63</v>
       </c>
       <c r="B14" s="5">
-        <v>46118.49537506944</v>
+        <v>46118.66204173611</v>
       </c>
       <c r="C14" s="5">
-        <v>46129.395261620375</v>
+        <v>46129.56192828703</v>
       </c>
       <c r="D14" s="5">
-        <v>46191.60559553241</v>
+        <v>46191.77226219907</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>64</v>
@@ -2242,13 +2242,13 @@
         <v>67</v>
       </c>
       <c r="B15" s="8">
-        <v>46118.49538085648</v>
+        <v>46118.66204752315</v>
       </c>
       <c r="C15" s="8">
-        <v>46129.39527212963</v>
+        <v>46129.561938796294</v>
       </c>
       <c r="D15" s="8">
-        <v>46191.60559559028</v>
+        <v>46191.77226225694</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>68</v>
@@ -2307,13 +2307,13 @@
         <v>71</v>
       </c>
       <c r="B16" s="5">
-        <v>46118.49538628472</v>
+        <v>46118.66205295139</v>
       </c>
       <c r="C16" s="5">
-        <v>46129.40045137731</v>
+        <v>46129.56711804398</v>
       </c>
       <c r="D16" s="5">
-        <v>46191.60559547454</v>
+        <v>46191.7722621412</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>72</v>
@@ -2372,13 +2372,13 @@
         <v>75</v>
       </c>
       <c r="B17" s="8">
-        <v>46118.495199490746</v>
+        <v>46118.6618661574</v>
       </c>
       <c r="C17" s="8">
-        <v>46184.563075972226</v>
+        <v>46184.72974263889</v>
       </c>
       <c r="D17" s="8">
-        <v>46184.563077349536</v>
+        <v>46184.72974401621</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>76</v>
@@ -2421,13 +2421,13 @@
         <v>78</v>
       </c>
       <c r="B18" s="5">
-        <v>46118.495399872685</v>
+        <v>46118.66206653936</v>
       </c>
       <c r="C18" s="5">
-        <v>46129.395672175924</v>
+        <v>46129.56233884259</v>
       </c>
       <c r="D18" s="5">
-        <v>46129.3956940625</v>
+        <v>46129.56236072916</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>79</v>
@@ -2486,13 +2486,13 @@
         <v>82</v>
       </c>
       <c r="B19" s="8">
-        <v>46118.49540508102</v>
+        <v>46118.66207174768</v>
       </c>
       <c r="C19" s="8">
-        <v>46129.39567921296</v>
+        <v>46129.56234587963</v>
       </c>
       <c r="D19" s="8">
-        <v>46129.39570070602</v>
+        <v>46129.56236737268</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>83</v>
@@ -2551,13 +2551,13 @@
         <v>85</v>
       </c>
       <c r="B20" s="5">
-        <v>46118.49541042824</v>
+        <v>46118.66207709491</v>
       </c>
       <c r="C20" s="5">
-        <v>46129.40467122685</v>
+        <v>46129.57133789352</v>
       </c>
       <c r="D20" s="5">
-        <v>46129.40468762731</v>
+        <v>46129.57135429398</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>86</v>
@@ -2616,13 +2616,13 @@
         <v>89</v>
       </c>
       <c r="B21" s="8">
-        <v>46118.49541564815</v>
+        <v>46118.66208231481</v>
       </c>
       <c r="C21" s="8">
-        <v>46183.71343438658</v>
+        <v>46183.88010105324</v>
       </c>
       <c r="D21" s="8">
-        <v>46183.71343625</v>
+        <v>46183.880102916664</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>90</v>
@@ -2681,13 +2681,13 @@
         <v>94</v>
       </c>
       <c r="B22" s="5">
-        <v>46118.49542085648</v>
+        <v>46118.662087523146</v>
       </c>
       <c r="C22" s="5">
-        <v>46183.72138519676</v>
+        <v>46183.888051863425</v>
       </c>
       <c r="D22" s="5">
-        <v>46183.721584768515</v>
+        <v>46183.888251435186</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>95</v>
@@ -2746,13 +2746,13 @@
         <v>100</v>
       </c>
       <c r="B23" s="8">
-        <v>46118.49520528935</v>
+        <v>46118.66187195602</v>
       </c>
       <c r="C23" s="8">
-        <v>46184.5195800463</v>
+        <v>46184.68624671296</v>
       </c>
       <c r="D23" s="8">
-        <v>46184.51958140046</v>
+        <v>46184.686248067126</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>101</v>
@@ -2795,13 +2795,13 @@
         <v>103</v>
       </c>
       <c r="B24" s="5">
-        <v>46118.49542702547</v>
+        <v>46118.662093692124</v>
       </c>
       <c r="C24" s="5">
-        <v>46182.509780231485</v>
+        <v>46182.67644689815</v>
       </c>
       <c r="D24" s="5">
-        <v>46182.50978262731</v>
+        <v>46182.676449293984</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>104</v>
@@ -2860,13 +2860,13 @@
         <v>109</v>
       </c>
       <c r="B25" s="8">
-        <v>46118.495431793985</v>
+        <v>46118.66209846065</v>
       </c>
       <c r="C25" s="8">
-        <v>46174.4590187037</v>
+        <v>46174.62568537037</v>
       </c>
       <c r="D25" s="8">
-        <v>46174.45902023149</v>
+        <v>46174.62568689814</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>110</v>
@@ -2915,13 +2915,13 @@
         <v>112</v>
       </c>
       <c r="B26" s="5">
-        <v>46118.49543604167</v>
+        <v>46118.66210270833</v>
       </c>
       <c r="C26" s="5">
-        <v>46182.476623263894</v>
+        <v>46182.64328993055</v>
       </c>
       <c r="D26" s="5">
-        <v>46182.47662475695</v>
+        <v>46182.64329142361</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>113</v>
@@ -2970,13 +2970,13 @@
         <v>115</v>
       </c>
       <c r="B27" s="8">
-        <v>46118.4954403125</v>
+        <v>46118.662106979165</v>
       </c>
       <c r="C27" s="8">
-        <v>46182.47440028936</v>
+        <v>46182.641066956014</v>
       </c>
       <c r="D27" s="8">
-        <v>46182.47440253472</v>
+        <v>46182.64106920139</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>116</v>
@@ -3035,13 +3035,13 @@
         <v>118</v>
       </c>
       <c r="B28" s="5">
-        <v>46118.49544542824</v>
+        <v>46118.662112094906</v>
       </c>
       <c r="C28" s="5">
-        <v>46174.459855</v>
+        <v>46174.626521666665</v>
       </c>
       <c r="D28" s="5">
-        <v>46174.45985648148</v>
+        <v>46174.62652314815</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>119</v>
@@ -3096,13 +3096,13 @@
         <v>121</v>
       </c>
       <c r="B29" s="8">
-        <v>46118.4954502662</v>
+        <v>46118.66211693287</v>
       </c>
       <c r="C29" s="8">
-        <v>46174.45996375</v>
+        <v>46174.626630416664</v>
       </c>
       <c r="D29" s="8">
-        <v>46174.45996519676</v>
+        <v>46174.62663186343</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>122</v>
@@ -3157,13 +3157,13 @@
         <v>124</v>
       </c>
       <c r="B30" s="5">
-        <v>46118.495455358796</v>
+        <v>46118.66212202546</v>
       </c>
       <c r="C30" s="5">
-        <v>46184.519414780094</v>
+        <v>46184.68608144676</v>
       </c>
       <c r="D30" s="5">
-        <v>46184.519416574076</v>
+        <v>46184.68608324074</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>125</v>
@@ -3222,13 +3222,13 @@
         <v>127</v>
       </c>
       <c r="B31" s="8">
-        <v>46118.495460011574</v>
+        <v>46118.662126678246</v>
       </c>
       <c r="C31" s="8">
-        <v>46184.519052372685</v>
+        <v>46184.68571903935</v>
       </c>
       <c r="D31" s="8">
-        <v>46184.519054143515</v>
+        <v>46184.68572081019</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>128</v>
@@ -3283,13 +3283,13 @@
         <v>130</v>
       </c>
       <c r="B32" s="5">
-        <v>46118.495464594904</v>
+        <v>46118.662131261575</v>
       </c>
       <c r="C32" s="5">
-        <v>46184.519122233796</v>
+        <v>46184.68578890046</v>
       </c>
       <c r="D32" s="5">
-        <v>46184.51912386574</v>
+        <v>46184.68579053241</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>131</v>
@@ -3344,13 +3344,13 @@
         <v>133</v>
       </c>
       <c r="B33" s="8">
-        <v>46118.49551706019</v>
+        <v>46118.66218372685</v>
       </c>
       <c r="C33" s="8">
-        <v>46156.654673321755</v>
+        <v>46156.821339988426</v>
       </c>
       <c r="D33" s="8">
-        <v>46169.657316111116</v>
+        <v>46169.82398277777</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>134</v>
@@ -3409,13 +3409,13 @@
         <v>136</v>
       </c>
       <c r="B34" s="5">
-        <v>46118.4955234375</v>
+        <v>46118.662190104165</v>
       </c>
       <c r="C34" s="5">
-        <v>46134.624486030094</v>
+        <v>46134.79115269676</v>
       </c>
       <c r="D34" s="5">
-        <v>46169.65732769676</v>
+        <v>46169.823994363425</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>137</v>
@@ -3470,13 +3470,13 @@
         <v>139</v>
       </c>
       <c r="B35" s="8">
-        <v>46118.49552902778</v>
+        <v>46118.662195694444</v>
       </c>
       <c r="C35" s="8">
-        <v>46155.736021006946</v>
+        <v>46155.90268767361</v>
       </c>
       <c r="D35" s="8">
-        <v>46169.657349201385</v>
+        <v>46169.82401586806</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>140</v>
@@ -3531,13 +3531,13 @@
         <v>142</v>
       </c>
       <c r="B36" s="5">
-        <v>46118.495534155096</v>
+        <v>46118.66220082176</v>
       </c>
       <c r="C36" s="5">
-        <v>46134.624528726854</v>
+        <v>46134.79119539352</v>
       </c>
       <c r="D36" s="5">
-        <v>46169.65736949074</v>
+        <v>46169.824036157406</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>143</v>
@@ -3592,13 +3592,13 @@
         <v>145</v>
       </c>
       <c r="B37" s="8">
-        <v>46118.495539675925</v>
+        <v>46118.66220634259</v>
       </c>
       <c r="C37" s="8">
-        <v>46184.51943712963</v>
+        <v>46184.686103796295</v>
       </c>
       <c r="D37" s="8">
-        <v>46184.519438564814</v>
+        <v>46184.68610523148</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>146</v>
@@ -3657,13 +3657,13 @@
         <v>149</v>
       </c>
       <c r="B38" s="5">
-        <v>46118.495545682876</v>
+        <v>46118.66221234953</v>
       </c>
       <c r="C38" s="5">
-        <v>46184.36428194444</v>
+        <v>46184.53094861111</v>
       </c>
       <c r="D38" s="5">
-        <v>46184.36428409722</v>
+        <v>46184.53095076389</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>150</v>
@@ -3718,13 +3718,13 @@
         <v>152</v>
       </c>
       <c r="B39" s="8">
-        <v>46118.495549907406</v>
+        <v>46118.66221657407</v>
       </c>
       <c r="C39" s="8">
-        <v>46184.36495873843</v>
+        <v>46184.53162540509</v>
       </c>
       <c r="D39" s="8">
-        <v>46184.36496005787</v>
+        <v>46184.531626724536</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>151</v>
@@ -3779,11 +3779,11 @@
         <v>154</v>
       </c>
       <c r="B40" s="5">
-        <v>46118.495554305555</v>
+        <v>46118.662220972226</v>
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="5">
-        <v>46134.63373538194</v>
+        <v>46134.80040204861</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>155</v>
@@ -3826,13 +3826,13 @@
         <v>157</v>
       </c>
       <c r="B41" s="8">
-        <v>46118.495558553244</v>
+        <v>46118.66222521991</v>
       </c>
       <c r="C41" s="8">
-        <v>46129.40051568287</v>
+        <v>46129.567182349536</v>
       </c>
       <c r="D41" s="8">
-        <v>46129.40751229167</v>
+        <v>46129.57417895833</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>158</v>
@@ -3891,13 +3891,13 @@
         <v>162</v>
       </c>
       <c r="B42" s="5">
-        <v>46118.495565034726</v>
+        <v>46118.66223170139</v>
       </c>
       <c r="C42" s="5">
-        <v>46134.633600057874</v>
+        <v>46134.80026672454</v>
       </c>
       <c r="D42" s="5">
-        <v>46134.63361603009</v>
+        <v>46134.80028269676</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>163</v>
@@ -3956,13 +3956,13 @@
         <v>168</v>
       </c>
       <c r="B43" s="8">
-        <v>46118.49557270833</v>
+        <v>46118.662239375</v>
       </c>
       <c r="C43" s="8">
-        <v>46134.63372706018</v>
+        <v>46134.80039372685</v>
       </c>
       <c r="D43" s="8">
-        <v>46134.633741701386</v>
+        <v>46134.80040836806</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>98</v>
@@ -4019,11 +4019,11 @@
         <v>170</v>
       </c>
       <c r="B44" s="5">
-        <v>46118.49557863426</v>
+        <v>46118.662245300926</v>
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="5">
-        <v>46193.59886046297</v>
+        <v>46193.765527129624</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>171</v>
@@ -4082,13 +4082,13 @@
         <v>176</v>
       </c>
       <c r="B45" s="8">
-        <v>46118.49558318287</v>
+        <v>46118.66224984954</v>
       </c>
       <c r="C45" s="8">
-        <v>46184.520520185186</v>
+        <v>46184.68718685185</v>
       </c>
       <c r="D45" s="8">
-        <v>46184.520521620376</v>
+        <v>46184.68718828703</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>177</v>
@@ -4131,13 +4131,13 @@
         <v>179</v>
       </c>
       <c r="B46" s="5">
-        <v>46118.495586840276</v>
+        <v>46118.66225350695</v>
       </c>
       <c r="C46" s="5">
-        <v>46184.52003991898</v>
+        <v>46184.68670658565</v>
       </c>
       <c r="D46" s="5">
-        <v>46184.52025868055</v>
+        <v>46184.686925347225</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>153</v>
@@ -4196,13 +4196,13 @@
         <v>183</v>
       </c>
       <c r="B47" s="8">
-        <v>46118.49559196759</v>
+        <v>46118.66225863426</v>
       </c>
       <c r="C47" s="8">
-        <v>46184.520299317126</v>
+        <v>46184.6869659838</v>
       </c>
       <c r="D47" s="8">
-        <v>46184.52047996528</v>
+        <v>46184.68714663194</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>184</v>
@@ -4261,13 +4261,13 @@
         <v>188</v>
       </c>
       <c r="B48" s="5">
-        <v>46118.49559715278</v>
+        <v>46118.662263819446</v>
       </c>
       <c r="C48" s="5">
-        <v>46193.88967060186</v>
+        <v>46194.056337268514</v>
       </c>
       <c r="D48" s="5">
-        <v>46193.889672453704</v>
+        <v>46194.05633912037</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>189</v>
@@ -4310,13 +4310,13 @@
         <v>191</v>
       </c>
       <c r="B49" s="8">
-        <v>46118.49560084491</v>
+        <v>46118.66226751157</v>
       </c>
       <c r="C49" s="8">
-        <v>46184.52128453704</v>
+        <v>46184.687951203705</v>
       </c>
       <c r="D49" s="8">
-        <v>46184.52128605324</v>
+        <v>46184.687952719905</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>192</v>
@@ -4375,13 +4375,13 @@
         <v>196</v>
       </c>
       <c r="B50" s="5">
-        <v>46118.49560603009</v>
+        <v>46118.66227269676</v>
       </c>
       <c r="C50" s="5">
-        <v>46193.39524637732</v>
+        <v>46193.56191304398</v>
       </c>
       <c r="D50" s="5">
-        <v>46193.39524827546</v>
+        <v>46193.561914942125</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>197</v>
@@ -4440,13 +4440,13 @@
         <v>200</v>
       </c>
       <c r="B51" s="8">
-        <v>46184.52131372685</v>
+        <v>46184.687980393515</v>
       </c>
       <c r="C51" s="8">
-        <v>46184.52255061343</v>
+        <v>46184.68921728009</v>
       </c>
       <c r="D51" s="8">
-        <v>46191.52051372685</v>
+        <v>46191.68718039352</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>201</v>
@@ -4495,13 +4495,13 @@
         <v>202</v>
       </c>
       <c r="B52" s="5">
-        <v>46184.52142638889</v>
+        <v>46184.688093055556</v>
       </c>
       <c r="C52" s="5">
-        <v>46195.53587391204</v>
+        <v>46195.7025405787</v>
       </c>
       <c r="D52" s="5">
-        <v>46195.53587571759</v>
+        <v>46195.70254238426</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>203</v>
@@ -4550,13 +4550,13 @@
         <v>204</v>
       </c>
       <c r="B53" s="8">
-        <v>46184.52150136574</v>
+        <v>46184.68816803241</v>
       </c>
       <c r="C53" s="8">
-        <v>46184.523340844906</v>
+        <v>46184.69000751157</v>
       </c>
       <c r="D53" s="8">
-        <v>46191.52050717593</v>
+        <v>46191.6871738426</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>205</v>
@@ -4605,13 +4605,13 @@
         <v>206</v>
       </c>
       <c r="B54" s="5">
-        <v>46184.52160033565</v>
+        <v>46184.68826700232</v>
       </c>
       <c r="C54" s="5">
-        <v>46184.52365296296</v>
+        <v>46184.69031962963</v>
       </c>
       <c r="D54" s="5">
-        <v>46191.520502326384</v>
+        <v>46191.687168993056</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>207</v>
@@ -4660,13 +4660,13 @@
         <v>208</v>
       </c>
       <c r="B55" s="8">
-        <v>46118.49561196759</v>
+        <v>46118.66227863426</v>
       </c>
       <c r="C55" s="8">
-        <v>46193.39573376157</v>
+        <v>46193.56240042824</v>
       </c>
       <c r="D55" s="8">
-        <v>46193.39573895834</v>
+        <v>46193.562405625</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>209</v>
@@ -4725,13 +4725,13 @@
         <v>212</v>
       </c>
       <c r="B56" s="5">
-        <v>46118.495618217596</v>
+        <v>46118.66228488426</v>
       </c>
       <c r="C56" s="5">
-        <v>46193.889654548606</v>
+        <v>46194.05632121528</v>
       </c>
       <c r="D56" s="5">
-        <v>46193.88965658565</v>
+        <v>46194.05632325231</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>177</v>
@@ -4774,13 +4774,13 @@
         <v>214</v>
       </c>
       <c r="B57" s="8">
-        <v>46118.49562136574</v>
+        <v>46118.66228803241</v>
       </c>
       <c r="C57" s="8">
-        <v>46193.3956787037</v>
+        <v>46193.562345370374</v>
       </c>
       <c r="D57" s="8">
-        <v>46193.395680671296</v>
+        <v>46193.56234733797</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>215</v>
@@ -4839,13 +4839,13 @@
         <v>217</v>
       </c>
       <c r="B58" s="5">
-        <v>46118.49562685185</v>
+        <v>46118.662293518515</v>
       </c>
       <c r="C58" s="5">
-        <v>46193.39530791667</v>
+        <v>46193.56197458333</v>
       </c>
       <c r="D58" s="5">
-        <v>46193.395309837964</v>
+        <v>46193.56197650463</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>58</v>
@@ -4904,13 +4904,13 @@
         <v>219</v>
       </c>
       <c r="B59" s="8">
-        <v>46118.49563322916</v>
+        <v>46118.662299895834</v>
       </c>
       <c r="C59" s="8">
-        <v>46193.39531820602</v>
+        <v>46193.561984872686</v>
       </c>
       <c r="D59" s="8">
-        <v>46193.39532001158</v>
+        <v>46193.561986678236</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>220</v>
@@ -4969,13 +4969,13 @@
         <v>222</v>
       </c>
       <c r="B60" s="5">
-        <v>46118.495688842595</v>
+        <v>46118.66235550926</v>
       </c>
       <c r="C60" s="5">
-        <v>46193.3953305787</v>
+        <v>46193.56199724537</v>
       </c>
       <c r="D60" s="5">
-        <v>46193.39533219907</v>
+        <v>46193.56199886574</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>223</v>
@@ -5034,13 +5034,13 @@
         <v>225</v>
       </c>
       <c r="B61" s="8">
-        <v>46118.49569628472</v>
+        <v>46118.66236295139</v>
       </c>
       <c r="C61" s="8">
-        <v>46193.598368692124</v>
+        <v>46193.765035358796</v>
       </c>
       <c r="D61" s="8">
-        <v>46196.756804930556</v>
+        <v>46196.92347159723</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>226</v>
@@ -5083,13 +5083,13 @@
         <v>228</v>
       </c>
       <c r="B62" s="5">
-        <v>46118.495702071756</v>
+        <v>46118.66236873843</v>
       </c>
       <c r="C62" s="5">
-        <v>46193.445946782405</v>
+        <v>46193.61261344908</v>
       </c>
       <c r="D62" s="5">
-        <v>46196.7553321875</v>
+        <v>46196.921998854166</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>229</v>
@@ -5148,13 +5148,13 @@
         <v>231</v>
       </c>
       <c r="B63" s="8">
-        <v>46118.49570939815</v>
+        <v>46118.662376064814</v>
       </c>
       <c r="C63" s="8">
-        <v>46193.445992037035</v>
+        <v>46193.6126587037</v>
       </c>
       <c r="D63" s="8">
-        <v>46193.44599390046</v>
+        <v>46193.61266056713</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>224</v>
@@ -5213,13 +5213,13 @@
         <v>234</v>
       </c>
       <c r="B64" s="5">
-        <v>46118.4957208912</v>
+        <v>46118.662387557866</v>
       </c>
       <c r="C64" s="5">
-        <v>46193.44601277778</v>
+        <v>46193.61267944444</v>
       </c>
       <c r="D64" s="5">
-        <v>46193.44601434028</v>
+        <v>46193.61268100694</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>235</v>
@@ -5278,13 +5278,13 @@
         <v>237</v>
       </c>
       <c r="B65" s="8">
-        <v>46118.495732129624</v>
+        <v>46118.662398796296</v>
       </c>
       <c r="C65" s="8">
-        <v>46193.44607049768</v>
+        <v>46193.61273716435</v>
       </c>
       <c r="D65" s="8">
-        <v>46193.44607288194</v>
+        <v>46193.61273954861</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>238</v>
@@ -5343,13 +5343,13 @@
         <v>240</v>
       </c>
       <c r="B66" s="5">
-        <v>46118.495743182866</v>
+        <v>46118.66240984954</v>
       </c>
       <c r="C66" s="5">
-        <v>46193.59884520833</v>
+        <v>46193.765511875</v>
       </c>
       <c r="D66" s="5">
-        <v>46193.59885226852</v>
+        <v>46193.765518935186</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>174</v>
@@ -5406,13 +5406,13 @@
         <v>243</v>
       </c>
       <c r="B67" s="8">
-        <v>46118.49575346065</v>
+        <v>46118.662420127315</v>
       </c>
       <c r="C67" s="8">
-        <v>46196.75679758102</v>
+        <v>46196.92346424768</v>
       </c>
       <c r="D67" s="8">
-        <v>46196.75679912037</v>
+        <v>46196.92346578704</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>244</v>
@@ -5471,11 +5471,11 @@
         <v>246</v>
       </c>
       <c r="B68" s="5">
-        <v>46118.49576103009</v>
+        <v>46118.66242769676</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46196.75640028935</v>
+        <v>46196.92306695602</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>247</v>
@@ -5518,11 +5518,11 @@
         <v>249</v>
       </c>
       <c r="B69" s="8">
-        <v>46118.49576510416</v>
+        <v>46118.662431770834</v>
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46196.75680685185</v>
+        <v>46196.92347351852</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>250</v>
@@ -5579,11 +5579,11 @@
         <v>254</v>
       </c>
       <c r="B70" s="5">
-        <v>46118.49577158564</v>
+        <v>46118.662438252315</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46196.72905917824</v>
+        <v>46196.89572584491</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>255</v>
@@ -5640,13 +5640,13 @@
         <v>258</v>
       </c>
       <c r="B71" s="8">
-        <v>46118.49578482639</v>
+        <v>46118.66245149306</v>
       </c>
       <c r="C71" s="8">
-        <v>46196.75639109954</v>
+        <v>46196.9230577662</v>
       </c>
       <c r="D71" s="8">
-        <v>46196.756393668984</v>
+        <v>46196.92306033565</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>259</v>
@@ -5703,11 +5703,11 @@
         <v>263</v>
       </c>
       <c r="B72" s="5">
-        <v>46118.49579103009</v>
+        <v>46118.66245769676</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46196.756401736115</v>
+        <v>46196.92306840278</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>264</v>
@@ -5764,11 +5764,11 @@
         <v>266</v>
       </c>
       <c r="B73" s="8">
-        <v>46118.49579800926</v>
+        <v>46118.66246467593</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46118.5961819213</v>
+        <v>46118.76284858796</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>267</v>
@@ -5811,11 +5811,11 @@
         <v>269</v>
       </c>
       <c r="B74" s="5">
-        <v>46118.495801296296</v>
+        <v>46118.66246796296</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46118.60144140046</v>
+        <v>46118.76810806713</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>270</v>
@@ -5874,11 +5874,11 @@
         <v>273</v>
       </c>
       <c r="B75" s="8">
-        <v>46118.49584592592</v>
+        <v>46118.66251259259</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46191.60559547454</v>
+        <v>46191.7722621412</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>274</v>
@@ -5937,11 +5937,11 @@
         <v>275</v>
       </c>
       <c r="B76" s="5">
-        <v>46118.49585471065</v>
+        <v>46118.662521377315</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46118.59695680556</v>
+        <v>46118.76362347222</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>276</v>
@@ -5984,11 +5984,11 @@
         <v>278</v>
       </c>
       <c r="B77" s="8">
-        <v>46118.495858993054</v>
+        <v>46118.66252565972</v>
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46118.60159583333</v>
+        <v>46118.7682625</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>279</v>
@@ -6047,11 +6047,11 @@
         <v>281</v>
       </c>
       <c r="B78" s="5">
-        <v>46118.49586534723</v>
+        <v>46118.662532013885</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46118.601592962965</v>
+        <v>46118.76825962963</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>282</v>

--- a/data/50001533 - GESVIAL.xlsx
+++ b/data/50001533 - GESVIAL.xlsx
@@ -3783,7 +3783,7 @@
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="5">
-        <v>46134.80040204861</v>
+        <v>46198.56946403935</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>155</v>
@@ -4021,9 +4021,11 @@
       <c r="B44" s="5">
         <v>46118.662245300926</v>
       </c>
-      <c r="C44" s="6"/>
+      <c r="C44" s="5">
+        <v>46198.5694571412</v>
+      </c>
       <c r="D44" s="5">
-        <v>46193.765527129624</v>
+        <v>46198.56945943287</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>171</v>
@@ -5412,7 +5414,7 @@
         <v>46196.92346424768</v>
       </c>
       <c r="D67" s="8">
-        <v>46196.92346578704</v>
+        <v>46198.56946547454</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>244</v>

--- a/data/50001533 - GESVIAL.xlsx
+++ b/data/50001533 - GESVIAL.xlsx
@@ -1577,13 +1577,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46118.66185005787</v>
+        <v>46118.495183391206</v>
       </c>
       <c r="C4" s="5">
-        <v>46129.56083631945</v>
+        <v>46129.394169652776</v>
       </c>
       <c r="D4" s="5">
-        <v>46148.01378729167</v>
+        <v>46147.847120624996</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1626,13 +1626,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46118.662012175926</v>
+        <v>46118.49534550926</v>
       </c>
       <c r="C5" s="8">
-        <v>46129.559856481486</v>
+        <v>46129.393189814815</v>
       </c>
       <c r="D5" s="8">
-        <v>46133.87722729167</v>
+        <v>46133.710560625</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1691,13 +1691,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46118.662015567126</v>
+        <v>46118.49534890046</v>
       </c>
       <c r="C6" s="5">
-        <v>46129.55991743055</v>
+        <v>46129.39325076389</v>
       </c>
       <c r="D6" s="5">
-        <v>46129.55993412037</v>
+        <v>46129.393267453706</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -1756,13 +1756,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="8">
-        <v>46118.662018773146</v>
+        <v>46118.49535210648</v>
       </c>
       <c r="C7" s="8">
-        <v>46129.56027341435</v>
+        <v>46129.39360674769</v>
       </c>
       <c r="D7" s="8">
-        <v>46129.560290416666</v>
+        <v>46129.39362375</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>38</v>
@@ -1821,13 +1821,13 @@
         <v>40</v>
       </c>
       <c r="B8" s="5">
-        <v>46118.66202195601</v>
+        <v>46118.49535528936</v>
       </c>
       <c r="C8" s="5">
-        <v>46129.56068634259</v>
+        <v>46129.39401967592</v>
       </c>
       <c r="D8" s="5">
-        <v>46129.56070206019</v>
+        <v>46129.39403539352</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>41</v>
@@ -1886,13 +1886,13 @@
         <v>44</v>
       </c>
       <c r="B9" s="8">
-        <v>46118.66202614583</v>
+        <v>46118.495359479166</v>
       </c>
       <c r="C9" s="8">
-        <v>46129.560821747684</v>
+        <v>46129.39415508102</v>
       </c>
       <c r="D9" s="8">
-        <v>46156.83862056713</v>
+        <v>46156.67195390046</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>45</v>
@@ -1951,11 +1951,11 @@
         <v>47</v>
       </c>
       <c r="B10" s="5">
-        <v>46118.66185618055</v>
+        <v>46118.49518951389</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46196.895724664355</v>
+        <v>46196.72905799768</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>48</v>
@@ -1998,13 +1998,13 @@
         <v>50</v>
       </c>
       <c r="B11" s="8">
-        <v>46118.6620300463</v>
+        <v>46118.495363379625</v>
       </c>
       <c r="C11" s="8">
-        <v>46129.57129943287</v>
+        <v>46129.40463276621</v>
       </c>
       <c r="D11" s="8">
-        <v>46129.57131482639</v>
+        <v>46129.40464815972</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>51</v>
@@ -2063,13 +2063,13 @@
         <v>56</v>
       </c>
       <c r="B12" s="5">
-        <v>46118.66203578704</v>
+        <v>46118.49536912037</v>
       </c>
       <c r="C12" s="5">
-        <v>46196.89571644676</v>
+        <v>46196.72904978009</v>
       </c>
       <c r="D12" s="5">
-        <v>46196.89571872685</v>
+        <v>46196.72905206018</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>57</v>
@@ -2128,13 +2128,13 @@
         <v>60</v>
       </c>
       <c r="B13" s="8">
-        <v>46118.66186076389</v>
+        <v>46118.495194097224</v>
       </c>
       <c r="C13" s="8">
-        <v>46193.56179229167</v>
+        <v>46193.395125625</v>
       </c>
       <c r="D13" s="8">
-        <v>46193.561794629626</v>
+        <v>46193.39512796296</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>61</v>
@@ -2177,13 +2177,13 @@
         <v>63</v>
       </c>
       <c r="B14" s="5">
-        <v>46118.66204173611</v>
+        <v>46118.49537506944</v>
       </c>
       <c r="C14" s="5">
-        <v>46129.56192828703</v>
+        <v>46129.395261620375</v>
       </c>
       <c r="D14" s="5">
-        <v>46191.77226219907</v>
+        <v>46191.60559553241</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>64</v>
@@ -2242,13 +2242,13 @@
         <v>67</v>
       </c>
       <c r="B15" s="8">
-        <v>46118.66204752315</v>
+        <v>46118.49538085648</v>
       </c>
       <c r="C15" s="8">
-        <v>46129.561938796294</v>
+        <v>46129.39527212963</v>
       </c>
       <c r="D15" s="8">
-        <v>46191.77226225694</v>
+        <v>46191.60559559028</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>68</v>
@@ -2307,13 +2307,13 @@
         <v>71</v>
       </c>
       <c r="B16" s="5">
-        <v>46118.66205295139</v>
+        <v>46118.49538628472</v>
       </c>
       <c r="C16" s="5">
-        <v>46129.56711804398</v>
+        <v>46129.40045137731</v>
       </c>
       <c r="D16" s="5">
-        <v>46191.7722621412</v>
+        <v>46191.60559547454</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>72</v>
@@ -2372,13 +2372,13 @@
         <v>75</v>
       </c>
       <c r="B17" s="8">
-        <v>46118.6618661574</v>
+        <v>46118.495199490746</v>
       </c>
       <c r="C17" s="8">
-        <v>46184.72974263889</v>
+        <v>46184.563075972226</v>
       </c>
       <c r="D17" s="8">
-        <v>46184.72974401621</v>
+        <v>46184.563077349536</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>76</v>
@@ -2421,13 +2421,13 @@
         <v>78</v>
       </c>
       <c r="B18" s="5">
-        <v>46118.66206653936</v>
+        <v>46118.495399872685</v>
       </c>
       <c r="C18" s="5">
-        <v>46129.56233884259</v>
+        <v>46129.395672175924</v>
       </c>
       <c r="D18" s="5">
-        <v>46129.56236072916</v>
+        <v>46129.3956940625</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>79</v>
@@ -2486,13 +2486,13 @@
         <v>82</v>
       </c>
       <c r="B19" s="8">
-        <v>46118.66207174768</v>
+        <v>46118.49540508102</v>
       </c>
       <c r="C19" s="8">
-        <v>46129.56234587963</v>
+        <v>46129.39567921296</v>
       </c>
       <c r="D19" s="8">
-        <v>46129.56236737268</v>
+        <v>46129.39570070602</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>83</v>
@@ -2551,13 +2551,13 @@
         <v>85</v>
       </c>
       <c r="B20" s="5">
-        <v>46118.66207709491</v>
+        <v>46118.49541042824</v>
       </c>
       <c r="C20" s="5">
-        <v>46129.57133789352</v>
+        <v>46129.40467122685</v>
       </c>
       <c r="D20" s="5">
-        <v>46129.57135429398</v>
+        <v>46129.40468762731</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>86</v>
@@ -2616,13 +2616,13 @@
         <v>89</v>
       </c>
       <c r="B21" s="8">
-        <v>46118.66208231481</v>
+        <v>46118.49541564815</v>
       </c>
       <c r="C21" s="8">
-        <v>46183.88010105324</v>
+        <v>46183.71343438658</v>
       </c>
       <c r="D21" s="8">
-        <v>46183.880102916664</v>
+        <v>46183.71343625</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>90</v>
@@ -2681,13 +2681,13 @@
         <v>94</v>
       </c>
       <c r="B22" s="5">
-        <v>46118.662087523146</v>
+        <v>46118.49542085648</v>
       </c>
       <c r="C22" s="5">
-        <v>46183.888051863425</v>
+        <v>46183.72138519676</v>
       </c>
       <c r="D22" s="5">
-        <v>46183.888251435186</v>
+        <v>46183.721584768515</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>95</v>
@@ -2746,13 +2746,13 @@
         <v>100</v>
       </c>
       <c r="B23" s="8">
-        <v>46118.66187195602</v>
+        <v>46118.49520528935</v>
       </c>
       <c r="C23" s="8">
-        <v>46184.68624671296</v>
+        <v>46184.5195800463</v>
       </c>
       <c r="D23" s="8">
-        <v>46184.686248067126</v>
+        <v>46184.51958140046</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>101</v>
@@ -2795,13 +2795,13 @@
         <v>103</v>
       </c>
       <c r="B24" s="5">
-        <v>46118.662093692124</v>
+        <v>46118.49542702547</v>
       </c>
       <c r="C24" s="5">
-        <v>46182.67644689815</v>
+        <v>46182.509780231485</v>
       </c>
       <c r="D24" s="5">
-        <v>46182.676449293984</v>
+        <v>46182.50978262731</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>104</v>
@@ -2860,13 +2860,13 @@
         <v>109</v>
       </c>
       <c r="B25" s="8">
-        <v>46118.66209846065</v>
+        <v>46118.495431793985</v>
       </c>
       <c r="C25" s="8">
-        <v>46174.62568537037</v>
+        <v>46174.4590187037</v>
       </c>
       <c r="D25" s="8">
-        <v>46174.62568689814</v>
+        <v>46174.45902023149</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>110</v>
@@ -2915,13 +2915,13 @@
         <v>112</v>
       </c>
       <c r="B26" s="5">
-        <v>46118.66210270833</v>
+        <v>46118.49543604167</v>
       </c>
       <c r="C26" s="5">
-        <v>46182.64328993055</v>
+        <v>46182.476623263894</v>
       </c>
       <c r="D26" s="5">
-        <v>46182.64329142361</v>
+        <v>46182.47662475695</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>113</v>
@@ -2970,13 +2970,13 @@
         <v>115</v>
       </c>
       <c r="B27" s="8">
-        <v>46118.662106979165</v>
+        <v>46118.4954403125</v>
       </c>
       <c r="C27" s="8">
-        <v>46182.641066956014</v>
+        <v>46182.47440028936</v>
       </c>
       <c r="D27" s="8">
-        <v>46182.64106920139</v>
+        <v>46182.47440253472</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>116</v>
@@ -3035,13 +3035,13 @@
         <v>118</v>
       </c>
       <c r="B28" s="5">
-        <v>46118.662112094906</v>
+        <v>46118.49544542824</v>
       </c>
       <c r="C28" s="5">
-        <v>46174.626521666665</v>
+        <v>46174.459855</v>
       </c>
       <c r="D28" s="5">
-        <v>46174.62652314815</v>
+        <v>46174.45985648148</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>119</v>
@@ -3096,13 +3096,13 @@
         <v>121</v>
       </c>
       <c r="B29" s="8">
-        <v>46118.66211693287</v>
+        <v>46118.4954502662</v>
       </c>
       <c r="C29" s="8">
-        <v>46174.626630416664</v>
+        <v>46174.45996375</v>
       </c>
       <c r="D29" s="8">
-        <v>46174.62663186343</v>
+        <v>46174.45996519676</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>122</v>
@@ -3157,13 +3157,13 @@
         <v>124</v>
       </c>
       <c r="B30" s="5">
-        <v>46118.66212202546</v>
+        <v>46118.495455358796</v>
       </c>
       <c r="C30" s="5">
-        <v>46184.68608144676</v>
+        <v>46184.519414780094</v>
       </c>
       <c r="D30" s="5">
-        <v>46184.68608324074</v>
+        <v>46184.519416574076</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>125</v>
@@ -3222,13 +3222,13 @@
         <v>127</v>
       </c>
       <c r="B31" s="8">
-        <v>46118.662126678246</v>
+        <v>46118.495460011574</v>
       </c>
       <c r="C31" s="8">
-        <v>46184.68571903935</v>
+        <v>46184.519052372685</v>
       </c>
       <c r="D31" s="8">
-        <v>46184.68572081019</v>
+        <v>46184.519054143515</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>128</v>
@@ -3283,13 +3283,13 @@
         <v>130</v>
       </c>
       <c r="B32" s="5">
-        <v>46118.662131261575</v>
+        <v>46118.495464594904</v>
       </c>
       <c r="C32" s="5">
-        <v>46184.68578890046</v>
+        <v>46184.519122233796</v>
       </c>
       <c r="D32" s="5">
-        <v>46184.68579053241</v>
+        <v>46184.51912386574</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>131</v>
@@ -3344,13 +3344,13 @@
         <v>133</v>
       </c>
       <c r="B33" s="8">
-        <v>46118.66218372685</v>
+        <v>46118.49551706019</v>
       </c>
       <c r="C33" s="8">
-        <v>46156.821339988426</v>
+        <v>46156.654673321755</v>
       </c>
       <c r="D33" s="8">
-        <v>46169.82398277777</v>
+        <v>46169.657316111116</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>134</v>
@@ -3409,13 +3409,13 @@
         <v>136</v>
       </c>
       <c r="B34" s="5">
-        <v>46118.662190104165</v>
+        <v>46118.4955234375</v>
       </c>
       <c r="C34" s="5">
-        <v>46134.79115269676</v>
+        <v>46134.624486030094</v>
       </c>
       <c r="D34" s="5">
-        <v>46169.823994363425</v>
+        <v>46169.65732769676</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>137</v>
@@ -3470,13 +3470,13 @@
         <v>139</v>
       </c>
       <c r="B35" s="8">
-        <v>46118.662195694444</v>
+        <v>46118.49552902778</v>
       </c>
       <c r="C35" s="8">
-        <v>46155.90268767361</v>
+        <v>46155.736021006946</v>
       </c>
       <c r="D35" s="8">
-        <v>46169.82401586806</v>
+        <v>46169.657349201385</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>140</v>
@@ -3531,13 +3531,13 @@
         <v>142</v>
       </c>
       <c r="B36" s="5">
-        <v>46118.66220082176</v>
+        <v>46118.495534155096</v>
       </c>
       <c r="C36" s="5">
-        <v>46134.79119539352</v>
+        <v>46134.624528726854</v>
       </c>
       <c r="D36" s="5">
-        <v>46169.824036157406</v>
+        <v>46169.65736949074</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>143</v>
@@ -3592,13 +3592,13 @@
         <v>145</v>
       </c>
       <c r="B37" s="8">
-        <v>46118.66220634259</v>
+        <v>46118.495539675925</v>
       </c>
       <c r="C37" s="8">
-        <v>46184.686103796295</v>
+        <v>46184.51943712963</v>
       </c>
       <c r="D37" s="8">
-        <v>46184.68610523148</v>
+        <v>46184.519438564814</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>146</v>
@@ -3657,13 +3657,13 @@
         <v>149</v>
       </c>
       <c r="B38" s="5">
-        <v>46118.66221234953</v>
+        <v>46118.495545682876</v>
       </c>
       <c r="C38" s="5">
-        <v>46184.53094861111</v>
+        <v>46184.36428194444</v>
       </c>
       <c r="D38" s="5">
-        <v>46184.53095076389</v>
+        <v>46184.36428409722</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>150</v>
@@ -3718,13 +3718,13 @@
         <v>152</v>
       </c>
       <c r="B39" s="8">
-        <v>46118.66221657407</v>
+        <v>46118.495549907406</v>
       </c>
       <c r="C39" s="8">
-        <v>46184.53162540509</v>
+        <v>46184.36495873843</v>
       </c>
       <c r="D39" s="8">
-        <v>46184.531626724536</v>
+        <v>46184.36496005787</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>151</v>
@@ -3779,11 +3779,11 @@
         <v>154</v>
       </c>
       <c r="B40" s="5">
-        <v>46118.662220972226</v>
+        <v>46118.495554305555</v>
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="5">
-        <v>46198.56946403935</v>
+        <v>46198.402797372684</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>155</v>
@@ -3826,13 +3826,13 @@
         <v>157</v>
       </c>
       <c r="B41" s="8">
-        <v>46118.66222521991</v>
+        <v>46118.495558553244</v>
       </c>
       <c r="C41" s="8">
-        <v>46129.567182349536</v>
+        <v>46129.40051568287</v>
       </c>
       <c r="D41" s="8">
-        <v>46129.57417895833</v>
+        <v>46129.40751229167</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>158</v>
@@ -3891,13 +3891,13 @@
         <v>162</v>
       </c>
       <c r="B42" s="5">
-        <v>46118.66223170139</v>
+        <v>46118.495565034726</v>
       </c>
       <c r="C42" s="5">
-        <v>46134.80026672454</v>
+        <v>46134.633600057874</v>
       </c>
       <c r="D42" s="5">
-        <v>46134.80028269676</v>
+        <v>46134.63361603009</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>163</v>
@@ -3956,13 +3956,13 @@
         <v>168</v>
       </c>
       <c r="B43" s="8">
-        <v>46118.662239375</v>
+        <v>46118.49557270833</v>
       </c>
       <c r="C43" s="8">
-        <v>46134.80039372685</v>
+        <v>46134.63372706018</v>
       </c>
       <c r="D43" s="8">
-        <v>46134.80040836806</v>
+        <v>46134.633741701386</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>98</v>
@@ -4019,13 +4019,13 @@
         <v>170</v>
       </c>
       <c r="B44" s="5">
-        <v>46118.662245300926</v>
+        <v>46118.49557863426</v>
       </c>
       <c r="C44" s="5">
-        <v>46198.5694571412</v>
+        <v>46198.40279047454</v>
       </c>
       <c r="D44" s="5">
-        <v>46198.56945943287</v>
+        <v>46198.4027927662</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>171</v>
@@ -4084,13 +4084,13 @@
         <v>176</v>
       </c>
       <c r="B45" s="8">
-        <v>46118.66224984954</v>
+        <v>46118.49558318287</v>
       </c>
       <c r="C45" s="8">
-        <v>46184.68718685185</v>
+        <v>46184.520520185186</v>
       </c>
       <c r="D45" s="8">
-        <v>46184.68718828703</v>
+        <v>46184.520521620376</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>177</v>
@@ -4133,13 +4133,13 @@
         <v>179</v>
       </c>
       <c r="B46" s="5">
-        <v>46118.66225350695</v>
+        <v>46118.495586840276</v>
       </c>
       <c r="C46" s="5">
-        <v>46184.68670658565</v>
+        <v>46184.52003991898</v>
       </c>
       <c r="D46" s="5">
-        <v>46184.686925347225</v>
+        <v>46184.52025868055</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>153</v>
@@ -4198,13 +4198,13 @@
         <v>183</v>
       </c>
       <c r="B47" s="8">
-        <v>46118.66225863426</v>
+        <v>46118.49559196759</v>
       </c>
       <c r="C47" s="8">
-        <v>46184.6869659838</v>
+        <v>46184.520299317126</v>
       </c>
       <c r="D47" s="8">
-        <v>46184.68714663194</v>
+        <v>46184.52047996528</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>184</v>
@@ -4263,13 +4263,13 @@
         <v>188</v>
       </c>
       <c r="B48" s="5">
-        <v>46118.662263819446</v>
+        <v>46118.49559715278</v>
       </c>
       <c r="C48" s="5">
-        <v>46194.056337268514</v>
+        <v>46193.88967060186</v>
       </c>
       <c r="D48" s="5">
-        <v>46194.05633912037</v>
+        <v>46193.889672453704</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>189</v>
@@ -4312,13 +4312,13 @@
         <v>191</v>
       </c>
       <c r="B49" s="8">
-        <v>46118.66226751157</v>
+        <v>46118.49560084491</v>
       </c>
       <c r="C49" s="8">
-        <v>46184.687951203705</v>
+        <v>46184.52128453704</v>
       </c>
       <c r="D49" s="8">
-        <v>46184.687952719905</v>
+        <v>46184.52128605324</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>192</v>
@@ -4377,13 +4377,13 @@
         <v>196</v>
       </c>
       <c r="B50" s="5">
-        <v>46118.66227269676</v>
+        <v>46118.49560603009</v>
       </c>
       <c r="C50" s="5">
-        <v>46193.56191304398</v>
+        <v>46193.39524637732</v>
       </c>
       <c r="D50" s="5">
-        <v>46193.561914942125</v>
+        <v>46193.39524827546</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>197</v>
@@ -4442,13 +4442,13 @@
         <v>200</v>
       </c>
       <c r="B51" s="8">
-        <v>46184.687980393515</v>
+        <v>46184.52131372685</v>
       </c>
       <c r="C51" s="8">
-        <v>46184.68921728009</v>
+        <v>46184.52255061343</v>
       </c>
       <c r="D51" s="8">
-        <v>46191.68718039352</v>
+        <v>46191.52051372685</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>201</v>
@@ -4497,13 +4497,13 @@
         <v>202</v>
       </c>
       <c r="B52" s="5">
-        <v>46184.688093055556</v>
+        <v>46184.52142638889</v>
       </c>
       <c r="C52" s="5">
-        <v>46195.7025405787</v>
+        <v>46195.53587391204</v>
       </c>
       <c r="D52" s="5">
-        <v>46195.70254238426</v>
+        <v>46195.53587571759</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>203</v>
@@ -4552,13 +4552,13 @@
         <v>204</v>
       </c>
       <c r="B53" s="8">
-        <v>46184.68816803241</v>
+        <v>46184.52150136574</v>
       </c>
       <c r="C53" s="8">
-        <v>46184.69000751157</v>
+        <v>46184.523340844906</v>
       </c>
       <c r="D53" s="8">
-        <v>46191.6871738426</v>
+        <v>46191.52050717593</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>205</v>
@@ -4607,13 +4607,13 @@
         <v>206</v>
       </c>
       <c r="B54" s="5">
-        <v>46184.68826700232</v>
+        <v>46184.52160033565</v>
       </c>
       <c r="C54" s="5">
-        <v>46184.69031962963</v>
+        <v>46184.52365296296</v>
       </c>
       <c r="D54" s="5">
-        <v>46191.687168993056</v>
+        <v>46191.520502326384</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>207</v>
@@ -4662,13 +4662,13 @@
         <v>208</v>
       </c>
       <c r="B55" s="8">
-        <v>46118.66227863426</v>
+        <v>46118.49561196759</v>
       </c>
       <c r="C55" s="8">
-        <v>46193.56240042824</v>
+        <v>46193.39573376157</v>
       </c>
       <c r="D55" s="8">
-        <v>46193.562405625</v>
+        <v>46193.39573895834</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>209</v>
@@ -4727,13 +4727,13 @@
         <v>212</v>
       </c>
       <c r="B56" s="5">
-        <v>46118.66228488426</v>
+        <v>46118.495618217596</v>
       </c>
       <c r="C56" s="5">
-        <v>46194.05632121528</v>
+        <v>46193.889654548606</v>
       </c>
       <c r="D56" s="5">
-        <v>46194.05632325231</v>
+        <v>46193.88965658565</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>177</v>
@@ -4776,13 +4776,13 @@
         <v>214</v>
       </c>
       <c r="B57" s="8">
-        <v>46118.66228803241</v>
+        <v>46118.49562136574</v>
       </c>
       <c r="C57" s="8">
-        <v>46193.562345370374</v>
+        <v>46193.3956787037</v>
       </c>
       <c r="D57" s="8">
-        <v>46193.56234733797</v>
+        <v>46193.395680671296</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>215</v>
@@ -4841,13 +4841,13 @@
         <v>217</v>
       </c>
       <c r="B58" s="5">
-        <v>46118.662293518515</v>
+        <v>46118.49562685185</v>
       </c>
       <c r="C58" s="5">
-        <v>46193.56197458333</v>
+        <v>46193.39530791667</v>
       </c>
       <c r="D58" s="5">
-        <v>46193.56197650463</v>
+        <v>46193.395309837964</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>58</v>
@@ -4906,13 +4906,13 @@
         <v>219</v>
       </c>
       <c r="B59" s="8">
-        <v>46118.662299895834</v>
+        <v>46118.49563322916</v>
       </c>
       <c r="C59" s="8">
-        <v>46193.561984872686</v>
+        <v>46193.39531820602</v>
       </c>
       <c r="D59" s="8">
-        <v>46193.561986678236</v>
+        <v>46193.39532001158</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>220</v>
@@ -4971,13 +4971,13 @@
         <v>222</v>
       </c>
       <c r="B60" s="5">
-        <v>46118.66235550926</v>
+        <v>46118.495688842595</v>
       </c>
       <c r="C60" s="5">
-        <v>46193.56199724537</v>
+        <v>46193.3953305787</v>
       </c>
       <c r="D60" s="5">
-        <v>46193.56199886574</v>
+        <v>46193.39533219907</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>223</v>
@@ -5036,13 +5036,13 @@
         <v>225</v>
       </c>
       <c r="B61" s="8">
-        <v>46118.66236295139</v>
+        <v>46118.49569628472</v>
       </c>
       <c r="C61" s="8">
-        <v>46193.765035358796</v>
+        <v>46193.598368692124</v>
       </c>
       <c r="D61" s="8">
-        <v>46196.92347159723</v>
+        <v>46196.756804930556</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>226</v>
@@ -5085,13 +5085,13 @@
         <v>228</v>
       </c>
       <c r="B62" s="5">
-        <v>46118.66236873843</v>
+        <v>46118.495702071756</v>
       </c>
       <c r="C62" s="5">
-        <v>46193.61261344908</v>
+        <v>46193.445946782405</v>
       </c>
       <c r="D62" s="5">
-        <v>46196.921998854166</v>
+        <v>46196.7553321875</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>229</v>
@@ -5150,13 +5150,13 @@
         <v>231</v>
       </c>
       <c r="B63" s="8">
-        <v>46118.662376064814</v>
+        <v>46118.49570939815</v>
       </c>
       <c r="C63" s="8">
-        <v>46193.6126587037</v>
+        <v>46193.445992037035</v>
       </c>
       <c r="D63" s="8">
-        <v>46193.61266056713</v>
+        <v>46193.44599390046</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>224</v>
@@ -5215,13 +5215,13 @@
         <v>234</v>
       </c>
       <c r="B64" s="5">
-        <v>46118.662387557866</v>
+        <v>46118.4957208912</v>
       </c>
       <c r="C64" s="5">
-        <v>46193.61267944444</v>
+        <v>46193.44601277778</v>
       </c>
       <c r="D64" s="5">
-        <v>46193.61268100694</v>
+        <v>46193.44601434028</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>235</v>
@@ -5280,13 +5280,13 @@
         <v>237</v>
       </c>
       <c r="B65" s="8">
-        <v>46118.662398796296</v>
+        <v>46118.495732129624</v>
       </c>
       <c r="C65" s="8">
-        <v>46193.61273716435</v>
+        <v>46193.44607049768</v>
       </c>
       <c r="D65" s="8">
-        <v>46193.61273954861</v>
+        <v>46193.44607288194</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>238</v>
@@ -5345,13 +5345,13 @@
         <v>240</v>
       </c>
       <c r="B66" s="5">
-        <v>46118.66240984954</v>
+        <v>46118.495743182866</v>
       </c>
       <c r="C66" s="5">
-        <v>46193.765511875</v>
+        <v>46193.59884520833</v>
       </c>
       <c r="D66" s="5">
-        <v>46193.765518935186</v>
+        <v>46193.59885226852</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>174</v>
@@ -5408,13 +5408,13 @@
         <v>243</v>
       </c>
       <c r="B67" s="8">
-        <v>46118.662420127315</v>
+        <v>46118.49575346065</v>
       </c>
       <c r="C67" s="8">
-        <v>46196.92346424768</v>
+        <v>46196.75679758102</v>
       </c>
       <c r="D67" s="8">
-        <v>46198.56946547454</v>
+        <v>46198.402798807874</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>244</v>
@@ -5473,11 +5473,11 @@
         <v>246</v>
       </c>
       <c r="B68" s="5">
-        <v>46118.66242769676</v>
+        <v>46118.49576103009</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46196.92306695602</v>
+        <v>46196.75640028935</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>247</v>
@@ -5520,11 +5520,11 @@
         <v>249</v>
       </c>
       <c r="B69" s="8">
-        <v>46118.662431770834</v>
+        <v>46118.49576510416</v>
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46196.92347351852</v>
+        <v>46196.75680685185</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>250</v>
@@ -5581,11 +5581,11 @@
         <v>254</v>
       </c>
       <c r="B70" s="5">
-        <v>46118.662438252315</v>
+        <v>46118.49577158564</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46196.89572584491</v>
+        <v>46196.72905917824</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>255</v>
@@ -5642,13 +5642,13 @@
         <v>258</v>
       </c>
       <c r="B71" s="8">
-        <v>46118.66245149306</v>
+        <v>46118.49578482639</v>
       </c>
       <c r="C71" s="8">
-        <v>46196.9230577662</v>
+        <v>46196.75639109954</v>
       </c>
       <c r="D71" s="8">
-        <v>46196.92306033565</v>
+        <v>46196.756393668984</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>259</v>
@@ -5705,11 +5705,11 @@
         <v>263</v>
       </c>
       <c r="B72" s="5">
-        <v>46118.66245769676</v>
+        <v>46118.49579103009</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46196.92306840278</v>
+        <v>46196.756401736115</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>264</v>
@@ -5766,11 +5766,11 @@
         <v>266</v>
       </c>
       <c r="B73" s="8">
-        <v>46118.66246467593</v>
+        <v>46118.49579800926</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46118.76284858796</v>
+        <v>46118.5961819213</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>267</v>
@@ -5813,11 +5813,11 @@
         <v>269</v>
       </c>
       <c r="B74" s="5">
-        <v>46118.66246796296</v>
+        <v>46118.495801296296</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46118.76810806713</v>
+        <v>46118.60144140046</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>270</v>
@@ -5876,11 +5876,11 @@
         <v>273</v>
       </c>
       <c r="B75" s="8">
-        <v>46118.66251259259</v>
+        <v>46118.49584592592</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46191.7722621412</v>
+        <v>46191.60559547454</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>274</v>
@@ -5939,11 +5939,11 @@
         <v>275</v>
       </c>
       <c r="B76" s="5">
-        <v>46118.662521377315</v>
+        <v>46118.49585471065</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46118.76362347222</v>
+        <v>46118.59695680556</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>276</v>
@@ -5986,11 +5986,11 @@
         <v>278</v>
       </c>
       <c r="B77" s="8">
-        <v>46118.66252565972</v>
+        <v>46118.495858993054</v>
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46118.7682625</v>
+        <v>46118.60159583333</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>279</v>
@@ -6049,11 +6049,11 @@
         <v>281</v>
       </c>
       <c r="B78" s="5">
-        <v>46118.662532013885</v>
+        <v>46118.49586534723</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46118.76825962963</v>
+        <v>46118.601592962965</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>282</v>

--- a/data/50001533 - GESVIAL.xlsx
+++ b/data/50001533 - GESVIAL.xlsx
@@ -1577,13 +1577,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46118.495183391206</v>
+        <v>46118.66185005787</v>
       </c>
       <c r="C4" s="5">
-        <v>46129.394169652776</v>
+        <v>46129.56083631945</v>
       </c>
       <c r="D4" s="5">
-        <v>46147.847120624996</v>
+        <v>46148.01378729167</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1626,13 +1626,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46118.49534550926</v>
+        <v>46118.662012175926</v>
       </c>
       <c r="C5" s="8">
-        <v>46129.393189814815</v>
+        <v>46129.559856481486</v>
       </c>
       <c r="D5" s="8">
-        <v>46133.710560625</v>
+        <v>46133.87722729167</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1691,13 +1691,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46118.49534890046</v>
+        <v>46118.662015567126</v>
       </c>
       <c r="C6" s="5">
-        <v>46129.39325076389</v>
+        <v>46129.55991743055</v>
       </c>
       <c r="D6" s="5">
-        <v>46129.393267453706</v>
+        <v>46129.55993412037</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -1756,13 +1756,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="8">
-        <v>46118.49535210648</v>
+        <v>46118.662018773146</v>
       </c>
       <c r="C7" s="8">
-        <v>46129.39360674769</v>
+        <v>46129.56027341435</v>
       </c>
       <c r="D7" s="8">
-        <v>46129.39362375</v>
+        <v>46129.560290416666</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>38</v>
@@ -1821,13 +1821,13 @@
         <v>40</v>
       </c>
       <c r="B8" s="5">
-        <v>46118.49535528936</v>
+        <v>46118.66202195601</v>
       </c>
       <c r="C8" s="5">
-        <v>46129.39401967592</v>
+        <v>46129.56068634259</v>
       </c>
       <c r="D8" s="5">
-        <v>46129.39403539352</v>
+        <v>46129.56070206019</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>41</v>
@@ -1886,13 +1886,13 @@
         <v>44</v>
       </c>
       <c r="B9" s="8">
-        <v>46118.495359479166</v>
+        <v>46118.66202614583</v>
       </c>
       <c r="C9" s="8">
-        <v>46129.39415508102</v>
+        <v>46129.560821747684</v>
       </c>
       <c r="D9" s="8">
-        <v>46156.67195390046</v>
+        <v>46156.83862056713</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>45</v>
@@ -1951,11 +1951,11 @@
         <v>47</v>
       </c>
       <c r="B10" s="5">
-        <v>46118.49518951389</v>
+        <v>46118.66185618055</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46196.72905799768</v>
+        <v>46196.895724664355</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>48</v>
@@ -1998,13 +1998,13 @@
         <v>50</v>
       </c>
       <c r="B11" s="8">
-        <v>46118.495363379625</v>
+        <v>46118.6620300463</v>
       </c>
       <c r="C11" s="8">
-        <v>46129.40463276621</v>
+        <v>46129.57129943287</v>
       </c>
       <c r="D11" s="8">
-        <v>46129.40464815972</v>
+        <v>46129.57131482639</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>51</v>
@@ -2063,13 +2063,13 @@
         <v>56</v>
       </c>
       <c r="B12" s="5">
-        <v>46118.49536912037</v>
+        <v>46118.66203578704</v>
       </c>
       <c r="C12" s="5">
-        <v>46196.72904978009</v>
+        <v>46196.89571644676</v>
       </c>
       <c r="D12" s="5">
-        <v>46196.72905206018</v>
+        <v>46196.89571872685</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>57</v>
@@ -2128,13 +2128,13 @@
         <v>60</v>
       </c>
       <c r="B13" s="8">
-        <v>46118.495194097224</v>
+        <v>46118.66186076389</v>
       </c>
       <c r="C13" s="8">
-        <v>46193.395125625</v>
+        <v>46193.56179229167</v>
       </c>
       <c r="D13" s="8">
-        <v>46193.39512796296</v>
+        <v>46193.561794629626</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>61</v>
@@ -2177,13 +2177,13 @@
         <v>63</v>
       </c>
       <c r="B14" s="5">
-        <v>46118.49537506944</v>
+        <v>46118.66204173611</v>
       </c>
       <c r="C14" s="5">
-        <v>46129.395261620375</v>
+        <v>46129.56192828703</v>
       </c>
       <c r="D14" s="5">
-        <v>46191.60559553241</v>
+        <v>46191.77226219907</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>64</v>
@@ -2242,13 +2242,13 @@
         <v>67</v>
       </c>
       <c r="B15" s="8">
-        <v>46118.49538085648</v>
+        <v>46118.66204752315</v>
       </c>
       <c r="C15" s="8">
-        <v>46129.39527212963</v>
+        <v>46129.561938796294</v>
       </c>
       <c r="D15" s="8">
-        <v>46191.60559559028</v>
+        <v>46191.77226225694</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>68</v>
@@ -2307,13 +2307,13 @@
         <v>71</v>
       </c>
       <c r="B16" s="5">
-        <v>46118.49538628472</v>
+        <v>46118.66205295139</v>
       </c>
       <c r="C16" s="5">
-        <v>46129.40045137731</v>
+        <v>46129.56711804398</v>
       </c>
       <c r="D16" s="5">
-        <v>46191.60559547454</v>
+        <v>46191.7722621412</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>72</v>
@@ -2372,13 +2372,13 @@
         <v>75</v>
       </c>
       <c r="B17" s="8">
-        <v>46118.495199490746</v>
+        <v>46118.6618661574</v>
       </c>
       <c r="C17" s="8">
-        <v>46184.563075972226</v>
+        <v>46184.72974263889</v>
       </c>
       <c r="D17" s="8">
-        <v>46184.563077349536</v>
+        <v>46184.72974401621</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>76</v>
@@ -2421,13 +2421,13 @@
         <v>78</v>
       </c>
       <c r="B18" s="5">
-        <v>46118.495399872685</v>
+        <v>46118.66206653936</v>
       </c>
       <c r="C18" s="5">
-        <v>46129.395672175924</v>
+        <v>46129.56233884259</v>
       </c>
       <c r="D18" s="5">
-        <v>46129.3956940625</v>
+        <v>46129.56236072916</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>79</v>
@@ -2486,13 +2486,13 @@
         <v>82</v>
       </c>
       <c r="B19" s="8">
-        <v>46118.49540508102</v>
+        <v>46118.66207174768</v>
       </c>
       <c r="C19" s="8">
-        <v>46129.39567921296</v>
+        <v>46129.56234587963</v>
       </c>
       <c r="D19" s="8">
-        <v>46129.39570070602</v>
+        <v>46129.56236737268</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>83</v>
@@ -2551,13 +2551,13 @@
         <v>85</v>
       </c>
       <c r="B20" s="5">
-        <v>46118.49541042824</v>
+        <v>46118.66207709491</v>
       </c>
       <c r="C20" s="5">
-        <v>46129.40467122685</v>
+        <v>46129.57133789352</v>
       </c>
       <c r="D20" s="5">
-        <v>46129.40468762731</v>
+        <v>46129.57135429398</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>86</v>
@@ -2616,13 +2616,13 @@
         <v>89</v>
       </c>
       <c r="B21" s="8">
-        <v>46118.49541564815</v>
+        <v>46118.66208231481</v>
       </c>
       <c r="C21" s="8">
-        <v>46183.71343438658</v>
+        <v>46183.88010105324</v>
       </c>
       <c r="D21" s="8">
-        <v>46183.71343625</v>
+        <v>46183.880102916664</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>90</v>
@@ -2681,13 +2681,13 @@
         <v>94</v>
       </c>
       <c r="B22" s="5">
-        <v>46118.49542085648</v>
+        <v>46118.662087523146</v>
       </c>
       <c r="C22" s="5">
-        <v>46183.72138519676</v>
+        <v>46183.888051863425</v>
       </c>
       <c r="D22" s="5">
-        <v>46183.721584768515</v>
+        <v>46183.888251435186</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>95</v>
@@ -2746,13 +2746,13 @@
         <v>100</v>
       </c>
       <c r="B23" s="8">
-        <v>46118.49520528935</v>
+        <v>46118.66187195602</v>
       </c>
       <c r="C23" s="8">
-        <v>46184.5195800463</v>
+        <v>46184.68624671296</v>
       </c>
       <c r="D23" s="8">
-        <v>46184.51958140046</v>
+        <v>46184.686248067126</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>101</v>
@@ -2795,13 +2795,13 @@
         <v>103</v>
       </c>
       <c r="B24" s="5">
-        <v>46118.49542702547</v>
+        <v>46118.662093692124</v>
       </c>
       <c r="C24" s="5">
-        <v>46182.509780231485</v>
+        <v>46182.67644689815</v>
       </c>
       <c r="D24" s="5">
-        <v>46182.50978262731</v>
+        <v>46182.676449293984</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>104</v>
@@ -2860,13 +2860,13 @@
         <v>109</v>
       </c>
       <c r="B25" s="8">
-        <v>46118.495431793985</v>
+        <v>46118.66209846065</v>
       </c>
       <c r="C25" s="8">
-        <v>46174.4590187037</v>
+        <v>46174.62568537037</v>
       </c>
       <c r="D25" s="8">
-        <v>46174.45902023149</v>
+        <v>46174.62568689814</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>110</v>
@@ -2915,13 +2915,13 @@
         <v>112</v>
       </c>
       <c r="B26" s="5">
-        <v>46118.49543604167</v>
+        <v>46118.66210270833</v>
       </c>
       <c r="C26" s="5">
-        <v>46182.476623263894</v>
+        <v>46182.64328993055</v>
       </c>
       <c r="D26" s="5">
-        <v>46182.47662475695</v>
+        <v>46182.64329142361</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>113</v>
@@ -2970,13 +2970,13 @@
         <v>115</v>
       </c>
       <c r="B27" s="8">
-        <v>46118.4954403125</v>
+        <v>46118.662106979165</v>
       </c>
       <c r="C27" s="8">
-        <v>46182.47440028936</v>
+        <v>46182.641066956014</v>
       </c>
       <c r="D27" s="8">
-        <v>46182.47440253472</v>
+        <v>46182.64106920139</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>116</v>
@@ -3035,13 +3035,13 @@
         <v>118</v>
       </c>
       <c r="B28" s="5">
-        <v>46118.49544542824</v>
+        <v>46118.662112094906</v>
       </c>
       <c r="C28" s="5">
-        <v>46174.459855</v>
+        <v>46174.626521666665</v>
       </c>
       <c r="D28" s="5">
-        <v>46174.45985648148</v>
+        <v>46174.62652314815</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>119</v>
@@ -3096,13 +3096,13 @@
         <v>121</v>
       </c>
       <c r="B29" s="8">
-        <v>46118.4954502662</v>
+        <v>46118.66211693287</v>
       </c>
       <c r="C29" s="8">
-        <v>46174.45996375</v>
+        <v>46174.626630416664</v>
       </c>
       <c r="D29" s="8">
-        <v>46174.45996519676</v>
+        <v>46174.62663186343</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>122</v>
@@ -3157,13 +3157,13 @@
         <v>124</v>
       </c>
       <c r="B30" s="5">
-        <v>46118.495455358796</v>
+        <v>46118.66212202546</v>
       </c>
       <c r="C30" s="5">
-        <v>46184.519414780094</v>
+        <v>46184.68608144676</v>
       </c>
       <c r="D30" s="5">
-        <v>46184.519416574076</v>
+        <v>46184.68608324074</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>125</v>
@@ -3222,13 +3222,13 @@
         <v>127</v>
       </c>
       <c r="B31" s="8">
-        <v>46118.495460011574</v>
+        <v>46118.662126678246</v>
       </c>
       <c r="C31" s="8">
-        <v>46184.519052372685</v>
+        <v>46184.68571903935</v>
       </c>
       <c r="D31" s="8">
-        <v>46184.519054143515</v>
+        <v>46184.68572081019</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>128</v>
@@ -3283,13 +3283,13 @@
         <v>130</v>
       </c>
       <c r="B32" s="5">
-        <v>46118.495464594904</v>
+        <v>46118.662131261575</v>
       </c>
       <c r="C32" s="5">
-        <v>46184.519122233796</v>
+        <v>46184.68578890046</v>
       </c>
       <c r="D32" s="5">
-        <v>46184.51912386574</v>
+        <v>46184.68579053241</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>131</v>
@@ -3344,13 +3344,13 @@
         <v>133</v>
       </c>
       <c r="B33" s="8">
-        <v>46118.49551706019</v>
+        <v>46118.66218372685</v>
       </c>
       <c r="C33" s="8">
-        <v>46156.654673321755</v>
+        <v>46156.821339988426</v>
       </c>
       <c r="D33" s="8">
-        <v>46169.657316111116</v>
+        <v>46169.82398277777</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>134</v>
@@ -3409,13 +3409,13 @@
         <v>136</v>
       </c>
       <c r="B34" s="5">
-        <v>46118.4955234375</v>
+        <v>46118.662190104165</v>
       </c>
       <c r="C34" s="5">
-        <v>46134.624486030094</v>
+        <v>46134.79115269676</v>
       </c>
       <c r="D34" s="5">
-        <v>46169.65732769676</v>
+        <v>46169.823994363425</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>137</v>
@@ -3470,13 +3470,13 @@
         <v>139</v>
       </c>
       <c r="B35" s="8">
-        <v>46118.49552902778</v>
+        <v>46118.662195694444</v>
       </c>
       <c r="C35" s="8">
-        <v>46155.736021006946</v>
+        <v>46155.90268767361</v>
       </c>
       <c r="D35" s="8">
-        <v>46169.657349201385</v>
+        <v>46169.82401586806</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>140</v>
@@ -3531,13 +3531,13 @@
         <v>142</v>
       </c>
       <c r="B36" s="5">
-        <v>46118.495534155096</v>
+        <v>46118.66220082176</v>
       </c>
       <c r="C36" s="5">
-        <v>46134.624528726854</v>
+        <v>46134.79119539352</v>
       </c>
       <c r="D36" s="5">
-        <v>46169.65736949074</v>
+        <v>46169.824036157406</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>143</v>
@@ -3592,13 +3592,13 @@
         <v>145</v>
       </c>
       <c r="B37" s="8">
-        <v>46118.495539675925</v>
+        <v>46118.66220634259</v>
       </c>
       <c r="C37" s="8">
-        <v>46184.51943712963</v>
+        <v>46184.686103796295</v>
       </c>
       <c r="D37" s="8">
-        <v>46184.519438564814</v>
+        <v>46184.68610523148</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>146</v>
@@ -3657,13 +3657,13 @@
         <v>149</v>
       </c>
       <c r="B38" s="5">
-        <v>46118.495545682876</v>
+        <v>46118.66221234953</v>
       </c>
       <c r="C38" s="5">
-        <v>46184.36428194444</v>
+        <v>46184.53094861111</v>
       </c>
       <c r="D38" s="5">
-        <v>46184.36428409722</v>
+        <v>46184.53095076389</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>150</v>
@@ -3718,13 +3718,13 @@
         <v>152</v>
       </c>
       <c r="B39" s="8">
-        <v>46118.495549907406</v>
+        <v>46118.66221657407</v>
       </c>
       <c r="C39" s="8">
-        <v>46184.36495873843</v>
+        <v>46184.53162540509</v>
       </c>
       <c r="D39" s="8">
-        <v>46184.36496005787</v>
+        <v>46184.531626724536</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>151</v>
@@ -3779,11 +3779,11 @@
         <v>154</v>
       </c>
       <c r="B40" s="5">
-        <v>46118.495554305555</v>
+        <v>46118.662220972226</v>
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="5">
-        <v>46198.402797372684</v>
+        <v>46198.56946403935</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>155</v>
@@ -3826,13 +3826,13 @@
         <v>157</v>
       </c>
       <c r="B41" s="8">
-        <v>46118.495558553244</v>
+        <v>46118.66222521991</v>
       </c>
       <c r="C41" s="8">
-        <v>46129.40051568287</v>
+        <v>46129.567182349536</v>
       </c>
       <c r="D41" s="8">
-        <v>46129.40751229167</v>
+        <v>46129.57417895833</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>158</v>
@@ -3891,13 +3891,13 @@
         <v>162</v>
       </c>
       <c r="B42" s="5">
-        <v>46118.495565034726</v>
+        <v>46118.66223170139</v>
       </c>
       <c r="C42" s="5">
-        <v>46134.633600057874</v>
+        <v>46134.80026672454</v>
       </c>
       <c r="D42" s="5">
-        <v>46134.63361603009</v>
+        <v>46134.80028269676</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>163</v>
@@ -3956,13 +3956,13 @@
         <v>168</v>
       </c>
       <c r="B43" s="8">
-        <v>46118.49557270833</v>
+        <v>46118.662239375</v>
       </c>
       <c r="C43" s="8">
-        <v>46134.63372706018</v>
+        <v>46134.80039372685</v>
       </c>
       <c r="D43" s="8">
-        <v>46134.633741701386</v>
+        <v>46134.80040836806</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>98</v>
@@ -4019,13 +4019,13 @@
         <v>170</v>
       </c>
       <c r="B44" s="5">
-        <v>46118.49557863426</v>
+        <v>46118.662245300926</v>
       </c>
       <c r="C44" s="5">
-        <v>46198.40279047454</v>
+        <v>46198.5694571412</v>
       </c>
       <c r="D44" s="5">
-        <v>46198.4027927662</v>
+        <v>46198.56945943287</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>171</v>
@@ -4084,13 +4084,13 @@
         <v>176</v>
       </c>
       <c r="B45" s="8">
-        <v>46118.49558318287</v>
+        <v>46118.66224984954</v>
       </c>
       <c r="C45" s="8">
-        <v>46184.520520185186</v>
+        <v>46184.68718685185</v>
       </c>
       <c r="D45" s="8">
-        <v>46184.520521620376</v>
+        <v>46184.68718828703</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>177</v>
@@ -4133,13 +4133,13 @@
         <v>179</v>
       </c>
       <c r="B46" s="5">
-        <v>46118.495586840276</v>
+        <v>46118.66225350695</v>
       </c>
       <c r="C46" s="5">
-        <v>46184.52003991898</v>
+        <v>46184.68670658565</v>
       </c>
       <c r="D46" s="5">
-        <v>46184.52025868055</v>
+        <v>46184.686925347225</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>153</v>
@@ -4198,13 +4198,13 @@
         <v>183</v>
       </c>
       <c r="B47" s="8">
-        <v>46118.49559196759</v>
+        <v>46118.66225863426</v>
       </c>
       <c r="C47" s="8">
-        <v>46184.520299317126</v>
+        <v>46184.6869659838</v>
       </c>
       <c r="D47" s="8">
-        <v>46184.52047996528</v>
+        <v>46184.68714663194</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>184</v>
@@ -4263,13 +4263,13 @@
         <v>188</v>
       </c>
       <c r="B48" s="5">
-        <v>46118.49559715278</v>
+        <v>46118.662263819446</v>
       </c>
       <c r="C48" s="5">
-        <v>46193.88967060186</v>
+        <v>46194.056337268514</v>
       </c>
       <c r="D48" s="5">
-        <v>46193.889672453704</v>
+        <v>46194.05633912037</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>189</v>
@@ -4312,13 +4312,13 @@
         <v>191</v>
       </c>
       <c r="B49" s="8">
-        <v>46118.49560084491</v>
+        <v>46118.66226751157</v>
       </c>
       <c r="C49" s="8">
-        <v>46184.52128453704</v>
+        <v>46184.687951203705</v>
       </c>
       <c r="D49" s="8">
-        <v>46184.52128605324</v>
+        <v>46184.687952719905</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>192</v>
@@ -4377,13 +4377,13 @@
         <v>196</v>
       </c>
       <c r="B50" s="5">
-        <v>46118.49560603009</v>
+        <v>46118.66227269676</v>
       </c>
       <c r="C50" s="5">
-        <v>46193.39524637732</v>
+        <v>46193.56191304398</v>
       </c>
       <c r="D50" s="5">
-        <v>46193.39524827546</v>
+        <v>46193.561914942125</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>197</v>
@@ -4442,13 +4442,13 @@
         <v>200</v>
       </c>
       <c r="B51" s="8">
-        <v>46184.52131372685</v>
+        <v>46184.687980393515</v>
       </c>
       <c r="C51" s="8">
-        <v>46184.52255061343</v>
+        <v>46184.68921728009</v>
       </c>
       <c r="D51" s="8">
-        <v>46191.52051372685</v>
+        <v>46191.68718039352</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>201</v>
@@ -4497,13 +4497,13 @@
         <v>202</v>
       </c>
       <c r="B52" s="5">
-        <v>46184.52142638889</v>
+        <v>46184.688093055556</v>
       </c>
       <c r="C52" s="5">
-        <v>46195.53587391204</v>
+        <v>46195.7025405787</v>
       </c>
       <c r="D52" s="5">
-        <v>46195.53587571759</v>
+        <v>46195.70254238426</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>203</v>
@@ -4552,13 +4552,13 @@
         <v>204</v>
       </c>
       <c r="B53" s="8">
-        <v>46184.52150136574</v>
+        <v>46184.68816803241</v>
       </c>
       <c r="C53" s="8">
-        <v>46184.523340844906</v>
+        <v>46184.69000751157</v>
       </c>
       <c r="D53" s="8">
-        <v>46191.52050717593</v>
+        <v>46191.6871738426</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>205</v>
@@ -4607,13 +4607,13 @@
         <v>206</v>
       </c>
       <c r="B54" s="5">
-        <v>46184.52160033565</v>
+        <v>46184.68826700232</v>
       </c>
       <c r="C54" s="5">
-        <v>46184.52365296296</v>
+        <v>46184.69031962963</v>
       </c>
       <c r="D54" s="5">
-        <v>46191.520502326384</v>
+        <v>46191.687168993056</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>207</v>
@@ -4662,13 +4662,13 @@
         <v>208</v>
       </c>
       <c r="B55" s="8">
-        <v>46118.49561196759</v>
+        <v>46118.66227863426</v>
       </c>
       <c r="C55" s="8">
-        <v>46193.39573376157</v>
+        <v>46193.56240042824</v>
       </c>
       <c r="D55" s="8">
-        <v>46193.39573895834</v>
+        <v>46193.562405625</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>209</v>
@@ -4727,13 +4727,13 @@
         <v>212</v>
       </c>
       <c r="B56" s="5">
-        <v>46118.495618217596</v>
+        <v>46118.66228488426</v>
       </c>
       <c r="C56" s="5">
-        <v>46193.889654548606</v>
+        <v>46194.05632121528</v>
       </c>
       <c r="D56" s="5">
-        <v>46193.88965658565</v>
+        <v>46194.05632325231</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>177</v>
@@ -4776,13 +4776,13 @@
         <v>214</v>
       </c>
       <c r="B57" s="8">
-        <v>46118.49562136574</v>
+        <v>46118.66228803241</v>
       </c>
       <c r="C57" s="8">
-        <v>46193.3956787037</v>
+        <v>46193.562345370374</v>
       </c>
       <c r="D57" s="8">
-        <v>46193.395680671296</v>
+        <v>46193.56234733797</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>215</v>
@@ -4841,13 +4841,13 @@
         <v>217</v>
       </c>
       <c r="B58" s="5">
-        <v>46118.49562685185</v>
+        <v>46118.662293518515</v>
       </c>
       <c r="C58" s="5">
-        <v>46193.39530791667</v>
+        <v>46193.56197458333</v>
       </c>
       <c r="D58" s="5">
-        <v>46193.395309837964</v>
+        <v>46193.56197650463</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>58</v>
@@ -4906,13 +4906,13 @@
         <v>219</v>
       </c>
       <c r="B59" s="8">
-        <v>46118.49563322916</v>
+        <v>46118.662299895834</v>
       </c>
       <c r="C59" s="8">
-        <v>46193.39531820602</v>
+        <v>46193.561984872686</v>
       </c>
       <c r="D59" s="8">
-        <v>46193.39532001158</v>
+        <v>46193.561986678236</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>220</v>
@@ -4971,13 +4971,13 @@
         <v>222</v>
       </c>
       <c r="B60" s="5">
-        <v>46118.495688842595</v>
+        <v>46118.66235550926</v>
       </c>
       <c r="C60" s="5">
-        <v>46193.3953305787</v>
+        <v>46193.56199724537</v>
       </c>
       <c r="D60" s="5">
-        <v>46193.39533219907</v>
+        <v>46193.56199886574</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>223</v>
@@ -5036,13 +5036,13 @@
         <v>225</v>
       </c>
       <c r="B61" s="8">
-        <v>46118.49569628472</v>
+        <v>46118.66236295139</v>
       </c>
       <c r="C61" s="8">
-        <v>46193.598368692124</v>
+        <v>46193.765035358796</v>
       </c>
       <c r="D61" s="8">
-        <v>46196.756804930556</v>
+        <v>46196.92347159723</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>226</v>
@@ -5085,13 +5085,13 @@
         <v>228</v>
       </c>
       <c r="B62" s="5">
-        <v>46118.495702071756</v>
+        <v>46118.66236873843</v>
       </c>
       <c r="C62" s="5">
-        <v>46193.445946782405</v>
+        <v>46193.61261344908</v>
       </c>
       <c r="D62" s="5">
-        <v>46196.7553321875</v>
+        <v>46196.921998854166</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>229</v>
@@ -5150,13 +5150,13 @@
         <v>231</v>
       </c>
       <c r="B63" s="8">
-        <v>46118.49570939815</v>
+        <v>46118.662376064814</v>
       </c>
       <c r="C63" s="8">
-        <v>46193.445992037035</v>
+        <v>46193.6126587037</v>
       </c>
       <c r="D63" s="8">
-        <v>46193.44599390046</v>
+        <v>46193.61266056713</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>224</v>
@@ -5215,13 +5215,13 @@
         <v>234</v>
       </c>
       <c r="B64" s="5">
-        <v>46118.4957208912</v>
+        <v>46118.662387557866</v>
       </c>
       <c r="C64" s="5">
-        <v>46193.44601277778</v>
+        <v>46193.61267944444</v>
       </c>
       <c r="D64" s="5">
-        <v>46193.44601434028</v>
+        <v>46193.61268100694</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>235</v>
@@ -5280,13 +5280,13 @@
         <v>237</v>
       </c>
       <c r="B65" s="8">
-        <v>46118.495732129624</v>
+        <v>46118.662398796296</v>
       </c>
       <c r="C65" s="8">
-        <v>46193.44607049768</v>
+        <v>46193.61273716435</v>
       </c>
       <c r="D65" s="8">
-        <v>46193.44607288194</v>
+        <v>46193.61273954861</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>238</v>
@@ -5345,13 +5345,13 @@
         <v>240</v>
       </c>
       <c r="B66" s="5">
-        <v>46118.495743182866</v>
+        <v>46118.66240984954</v>
       </c>
       <c r="C66" s="5">
-        <v>46193.59884520833</v>
+        <v>46193.765511875</v>
       </c>
       <c r="D66" s="5">
-        <v>46193.59885226852</v>
+        <v>46193.765518935186</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>174</v>
@@ -5408,13 +5408,13 @@
         <v>243</v>
       </c>
       <c r="B67" s="8">
-        <v>46118.49575346065</v>
+        <v>46118.662420127315</v>
       </c>
       <c r="C67" s="8">
-        <v>46196.75679758102</v>
+        <v>46196.92346424768</v>
       </c>
       <c r="D67" s="8">
-        <v>46198.402798807874</v>
+        <v>46198.56946547454</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>244</v>
@@ -5473,11 +5473,11 @@
         <v>246</v>
       </c>
       <c r="B68" s="5">
-        <v>46118.49576103009</v>
+        <v>46118.66242769676</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46196.75640028935</v>
+        <v>46196.92306695602</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>247</v>
@@ -5520,11 +5520,11 @@
         <v>249</v>
       </c>
       <c r="B69" s="8">
-        <v>46118.49576510416</v>
+        <v>46118.662431770834</v>
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46196.75680685185</v>
+        <v>46196.92347351852</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>250</v>
@@ -5581,11 +5581,11 @@
         <v>254</v>
       </c>
       <c r="B70" s="5">
-        <v>46118.49577158564</v>
+        <v>46118.662438252315</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46196.72905917824</v>
+        <v>46196.89572584491</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>255</v>
@@ -5642,13 +5642,13 @@
         <v>258</v>
       </c>
       <c r="B71" s="8">
-        <v>46118.49578482639</v>
+        <v>46118.66245149306</v>
       </c>
       <c r="C71" s="8">
-        <v>46196.75639109954</v>
+        <v>46196.9230577662</v>
       </c>
       <c r="D71" s="8">
-        <v>46196.756393668984</v>
+        <v>46196.92306033565</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>259</v>
@@ -5705,11 +5705,11 @@
         <v>263</v>
       </c>
       <c r="B72" s="5">
-        <v>46118.49579103009</v>
+        <v>46118.66245769676</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46196.756401736115</v>
+        <v>46196.92306840278</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>264</v>
@@ -5766,11 +5766,11 @@
         <v>266</v>
       </c>
       <c r="B73" s="8">
-        <v>46118.49579800926</v>
+        <v>46118.66246467593</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46118.5961819213</v>
+        <v>46118.76284858796</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>267</v>
@@ -5813,11 +5813,11 @@
         <v>269</v>
       </c>
       <c r="B74" s="5">
-        <v>46118.495801296296</v>
+        <v>46118.66246796296</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46118.60144140046</v>
+        <v>46118.76810806713</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>270</v>
@@ -5876,11 +5876,11 @@
         <v>273</v>
       </c>
       <c r="B75" s="8">
-        <v>46118.49584592592</v>
+        <v>46118.66251259259</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46191.60559547454</v>
+        <v>46191.7722621412</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>274</v>
@@ -5939,11 +5939,11 @@
         <v>275</v>
       </c>
       <c r="B76" s="5">
-        <v>46118.49585471065</v>
+        <v>46118.662521377315</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46118.59695680556</v>
+        <v>46118.76362347222</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>276</v>
@@ -5986,11 +5986,11 @@
         <v>278</v>
       </c>
       <c r="B77" s="8">
-        <v>46118.495858993054</v>
+        <v>46118.66252565972</v>
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46118.60159583333</v>
+        <v>46118.7682625</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>279</v>
@@ -6049,11 +6049,11 @@
         <v>281</v>
       </c>
       <c r="B78" s="5">
-        <v>46118.49586534723</v>
+        <v>46118.662532013885</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46118.601592962965</v>
+        <v>46118.76825962963</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>282</v>

--- a/data/50001533 - GESVIAL.xlsx
+++ b/data/50001533 - GESVIAL.xlsx
@@ -5524,7 +5524,7 @@
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46196.92347351852</v>
+        <v>46203.57157956019</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>250</v>

--- a/data/50001533 - GESVIAL.xlsx
+++ b/data/50001533 - GESVIAL.xlsx
@@ -5477,7 +5477,7 @@
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46196.92306695602</v>
+        <v>46203.815654895836</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>247</v>
@@ -5522,9 +5522,11 @@
       <c r="B69" s="8">
         <v>46118.662431770834</v>
       </c>
-      <c r="C69" s="9"/>
+      <c r="C69" s="8">
+        <v>46203.81564377315</v>
+      </c>
       <c r="D69" s="8">
-        <v>46203.57157956019</v>
+        <v>46203.8156465625</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>250</v>
@@ -5585,7 +5587,7 @@
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46196.89572584491</v>
+        <v>46203.81565671296</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>255</v>

--- a/data/50001533 - GESVIAL.xlsx
+++ b/data/50001533 - GESVIAL.xlsx
@@ -1953,9 +1953,11 @@
       <c r="B10" s="5">
         <v>46118.66185618055</v>
       </c>
-      <c r="C10" s="6"/>
+      <c r="C10" s="5">
+        <v>46204.65215401621</v>
+      </c>
       <c r="D10" s="5">
-        <v>46196.895724664355</v>
+        <v>46204.65215631944</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>48</v>
@@ -3781,9 +3783,11 @@
       <c r="B40" s="5">
         <v>46118.662220972226</v>
       </c>
-      <c r="C40" s="6"/>
+      <c r="C40" s="5">
+        <v>46204.65218209491</v>
+      </c>
       <c r="D40" s="5">
-        <v>46198.56946403935</v>
+        <v>46204.652183645834</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>155</v>

--- a/data/50001533 - GESVIAL.xlsx
+++ b/data/50001533 - GESVIAL.xlsx
@@ -5046,7 +5046,7 @@
         <v>46193.765035358796</v>
       </c>
       <c r="D61" s="8">
-        <v>46196.92347159723</v>
+        <v>46204.900153703704</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>226</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46203.815654895836</v>
+        <v>46204.897786747686</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>247</v>
@@ -5530,7 +5530,7 @@
         <v>46203.81564377315</v>
       </c>
       <c r="D69" s="8">
-        <v>46203.8156465625</v>
+        <v>46204.900270983795</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>250</v>
@@ -5578,8 +5578,8 @@
       <c r="T69" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="U69" s="11" t="s">
-        <v>108</v>
+      <c r="U69" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
@@ -5589,9 +5589,11 @@
       <c r="B70" s="5">
         <v>46118.662438252315</v>
       </c>
-      <c r="C70" s="6"/>
+      <c r="C70" s="5">
+        <v>46204.89777927083</v>
+      </c>
       <c r="D70" s="5">
-        <v>46203.81565671296</v>
+        <v>46204.90025034722</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>255</v>
@@ -5639,8 +5641,8 @@
       <c r="T70" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="U70" s="11" t="s">
-        <v>108</v>
+      <c r="U70" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
@@ -5654,7 +5656,7 @@
         <v>46196.9230577662</v>
       </c>
       <c r="D71" s="8">
-        <v>46196.92306033565</v>
+        <v>46204.900126967594</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>259</v>
@@ -5702,8 +5704,8 @@
       <c r="T71" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="U71" s="11" t="s">
-        <v>108</v>
+      <c r="U71" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001533 - GESVIAL.xlsx
+++ b/data/50001533 - GESVIAL.xlsx
@@ -1577,13 +1577,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46118.66185005787</v>
+        <v>46118.495183391206</v>
       </c>
       <c r="C4" s="5">
-        <v>46129.56083631945</v>
+        <v>46129.394169652776</v>
       </c>
       <c r="D4" s="5">
-        <v>46148.01378729167</v>
+        <v>46147.847120624996</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1626,13 +1626,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46118.662012175926</v>
+        <v>46118.49534550926</v>
       </c>
       <c r="C5" s="8">
-        <v>46129.559856481486</v>
+        <v>46129.393189814815</v>
       </c>
       <c r="D5" s="8">
-        <v>46133.87722729167</v>
+        <v>46133.710560625</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1691,13 +1691,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46118.662015567126</v>
+        <v>46118.49534890046</v>
       </c>
       <c r="C6" s="5">
-        <v>46129.55991743055</v>
+        <v>46129.39325076389</v>
       </c>
       <c r="D6" s="5">
-        <v>46129.55993412037</v>
+        <v>46129.393267453706</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -1756,13 +1756,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="8">
-        <v>46118.662018773146</v>
+        <v>46118.49535210648</v>
       </c>
       <c r="C7" s="8">
-        <v>46129.56027341435</v>
+        <v>46129.39360674769</v>
       </c>
       <c r="D7" s="8">
-        <v>46129.560290416666</v>
+        <v>46129.39362375</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>38</v>
@@ -1821,13 +1821,13 @@
         <v>40</v>
       </c>
       <c r="B8" s="5">
-        <v>46118.66202195601</v>
+        <v>46118.49535528936</v>
       </c>
       <c r="C8" s="5">
-        <v>46129.56068634259</v>
+        <v>46129.39401967592</v>
       </c>
       <c r="D8" s="5">
-        <v>46129.56070206019</v>
+        <v>46129.39403539352</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>41</v>
@@ -1886,13 +1886,13 @@
         <v>44</v>
       </c>
       <c r="B9" s="8">
-        <v>46118.66202614583</v>
+        <v>46118.495359479166</v>
       </c>
       <c r="C9" s="8">
-        <v>46129.560821747684</v>
+        <v>46129.39415508102</v>
       </c>
       <c r="D9" s="8">
-        <v>46156.83862056713</v>
+        <v>46156.67195390046</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>45</v>
@@ -1951,13 +1951,13 @@
         <v>47</v>
       </c>
       <c r="B10" s="5">
-        <v>46118.66185618055</v>
+        <v>46118.49518951389</v>
       </c>
       <c r="C10" s="5">
-        <v>46204.65215401621</v>
+        <v>46204.485487349535</v>
       </c>
       <c r="D10" s="5">
-        <v>46204.65215631944</v>
+        <v>46204.48548965278</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>48</v>
@@ -2000,13 +2000,13 @@
         <v>50</v>
       </c>
       <c r="B11" s="8">
-        <v>46118.6620300463</v>
+        <v>46118.495363379625</v>
       </c>
       <c r="C11" s="8">
-        <v>46129.57129943287</v>
+        <v>46129.40463276621</v>
       </c>
       <c r="D11" s="8">
-        <v>46129.57131482639</v>
+        <v>46129.40464815972</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>51</v>
@@ -2065,13 +2065,13 @@
         <v>56</v>
       </c>
       <c r="B12" s="5">
-        <v>46118.66203578704</v>
+        <v>46118.49536912037</v>
       </c>
       <c r="C12" s="5">
-        <v>46196.89571644676</v>
+        <v>46196.72904978009</v>
       </c>
       <c r="D12" s="5">
-        <v>46196.89571872685</v>
+        <v>46196.72905206018</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>57</v>
@@ -2130,13 +2130,13 @@
         <v>60</v>
       </c>
       <c r="B13" s="8">
-        <v>46118.66186076389</v>
+        <v>46118.495194097224</v>
       </c>
       <c r="C13" s="8">
-        <v>46193.56179229167</v>
+        <v>46193.395125625</v>
       </c>
       <c r="D13" s="8">
-        <v>46193.561794629626</v>
+        <v>46193.39512796296</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>61</v>
@@ -2179,13 +2179,13 @@
         <v>63</v>
       </c>
       <c r="B14" s="5">
-        <v>46118.66204173611</v>
+        <v>46118.49537506944</v>
       </c>
       <c r="C14" s="5">
-        <v>46129.56192828703</v>
+        <v>46129.395261620375</v>
       </c>
       <c r="D14" s="5">
-        <v>46191.77226219907</v>
+        <v>46191.60559553241</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>64</v>
@@ -2244,13 +2244,13 @@
         <v>67</v>
       </c>
       <c r="B15" s="8">
-        <v>46118.66204752315</v>
+        <v>46118.49538085648</v>
       </c>
       <c r="C15" s="8">
-        <v>46129.561938796294</v>
+        <v>46129.39527212963</v>
       </c>
       <c r="D15" s="8">
-        <v>46191.77226225694</v>
+        <v>46191.60559559028</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>68</v>
@@ -2309,13 +2309,13 @@
         <v>71</v>
       </c>
       <c r="B16" s="5">
-        <v>46118.66205295139</v>
+        <v>46118.49538628472</v>
       </c>
       <c r="C16" s="5">
-        <v>46129.56711804398</v>
+        <v>46129.40045137731</v>
       </c>
       <c r="D16" s="5">
-        <v>46191.7722621412</v>
+        <v>46191.60559547454</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>72</v>
@@ -2374,13 +2374,13 @@
         <v>75</v>
       </c>
       <c r="B17" s="8">
-        <v>46118.6618661574</v>
+        <v>46118.495199490746</v>
       </c>
       <c r="C17" s="8">
-        <v>46184.72974263889</v>
+        <v>46184.563075972226</v>
       </c>
       <c r="D17" s="8">
-        <v>46184.72974401621</v>
+        <v>46184.563077349536</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>76</v>
@@ -2423,13 +2423,13 @@
         <v>78</v>
       </c>
       <c r="B18" s="5">
-        <v>46118.66206653936</v>
+        <v>46118.495399872685</v>
       </c>
       <c r="C18" s="5">
-        <v>46129.56233884259</v>
+        <v>46129.395672175924</v>
       </c>
       <c r="D18" s="5">
-        <v>46129.56236072916</v>
+        <v>46129.3956940625</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>79</v>
@@ -2488,13 +2488,13 @@
         <v>82</v>
       </c>
       <c r="B19" s="8">
-        <v>46118.66207174768</v>
+        <v>46118.49540508102</v>
       </c>
       <c r="C19" s="8">
-        <v>46129.56234587963</v>
+        <v>46129.39567921296</v>
       </c>
       <c r="D19" s="8">
-        <v>46129.56236737268</v>
+        <v>46129.39570070602</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>83</v>
@@ -2553,13 +2553,13 @@
         <v>85</v>
       </c>
       <c r="B20" s="5">
-        <v>46118.66207709491</v>
+        <v>46118.49541042824</v>
       </c>
       <c r="C20" s="5">
-        <v>46129.57133789352</v>
+        <v>46129.40467122685</v>
       </c>
       <c r="D20" s="5">
-        <v>46129.57135429398</v>
+        <v>46129.40468762731</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>86</v>
@@ -2618,13 +2618,13 @@
         <v>89</v>
       </c>
       <c r="B21" s="8">
-        <v>46118.66208231481</v>
+        <v>46118.49541564815</v>
       </c>
       <c r="C21" s="8">
-        <v>46183.88010105324</v>
+        <v>46183.71343438658</v>
       </c>
       <c r="D21" s="8">
-        <v>46183.880102916664</v>
+        <v>46183.71343625</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>90</v>
@@ -2683,13 +2683,13 @@
         <v>94</v>
       </c>
       <c r="B22" s="5">
-        <v>46118.662087523146</v>
+        <v>46118.49542085648</v>
       </c>
       <c r="C22" s="5">
-        <v>46183.888051863425</v>
+        <v>46183.72138519676</v>
       </c>
       <c r="D22" s="5">
-        <v>46183.888251435186</v>
+        <v>46183.721584768515</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>95</v>
@@ -2748,13 +2748,13 @@
         <v>100</v>
       </c>
       <c r="B23" s="8">
-        <v>46118.66187195602</v>
+        <v>46118.49520528935</v>
       </c>
       <c r="C23" s="8">
-        <v>46184.68624671296</v>
+        <v>46184.5195800463</v>
       </c>
       <c r="D23" s="8">
-        <v>46184.686248067126</v>
+        <v>46184.51958140046</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>101</v>
@@ -2797,13 +2797,13 @@
         <v>103</v>
       </c>
       <c r="B24" s="5">
-        <v>46118.662093692124</v>
+        <v>46118.49542702547</v>
       </c>
       <c r="C24" s="5">
-        <v>46182.67644689815</v>
+        <v>46182.509780231485</v>
       </c>
       <c r="D24" s="5">
-        <v>46182.676449293984</v>
+        <v>46182.50978262731</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>104</v>
@@ -2862,13 +2862,13 @@
         <v>109</v>
       </c>
       <c r="B25" s="8">
-        <v>46118.66209846065</v>
+        <v>46118.495431793985</v>
       </c>
       <c r="C25" s="8">
-        <v>46174.62568537037</v>
+        <v>46174.4590187037</v>
       </c>
       <c r="D25" s="8">
-        <v>46174.62568689814</v>
+        <v>46174.45902023149</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>110</v>
@@ -2917,13 +2917,13 @@
         <v>112</v>
       </c>
       <c r="B26" s="5">
-        <v>46118.66210270833</v>
+        <v>46118.49543604167</v>
       </c>
       <c r="C26" s="5">
-        <v>46182.64328993055</v>
+        <v>46182.476623263894</v>
       </c>
       <c r="D26" s="5">
-        <v>46182.64329142361</v>
+        <v>46182.47662475695</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>113</v>
@@ -2972,13 +2972,13 @@
         <v>115</v>
       </c>
       <c r="B27" s="8">
-        <v>46118.662106979165</v>
+        <v>46118.4954403125</v>
       </c>
       <c r="C27" s="8">
-        <v>46182.641066956014</v>
+        <v>46182.47440028936</v>
       </c>
       <c r="D27" s="8">
-        <v>46182.64106920139</v>
+        <v>46182.47440253472</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>116</v>
@@ -3037,13 +3037,13 @@
         <v>118</v>
       </c>
       <c r="B28" s="5">
-        <v>46118.662112094906</v>
+        <v>46118.49544542824</v>
       </c>
       <c r="C28" s="5">
-        <v>46174.626521666665</v>
+        <v>46174.459855</v>
       </c>
       <c r="D28" s="5">
-        <v>46174.62652314815</v>
+        <v>46174.45985648148</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>119</v>
@@ -3098,13 +3098,13 @@
         <v>121</v>
       </c>
       <c r="B29" s="8">
-        <v>46118.66211693287</v>
+        <v>46118.4954502662</v>
       </c>
       <c r="C29" s="8">
-        <v>46174.626630416664</v>
+        <v>46174.45996375</v>
       </c>
       <c r="D29" s="8">
-        <v>46174.62663186343</v>
+        <v>46174.45996519676</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>122</v>
@@ -3159,13 +3159,13 @@
         <v>124</v>
       </c>
       <c r="B30" s="5">
-        <v>46118.66212202546</v>
+        <v>46118.495455358796</v>
       </c>
       <c r="C30" s="5">
-        <v>46184.68608144676</v>
+        <v>46184.519414780094</v>
       </c>
       <c r="D30" s="5">
-        <v>46184.68608324074</v>
+        <v>46184.519416574076</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>125</v>
@@ -3224,13 +3224,13 @@
         <v>127</v>
       </c>
       <c r="B31" s="8">
-        <v>46118.662126678246</v>
+        <v>46118.495460011574</v>
       </c>
       <c r="C31" s="8">
-        <v>46184.68571903935</v>
+        <v>46184.519052372685</v>
       </c>
       <c r="D31" s="8">
-        <v>46184.68572081019</v>
+        <v>46184.519054143515</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>128</v>
@@ -3285,13 +3285,13 @@
         <v>130</v>
       </c>
       <c r="B32" s="5">
-        <v>46118.662131261575</v>
+        <v>46118.495464594904</v>
       </c>
       <c r="C32" s="5">
-        <v>46184.68578890046</v>
+        <v>46184.519122233796</v>
       </c>
       <c r="D32" s="5">
-        <v>46184.68579053241</v>
+        <v>46184.51912386574</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>131</v>
@@ -3346,13 +3346,13 @@
         <v>133</v>
       </c>
       <c r="B33" s="8">
-        <v>46118.66218372685</v>
+        <v>46118.49551706019</v>
       </c>
       <c r="C33" s="8">
-        <v>46156.821339988426</v>
+        <v>46156.654673321755</v>
       </c>
       <c r="D33" s="8">
-        <v>46169.82398277777</v>
+        <v>46169.657316111116</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>134</v>
@@ -3411,13 +3411,13 @@
         <v>136</v>
       </c>
       <c r="B34" s="5">
-        <v>46118.662190104165</v>
+        <v>46118.4955234375</v>
       </c>
       <c r="C34" s="5">
-        <v>46134.79115269676</v>
+        <v>46134.624486030094</v>
       </c>
       <c r="D34" s="5">
-        <v>46169.823994363425</v>
+        <v>46169.65732769676</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>137</v>
@@ -3472,13 +3472,13 @@
         <v>139</v>
       </c>
       <c r="B35" s="8">
-        <v>46118.662195694444</v>
+        <v>46118.49552902778</v>
       </c>
       <c r="C35" s="8">
-        <v>46155.90268767361</v>
+        <v>46155.736021006946</v>
       </c>
       <c r="D35" s="8">
-        <v>46169.82401586806</v>
+        <v>46169.657349201385</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>140</v>
@@ -3533,13 +3533,13 @@
         <v>142</v>
       </c>
       <c r="B36" s="5">
-        <v>46118.66220082176</v>
+        <v>46118.495534155096</v>
       </c>
       <c r="C36" s="5">
-        <v>46134.79119539352</v>
+        <v>46134.624528726854</v>
       </c>
       <c r="D36" s="5">
-        <v>46169.824036157406</v>
+        <v>46169.65736949074</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>143</v>
@@ -3594,13 +3594,13 @@
         <v>145</v>
       </c>
       <c r="B37" s="8">
-        <v>46118.66220634259</v>
+        <v>46118.495539675925</v>
       </c>
       <c r="C37" s="8">
-        <v>46184.686103796295</v>
+        <v>46184.51943712963</v>
       </c>
       <c r="D37" s="8">
-        <v>46184.68610523148</v>
+        <v>46184.519438564814</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>146</v>
@@ -3659,13 +3659,13 @@
         <v>149</v>
       </c>
       <c r="B38" s="5">
-        <v>46118.66221234953</v>
+        <v>46118.495545682876</v>
       </c>
       <c r="C38" s="5">
-        <v>46184.53094861111</v>
+        <v>46184.36428194444</v>
       </c>
       <c r="D38" s="5">
-        <v>46184.53095076389</v>
+        <v>46184.36428409722</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>150</v>
@@ -3720,13 +3720,13 @@
         <v>152</v>
       </c>
       <c r="B39" s="8">
-        <v>46118.66221657407</v>
+        <v>46118.495549907406</v>
       </c>
       <c r="C39" s="8">
-        <v>46184.53162540509</v>
+        <v>46184.36495873843</v>
       </c>
       <c r="D39" s="8">
-        <v>46184.531626724536</v>
+        <v>46184.36496005787</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>151</v>
@@ -3781,13 +3781,13 @@
         <v>154</v>
       </c>
       <c r="B40" s="5">
-        <v>46118.662220972226</v>
+        <v>46118.495554305555</v>
       </c>
       <c r="C40" s="5">
-        <v>46204.65218209491</v>
+        <v>46204.48551542824</v>
       </c>
       <c r="D40" s="5">
-        <v>46204.652183645834</v>
+        <v>46204.48551697917</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>155</v>
@@ -3830,13 +3830,13 @@
         <v>157</v>
       </c>
       <c r="B41" s="8">
-        <v>46118.66222521991</v>
+        <v>46118.495558553244</v>
       </c>
       <c r="C41" s="8">
-        <v>46129.567182349536</v>
+        <v>46129.40051568287</v>
       </c>
       <c r="D41" s="8">
-        <v>46129.57417895833</v>
+        <v>46129.40751229167</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>158</v>
@@ -3895,13 +3895,13 @@
         <v>162</v>
       </c>
       <c r="B42" s="5">
-        <v>46118.66223170139</v>
+        <v>46118.495565034726</v>
       </c>
       <c r="C42" s="5">
-        <v>46134.80026672454</v>
+        <v>46134.633600057874</v>
       </c>
       <c r="D42" s="5">
-        <v>46134.80028269676</v>
+        <v>46134.63361603009</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>163</v>
@@ -3960,13 +3960,13 @@
         <v>168</v>
       </c>
       <c r="B43" s="8">
-        <v>46118.662239375</v>
+        <v>46118.49557270833</v>
       </c>
       <c r="C43" s="8">
-        <v>46134.80039372685</v>
+        <v>46134.63372706018</v>
       </c>
       <c r="D43" s="8">
-        <v>46134.80040836806</v>
+        <v>46134.633741701386</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>98</v>
@@ -4023,13 +4023,13 @@
         <v>170</v>
       </c>
       <c r="B44" s="5">
-        <v>46118.662245300926</v>
+        <v>46118.49557863426</v>
       </c>
       <c r="C44" s="5">
-        <v>46198.5694571412</v>
+        <v>46198.40279047454</v>
       </c>
       <c r="D44" s="5">
-        <v>46198.56945943287</v>
+        <v>46198.4027927662</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>171</v>
@@ -4088,13 +4088,13 @@
         <v>176</v>
       </c>
       <c r="B45" s="8">
-        <v>46118.66224984954</v>
+        <v>46118.49558318287</v>
       </c>
       <c r="C45" s="8">
-        <v>46184.68718685185</v>
+        <v>46184.520520185186</v>
       </c>
       <c r="D45" s="8">
-        <v>46184.68718828703</v>
+        <v>46184.520521620376</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>177</v>
@@ -4137,13 +4137,13 @@
         <v>179</v>
       </c>
       <c r="B46" s="5">
-        <v>46118.66225350695</v>
+        <v>46118.495586840276</v>
       </c>
       <c r="C46" s="5">
-        <v>46184.68670658565</v>
+        <v>46184.52003991898</v>
       </c>
       <c r="D46" s="5">
-        <v>46184.686925347225</v>
+        <v>46184.52025868055</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>153</v>
@@ -4202,13 +4202,13 @@
         <v>183</v>
       </c>
       <c r="B47" s="8">
-        <v>46118.66225863426</v>
+        <v>46118.49559196759</v>
       </c>
       <c r="C47" s="8">
-        <v>46184.6869659838</v>
+        <v>46184.520299317126</v>
       </c>
       <c r="D47" s="8">
-        <v>46184.68714663194</v>
+        <v>46184.52047996528</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>184</v>
@@ -4267,13 +4267,13 @@
         <v>188</v>
       </c>
       <c r="B48" s="5">
-        <v>46118.662263819446</v>
+        <v>46118.49559715278</v>
       </c>
       <c r="C48" s="5">
-        <v>46194.056337268514</v>
+        <v>46193.88967060186</v>
       </c>
       <c r="D48" s="5">
-        <v>46194.05633912037</v>
+        <v>46193.889672453704</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>189</v>
@@ -4316,13 +4316,13 @@
         <v>191</v>
       </c>
       <c r="B49" s="8">
-        <v>46118.66226751157</v>
+        <v>46118.49560084491</v>
       </c>
       <c r="C49" s="8">
-        <v>46184.687951203705</v>
+        <v>46184.52128453704</v>
       </c>
       <c r="D49" s="8">
-        <v>46184.687952719905</v>
+        <v>46184.52128605324</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>192</v>
@@ -4381,13 +4381,13 @@
         <v>196</v>
       </c>
       <c r="B50" s="5">
-        <v>46118.66227269676</v>
+        <v>46118.49560603009</v>
       </c>
       <c r="C50" s="5">
-        <v>46193.56191304398</v>
+        <v>46193.39524637732</v>
       </c>
       <c r="D50" s="5">
-        <v>46193.561914942125</v>
+        <v>46193.39524827546</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>197</v>
@@ -4446,13 +4446,13 @@
         <v>200</v>
       </c>
       <c r="B51" s="8">
-        <v>46184.687980393515</v>
+        <v>46184.52131372685</v>
       </c>
       <c r="C51" s="8">
-        <v>46184.68921728009</v>
+        <v>46184.52255061343</v>
       </c>
       <c r="D51" s="8">
-        <v>46191.68718039352</v>
+        <v>46191.52051372685</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>201</v>
@@ -4501,13 +4501,13 @@
         <v>202</v>
       </c>
       <c r="B52" s="5">
-        <v>46184.688093055556</v>
+        <v>46184.52142638889</v>
       </c>
       <c r="C52" s="5">
-        <v>46195.7025405787</v>
+        <v>46195.53587391204</v>
       </c>
       <c r="D52" s="5">
-        <v>46195.70254238426</v>
+        <v>46195.53587571759</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>203</v>
@@ -4556,13 +4556,13 @@
         <v>204</v>
       </c>
       <c r="B53" s="8">
-        <v>46184.68816803241</v>
+        <v>46184.52150136574</v>
       </c>
       <c r="C53" s="8">
-        <v>46184.69000751157</v>
+        <v>46184.523340844906</v>
       </c>
       <c r="D53" s="8">
-        <v>46191.6871738426</v>
+        <v>46191.52050717593</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>205</v>
@@ -4611,13 +4611,13 @@
         <v>206</v>
       </c>
       <c r="B54" s="5">
-        <v>46184.68826700232</v>
+        <v>46184.52160033565</v>
       </c>
       <c r="C54" s="5">
-        <v>46184.69031962963</v>
+        <v>46184.52365296296</v>
       </c>
       <c r="D54" s="5">
-        <v>46191.687168993056</v>
+        <v>46191.520502326384</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>207</v>
@@ -4666,13 +4666,13 @@
         <v>208</v>
       </c>
       <c r="B55" s="8">
-        <v>46118.66227863426</v>
+        <v>46118.49561196759</v>
       </c>
       <c r="C55" s="8">
-        <v>46193.56240042824</v>
+        <v>46193.39573376157</v>
       </c>
       <c r="D55" s="8">
-        <v>46193.562405625</v>
+        <v>46193.39573895834</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>209</v>
@@ -4731,13 +4731,13 @@
         <v>212</v>
       </c>
       <c r="B56" s="5">
-        <v>46118.66228488426</v>
+        <v>46118.495618217596</v>
       </c>
       <c r="C56" s="5">
-        <v>46194.05632121528</v>
+        <v>46193.889654548606</v>
       </c>
       <c r="D56" s="5">
-        <v>46194.05632325231</v>
+        <v>46193.88965658565</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>177</v>
@@ -4780,13 +4780,13 @@
         <v>214</v>
       </c>
       <c r="B57" s="8">
-        <v>46118.66228803241</v>
+        <v>46118.49562136574</v>
       </c>
       <c r="C57" s="8">
-        <v>46193.562345370374</v>
+        <v>46193.3956787037</v>
       </c>
       <c r="D57" s="8">
-        <v>46193.56234733797</v>
+        <v>46193.395680671296</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>215</v>
@@ -4845,13 +4845,13 @@
         <v>217</v>
       </c>
       <c r="B58" s="5">
-        <v>46118.662293518515</v>
+        <v>46118.49562685185</v>
       </c>
       <c r="C58" s="5">
-        <v>46193.56197458333</v>
+        <v>46193.39530791667</v>
       </c>
       <c r="D58" s="5">
-        <v>46193.56197650463</v>
+        <v>46193.395309837964</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>58</v>
@@ -4910,13 +4910,13 @@
         <v>219</v>
       </c>
       <c r="B59" s="8">
-        <v>46118.662299895834</v>
+        <v>46118.49563322916</v>
       </c>
       <c r="C59" s="8">
-        <v>46193.561984872686</v>
+        <v>46193.39531820602</v>
       </c>
       <c r="D59" s="8">
-        <v>46193.561986678236</v>
+        <v>46193.39532001158</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>220</v>
@@ -4975,13 +4975,13 @@
         <v>222</v>
       </c>
       <c r="B60" s="5">
-        <v>46118.66235550926</v>
+        <v>46118.495688842595</v>
       </c>
       <c r="C60" s="5">
-        <v>46193.56199724537</v>
+        <v>46193.3953305787</v>
       </c>
       <c r="D60" s="5">
-        <v>46193.56199886574</v>
+        <v>46193.39533219907</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>223</v>
@@ -5040,13 +5040,13 @@
         <v>225</v>
       </c>
       <c r="B61" s="8">
-        <v>46118.66236295139</v>
+        <v>46118.49569628472</v>
       </c>
       <c r="C61" s="8">
-        <v>46193.765035358796</v>
+        <v>46193.598368692124</v>
       </c>
       <c r="D61" s="8">
-        <v>46204.900153703704</v>
+        <v>46204.73348703704</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>226</v>
@@ -5089,13 +5089,13 @@
         <v>228</v>
       </c>
       <c r="B62" s="5">
-        <v>46118.66236873843</v>
+        <v>46118.495702071756</v>
       </c>
       <c r="C62" s="5">
-        <v>46193.61261344908</v>
+        <v>46193.445946782405</v>
       </c>
       <c r="D62" s="5">
-        <v>46196.921998854166</v>
+        <v>46196.7553321875</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>229</v>
@@ -5154,13 +5154,13 @@
         <v>231</v>
       </c>
       <c r="B63" s="8">
-        <v>46118.662376064814</v>
+        <v>46118.49570939815</v>
       </c>
       <c r="C63" s="8">
-        <v>46193.6126587037</v>
+        <v>46193.445992037035</v>
       </c>
       <c r="D63" s="8">
-        <v>46193.61266056713</v>
+        <v>46193.44599390046</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>224</v>
@@ -5219,13 +5219,13 @@
         <v>234</v>
       </c>
       <c r="B64" s="5">
-        <v>46118.662387557866</v>
+        <v>46118.4957208912</v>
       </c>
       <c r="C64" s="5">
-        <v>46193.61267944444</v>
+        <v>46193.44601277778</v>
       </c>
       <c r="D64" s="5">
-        <v>46193.61268100694</v>
+        <v>46193.44601434028</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>235</v>
@@ -5284,13 +5284,13 @@
         <v>237</v>
       </c>
       <c r="B65" s="8">
-        <v>46118.662398796296</v>
+        <v>46118.495732129624</v>
       </c>
       <c r="C65" s="8">
-        <v>46193.61273716435</v>
+        <v>46193.44607049768</v>
       </c>
       <c r="D65" s="8">
-        <v>46193.61273954861</v>
+        <v>46193.44607288194</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>238</v>
@@ -5349,13 +5349,13 @@
         <v>240</v>
       </c>
       <c r="B66" s="5">
-        <v>46118.66240984954</v>
+        <v>46118.495743182866</v>
       </c>
       <c r="C66" s="5">
-        <v>46193.765511875</v>
+        <v>46193.59884520833</v>
       </c>
       <c r="D66" s="5">
-        <v>46193.765518935186</v>
+        <v>46193.59885226852</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>174</v>
@@ -5412,13 +5412,13 @@
         <v>243</v>
       </c>
       <c r="B67" s="8">
-        <v>46118.662420127315</v>
+        <v>46118.49575346065</v>
       </c>
       <c r="C67" s="8">
-        <v>46196.92346424768</v>
+        <v>46196.75679758102</v>
       </c>
       <c r="D67" s="8">
-        <v>46198.56946547454</v>
+        <v>46198.402798807874</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>244</v>
@@ -5477,11 +5477,11 @@
         <v>246</v>
       </c>
       <c r="B68" s="5">
-        <v>46118.66242769676</v>
+        <v>46118.49576103009</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46204.897786747686</v>
+        <v>46204.73112008102</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>247</v>
@@ -5524,13 +5524,13 @@
         <v>249</v>
       </c>
       <c r="B69" s="8">
-        <v>46118.662431770834</v>
+        <v>46118.49576510416</v>
       </c>
       <c r="C69" s="8">
-        <v>46203.81564377315</v>
+        <v>46203.64897710648</v>
       </c>
       <c r="D69" s="8">
-        <v>46204.900270983795</v>
+        <v>46204.73360431713</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>250</v>
@@ -5587,13 +5587,13 @@
         <v>254</v>
       </c>
       <c r="B70" s="5">
-        <v>46118.662438252315</v>
+        <v>46118.49577158564</v>
       </c>
       <c r="C70" s="5">
-        <v>46204.89777927083</v>
+        <v>46204.73111260417</v>
       </c>
       <c r="D70" s="5">
-        <v>46204.90025034722</v>
+        <v>46204.73358368056</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>255</v>
@@ -5650,13 +5650,13 @@
         <v>258</v>
       </c>
       <c r="B71" s="8">
-        <v>46118.66245149306</v>
+        <v>46118.49578482639</v>
       </c>
       <c r="C71" s="8">
-        <v>46196.9230577662</v>
+        <v>46196.75639109954</v>
       </c>
       <c r="D71" s="8">
-        <v>46204.900126967594</v>
+        <v>46204.73346030092</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>259</v>
@@ -5713,11 +5713,11 @@
         <v>263</v>
       </c>
       <c r="B72" s="5">
-        <v>46118.66245769676</v>
+        <v>46118.49579103009</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46196.92306840278</v>
+        <v>46196.756401736115</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>264</v>
@@ -5774,11 +5774,11 @@
         <v>266</v>
       </c>
       <c r="B73" s="8">
-        <v>46118.66246467593</v>
+        <v>46118.49579800926</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46118.76284858796</v>
+        <v>46118.5961819213</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>267</v>
@@ -5821,11 +5821,11 @@
         <v>269</v>
       </c>
       <c r="B74" s="5">
-        <v>46118.66246796296</v>
+        <v>46118.495801296296</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46118.76810806713</v>
+        <v>46118.60144140046</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>270</v>
@@ -5884,11 +5884,11 @@
         <v>273</v>
       </c>
       <c r="B75" s="8">
-        <v>46118.66251259259</v>
+        <v>46118.49584592592</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46191.7722621412</v>
+        <v>46191.60559547454</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>274</v>
@@ -5947,11 +5947,11 @@
         <v>275</v>
       </c>
       <c r="B76" s="5">
-        <v>46118.662521377315</v>
+        <v>46118.49585471065</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46118.76362347222</v>
+        <v>46118.59695680556</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>276</v>
@@ -5994,11 +5994,11 @@
         <v>278</v>
       </c>
       <c r="B77" s="8">
-        <v>46118.66252565972</v>
+        <v>46118.495858993054</v>
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46118.7682625</v>
+        <v>46118.60159583333</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>279</v>
@@ -6057,11 +6057,11 @@
         <v>281</v>
       </c>
       <c r="B78" s="5">
-        <v>46118.662532013885</v>
+        <v>46118.49586534723</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46118.76825962963</v>
+        <v>46118.601592962965</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>282</v>

--- a/data/50001533 - GESVIAL.xlsx
+++ b/data/50001533 - GESVIAL.xlsx
@@ -1577,13 +1577,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46118.495183391206</v>
+        <v>46118.66185005787</v>
       </c>
       <c r="C4" s="5">
-        <v>46129.394169652776</v>
+        <v>46129.56083631945</v>
       </c>
       <c r="D4" s="5">
-        <v>46147.847120624996</v>
+        <v>46148.01378729167</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1626,13 +1626,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46118.49534550926</v>
+        <v>46118.662012175926</v>
       </c>
       <c r="C5" s="8">
-        <v>46129.393189814815</v>
+        <v>46129.559856481486</v>
       </c>
       <c r="D5" s="8">
-        <v>46133.710560625</v>
+        <v>46133.87722729167</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1691,13 +1691,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46118.49534890046</v>
+        <v>46118.662015567126</v>
       </c>
       <c r="C6" s="5">
-        <v>46129.39325076389</v>
+        <v>46129.55991743055</v>
       </c>
       <c r="D6" s="5">
-        <v>46129.393267453706</v>
+        <v>46129.55993412037</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -1756,13 +1756,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="8">
-        <v>46118.49535210648</v>
+        <v>46118.662018773146</v>
       </c>
       <c r="C7" s="8">
-        <v>46129.39360674769</v>
+        <v>46129.56027341435</v>
       </c>
       <c r="D7" s="8">
-        <v>46129.39362375</v>
+        <v>46129.560290416666</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>38</v>
@@ -1821,13 +1821,13 @@
         <v>40</v>
       </c>
       <c r="B8" s="5">
-        <v>46118.49535528936</v>
+        <v>46118.66202195601</v>
       </c>
       <c r="C8" s="5">
-        <v>46129.39401967592</v>
+        <v>46129.56068634259</v>
       </c>
       <c r="D8" s="5">
-        <v>46129.39403539352</v>
+        <v>46129.56070206019</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>41</v>
@@ -1886,13 +1886,13 @@
         <v>44</v>
       </c>
       <c r="B9" s="8">
-        <v>46118.495359479166</v>
+        <v>46118.66202614583</v>
       </c>
       <c r="C9" s="8">
-        <v>46129.39415508102</v>
+        <v>46129.560821747684</v>
       </c>
       <c r="D9" s="8">
-        <v>46156.67195390046</v>
+        <v>46156.83862056713</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>45</v>
@@ -1951,13 +1951,13 @@
         <v>47</v>
       </c>
       <c r="B10" s="5">
-        <v>46118.49518951389</v>
+        <v>46118.66185618055</v>
       </c>
       <c r="C10" s="5">
-        <v>46204.485487349535</v>
+        <v>46204.65215401621</v>
       </c>
       <c r="D10" s="5">
-        <v>46204.48548965278</v>
+        <v>46204.65215631944</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>48</v>
@@ -2000,13 +2000,13 @@
         <v>50</v>
       </c>
       <c r="B11" s="8">
-        <v>46118.495363379625</v>
+        <v>46118.6620300463</v>
       </c>
       <c r="C11" s="8">
-        <v>46129.40463276621</v>
+        <v>46129.57129943287</v>
       </c>
       <c r="D11" s="8">
-        <v>46129.40464815972</v>
+        <v>46129.57131482639</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>51</v>
@@ -2065,13 +2065,13 @@
         <v>56</v>
       </c>
       <c r="B12" s="5">
-        <v>46118.49536912037</v>
+        <v>46118.66203578704</v>
       </c>
       <c r="C12" s="5">
-        <v>46196.72904978009</v>
+        <v>46196.89571644676</v>
       </c>
       <c r="D12" s="5">
-        <v>46196.72905206018</v>
+        <v>46196.89571872685</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>57</v>
@@ -2130,13 +2130,13 @@
         <v>60</v>
       </c>
       <c r="B13" s="8">
-        <v>46118.495194097224</v>
+        <v>46118.66186076389</v>
       </c>
       <c r="C13" s="8">
-        <v>46193.395125625</v>
+        <v>46193.56179229167</v>
       </c>
       <c r="D13" s="8">
-        <v>46193.39512796296</v>
+        <v>46193.561794629626</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>61</v>
@@ -2179,13 +2179,13 @@
         <v>63</v>
       </c>
       <c r="B14" s="5">
-        <v>46118.49537506944</v>
+        <v>46118.66204173611</v>
       </c>
       <c r="C14" s="5">
-        <v>46129.395261620375</v>
+        <v>46129.56192828703</v>
       </c>
       <c r="D14" s="5">
-        <v>46191.60559553241</v>
+        <v>46191.77226219907</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>64</v>
@@ -2244,13 +2244,13 @@
         <v>67</v>
       </c>
       <c r="B15" s="8">
-        <v>46118.49538085648</v>
+        <v>46118.66204752315</v>
       </c>
       <c r="C15" s="8">
-        <v>46129.39527212963</v>
+        <v>46129.561938796294</v>
       </c>
       <c r="D15" s="8">
-        <v>46191.60559559028</v>
+        <v>46191.77226225694</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>68</v>
@@ -2309,13 +2309,13 @@
         <v>71</v>
       </c>
       <c r="B16" s="5">
-        <v>46118.49538628472</v>
+        <v>46118.66205295139</v>
       </c>
       <c r="C16" s="5">
-        <v>46129.40045137731</v>
+        <v>46129.56711804398</v>
       </c>
       <c r="D16" s="5">
-        <v>46191.60559547454</v>
+        <v>46191.7722621412</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>72</v>
@@ -2374,13 +2374,13 @@
         <v>75</v>
       </c>
       <c r="B17" s="8">
-        <v>46118.495199490746</v>
+        <v>46118.6618661574</v>
       </c>
       <c r="C17" s="8">
-        <v>46184.563075972226</v>
+        <v>46184.72974263889</v>
       </c>
       <c r="D17" s="8">
-        <v>46184.563077349536</v>
+        <v>46184.72974401621</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>76</v>
@@ -2423,13 +2423,13 @@
         <v>78</v>
       </c>
       <c r="B18" s="5">
-        <v>46118.495399872685</v>
+        <v>46118.66206653936</v>
       </c>
       <c r="C18" s="5">
-        <v>46129.395672175924</v>
+        <v>46129.56233884259</v>
       </c>
       <c r="D18" s="5">
-        <v>46129.3956940625</v>
+        <v>46129.56236072916</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>79</v>
@@ -2488,13 +2488,13 @@
         <v>82</v>
       </c>
       <c r="B19" s="8">
-        <v>46118.49540508102</v>
+        <v>46118.66207174768</v>
       </c>
       <c r="C19" s="8">
-        <v>46129.39567921296</v>
+        <v>46129.56234587963</v>
       </c>
       <c r="D19" s="8">
-        <v>46129.39570070602</v>
+        <v>46129.56236737268</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>83</v>
@@ -2553,13 +2553,13 @@
         <v>85</v>
       </c>
       <c r="B20" s="5">
-        <v>46118.49541042824</v>
+        <v>46118.66207709491</v>
       </c>
       <c r="C20" s="5">
-        <v>46129.40467122685</v>
+        <v>46129.57133789352</v>
       </c>
       <c r="D20" s="5">
-        <v>46129.40468762731</v>
+        <v>46129.57135429398</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>86</v>
@@ -2618,13 +2618,13 @@
         <v>89</v>
       </c>
       <c r="B21" s="8">
-        <v>46118.49541564815</v>
+        <v>46118.66208231481</v>
       </c>
       <c r="C21" s="8">
-        <v>46183.71343438658</v>
+        <v>46183.88010105324</v>
       </c>
       <c r="D21" s="8">
-        <v>46183.71343625</v>
+        <v>46183.880102916664</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>90</v>
@@ -2683,13 +2683,13 @@
         <v>94</v>
       </c>
       <c r="B22" s="5">
-        <v>46118.49542085648</v>
+        <v>46118.662087523146</v>
       </c>
       <c r="C22" s="5">
-        <v>46183.72138519676</v>
+        <v>46183.888051863425</v>
       </c>
       <c r="D22" s="5">
-        <v>46183.721584768515</v>
+        <v>46183.888251435186</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>95</v>
@@ -2748,13 +2748,13 @@
         <v>100</v>
       </c>
       <c r="B23" s="8">
-        <v>46118.49520528935</v>
+        <v>46118.66187195602</v>
       </c>
       <c r="C23" s="8">
-        <v>46184.5195800463</v>
+        <v>46184.68624671296</v>
       </c>
       <c r="D23" s="8">
-        <v>46184.51958140046</v>
+        <v>46184.686248067126</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>101</v>
@@ -2797,13 +2797,13 @@
         <v>103</v>
       </c>
       <c r="B24" s="5">
-        <v>46118.49542702547</v>
+        <v>46118.662093692124</v>
       </c>
       <c r="C24" s="5">
-        <v>46182.509780231485</v>
+        <v>46182.67644689815</v>
       </c>
       <c r="D24" s="5">
-        <v>46182.50978262731</v>
+        <v>46182.676449293984</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>104</v>
@@ -2862,13 +2862,13 @@
         <v>109</v>
       </c>
       <c r="B25" s="8">
-        <v>46118.495431793985</v>
+        <v>46118.66209846065</v>
       </c>
       <c r="C25" s="8">
-        <v>46174.4590187037</v>
+        <v>46174.62568537037</v>
       </c>
       <c r="D25" s="8">
-        <v>46174.45902023149</v>
+        <v>46174.62568689814</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>110</v>
@@ -2917,13 +2917,13 @@
         <v>112</v>
       </c>
       <c r="B26" s="5">
-        <v>46118.49543604167</v>
+        <v>46118.66210270833</v>
       </c>
       <c r="C26" s="5">
-        <v>46182.476623263894</v>
+        <v>46182.64328993055</v>
       </c>
       <c r="D26" s="5">
-        <v>46182.47662475695</v>
+        <v>46182.64329142361</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>113</v>
@@ -2972,13 +2972,13 @@
         <v>115</v>
       </c>
       <c r="B27" s="8">
-        <v>46118.4954403125</v>
+        <v>46118.662106979165</v>
       </c>
       <c r="C27" s="8">
-        <v>46182.47440028936</v>
+        <v>46182.641066956014</v>
       </c>
       <c r="D27" s="8">
-        <v>46182.47440253472</v>
+        <v>46182.64106920139</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>116</v>
@@ -3037,13 +3037,13 @@
         <v>118</v>
       </c>
       <c r="B28" s="5">
-        <v>46118.49544542824</v>
+        <v>46118.662112094906</v>
       </c>
       <c r="C28" s="5">
-        <v>46174.459855</v>
+        <v>46174.626521666665</v>
       </c>
       <c r="D28" s="5">
-        <v>46174.45985648148</v>
+        <v>46174.62652314815</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>119</v>
@@ -3098,13 +3098,13 @@
         <v>121</v>
       </c>
       <c r="B29" s="8">
-        <v>46118.4954502662</v>
+        <v>46118.66211693287</v>
       </c>
       <c r="C29" s="8">
-        <v>46174.45996375</v>
+        <v>46174.626630416664</v>
       </c>
       <c r="D29" s="8">
-        <v>46174.45996519676</v>
+        <v>46174.62663186343</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>122</v>
@@ -3159,13 +3159,13 @@
         <v>124</v>
       </c>
       <c r="B30" s="5">
-        <v>46118.495455358796</v>
+        <v>46118.66212202546</v>
       </c>
       <c r="C30" s="5">
-        <v>46184.519414780094</v>
+        <v>46184.68608144676</v>
       </c>
       <c r="D30" s="5">
-        <v>46184.519416574076</v>
+        <v>46184.68608324074</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>125</v>
@@ -3224,13 +3224,13 @@
         <v>127</v>
       </c>
       <c r="B31" s="8">
-        <v>46118.495460011574</v>
+        <v>46118.662126678246</v>
       </c>
       <c r="C31" s="8">
-        <v>46184.519052372685</v>
+        <v>46184.68571903935</v>
       </c>
       <c r="D31" s="8">
-        <v>46184.519054143515</v>
+        <v>46184.68572081019</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>128</v>
@@ -3285,13 +3285,13 @@
         <v>130</v>
       </c>
       <c r="B32" s="5">
-        <v>46118.495464594904</v>
+        <v>46118.662131261575</v>
       </c>
       <c r="C32" s="5">
-        <v>46184.519122233796</v>
+        <v>46184.68578890046</v>
       </c>
       <c r="D32" s="5">
-        <v>46184.51912386574</v>
+        <v>46184.68579053241</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>131</v>
@@ -3346,13 +3346,13 @@
         <v>133</v>
       </c>
       <c r="B33" s="8">
-        <v>46118.49551706019</v>
+        <v>46118.66218372685</v>
       </c>
       <c r="C33" s="8">
-        <v>46156.654673321755</v>
+        <v>46156.821339988426</v>
       </c>
       <c r="D33" s="8">
-        <v>46169.657316111116</v>
+        <v>46169.82398277777</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>134</v>
@@ -3411,13 +3411,13 @@
         <v>136</v>
       </c>
       <c r="B34" s="5">
-        <v>46118.4955234375</v>
+        <v>46118.662190104165</v>
       </c>
       <c r="C34" s="5">
-        <v>46134.624486030094</v>
+        <v>46134.79115269676</v>
       </c>
       <c r="D34" s="5">
-        <v>46169.65732769676</v>
+        <v>46169.823994363425</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>137</v>
@@ -3472,13 +3472,13 @@
         <v>139</v>
       </c>
       <c r="B35" s="8">
-        <v>46118.49552902778</v>
+        <v>46118.662195694444</v>
       </c>
       <c r="C35" s="8">
-        <v>46155.736021006946</v>
+        <v>46155.90268767361</v>
       </c>
       <c r="D35" s="8">
-        <v>46169.657349201385</v>
+        <v>46169.82401586806</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>140</v>
@@ -3533,13 +3533,13 @@
         <v>142</v>
       </c>
       <c r="B36" s="5">
-        <v>46118.495534155096</v>
+        <v>46118.66220082176</v>
       </c>
       <c r="C36" s="5">
-        <v>46134.624528726854</v>
+        <v>46134.79119539352</v>
       </c>
       <c r="D36" s="5">
-        <v>46169.65736949074</v>
+        <v>46169.824036157406</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>143</v>
@@ -3594,13 +3594,13 @@
         <v>145</v>
       </c>
       <c r="B37" s="8">
-        <v>46118.495539675925</v>
+        <v>46118.66220634259</v>
       </c>
       <c r="C37" s="8">
-        <v>46184.51943712963</v>
+        <v>46184.686103796295</v>
       </c>
       <c r="D37" s="8">
-        <v>46184.519438564814</v>
+        <v>46184.68610523148</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>146</v>
@@ -3659,13 +3659,13 @@
         <v>149</v>
       </c>
       <c r="B38" s="5">
-        <v>46118.495545682876</v>
+        <v>46118.66221234953</v>
       </c>
       <c r="C38" s="5">
-        <v>46184.36428194444</v>
+        <v>46184.53094861111</v>
       </c>
       <c r="D38" s="5">
-        <v>46184.36428409722</v>
+        <v>46184.53095076389</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>150</v>
@@ -3720,13 +3720,13 @@
         <v>152</v>
       </c>
       <c r="B39" s="8">
-        <v>46118.495549907406</v>
+        <v>46118.66221657407</v>
       </c>
       <c r="C39" s="8">
-        <v>46184.36495873843</v>
+        <v>46184.53162540509</v>
       </c>
       <c r="D39" s="8">
-        <v>46184.36496005787</v>
+        <v>46184.531626724536</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>151</v>
@@ -3781,13 +3781,13 @@
         <v>154</v>
       </c>
       <c r="B40" s="5">
-        <v>46118.495554305555</v>
+        <v>46118.662220972226</v>
       </c>
       <c r="C40" s="5">
-        <v>46204.48551542824</v>
+        <v>46204.65218209491</v>
       </c>
       <c r="D40" s="5">
-        <v>46204.48551697917</v>
+        <v>46204.652183645834</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>155</v>
@@ -3830,13 +3830,13 @@
         <v>157</v>
       </c>
       <c r="B41" s="8">
-        <v>46118.495558553244</v>
+        <v>46118.66222521991</v>
       </c>
       <c r="C41" s="8">
-        <v>46129.40051568287</v>
+        <v>46129.567182349536</v>
       </c>
       <c r="D41" s="8">
-        <v>46129.40751229167</v>
+        <v>46129.57417895833</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>158</v>
@@ -3895,13 +3895,13 @@
         <v>162</v>
       </c>
       <c r="B42" s="5">
-        <v>46118.495565034726</v>
+        <v>46118.66223170139</v>
       </c>
       <c r="C42" s="5">
-        <v>46134.633600057874</v>
+        <v>46134.80026672454</v>
       </c>
       <c r="D42" s="5">
-        <v>46134.63361603009</v>
+        <v>46134.80028269676</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>163</v>
@@ -3960,13 +3960,13 @@
         <v>168</v>
       </c>
       <c r="B43" s="8">
-        <v>46118.49557270833</v>
+        <v>46118.662239375</v>
       </c>
       <c r="C43" s="8">
-        <v>46134.63372706018</v>
+        <v>46134.80039372685</v>
       </c>
       <c r="D43" s="8">
-        <v>46134.633741701386</v>
+        <v>46134.80040836806</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>98</v>
@@ -4023,13 +4023,13 @@
         <v>170</v>
       </c>
       <c r="B44" s="5">
-        <v>46118.49557863426</v>
+        <v>46118.662245300926</v>
       </c>
       <c r="C44" s="5">
-        <v>46198.40279047454</v>
+        <v>46198.5694571412</v>
       </c>
       <c r="D44" s="5">
-        <v>46198.4027927662</v>
+        <v>46198.56945943287</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>171</v>
@@ -4088,13 +4088,13 @@
         <v>176</v>
       </c>
       <c r="B45" s="8">
-        <v>46118.49558318287</v>
+        <v>46118.66224984954</v>
       </c>
       <c r="C45" s="8">
-        <v>46184.520520185186</v>
+        <v>46184.68718685185</v>
       </c>
       <c r="D45" s="8">
-        <v>46184.520521620376</v>
+        <v>46184.68718828703</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>177</v>
@@ -4137,13 +4137,13 @@
         <v>179</v>
       </c>
       <c r="B46" s="5">
-        <v>46118.495586840276</v>
+        <v>46118.66225350695</v>
       </c>
       <c r="C46" s="5">
-        <v>46184.52003991898</v>
+        <v>46184.68670658565</v>
       </c>
       <c r="D46" s="5">
-        <v>46184.52025868055</v>
+        <v>46184.686925347225</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>153</v>
@@ -4202,13 +4202,13 @@
         <v>183</v>
       </c>
       <c r="B47" s="8">
-        <v>46118.49559196759</v>
+        <v>46118.66225863426</v>
       </c>
       <c r="C47" s="8">
-        <v>46184.520299317126</v>
+        <v>46184.6869659838</v>
       </c>
       <c r="D47" s="8">
-        <v>46184.52047996528</v>
+        <v>46184.68714663194</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>184</v>
@@ -4267,13 +4267,13 @@
         <v>188</v>
       </c>
       <c r="B48" s="5">
-        <v>46118.49559715278</v>
+        <v>46118.662263819446</v>
       </c>
       <c r="C48" s="5">
-        <v>46193.88967060186</v>
+        <v>46194.056337268514</v>
       </c>
       <c r="D48" s="5">
-        <v>46193.889672453704</v>
+        <v>46194.05633912037</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>189</v>
@@ -4316,13 +4316,13 @@
         <v>191</v>
       </c>
       <c r="B49" s="8">
-        <v>46118.49560084491</v>
+        <v>46118.66226751157</v>
       </c>
       <c r="C49" s="8">
-        <v>46184.52128453704</v>
+        <v>46184.687951203705</v>
       </c>
       <c r="D49" s="8">
-        <v>46184.52128605324</v>
+        <v>46184.687952719905</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>192</v>
@@ -4381,13 +4381,13 @@
         <v>196</v>
       </c>
       <c r="B50" s="5">
-        <v>46118.49560603009</v>
+        <v>46118.66227269676</v>
       </c>
       <c r="C50" s="5">
-        <v>46193.39524637732</v>
+        <v>46193.56191304398</v>
       </c>
       <c r="D50" s="5">
-        <v>46193.39524827546</v>
+        <v>46193.561914942125</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>197</v>
@@ -4446,13 +4446,13 @@
         <v>200</v>
       </c>
       <c r="B51" s="8">
-        <v>46184.52131372685</v>
+        <v>46184.687980393515</v>
       </c>
       <c r="C51" s="8">
-        <v>46184.52255061343</v>
+        <v>46184.68921728009</v>
       </c>
       <c r="D51" s="8">
-        <v>46191.52051372685</v>
+        <v>46191.68718039352</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>201</v>
@@ -4501,13 +4501,13 @@
         <v>202</v>
       </c>
       <c r="B52" s="5">
-        <v>46184.52142638889</v>
+        <v>46184.688093055556</v>
       </c>
       <c r="C52" s="5">
-        <v>46195.53587391204</v>
+        <v>46195.7025405787</v>
       </c>
       <c r="D52" s="5">
-        <v>46195.53587571759</v>
+        <v>46195.70254238426</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>203</v>
@@ -4556,13 +4556,13 @@
         <v>204</v>
       </c>
       <c r="B53" s="8">
-        <v>46184.52150136574</v>
+        <v>46184.68816803241</v>
       </c>
       <c r="C53" s="8">
-        <v>46184.523340844906</v>
+        <v>46184.69000751157</v>
       </c>
       <c r="D53" s="8">
-        <v>46191.52050717593</v>
+        <v>46191.6871738426</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>205</v>
@@ -4611,13 +4611,13 @@
         <v>206</v>
       </c>
       <c r="B54" s="5">
-        <v>46184.52160033565</v>
+        <v>46184.68826700232</v>
       </c>
       <c r="C54" s="5">
-        <v>46184.52365296296</v>
+        <v>46184.69031962963</v>
       </c>
       <c r="D54" s="5">
-        <v>46191.520502326384</v>
+        <v>46191.687168993056</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>207</v>
@@ -4666,13 +4666,13 @@
         <v>208</v>
       </c>
       <c r="B55" s="8">
-        <v>46118.49561196759</v>
+        <v>46118.66227863426</v>
       </c>
       <c r="C55" s="8">
-        <v>46193.39573376157</v>
+        <v>46193.56240042824</v>
       </c>
       <c r="D55" s="8">
-        <v>46193.39573895834</v>
+        <v>46193.562405625</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>209</v>
@@ -4731,13 +4731,13 @@
         <v>212</v>
       </c>
       <c r="B56" s="5">
-        <v>46118.495618217596</v>
+        <v>46118.66228488426</v>
       </c>
       <c r="C56" s="5">
-        <v>46193.889654548606</v>
+        <v>46194.05632121528</v>
       </c>
       <c r="D56" s="5">
-        <v>46193.88965658565</v>
+        <v>46194.05632325231</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>177</v>
@@ -4780,13 +4780,13 @@
         <v>214</v>
       </c>
       <c r="B57" s="8">
-        <v>46118.49562136574</v>
+        <v>46118.66228803241</v>
       </c>
       <c r="C57" s="8">
-        <v>46193.3956787037</v>
+        <v>46193.562345370374</v>
       </c>
       <c r="D57" s="8">
-        <v>46193.395680671296</v>
+        <v>46193.56234733797</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>215</v>
@@ -4845,13 +4845,13 @@
         <v>217</v>
       </c>
       <c r="B58" s="5">
-        <v>46118.49562685185</v>
+        <v>46118.662293518515</v>
       </c>
       <c r="C58" s="5">
-        <v>46193.39530791667</v>
+        <v>46193.56197458333</v>
       </c>
       <c r="D58" s="5">
-        <v>46193.395309837964</v>
+        <v>46193.56197650463</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>58</v>
@@ -4910,13 +4910,13 @@
         <v>219</v>
       </c>
       <c r="B59" s="8">
-        <v>46118.49563322916</v>
+        <v>46118.662299895834</v>
       </c>
       <c r="C59" s="8">
-        <v>46193.39531820602</v>
+        <v>46193.561984872686</v>
       </c>
       <c r="D59" s="8">
-        <v>46193.39532001158</v>
+        <v>46193.561986678236</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>220</v>
@@ -4975,13 +4975,13 @@
         <v>222</v>
       </c>
       <c r="B60" s="5">
-        <v>46118.495688842595</v>
+        <v>46118.66235550926</v>
       </c>
       <c r="C60" s="5">
-        <v>46193.3953305787</v>
+        <v>46193.56199724537</v>
       </c>
       <c r="D60" s="5">
-        <v>46193.39533219907</v>
+        <v>46193.56199886574</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>223</v>
@@ -5040,13 +5040,13 @@
         <v>225</v>
       </c>
       <c r="B61" s="8">
-        <v>46118.49569628472</v>
+        <v>46118.66236295139</v>
       </c>
       <c r="C61" s="8">
-        <v>46193.598368692124</v>
+        <v>46193.765035358796</v>
       </c>
       <c r="D61" s="8">
-        <v>46204.73348703704</v>
+        <v>46204.900153703704</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>226</v>
@@ -5089,13 +5089,13 @@
         <v>228</v>
       </c>
       <c r="B62" s="5">
-        <v>46118.495702071756</v>
+        <v>46118.66236873843</v>
       </c>
       <c r="C62" s="5">
-        <v>46193.445946782405</v>
+        <v>46193.61261344908</v>
       </c>
       <c r="D62" s="5">
-        <v>46196.7553321875</v>
+        <v>46196.921998854166</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>229</v>
@@ -5154,13 +5154,13 @@
         <v>231</v>
       </c>
       <c r="B63" s="8">
-        <v>46118.49570939815</v>
+        <v>46118.662376064814</v>
       </c>
       <c r="C63" s="8">
-        <v>46193.445992037035</v>
+        <v>46193.6126587037</v>
       </c>
       <c r="D63" s="8">
-        <v>46193.44599390046</v>
+        <v>46193.61266056713</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>224</v>
@@ -5219,13 +5219,13 @@
         <v>234</v>
       </c>
       <c r="B64" s="5">
-        <v>46118.4957208912</v>
+        <v>46118.662387557866</v>
       </c>
       <c r="C64" s="5">
-        <v>46193.44601277778</v>
+        <v>46193.61267944444</v>
       </c>
       <c r="D64" s="5">
-        <v>46193.44601434028</v>
+        <v>46193.61268100694</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>235</v>
@@ -5284,13 +5284,13 @@
         <v>237</v>
       </c>
       <c r="B65" s="8">
-        <v>46118.495732129624</v>
+        <v>46118.662398796296</v>
       </c>
       <c r="C65" s="8">
-        <v>46193.44607049768</v>
+        <v>46193.61273716435</v>
       </c>
       <c r="D65" s="8">
-        <v>46193.44607288194</v>
+        <v>46193.61273954861</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>238</v>
@@ -5349,13 +5349,13 @@
         <v>240</v>
       </c>
       <c r="B66" s="5">
-        <v>46118.495743182866</v>
+        <v>46118.66240984954</v>
       </c>
       <c r="C66" s="5">
-        <v>46193.59884520833</v>
+        <v>46193.765511875</v>
       </c>
       <c r="D66" s="5">
-        <v>46193.59885226852</v>
+        <v>46193.765518935186</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>174</v>
@@ -5412,13 +5412,13 @@
         <v>243</v>
       </c>
       <c r="B67" s="8">
-        <v>46118.49575346065</v>
+        <v>46118.662420127315</v>
       </c>
       <c r="C67" s="8">
-        <v>46196.75679758102</v>
+        <v>46196.92346424768</v>
       </c>
       <c r="D67" s="8">
-        <v>46198.402798807874</v>
+        <v>46198.56946547454</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>244</v>
@@ -5477,11 +5477,11 @@
         <v>246</v>
       </c>
       <c r="B68" s="5">
-        <v>46118.49576103009</v>
+        <v>46118.66242769676</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46204.73112008102</v>
+        <v>46204.897786747686</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>247</v>
@@ -5524,13 +5524,13 @@
         <v>249</v>
       </c>
       <c r="B69" s="8">
-        <v>46118.49576510416</v>
+        <v>46118.662431770834</v>
       </c>
       <c r="C69" s="8">
-        <v>46203.64897710648</v>
+        <v>46203.81564377315</v>
       </c>
       <c r="D69" s="8">
-        <v>46204.73360431713</v>
+        <v>46204.900270983795</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>250</v>
@@ -5587,13 +5587,13 @@
         <v>254</v>
       </c>
       <c r="B70" s="5">
-        <v>46118.49577158564</v>
+        <v>46118.662438252315</v>
       </c>
       <c r="C70" s="5">
-        <v>46204.73111260417</v>
+        <v>46204.89777927083</v>
       </c>
       <c r="D70" s="5">
-        <v>46204.73358368056</v>
+        <v>46204.90025034722</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>255</v>
@@ -5650,13 +5650,13 @@
         <v>258</v>
       </c>
       <c r="B71" s="8">
-        <v>46118.49578482639</v>
+        <v>46118.66245149306</v>
       </c>
       <c r="C71" s="8">
-        <v>46196.75639109954</v>
+        <v>46196.9230577662</v>
       </c>
       <c r="D71" s="8">
-        <v>46204.73346030092</v>
+        <v>46204.900126967594</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>259</v>
@@ -5713,11 +5713,11 @@
         <v>263</v>
       </c>
       <c r="B72" s="5">
-        <v>46118.49579103009</v>
+        <v>46118.66245769676</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46196.756401736115</v>
+        <v>46196.92306840278</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>264</v>
@@ -5774,11 +5774,11 @@
         <v>266</v>
       </c>
       <c r="B73" s="8">
-        <v>46118.49579800926</v>
+        <v>46118.66246467593</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46118.5961819213</v>
+        <v>46118.76284858796</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>267</v>
@@ -5821,11 +5821,11 @@
         <v>269</v>
       </c>
       <c r="B74" s="5">
-        <v>46118.495801296296</v>
+        <v>46118.66246796296</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46118.60144140046</v>
+        <v>46118.76810806713</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>270</v>
@@ -5884,11 +5884,11 @@
         <v>273</v>
       </c>
       <c r="B75" s="8">
-        <v>46118.49584592592</v>
+        <v>46118.66251259259</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46191.60559547454</v>
+        <v>46191.7722621412</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>274</v>
@@ -5947,11 +5947,11 @@
         <v>275</v>
       </c>
       <c r="B76" s="5">
-        <v>46118.49585471065</v>
+        <v>46118.662521377315</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46118.59695680556</v>
+        <v>46118.76362347222</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>276</v>
@@ -5994,11 +5994,11 @@
         <v>278</v>
       </c>
       <c r="B77" s="8">
-        <v>46118.495858993054</v>
+        <v>46118.66252565972</v>
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46118.60159583333</v>
+        <v>46118.7682625</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>279</v>
@@ -6057,11 +6057,11 @@
         <v>281</v>
       </c>
       <c r="B78" s="5">
-        <v>46118.49586534723</v>
+        <v>46118.662532013885</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46118.601592962965</v>
+        <v>46118.76825962963</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>282</v>

--- a/data/50001533 - GESVIAL.xlsx
+++ b/data/50001533 - GESVIAL.xlsx
@@ -2624,7 +2624,7 @@
         <v>46183.88010105324</v>
       </c>
       <c r="D21" s="8">
-        <v>46183.880102916664</v>
+        <v>46208.21006932871</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>90</v>
@@ -2669,7 +2669,7 @@
         <v>46115</v>
       </c>
       <c r="S21" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T21" s="11" t="s">
         <v>55</v>
@@ -2689,7 +2689,7 @@
         <v>46183.888051863425</v>
       </c>
       <c r="D22" s="5">
-        <v>46183.888251435186</v>
+        <v>46208.21011525463</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>95</v>
@@ -2734,7 +2734,7 @@
         <v>46150</v>
       </c>
       <c r="S22" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T22" s="10" t="s">
         <v>32</v>
@@ -2803,7 +2803,7 @@
         <v>46182.67644689815</v>
       </c>
       <c r="D24" s="5">
-        <v>46182.676449293984</v>
+        <v>46208.21003241898</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>104</v>
@@ -2848,7 +2848,7 @@
         <v>46119</v>
       </c>
       <c r="S24" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T24" s="10" t="s">
         <v>32</v>
@@ -2868,7 +2868,7 @@
         <v>46174.62568537037</v>
       </c>
       <c r="D25" s="8">
-        <v>46174.62568689814</v>
+        <v>46208.21094784723</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>110</v>
@@ -2908,7 +2908,9 @@
       </c>
       <c r="Q25" s="9"/>
       <c r="R25" s="9"/>
-      <c r="S25" s="9"/>
+      <c r="S25" s="9">
+        <v>1</v>
+      </c>
       <c r="T25" s="9"/>
       <c r="U25" s="9"/>
     </row>
@@ -2923,7 +2925,7 @@
         <v>46182.64328993055</v>
       </c>
       <c r="D26" s="5">
-        <v>46182.64329142361</v>
+        <v>46208.21109037037</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>113</v>
@@ -2963,7 +2965,9 @@
       </c>
       <c r="Q26" s="6"/>
       <c r="R26" s="6"/>
-      <c r="S26" s="6"/>
+      <c r="S26" s="6">
+        <v>1</v>
+      </c>
       <c r="T26" s="6"/>
       <c r="U26" s="6"/>
     </row>
@@ -2978,7 +2982,7 @@
         <v>46182.641066956014</v>
       </c>
       <c r="D27" s="8">
-        <v>46182.64106920139</v>
+        <v>46208.209962824076</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>116</v>
@@ -3023,7 +3027,7 @@
         <v>46111</v>
       </c>
       <c r="S27" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T27" s="10" t="s">
         <v>32</v>
@@ -3043,7 +3047,7 @@
         <v>46174.626521666665</v>
       </c>
       <c r="D28" s="5">
-        <v>46174.62652314815</v>
+        <v>46208.21118949074</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>119</v>
@@ -3084,7 +3088,7 @@
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
       <c r="S28" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T28" s="10" t="s">
         <v>32</v>
@@ -3104,7 +3108,7 @@
         <v>46174.626630416664</v>
       </c>
       <c r="D29" s="8">
-        <v>46174.62663186343</v>
+        <v>46208.21130763889</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>122</v>
@@ -3145,7 +3149,7 @@
       <c r="Q29" s="9"/>
       <c r="R29" s="9"/>
       <c r="S29" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T29" s="10" t="s">
         <v>32</v>
@@ -3165,7 +3169,7 @@
         <v>46184.68608144676</v>
       </c>
       <c r="D30" s="5">
-        <v>46184.68608324074</v>
+        <v>46208.20888993055</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>125</v>
@@ -3210,7 +3214,7 @@
         <v>46119</v>
       </c>
       <c r="S30" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T30" s="10" t="s">
         <v>32</v>
@@ -3230,7 +3234,7 @@
         <v>46184.68571903935</v>
       </c>
       <c r="D31" s="8">
-        <v>46184.68572081019</v>
+        <v>46208.211394502316</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>128</v>
@@ -3271,7 +3275,7 @@
       <c r="Q31" s="9"/>
       <c r="R31" s="9"/>
       <c r="S31" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T31" s="10" t="s">
         <v>32</v>
@@ -3291,7 +3295,7 @@
         <v>46184.68578890046</v>
       </c>
       <c r="D32" s="5">
-        <v>46184.68579053241</v>
+        <v>46208.21147013889</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>131</v>
@@ -3332,7 +3336,7 @@
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
       <c r="S32" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T32" s="10" t="s">
         <v>32</v>
@@ -3417,7 +3421,7 @@
         <v>46134.79115269676</v>
       </c>
       <c r="D34" s="5">
-        <v>46169.823994363425</v>
+        <v>46208.211555636575</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>137</v>
@@ -3458,7 +3462,7 @@
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
       <c r="S34" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T34" s="10" t="s">
         <v>32</v>
@@ -3478,7 +3482,7 @@
         <v>46155.90268767361</v>
       </c>
       <c r="D35" s="8">
-        <v>46169.82401586806</v>
+        <v>46208.21164188658</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>140</v>
@@ -3519,7 +3523,7 @@
       <c r="Q35" s="9"/>
       <c r="R35" s="9"/>
       <c r="S35" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T35" s="10" t="s">
         <v>32</v>
@@ -3539,7 +3543,7 @@
         <v>46134.79119539352</v>
       </c>
       <c r="D36" s="5">
-        <v>46169.824036157406</v>
+        <v>46208.211714791665</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>143</v>
@@ -3580,7 +3584,7 @@
       <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
       <c r="S36" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T36" s="10" t="s">
         <v>32</v>
@@ -3600,7 +3604,7 @@
         <v>46184.686103796295</v>
       </c>
       <c r="D37" s="8">
-        <v>46184.68610523148</v>
+        <v>46208.208834942125</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>146</v>
@@ -3645,7 +3649,7 @@
         <v>46154</v>
       </c>
       <c r="S37" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T37" s="10" t="s">
         <v>32</v>
@@ -3665,7 +3669,7 @@
         <v>46184.53094861111</v>
       </c>
       <c r="D38" s="5">
-        <v>46184.53095076389</v>
+        <v>46208.21179649305</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>150</v>
@@ -3706,7 +3710,7 @@
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
       <c r="S38" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T38" s="10" t="s">
         <v>32</v>
@@ -3726,7 +3730,7 @@
         <v>46184.53162540509</v>
       </c>
       <c r="D39" s="8">
-        <v>46184.531626724536</v>
+        <v>46208.211892453706</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>151</v>
@@ -3767,7 +3771,7 @@
       <c r="Q39" s="9"/>
       <c r="R39" s="9"/>
       <c r="S39" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T39" s="10" t="s">
         <v>32</v>
@@ -4029,7 +4033,7 @@
         <v>46198.5694571412</v>
       </c>
       <c r="D44" s="5">
-        <v>46198.56945943287</v>
+        <v>46208.20879145833</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>171</v>
@@ -4074,7 +4078,7 @@
         <v>46268</v>
       </c>
       <c r="S44" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T44" s="10" t="s">
         <v>32</v>
@@ -4143,7 +4147,7 @@
         <v>46184.68670658565</v>
       </c>
       <c r="D46" s="5">
-        <v>46184.686925347225</v>
+        <v>46208.20988328704</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>153</v>
@@ -4188,7 +4192,7 @@
         <v>46171</v>
       </c>
       <c r="S46" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T46" s="10" t="s">
         <v>32</v>
@@ -4208,7 +4212,7 @@
         <v>46184.6869659838</v>
       </c>
       <c r="D47" s="8">
-        <v>46184.68714663194</v>
+        <v>46208.20991337963</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>184</v>
@@ -4253,7 +4257,7 @@
         <v>46175</v>
       </c>
       <c r="S47" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T47" s="10" t="s">
         <v>32</v>
@@ -4322,7 +4326,7 @@
         <v>46184.687951203705</v>
       </c>
       <c r="D49" s="8">
-        <v>46184.687952719905</v>
+        <v>46208.210227986114</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>192</v>
@@ -4367,7 +4371,7 @@
         <v>46177</v>
       </c>
       <c r="S49" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T49" s="10" t="s">
         <v>32</v>
@@ -4387,7 +4391,7 @@
         <v>46193.56191304398</v>
       </c>
       <c r="D50" s="5">
-        <v>46193.561914942125</v>
+        <v>46208.210261203705</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>197</v>
@@ -4432,7 +4436,7 @@
         <v>46188</v>
       </c>
       <c r="S50" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T50" s="10" t="s">
         <v>32</v>
@@ -4672,7 +4676,7 @@
         <v>46193.56240042824</v>
       </c>
       <c r="D55" s="8">
-        <v>46193.562405625</v>
+        <v>46208.21032709491</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>209</v>
@@ -4717,7 +4721,7 @@
         <v>46206</v>
       </c>
       <c r="S55" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T55" s="10" t="s">
         <v>32</v>
@@ -4786,7 +4790,7 @@
         <v>46193.562345370374</v>
       </c>
       <c r="D57" s="8">
-        <v>46193.56234733797</v>
+        <v>46208.21036678241</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>215</v>
@@ -4831,7 +4835,7 @@
         <v>46168</v>
       </c>
       <c r="S57" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T57" s="10" t="s">
         <v>32</v>
@@ -4851,7 +4855,7 @@
         <v>46193.56197458333</v>
       </c>
       <c r="D58" s="5">
-        <v>46193.56197650463</v>
+        <v>46208.210472280094</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>58</v>
@@ -4896,7 +4900,7 @@
         <v>46189</v>
       </c>
       <c r="S58" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T58" s="10" t="s">
         <v>32</v>
@@ -4916,7 +4920,7 @@
         <v>46193.561984872686</v>
       </c>
       <c r="D59" s="8">
-        <v>46193.561986678236</v>
+        <v>46208.21047276621</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>220</v>
@@ -4961,7 +4965,7 @@
         <v>46233</v>
       </c>
       <c r="S59" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T59" s="10" t="s">
         <v>32</v>
@@ -4981,7 +4985,7 @@
         <v>46193.56199724537</v>
       </c>
       <c r="D60" s="5">
-        <v>46193.56199886574</v>
+        <v>46208.210473217594</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>223</v>
@@ -5026,7 +5030,7 @@
         <v>46255</v>
       </c>
       <c r="S60" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T60" s="10" t="s">
         <v>32</v>
@@ -5095,7 +5099,7 @@
         <v>46193.61261344908</v>
       </c>
       <c r="D62" s="5">
-        <v>46196.921998854166</v>
+        <v>46208.21062993056</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>229</v>
@@ -5140,7 +5144,7 @@
         <v>46210</v>
       </c>
       <c r="S62" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T62" s="10" t="s">
         <v>32</v>
@@ -5160,7 +5164,7 @@
         <v>46193.6126587037</v>
       </c>
       <c r="D63" s="8">
-        <v>46193.61266056713</v>
+        <v>46208.21062945602</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>224</v>
@@ -5205,7 +5209,7 @@
         <v>46259</v>
       </c>
       <c r="S63" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T63" s="10" t="s">
         <v>32</v>
@@ -5225,7 +5229,7 @@
         <v>46193.61267944444</v>
       </c>
       <c r="D64" s="5">
-        <v>46193.61268100694</v>
+        <v>46208.21063037037</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>235</v>
@@ -5270,7 +5274,7 @@
         <v>46261</v>
       </c>
       <c r="S64" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T64" s="10" t="s">
         <v>32</v>
@@ -5290,7 +5294,7 @@
         <v>46193.61273716435</v>
       </c>
       <c r="D65" s="8">
-        <v>46193.61273954861</v>
+        <v>46208.21062888889</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>238</v>
@@ -5335,7 +5339,7 @@
         <v>46265</v>
       </c>
       <c r="S65" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T65" s="10" t="s">
         <v>32</v>
@@ -5355,7 +5359,7 @@
         <v>46193.765511875</v>
       </c>
       <c r="D66" s="5">
-        <v>46193.765518935186</v>
+        <v>46208.21062840278</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>174</v>
@@ -5398,7 +5402,7 @@
         <v>46267</v>
       </c>
       <c r="S66" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T66" s="10" t="s">
         <v>32</v>
@@ -5418,7 +5422,7 @@
         <v>46196.92346424768</v>
       </c>
       <c r="D67" s="8">
-        <v>46198.56946547454</v>
+        <v>46208.21062791666</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>244</v>
@@ -5463,7 +5467,7 @@
         <v>46269</v>
       </c>
       <c r="S67" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T67" s="10" t="s">
         <v>32</v>
@@ -5530,7 +5534,7 @@
         <v>46203.81564377315</v>
       </c>
       <c r="D69" s="8">
-        <v>46204.900270983795</v>
+        <v>46208.21071721065</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>250</v>
@@ -5573,7 +5577,7 @@
         <v>46272</v>
       </c>
       <c r="S69" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T69" s="10" t="s">
         <v>32</v>
@@ -5593,7 +5597,7 @@
         <v>46204.89777927083</v>
       </c>
       <c r="D70" s="5">
-        <v>46204.90025034722</v>
+        <v>46208.210717662034</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>255</v>
@@ -5636,7 +5640,7 @@
         <v>46273</v>
       </c>
       <c r="S70" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T70" s="10" t="s">
         <v>32</v>
@@ -5656,7 +5660,7 @@
         <v>46196.9230577662</v>
       </c>
       <c r="D71" s="8">
-        <v>46204.900126967594</v>
+        <v>46208.210718125</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>259</v>
@@ -5699,7 +5703,7 @@
         <v>46274</v>
       </c>
       <c r="S71" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T71" s="10" t="s">
         <v>32</v>

--- a/data/50001533 - GESVIAL.xlsx
+++ b/data/50001533 - GESVIAL.xlsx
@@ -5721,7 +5721,7 @@
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46196.92306840278</v>
+        <v>46209.53540731482</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>264</v>

--- a/data/50001533 - GESVIAL.xlsx
+++ b/data/50001533 - GESVIAL.xlsx
@@ -5721,7 +5721,7 @@
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46209.53540731482</v>
+        <v>46209.72177900463</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>264</v>
@@ -5769,8 +5769,8 @@
       <c r="T72" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="U72" s="11" t="s">
-        <v>108</v>
+      <c r="U72" s="12" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001533 - GESVIAL.xlsx
+++ b/data/50001533 - GESVIAL.xlsx
@@ -4676,7 +4676,7 @@
         <v>46193.56240042824</v>
       </c>
       <c r="D55" s="8">
-        <v>46208.21032709491</v>
+        <v>46210.19828702546</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>209</v>
@@ -4723,8 +4723,8 @@
       <c r="S55" s="9">
         <v>1</v>
       </c>
-      <c r="T55" s="10" t="s">
-        <v>32</v>
+      <c r="T55" s="11" t="s">
+        <v>55</v>
       </c>
       <c r="U55" s="11" t="s">
         <v>108</v>
@@ -5721,7 +5721,7 @@
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46209.72177900463</v>
+        <v>46210.542481145836</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>264</v>

--- a/data/50001533 - GESVIAL.xlsx
+++ b/data/50001533 - GESVIAL.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="947" uniqueCount="283">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="948" uniqueCount="283">
   <si>
     <t xml:space="preserve"> 50001533 - GESVIAL</t>
   </si>
@@ -5483,9 +5483,11 @@
       <c r="B68" s="5">
         <v>46118.66242769676</v>
       </c>
-      <c r="C68" s="6"/>
+      <c r="C68" s="5">
+        <v>46210.640963275466</v>
+      </c>
       <c r="D68" s="5">
-        <v>46204.897786747686</v>
+        <v>46210.64097907407</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>247</v>
@@ -5519,9 +5521,13 @@
       </c>
       <c r="Q68" s="6"/>
       <c r="R68" s="6"/>
-      <c r="S68" s="6"/>
+      <c r="S68" s="6">
+        <v>1</v>
+      </c>
       <c r="T68" s="6"/>
-      <c r="U68" s="6"/>
+      <c r="U68" s="10" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
@@ -5719,9 +5725,11 @@
       <c r="B72" s="5">
         <v>46118.66245769676</v>
       </c>
-      <c r="C72" s="6"/>
+      <c r="C72" s="5">
+        <v>46210.64094128472</v>
+      </c>
       <c r="D72" s="5">
-        <v>46210.542481145836</v>
+        <v>46210.64281188657</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>264</v>
@@ -5764,13 +5772,13 @@
         <v>46275</v>
       </c>
       <c r="S72" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T72" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="U72" s="12" t="s">
-        <v>93</v>
+      <c r="U72" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
@@ -5829,7 +5837,7 @@
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46118.76810806713</v>
+        <v>46210.64097208333</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>270</v>
@@ -5879,8 +5887,8 @@
       <c r="T74" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="U74" s="11" t="s">
-        <v>108</v>
+      <c r="U74" s="12" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
@@ -5892,7 +5900,7 @@
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46191.7722621412</v>
+        <v>46210.64097256944</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>274</v>
@@ -5942,8 +5950,8 @@
       <c r="T75" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="U75" s="11" t="s">
-        <v>108</v>
+      <c r="U75" s="12" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
@@ -6002,7 +6010,7 @@
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46118.7682625</v>
+        <v>46210.64097050926</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>279</v>
@@ -6052,8 +6060,8 @@
       <c r="T77" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="U77" s="11" t="s">
-        <v>108</v>
+      <c r="U77" s="12" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001533 - GESVIAL.xlsx
+++ b/data/50001533 - GESVIAL.xlsx
@@ -1577,13 +1577,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46118.66185005787</v>
+        <v>46118.495183391206</v>
       </c>
       <c r="C4" s="5">
-        <v>46129.56083631945</v>
+        <v>46129.394169652776</v>
       </c>
       <c r="D4" s="5">
-        <v>46148.01378729167</v>
+        <v>46147.847120624996</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1626,13 +1626,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46118.662012175926</v>
+        <v>46118.49534550926</v>
       </c>
       <c r="C5" s="8">
-        <v>46129.559856481486</v>
+        <v>46129.393189814815</v>
       </c>
       <c r="D5" s="8">
-        <v>46133.87722729167</v>
+        <v>46133.710560625</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1691,13 +1691,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46118.662015567126</v>
+        <v>46118.49534890046</v>
       </c>
       <c r="C6" s="5">
-        <v>46129.55991743055</v>
+        <v>46129.39325076389</v>
       </c>
       <c r="D6" s="5">
-        <v>46129.55993412037</v>
+        <v>46129.393267453706</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -1756,13 +1756,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="8">
-        <v>46118.662018773146</v>
+        <v>46118.49535210648</v>
       </c>
       <c r="C7" s="8">
-        <v>46129.56027341435</v>
+        <v>46129.39360674769</v>
       </c>
       <c r="D7" s="8">
-        <v>46129.560290416666</v>
+        <v>46129.39362375</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>38</v>
@@ -1821,13 +1821,13 @@
         <v>40</v>
       </c>
       <c r="B8" s="5">
-        <v>46118.66202195601</v>
+        <v>46118.49535528936</v>
       </c>
       <c r="C8" s="5">
-        <v>46129.56068634259</v>
+        <v>46129.39401967592</v>
       </c>
       <c r="D8" s="5">
-        <v>46129.56070206019</v>
+        <v>46129.39403539352</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>41</v>
@@ -1886,13 +1886,13 @@
         <v>44</v>
       </c>
       <c r="B9" s="8">
-        <v>46118.66202614583</v>
+        <v>46118.495359479166</v>
       </c>
       <c r="C9" s="8">
-        <v>46129.560821747684</v>
+        <v>46129.39415508102</v>
       </c>
       <c r="D9" s="8">
-        <v>46156.83862056713</v>
+        <v>46156.67195390046</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>45</v>
@@ -1951,13 +1951,13 @@
         <v>47</v>
       </c>
       <c r="B10" s="5">
-        <v>46118.66185618055</v>
+        <v>46118.49518951389</v>
       </c>
       <c r="C10" s="5">
-        <v>46204.65215401621</v>
+        <v>46204.485487349535</v>
       </c>
       <c r="D10" s="5">
-        <v>46204.65215631944</v>
+        <v>46204.48548965278</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>48</v>
@@ -2000,13 +2000,13 @@
         <v>50</v>
       </c>
       <c r="B11" s="8">
-        <v>46118.6620300463</v>
+        <v>46118.495363379625</v>
       </c>
       <c r="C11" s="8">
-        <v>46129.57129943287</v>
+        <v>46129.40463276621</v>
       </c>
       <c r="D11" s="8">
-        <v>46129.57131482639</v>
+        <v>46129.40464815972</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>51</v>
@@ -2065,13 +2065,13 @@
         <v>56</v>
       </c>
       <c r="B12" s="5">
-        <v>46118.66203578704</v>
+        <v>46118.49536912037</v>
       </c>
       <c r="C12" s="5">
-        <v>46196.89571644676</v>
+        <v>46196.72904978009</v>
       </c>
       <c r="D12" s="5">
-        <v>46196.89571872685</v>
+        <v>46196.72905206018</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>57</v>
@@ -2130,13 +2130,13 @@
         <v>60</v>
       </c>
       <c r="B13" s="8">
-        <v>46118.66186076389</v>
+        <v>46118.495194097224</v>
       </c>
       <c r="C13" s="8">
-        <v>46193.56179229167</v>
+        <v>46193.395125625</v>
       </c>
       <c r="D13" s="8">
-        <v>46193.561794629626</v>
+        <v>46193.39512796296</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>61</v>
@@ -2179,13 +2179,13 @@
         <v>63</v>
       </c>
       <c r="B14" s="5">
-        <v>46118.66204173611</v>
+        <v>46118.49537506944</v>
       </c>
       <c r="C14" s="5">
-        <v>46129.56192828703</v>
+        <v>46129.395261620375</v>
       </c>
       <c r="D14" s="5">
-        <v>46191.77226219907</v>
+        <v>46191.60559553241</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>64</v>
@@ -2244,13 +2244,13 @@
         <v>67</v>
       </c>
       <c r="B15" s="8">
-        <v>46118.66204752315</v>
+        <v>46118.49538085648</v>
       </c>
       <c r="C15" s="8">
-        <v>46129.561938796294</v>
+        <v>46129.39527212963</v>
       </c>
       <c r="D15" s="8">
-        <v>46191.77226225694</v>
+        <v>46191.60559559028</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>68</v>
@@ -2309,13 +2309,13 @@
         <v>71</v>
       </c>
       <c r="B16" s="5">
-        <v>46118.66205295139</v>
+        <v>46118.49538628472</v>
       </c>
       <c r="C16" s="5">
-        <v>46129.56711804398</v>
+        <v>46129.40045137731</v>
       </c>
       <c r="D16" s="5">
-        <v>46191.7722621412</v>
+        <v>46191.60559547454</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>72</v>
@@ -2374,13 +2374,13 @@
         <v>75</v>
       </c>
       <c r="B17" s="8">
-        <v>46118.6618661574</v>
+        <v>46118.495199490746</v>
       </c>
       <c r="C17" s="8">
-        <v>46184.72974263889</v>
+        <v>46184.563075972226</v>
       </c>
       <c r="D17" s="8">
-        <v>46184.72974401621</v>
+        <v>46184.563077349536</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>76</v>
@@ -2423,13 +2423,13 @@
         <v>78</v>
       </c>
       <c r="B18" s="5">
-        <v>46118.66206653936</v>
+        <v>46118.495399872685</v>
       </c>
       <c r="C18" s="5">
-        <v>46129.56233884259</v>
+        <v>46129.395672175924</v>
       </c>
       <c r="D18" s="5">
-        <v>46129.56236072916</v>
+        <v>46129.3956940625</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>79</v>
@@ -2488,13 +2488,13 @@
         <v>82</v>
       </c>
       <c r="B19" s="8">
-        <v>46118.66207174768</v>
+        <v>46118.49540508102</v>
       </c>
       <c r="C19" s="8">
-        <v>46129.56234587963</v>
+        <v>46129.39567921296</v>
       </c>
       <c r="D19" s="8">
-        <v>46129.56236737268</v>
+        <v>46129.39570070602</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>83</v>
@@ -2553,13 +2553,13 @@
         <v>85</v>
       </c>
       <c r="B20" s="5">
-        <v>46118.66207709491</v>
+        <v>46118.49541042824</v>
       </c>
       <c r="C20" s="5">
-        <v>46129.57133789352</v>
+        <v>46129.40467122685</v>
       </c>
       <c r="D20" s="5">
-        <v>46129.57135429398</v>
+        <v>46129.40468762731</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>86</v>
@@ -2618,13 +2618,13 @@
         <v>89</v>
       </c>
       <c r="B21" s="8">
-        <v>46118.66208231481</v>
+        <v>46118.49541564815</v>
       </c>
       <c r="C21" s="8">
-        <v>46183.88010105324</v>
+        <v>46183.71343438658</v>
       </c>
       <c r="D21" s="8">
-        <v>46208.21006932871</v>
+        <v>46208.043402662035</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>90</v>
@@ -2683,13 +2683,13 @@
         <v>94</v>
       </c>
       <c r="B22" s="5">
-        <v>46118.662087523146</v>
+        <v>46118.49542085648</v>
       </c>
       <c r="C22" s="5">
-        <v>46183.888051863425</v>
+        <v>46183.72138519676</v>
       </c>
       <c r="D22" s="5">
-        <v>46208.21011525463</v>
+        <v>46208.04344858797</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>95</v>
@@ -2748,13 +2748,13 @@
         <v>100</v>
       </c>
       <c r="B23" s="8">
-        <v>46118.66187195602</v>
+        <v>46118.49520528935</v>
       </c>
       <c r="C23" s="8">
-        <v>46184.68624671296</v>
+        <v>46184.5195800463</v>
       </c>
       <c r="D23" s="8">
-        <v>46184.686248067126</v>
+        <v>46184.51958140046</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>101</v>
@@ -2797,13 +2797,13 @@
         <v>103</v>
       </c>
       <c r="B24" s="5">
-        <v>46118.662093692124</v>
+        <v>46118.49542702547</v>
       </c>
       <c r="C24" s="5">
-        <v>46182.67644689815</v>
+        <v>46182.509780231485</v>
       </c>
       <c r="D24" s="5">
-        <v>46208.21003241898</v>
+        <v>46208.04336575231</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>104</v>
@@ -2862,13 +2862,13 @@
         <v>109</v>
       </c>
       <c r="B25" s="8">
-        <v>46118.66209846065</v>
+        <v>46118.495431793985</v>
       </c>
       <c r="C25" s="8">
-        <v>46174.62568537037</v>
+        <v>46174.4590187037</v>
       </c>
       <c r="D25" s="8">
-        <v>46208.21094784723</v>
+        <v>46208.044281180555</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>110</v>
@@ -2919,13 +2919,13 @@
         <v>112</v>
       </c>
       <c r="B26" s="5">
-        <v>46118.66210270833</v>
+        <v>46118.49543604167</v>
       </c>
       <c r="C26" s="5">
-        <v>46182.64328993055</v>
+        <v>46182.476623263894</v>
       </c>
       <c r="D26" s="5">
-        <v>46208.21109037037</v>
+        <v>46208.0444237037</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>113</v>
@@ -2976,13 +2976,13 @@
         <v>115</v>
       </c>
       <c r="B27" s="8">
-        <v>46118.662106979165</v>
+        <v>46118.4954403125</v>
       </c>
       <c r="C27" s="8">
-        <v>46182.641066956014</v>
+        <v>46182.47440028936</v>
       </c>
       <c r="D27" s="8">
-        <v>46208.209962824076</v>
+        <v>46208.04329615741</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>116</v>
@@ -3041,13 +3041,13 @@
         <v>118</v>
       </c>
       <c r="B28" s="5">
-        <v>46118.662112094906</v>
+        <v>46118.49544542824</v>
       </c>
       <c r="C28" s="5">
-        <v>46174.626521666665</v>
+        <v>46174.459855</v>
       </c>
       <c r="D28" s="5">
-        <v>46208.21118949074</v>
+        <v>46208.04452282407</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>119</v>
@@ -3102,13 +3102,13 @@
         <v>121</v>
       </c>
       <c r="B29" s="8">
-        <v>46118.66211693287</v>
+        <v>46118.4954502662</v>
       </c>
       <c r="C29" s="8">
-        <v>46174.626630416664</v>
+        <v>46174.45996375</v>
       </c>
       <c r="D29" s="8">
-        <v>46208.21130763889</v>
+        <v>46208.04464097222</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>122</v>
@@ -3163,13 +3163,13 @@
         <v>124</v>
       </c>
       <c r="B30" s="5">
-        <v>46118.66212202546</v>
+        <v>46118.495455358796</v>
       </c>
       <c r="C30" s="5">
-        <v>46184.68608144676</v>
+        <v>46184.519414780094</v>
       </c>
       <c r="D30" s="5">
-        <v>46208.20888993055</v>
+        <v>46208.04222326389</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>125</v>
@@ -3228,13 +3228,13 @@
         <v>127</v>
       </c>
       <c r="B31" s="8">
-        <v>46118.662126678246</v>
+        <v>46118.495460011574</v>
       </c>
       <c r="C31" s="8">
-        <v>46184.68571903935</v>
+        <v>46184.519052372685</v>
       </c>
       <c r="D31" s="8">
-        <v>46208.211394502316</v>
+        <v>46208.044727835644</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>128</v>
@@ -3289,13 +3289,13 @@
         <v>130</v>
       </c>
       <c r="B32" s="5">
-        <v>46118.662131261575</v>
+        <v>46118.495464594904</v>
       </c>
       <c r="C32" s="5">
-        <v>46184.68578890046</v>
+        <v>46184.519122233796</v>
       </c>
       <c r="D32" s="5">
-        <v>46208.21147013889</v>
+        <v>46208.04480347222</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>131</v>
@@ -3350,13 +3350,13 @@
         <v>133</v>
       </c>
       <c r="B33" s="8">
-        <v>46118.66218372685</v>
+        <v>46118.49551706019</v>
       </c>
       <c r="C33" s="8">
-        <v>46156.821339988426</v>
+        <v>46156.654673321755</v>
       </c>
       <c r="D33" s="8">
-        <v>46169.82398277777</v>
+        <v>46169.657316111116</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>134</v>
@@ -3415,13 +3415,13 @@
         <v>136</v>
       </c>
       <c r="B34" s="5">
-        <v>46118.662190104165</v>
+        <v>46118.4955234375</v>
       </c>
       <c r="C34" s="5">
-        <v>46134.79115269676</v>
+        <v>46134.624486030094</v>
       </c>
       <c r="D34" s="5">
-        <v>46208.211555636575</v>
+        <v>46208.044888969904</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>137</v>
@@ -3476,13 +3476,13 @@
         <v>139</v>
       </c>
       <c r="B35" s="8">
-        <v>46118.662195694444</v>
+        <v>46118.49552902778</v>
       </c>
       <c r="C35" s="8">
-        <v>46155.90268767361</v>
+        <v>46155.736021006946</v>
       </c>
       <c r="D35" s="8">
-        <v>46208.21164188658</v>
+        <v>46208.044975219906</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>140</v>
@@ -3537,13 +3537,13 @@
         <v>142</v>
       </c>
       <c r="B36" s="5">
-        <v>46118.66220082176</v>
+        <v>46118.495534155096</v>
       </c>
       <c r="C36" s="5">
-        <v>46134.79119539352</v>
+        <v>46134.624528726854</v>
       </c>
       <c r="D36" s="5">
-        <v>46208.211714791665</v>
+        <v>46208.045048125</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>143</v>
@@ -3598,13 +3598,13 @@
         <v>145</v>
       </c>
       <c r="B37" s="8">
-        <v>46118.66220634259</v>
+        <v>46118.495539675925</v>
       </c>
       <c r="C37" s="8">
-        <v>46184.686103796295</v>
+        <v>46184.51943712963</v>
       </c>
       <c r="D37" s="8">
-        <v>46208.208834942125</v>
+        <v>46208.04216827547</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>146</v>
@@ -3663,13 +3663,13 @@
         <v>149</v>
       </c>
       <c r="B38" s="5">
-        <v>46118.66221234953</v>
+        <v>46118.495545682876</v>
       </c>
       <c r="C38" s="5">
-        <v>46184.53094861111</v>
+        <v>46184.36428194444</v>
       </c>
       <c r="D38" s="5">
-        <v>46208.21179649305</v>
+        <v>46208.045129826394</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>150</v>
@@ -3724,13 +3724,13 @@
         <v>152</v>
       </c>
       <c r="B39" s="8">
-        <v>46118.66221657407</v>
+        <v>46118.495549907406</v>
       </c>
       <c r="C39" s="8">
-        <v>46184.53162540509</v>
+        <v>46184.36495873843</v>
       </c>
       <c r="D39" s="8">
-        <v>46208.211892453706</v>
+        <v>46208.045225787035</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>151</v>
@@ -3785,13 +3785,13 @@
         <v>154</v>
       </c>
       <c r="B40" s="5">
-        <v>46118.662220972226</v>
+        <v>46118.495554305555</v>
       </c>
       <c r="C40" s="5">
-        <v>46204.65218209491</v>
+        <v>46204.48551542824</v>
       </c>
       <c r="D40" s="5">
-        <v>46204.652183645834</v>
+        <v>46204.48551697917</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>155</v>
@@ -3834,13 +3834,13 @@
         <v>157</v>
       </c>
       <c r="B41" s="8">
-        <v>46118.66222521991</v>
+        <v>46118.495558553244</v>
       </c>
       <c r="C41" s="8">
-        <v>46129.567182349536</v>
+        <v>46129.40051568287</v>
       </c>
       <c r="D41" s="8">
-        <v>46129.57417895833</v>
+        <v>46129.40751229167</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>158</v>
@@ -3899,13 +3899,13 @@
         <v>162</v>
       </c>
       <c r="B42" s="5">
-        <v>46118.66223170139</v>
+        <v>46118.495565034726</v>
       </c>
       <c r="C42" s="5">
-        <v>46134.80026672454</v>
+        <v>46134.633600057874</v>
       </c>
       <c r="D42" s="5">
-        <v>46134.80028269676</v>
+        <v>46134.63361603009</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>163</v>
@@ -3964,13 +3964,13 @@
         <v>168</v>
       </c>
       <c r="B43" s="8">
-        <v>46118.662239375</v>
+        <v>46118.49557270833</v>
       </c>
       <c r="C43" s="8">
-        <v>46134.80039372685</v>
+        <v>46134.63372706018</v>
       </c>
       <c r="D43" s="8">
-        <v>46134.80040836806</v>
+        <v>46134.633741701386</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>98</v>
@@ -4027,13 +4027,13 @@
         <v>170</v>
       </c>
       <c r="B44" s="5">
-        <v>46118.662245300926</v>
+        <v>46118.49557863426</v>
       </c>
       <c r="C44" s="5">
-        <v>46198.5694571412</v>
+        <v>46198.40279047454</v>
       </c>
       <c r="D44" s="5">
-        <v>46208.20879145833</v>
+        <v>46208.04212479167</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>171</v>
@@ -4092,13 +4092,13 @@
         <v>176</v>
       </c>
       <c r="B45" s="8">
-        <v>46118.66224984954</v>
+        <v>46118.49558318287</v>
       </c>
       <c r="C45" s="8">
-        <v>46184.68718685185</v>
+        <v>46184.520520185186</v>
       </c>
       <c r="D45" s="8">
-        <v>46184.68718828703</v>
+        <v>46184.520521620376</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>177</v>
@@ -4141,13 +4141,13 @@
         <v>179</v>
       </c>
       <c r="B46" s="5">
-        <v>46118.66225350695</v>
+        <v>46118.495586840276</v>
       </c>
       <c r="C46" s="5">
-        <v>46184.68670658565</v>
+        <v>46184.52003991898</v>
       </c>
       <c r="D46" s="5">
-        <v>46208.20988328704</v>
+        <v>46208.04321662037</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>153</v>
@@ -4206,13 +4206,13 @@
         <v>183</v>
       </c>
       <c r="B47" s="8">
-        <v>46118.66225863426</v>
+        <v>46118.49559196759</v>
       </c>
       <c r="C47" s="8">
-        <v>46184.6869659838</v>
+        <v>46184.520299317126</v>
       </c>
       <c r="D47" s="8">
-        <v>46208.20991337963</v>
+        <v>46208.04324671296</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>184</v>
@@ -4271,13 +4271,13 @@
         <v>188</v>
       </c>
       <c r="B48" s="5">
-        <v>46118.662263819446</v>
+        <v>46118.49559715278</v>
       </c>
       <c r="C48" s="5">
-        <v>46194.056337268514</v>
+        <v>46193.88967060186</v>
       </c>
       <c r="D48" s="5">
-        <v>46194.05633912037</v>
+        <v>46193.889672453704</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>189</v>
@@ -4320,13 +4320,13 @@
         <v>191</v>
       </c>
       <c r="B49" s="8">
-        <v>46118.66226751157</v>
+        <v>46118.49560084491</v>
       </c>
       <c r="C49" s="8">
-        <v>46184.687951203705</v>
+        <v>46184.52128453704</v>
       </c>
       <c r="D49" s="8">
-        <v>46208.210227986114</v>
+        <v>46208.04356131944</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>192</v>
@@ -4385,13 +4385,13 @@
         <v>196</v>
       </c>
       <c r="B50" s="5">
-        <v>46118.66227269676</v>
+        <v>46118.49560603009</v>
       </c>
       <c r="C50" s="5">
-        <v>46193.56191304398</v>
+        <v>46193.39524637732</v>
       </c>
       <c r="D50" s="5">
-        <v>46208.210261203705</v>
+        <v>46208.04359453704</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>197</v>
@@ -4450,13 +4450,13 @@
         <v>200</v>
       </c>
       <c r="B51" s="8">
-        <v>46184.687980393515</v>
+        <v>46184.52131372685</v>
       </c>
       <c r="C51" s="8">
-        <v>46184.68921728009</v>
+        <v>46184.52255061343</v>
       </c>
       <c r="D51" s="8">
-        <v>46191.68718039352</v>
+        <v>46191.52051372685</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>201</v>
@@ -4505,13 +4505,13 @@
         <v>202</v>
       </c>
       <c r="B52" s="5">
-        <v>46184.688093055556</v>
+        <v>46184.52142638889</v>
       </c>
       <c r="C52" s="5">
-        <v>46195.7025405787</v>
+        <v>46195.53587391204</v>
       </c>
       <c r="D52" s="5">
-        <v>46195.70254238426</v>
+        <v>46195.53587571759</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>203</v>
@@ -4560,13 +4560,13 @@
         <v>204</v>
       </c>
       <c r="B53" s="8">
-        <v>46184.68816803241</v>
+        <v>46184.52150136574</v>
       </c>
       <c r="C53" s="8">
-        <v>46184.69000751157</v>
+        <v>46184.523340844906</v>
       </c>
       <c r="D53" s="8">
-        <v>46191.6871738426</v>
+        <v>46191.52050717593</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>205</v>
@@ -4615,13 +4615,13 @@
         <v>206</v>
       </c>
       <c r="B54" s="5">
-        <v>46184.68826700232</v>
+        <v>46184.52160033565</v>
       </c>
       <c r="C54" s="5">
-        <v>46184.69031962963</v>
+        <v>46184.52365296296</v>
       </c>
       <c r="D54" s="5">
-        <v>46191.687168993056</v>
+        <v>46191.520502326384</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>207</v>
@@ -4670,13 +4670,13 @@
         <v>208</v>
       </c>
       <c r="B55" s="8">
-        <v>46118.66227863426</v>
+        <v>46118.49561196759</v>
       </c>
       <c r="C55" s="8">
-        <v>46193.56240042824</v>
+        <v>46193.39573376157</v>
       </c>
       <c r="D55" s="8">
-        <v>46210.19828702546</v>
+        <v>46210.0316203588</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>209</v>
@@ -4735,13 +4735,13 @@
         <v>212</v>
       </c>
       <c r="B56" s="5">
-        <v>46118.66228488426</v>
+        <v>46118.495618217596</v>
       </c>
       <c r="C56" s="5">
-        <v>46194.05632121528</v>
+        <v>46193.889654548606</v>
       </c>
       <c r="D56" s="5">
-        <v>46194.05632325231</v>
+        <v>46193.88965658565</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>177</v>
@@ -4784,13 +4784,13 @@
         <v>214</v>
       </c>
       <c r="B57" s="8">
-        <v>46118.66228803241</v>
+        <v>46118.49562136574</v>
       </c>
       <c r="C57" s="8">
-        <v>46193.562345370374</v>
+        <v>46193.3956787037</v>
       </c>
       <c r="D57" s="8">
-        <v>46208.21036678241</v>
+        <v>46208.04370011574</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>215</v>
@@ -4849,13 +4849,13 @@
         <v>217</v>
       </c>
       <c r="B58" s="5">
-        <v>46118.662293518515</v>
+        <v>46118.49562685185</v>
       </c>
       <c r="C58" s="5">
-        <v>46193.56197458333</v>
+        <v>46193.39530791667</v>
       </c>
       <c r="D58" s="5">
-        <v>46208.210472280094</v>
+        <v>46208.04380561343</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>58</v>
@@ -4914,13 +4914,13 @@
         <v>219</v>
       </c>
       <c r="B59" s="8">
-        <v>46118.662299895834</v>
+        <v>46118.49563322916</v>
       </c>
       <c r="C59" s="8">
-        <v>46193.561984872686</v>
+        <v>46193.39531820602</v>
       </c>
       <c r="D59" s="8">
-        <v>46208.21047276621</v>
+        <v>46208.04380609954</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>220</v>
@@ -4979,13 +4979,13 @@
         <v>222</v>
       </c>
       <c r="B60" s="5">
-        <v>46118.66235550926</v>
+        <v>46118.495688842595</v>
       </c>
       <c r="C60" s="5">
-        <v>46193.56199724537</v>
+        <v>46193.3953305787</v>
       </c>
       <c r="D60" s="5">
-        <v>46208.210473217594</v>
+        <v>46208.04380655092</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>223</v>
@@ -5044,13 +5044,13 @@
         <v>225</v>
       </c>
       <c r="B61" s="8">
-        <v>46118.66236295139</v>
+        <v>46118.49569628472</v>
       </c>
       <c r="C61" s="8">
-        <v>46193.765035358796</v>
+        <v>46193.598368692124</v>
       </c>
       <c r="D61" s="8">
-        <v>46204.900153703704</v>
+        <v>46204.73348703704</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>226</v>
@@ -5093,13 +5093,13 @@
         <v>228</v>
       </c>
       <c r="B62" s="5">
-        <v>46118.66236873843</v>
+        <v>46118.495702071756</v>
       </c>
       <c r="C62" s="5">
-        <v>46193.61261344908</v>
+        <v>46193.445946782405</v>
       </c>
       <c r="D62" s="5">
-        <v>46208.21062993056</v>
+        <v>46208.04396326389</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>229</v>
@@ -5158,13 +5158,13 @@
         <v>231</v>
       </c>
       <c r="B63" s="8">
-        <v>46118.662376064814</v>
+        <v>46118.49570939815</v>
       </c>
       <c r="C63" s="8">
-        <v>46193.6126587037</v>
+        <v>46193.445992037035</v>
       </c>
       <c r="D63" s="8">
-        <v>46208.21062945602</v>
+        <v>46208.04396278935</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>224</v>
@@ -5223,13 +5223,13 @@
         <v>234</v>
       </c>
       <c r="B64" s="5">
-        <v>46118.662387557866</v>
+        <v>46118.4957208912</v>
       </c>
       <c r="C64" s="5">
-        <v>46193.61267944444</v>
+        <v>46193.44601277778</v>
       </c>
       <c r="D64" s="5">
-        <v>46208.21063037037</v>
+        <v>46208.043963703705</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>235</v>
@@ -5288,13 +5288,13 @@
         <v>237</v>
       </c>
       <c r="B65" s="8">
-        <v>46118.662398796296</v>
+        <v>46118.495732129624</v>
       </c>
       <c r="C65" s="8">
-        <v>46193.61273716435</v>
+        <v>46193.44607049768</v>
       </c>
       <c r="D65" s="8">
-        <v>46208.21062888889</v>
+        <v>46208.04396222222</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>238</v>
@@ -5353,13 +5353,13 @@
         <v>240</v>
       </c>
       <c r="B66" s="5">
-        <v>46118.66240984954</v>
+        <v>46118.495743182866</v>
       </c>
       <c r="C66" s="5">
-        <v>46193.765511875</v>
+        <v>46193.59884520833</v>
       </c>
       <c r="D66" s="5">
-        <v>46208.21062840278</v>
+        <v>46208.04396173611</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>174</v>
@@ -5416,13 +5416,13 @@
         <v>243</v>
       </c>
       <c r="B67" s="8">
-        <v>46118.662420127315</v>
+        <v>46118.49575346065</v>
       </c>
       <c r="C67" s="8">
-        <v>46196.92346424768</v>
+        <v>46196.75679758102</v>
       </c>
       <c r="D67" s="8">
-        <v>46208.21062791666</v>
+        <v>46208.043961250005</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>244</v>
@@ -5481,13 +5481,13 @@
         <v>246</v>
       </c>
       <c r="B68" s="5">
-        <v>46118.66242769676</v>
+        <v>46118.49576103009</v>
       </c>
       <c r="C68" s="5">
-        <v>46210.640963275466</v>
+        <v>46210.474296608794</v>
       </c>
       <c r="D68" s="5">
-        <v>46210.64097907407</v>
+        <v>46210.47431240741</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>247</v>
@@ -5534,13 +5534,13 @@
         <v>249</v>
       </c>
       <c r="B69" s="8">
-        <v>46118.662431770834</v>
+        <v>46118.49576510416</v>
       </c>
       <c r="C69" s="8">
-        <v>46203.81564377315</v>
+        <v>46203.64897710648</v>
       </c>
       <c r="D69" s="8">
-        <v>46208.21071721065</v>
+        <v>46208.04405054398</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>250</v>
@@ -5597,13 +5597,13 @@
         <v>254</v>
       </c>
       <c r="B70" s="5">
-        <v>46118.662438252315</v>
+        <v>46118.49577158564</v>
       </c>
       <c r="C70" s="5">
-        <v>46204.89777927083</v>
+        <v>46204.73111260417</v>
       </c>
       <c r="D70" s="5">
-        <v>46208.210717662034</v>
+        <v>46208.04405099537</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>255</v>
@@ -5660,13 +5660,13 @@
         <v>258</v>
       </c>
       <c r="B71" s="8">
-        <v>46118.66245149306</v>
+        <v>46118.49578482639</v>
       </c>
       <c r="C71" s="8">
-        <v>46196.9230577662</v>
+        <v>46196.75639109954</v>
       </c>
       <c r="D71" s="8">
-        <v>46208.210718125</v>
+        <v>46208.04405145833</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>259</v>
@@ -5723,13 +5723,13 @@
         <v>263</v>
       </c>
       <c r="B72" s="5">
-        <v>46118.66245769676</v>
+        <v>46118.49579103009</v>
       </c>
       <c r="C72" s="5">
-        <v>46210.64094128472</v>
+        <v>46210.47427461806</v>
       </c>
       <c r="D72" s="5">
-        <v>46210.64281188657</v>
+        <v>46210.47614521991</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>264</v>
@@ -5786,11 +5786,11 @@
         <v>266</v>
       </c>
       <c r="B73" s="8">
-        <v>46118.66246467593</v>
+        <v>46118.49579800926</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46118.76284858796</v>
+        <v>46118.5961819213</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>267</v>
@@ -5833,11 +5833,11 @@
         <v>269</v>
       </c>
       <c r="B74" s="5">
-        <v>46118.66246796296</v>
+        <v>46118.495801296296</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46210.64097208333</v>
+        <v>46210.47430541667</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>270</v>
@@ -5896,11 +5896,11 @@
         <v>273</v>
       </c>
       <c r="B75" s="8">
-        <v>46118.66251259259</v>
+        <v>46118.49584592592</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46210.64097256944</v>
+        <v>46210.47430590278</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>274</v>
@@ -5959,11 +5959,11 @@
         <v>275</v>
       </c>
       <c r="B76" s="5">
-        <v>46118.662521377315</v>
+        <v>46118.49585471065</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46118.76362347222</v>
+        <v>46118.59695680556</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>276</v>
@@ -6006,11 +6006,11 @@
         <v>278</v>
       </c>
       <c r="B77" s="8">
-        <v>46118.66252565972</v>
+        <v>46118.495858993054</v>
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46210.64097050926</v>
+        <v>46210.474303842595</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>279</v>
@@ -6069,11 +6069,11 @@
         <v>281</v>
       </c>
       <c r="B78" s="5">
-        <v>46118.662532013885</v>
+        <v>46118.49586534723</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46118.76825962963</v>
+        <v>46118.601592962965</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>282</v>

--- a/data/50001533 - GESVIAL.xlsx
+++ b/data/50001533 - GESVIAL.xlsx
@@ -1577,13 +1577,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46118.495183391206</v>
+        <v>46118.66185005787</v>
       </c>
       <c r="C4" s="5">
-        <v>46129.394169652776</v>
+        <v>46129.56083631945</v>
       </c>
       <c r="D4" s="5">
-        <v>46147.847120624996</v>
+        <v>46148.01378729167</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1626,13 +1626,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46118.49534550926</v>
+        <v>46118.662012175926</v>
       </c>
       <c r="C5" s="8">
-        <v>46129.393189814815</v>
+        <v>46129.559856481486</v>
       </c>
       <c r="D5" s="8">
-        <v>46133.710560625</v>
+        <v>46133.87722729167</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1691,13 +1691,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46118.49534890046</v>
+        <v>46118.662015567126</v>
       </c>
       <c r="C6" s="5">
-        <v>46129.39325076389</v>
+        <v>46129.55991743055</v>
       </c>
       <c r="D6" s="5">
-        <v>46129.393267453706</v>
+        <v>46129.55993412037</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -1756,13 +1756,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="8">
-        <v>46118.49535210648</v>
+        <v>46118.662018773146</v>
       </c>
       <c r="C7" s="8">
-        <v>46129.39360674769</v>
+        <v>46129.56027341435</v>
       </c>
       <c r="D7" s="8">
-        <v>46129.39362375</v>
+        <v>46129.560290416666</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>38</v>
@@ -1821,13 +1821,13 @@
         <v>40</v>
       </c>
       <c r="B8" s="5">
-        <v>46118.49535528936</v>
+        <v>46118.66202195601</v>
       </c>
       <c r="C8" s="5">
-        <v>46129.39401967592</v>
+        <v>46129.56068634259</v>
       </c>
       <c r="D8" s="5">
-        <v>46129.39403539352</v>
+        <v>46129.56070206019</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>41</v>
@@ -1886,13 +1886,13 @@
         <v>44</v>
       </c>
       <c r="B9" s="8">
-        <v>46118.495359479166</v>
+        <v>46118.66202614583</v>
       </c>
       <c r="C9" s="8">
-        <v>46129.39415508102</v>
+        <v>46129.560821747684</v>
       </c>
       <c r="D9" s="8">
-        <v>46156.67195390046</v>
+        <v>46156.83862056713</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>45</v>
@@ -1951,13 +1951,13 @@
         <v>47</v>
       </c>
       <c r="B10" s="5">
-        <v>46118.49518951389</v>
+        <v>46118.66185618055</v>
       </c>
       <c r="C10" s="5">
-        <v>46204.485487349535</v>
+        <v>46204.65215401621</v>
       </c>
       <c r="D10" s="5">
-        <v>46204.48548965278</v>
+        <v>46204.65215631944</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>48</v>
@@ -2000,13 +2000,13 @@
         <v>50</v>
       </c>
       <c r="B11" s="8">
-        <v>46118.495363379625</v>
+        <v>46118.6620300463</v>
       </c>
       <c r="C11" s="8">
-        <v>46129.40463276621</v>
+        <v>46129.57129943287</v>
       </c>
       <c r="D11" s="8">
-        <v>46129.40464815972</v>
+        <v>46129.57131482639</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>51</v>
@@ -2065,13 +2065,13 @@
         <v>56</v>
       </c>
       <c r="B12" s="5">
-        <v>46118.49536912037</v>
+        <v>46118.66203578704</v>
       </c>
       <c r="C12" s="5">
-        <v>46196.72904978009</v>
+        <v>46196.89571644676</v>
       </c>
       <c r="D12" s="5">
-        <v>46196.72905206018</v>
+        <v>46196.89571872685</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>57</v>
@@ -2130,13 +2130,13 @@
         <v>60</v>
       </c>
       <c r="B13" s="8">
-        <v>46118.495194097224</v>
+        <v>46118.66186076389</v>
       </c>
       <c r="C13" s="8">
-        <v>46193.395125625</v>
+        <v>46193.56179229167</v>
       </c>
       <c r="D13" s="8">
-        <v>46193.39512796296</v>
+        <v>46193.561794629626</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>61</v>
@@ -2179,13 +2179,13 @@
         <v>63</v>
       </c>
       <c r="B14" s="5">
-        <v>46118.49537506944</v>
+        <v>46118.66204173611</v>
       </c>
       <c r="C14" s="5">
-        <v>46129.395261620375</v>
+        <v>46129.56192828703</v>
       </c>
       <c r="D14" s="5">
-        <v>46191.60559553241</v>
+        <v>46191.77226219907</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>64</v>
@@ -2244,13 +2244,13 @@
         <v>67</v>
       </c>
       <c r="B15" s="8">
-        <v>46118.49538085648</v>
+        <v>46118.66204752315</v>
       </c>
       <c r="C15" s="8">
-        <v>46129.39527212963</v>
+        <v>46129.561938796294</v>
       </c>
       <c r="D15" s="8">
-        <v>46191.60559559028</v>
+        <v>46191.77226225694</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>68</v>
@@ -2309,13 +2309,13 @@
         <v>71</v>
       </c>
       <c r="B16" s="5">
-        <v>46118.49538628472</v>
+        <v>46118.66205295139</v>
       </c>
       <c r="C16" s="5">
-        <v>46129.40045137731</v>
+        <v>46129.56711804398</v>
       </c>
       <c r="D16" s="5">
-        <v>46191.60559547454</v>
+        <v>46191.7722621412</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>72</v>
@@ -2374,13 +2374,13 @@
         <v>75</v>
       </c>
       <c r="B17" s="8">
-        <v>46118.495199490746</v>
+        <v>46118.6618661574</v>
       </c>
       <c r="C17" s="8">
-        <v>46184.563075972226</v>
+        <v>46184.72974263889</v>
       </c>
       <c r="D17" s="8">
-        <v>46184.563077349536</v>
+        <v>46184.72974401621</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>76</v>
@@ -2423,13 +2423,13 @@
         <v>78</v>
       </c>
       <c r="B18" s="5">
-        <v>46118.495399872685</v>
+        <v>46118.66206653936</v>
       </c>
       <c r="C18" s="5">
-        <v>46129.395672175924</v>
+        <v>46129.56233884259</v>
       </c>
       <c r="D18" s="5">
-        <v>46129.3956940625</v>
+        <v>46129.56236072916</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>79</v>
@@ -2488,13 +2488,13 @@
         <v>82</v>
       </c>
       <c r="B19" s="8">
-        <v>46118.49540508102</v>
+        <v>46118.66207174768</v>
       </c>
       <c r="C19" s="8">
-        <v>46129.39567921296</v>
+        <v>46129.56234587963</v>
       </c>
       <c r="D19" s="8">
-        <v>46129.39570070602</v>
+        <v>46129.56236737268</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>83</v>
@@ -2553,13 +2553,13 @@
         <v>85</v>
       </c>
       <c r="B20" s="5">
-        <v>46118.49541042824</v>
+        <v>46118.66207709491</v>
       </c>
       <c r="C20" s="5">
-        <v>46129.40467122685</v>
+        <v>46129.57133789352</v>
       </c>
       <c r="D20" s="5">
-        <v>46129.40468762731</v>
+        <v>46129.57135429398</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>86</v>
@@ -2618,13 +2618,13 @@
         <v>89</v>
       </c>
       <c r="B21" s="8">
-        <v>46118.49541564815</v>
+        <v>46118.66208231481</v>
       </c>
       <c r="C21" s="8">
-        <v>46183.71343438658</v>
+        <v>46183.88010105324</v>
       </c>
       <c r="D21" s="8">
-        <v>46208.043402662035</v>
+        <v>46208.21006932871</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>90</v>
@@ -2683,13 +2683,13 @@
         <v>94</v>
       </c>
       <c r="B22" s="5">
-        <v>46118.49542085648</v>
+        <v>46118.662087523146</v>
       </c>
       <c r="C22" s="5">
-        <v>46183.72138519676</v>
+        <v>46183.888051863425</v>
       </c>
       <c r="D22" s="5">
-        <v>46208.04344858797</v>
+        <v>46208.21011525463</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>95</v>
@@ -2748,13 +2748,13 @@
         <v>100</v>
       </c>
       <c r="B23" s="8">
-        <v>46118.49520528935</v>
+        <v>46118.66187195602</v>
       </c>
       <c r="C23" s="8">
-        <v>46184.5195800463</v>
+        <v>46184.68624671296</v>
       </c>
       <c r="D23" s="8">
-        <v>46184.51958140046</v>
+        <v>46184.686248067126</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>101</v>
@@ -2797,13 +2797,13 @@
         <v>103</v>
       </c>
       <c r="B24" s="5">
-        <v>46118.49542702547</v>
+        <v>46118.662093692124</v>
       </c>
       <c r="C24" s="5">
-        <v>46182.509780231485</v>
+        <v>46182.67644689815</v>
       </c>
       <c r="D24" s="5">
-        <v>46208.04336575231</v>
+        <v>46208.21003241898</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>104</v>
@@ -2862,13 +2862,13 @@
         <v>109</v>
       </c>
       <c r="B25" s="8">
-        <v>46118.495431793985</v>
+        <v>46118.66209846065</v>
       </c>
       <c r="C25" s="8">
-        <v>46174.4590187037</v>
+        <v>46174.62568537037</v>
       </c>
       <c r="D25" s="8">
-        <v>46208.044281180555</v>
+        <v>46208.21094784723</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>110</v>
@@ -2919,13 +2919,13 @@
         <v>112</v>
       </c>
       <c r="B26" s="5">
-        <v>46118.49543604167</v>
+        <v>46118.66210270833</v>
       </c>
       <c r="C26" s="5">
-        <v>46182.476623263894</v>
+        <v>46182.64328993055</v>
       </c>
       <c r="D26" s="5">
-        <v>46208.0444237037</v>
+        <v>46208.21109037037</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>113</v>
@@ -2976,13 +2976,13 @@
         <v>115</v>
       </c>
       <c r="B27" s="8">
-        <v>46118.4954403125</v>
+        <v>46118.662106979165</v>
       </c>
       <c r="C27" s="8">
-        <v>46182.47440028936</v>
+        <v>46182.641066956014</v>
       </c>
       <c r="D27" s="8">
-        <v>46208.04329615741</v>
+        <v>46208.209962824076</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>116</v>
@@ -3041,13 +3041,13 @@
         <v>118</v>
       </c>
       <c r="B28" s="5">
-        <v>46118.49544542824</v>
+        <v>46118.662112094906</v>
       </c>
       <c r="C28" s="5">
-        <v>46174.459855</v>
+        <v>46174.626521666665</v>
       </c>
       <c r="D28" s="5">
-        <v>46208.04452282407</v>
+        <v>46208.21118949074</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>119</v>
@@ -3102,13 +3102,13 @@
         <v>121</v>
       </c>
       <c r="B29" s="8">
-        <v>46118.4954502662</v>
+        <v>46118.66211693287</v>
       </c>
       <c r="C29" s="8">
-        <v>46174.45996375</v>
+        <v>46174.626630416664</v>
       </c>
       <c r="D29" s="8">
-        <v>46208.04464097222</v>
+        <v>46208.21130763889</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>122</v>
@@ -3163,13 +3163,13 @@
         <v>124</v>
       </c>
       <c r="B30" s="5">
-        <v>46118.495455358796</v>
+        <v>46118.66212202546</v>
       </c>
       <c r="C30" s="5">
-        <v>46184.519414780094</v>
+        <v>46184.68608144676</v>
       </c>
       <c r="D30" s="5">
-        <v>46208.04222326389</v>
+        <v>46208.20888993055</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>125</v>
@@ -3228,13 +3228,13 @@
         <v>127</v>
       </c>
       <c r="B31" s="8">
-        <v>46118.495460011574</v>
+        <v>46118.662126678246</v>
       </c>
       <c r="C31" s="8">
-        <v>46184.519052372685</v>
+        <v>46184.68571903935</v>
       </c>
       <c r="D31" s="8">
-        <v>46208.044727835644</v>
+        <v>46208.211394502316</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>128</v>
@@ -3289,13 +3289,13 @@
         <v>130</v>
       </c>
       <c r="B32" s="5">
-        <v>46118.495464594904</v>
+        <v>46118.662131261575</v>
       </c>
       <c r="C32" s="5">
-        <v>46184.519122233796</v>
+        <v>46184.68578890046</v>
       </c>
       <c r="D32" s="5">
-        <v>46208.04480347222</v>
+        <v>46208.21147013889</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>131</v>
@@ -3350,13 +3350,13 @@
         <v>133</v>
       </c>
       <c r="B33" s="8">
-        <v>46118.49551706019</v>
+        <v>46118.66218372685</v>
       </c>
       <c r="C33" s="8">
-        <v>46156.654673321755</v>
+        <v>46156.821339988426</v>
       </c>
       <c r="D33" s="8">
-        <v>46169.657316111116</v>
+        <v>46169.82398277777</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>134</v>
@@ -3415,13 +3415,13 @@
         <v>136</v>
       </c>
       <c r="B34" s="5">
-        <v>46118.4955234375</v>
+        <v>46118.662190104165</v>
       </c>
       <c r="C34" s="5">
-        <v>46134.624486030094</v>
+        <v>46134.79115269676</v>
       </c>
       <c r="D34" s="5">
-        <v>46208.044888969904</v>
+        <v>46208.211555636575</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>137</v>
@@ -3476,13 +3476,13 @@
         <v>139</v>
       </c>
       <c r="B35" s="8">
-        <v>46118.49552902778</v>
+        <v>46118.662195694444</v>
       </c>
       <c r="C35" s="8">
-        <v>46155.736021006946</v>
+        <v>46155.90268767361</v>
       </c>
       <c r="D35" s="8">
-        <v>46208.044975219906</v>
+        <v>46208.21164188658</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>140</v>
@@ -3537,13 +3537,13 @@
         <v>142</v>
       </c>
       <c r="B36" s="5">
-        <v>46118.495534155096</v>
+        <v>46118.66220082176</v>
       </c>
       <c r="C36" s="5">
-        <v>46134.624528726854</v>
+        <v>46134.79119539352</v>
       </c>
       <c r="D36" s="5">
-        <v>46208.045048125</v>
+        <v>46208.211714791665</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>143</v>
@@ -3598,13 +3598,13 @@
         <v>145</v>
       </c>
       <c r="B37" s="8">
-        <v>46118.495539675925</v>
+        <v>46118.66220634259</v>
       </c>
       <c r="C37" s="8">
-        <v>46184.51943712963</v>
+        <v>46184.686103796295</v>
       </c>
       <c r="D37" s="8">
-        <v>46208.04216827547</v>
+        <v>46208.208834942125</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>146</v>
@@ -3663,13 +3663,13 @@
         <v>149</v>
       </c>
       <c r="B38" s="5">
-        <v>46118.495545682876</v>
+        <v>46118.66221234953</v>
       </c>
       <c r="C38" s="5">
-        <v>46184.36428194444</v>
+        <v>46184.53094861111</v>
       </c>
       <c r="D38" s="5">
-        <v>46208.045129826394</v>
+        <v>46208.21179649305</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>150</v>
@@ -3724,13 +3724,13 @@
         <v>152</v>
       </c>
       <c r="B39" s="8">
-        <v>46118.495549907406</v>
+        <v>46118.66221657407</v>
       </c>
       <c r="C39" s="8">
-        <v>46184.36495873843</v>
+        <v>46184.53162540509</v>
       </c>
       <c r="D39" s="8">
-        <v>46208.045225787035</v>
+        <v>46208.211892453706</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>151</v>
@@ -3785,13 +3785,13 @@
         <v>154</v>
       </c>
       <c r="B40" s="5">
-        <v>46118.495554305555</v>
+        <v>46118.662220972226</v>
       </c>
       <c r="C40" s="5">
-        <v>46204.48551542824</v>
+        <v>46204.65218209491</v>
       </c>
       <c r="D40" s="5">
-        <v>46204.48551697917</v>
+        <v>46204.652183645834</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>155</v>
@@ -3834,13 +3834,13 @@
         <v>157</v>
       </c>
       <c r="B41" s="8">
-        <v>46118.495558553244</v>
+        <v>46118.66222521991</v>
       </c>
       <c r="C41" s="8">
-        <v>46129.40051568287</v>
+        <v>46129.567182349536</v>
       </c>
       <c r="D41" s="8">
-        <v>46129.40751229167</v>
+        <v>46129.57417895833</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>158</v>
@@ -3899,13 +3899,13 @@
         <v>162</v>
       </c>
       <c r="B42" s="5">
-        <v>46118.495565034726</v>
+        <v>46118.66223170139</v>
       </c>
       <c r="C42" s="5">
-        <v>46134.633600057874</v>
+        <v>46134.80026672454</v>
       </c>
       <c r="D42" s="5">
-        <v>46134.63361603009</v>
+        <v>46134.80028269676</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>163</v>
@@ -3964,13 +3964,13 @@
         <v>168</v>
       </c>
       <c r="B43" s="8">
-        <v>46118.49557270833</v>
+        <v>46118.662239375</v>
       </c>
       <c r="C43" s="8">
-        <v>46134.63372706018</v>
+        <v>46134.80039372685</v>
       </c>
       <c r="D43" s="8">
-        <v>46134.633741701386</v>
+        <v>46134.80040836806</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>98</v>
@@ -4027,13 +4027,13 @@
         <v>170</v>
       </c>
       <c r="B44" s="5">
-        <v>46118.49557863426</v>
+        <v>46118.662245300926</v>
       </c>
       <c r="C44" s="5">
-        <v>46198.40279047454</v>
+        <v>46198.5694571412</v>
       </c>
       <c r="D44" s="5">
-        <v>46208.04212479167</v>
+        <v>46208.20879145833</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>171</v>
@@ -4092,13 +4092,13 @@
         <v>176</v>
       </c>
       <c r="B45" s="8">
-        <v>46118.49558318287</v>
+        <v>46118.66224984954</v>
       </c>
       <c r="C45" s="8">
-        <v>46184.520520185186</v>
+        <v>46184.68718685185</v>
       </c>
       <c r="D45" s="8">
-        <v>46184.520521620376</v>
+        <v>46184.68718828703</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>177</v>
@@ -4141,13 +4141,13 @@
         <v>179</v>
       </c>
       <c r="B46" s="5">
-        <v>46118.495586840276</v>
+        <v>46118.66225350695</v>
       </c>
       <c r="C46" s="5">
-        <v>46184.52003991898</v>
+        <v>46184.68670658565</v>
       </c>
       <c r="D46" s="5">
-        <v>46208.04321662037</v>
+        <v>46208.20988328704</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>153</v>
@@ -4206,13 +4206,13 @@
         <v>183</v>
       </c>
       <c r="B47" s="8">
-        <v>46118.49559196759</v>
+        <v>46118.66225863426</v>
       </c>
       <c r="C47" s="8">
-        <v>46184.520299317126</v>
+        <v>46184.6869659838</v>
       </c>
       <c r="D47" s="8">
-        <v>46208.04324671296</v>
+        <v>46208.20991337963</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>184</v>
@@ -4271,13 +4271,13 @@
         <v>188</v>
       </c>
       <c r="B48" s="5">
-        <v>46118.49559715278</v>
+        <v>46118.662263819446</v>
       </c>
       <c r="C48" s="5">
-        <v>46193.88967060186</v>
+        <v>46194.056337268514</v>
       </c>
       <c r="D48" s="5">
-        <v>46193.889672453704</v>
+        <v>46194.05633912037</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>189</v>
@@ -4320,13 +4320,13 @@
         <v>191</v>
       </c>
       <c r="B49" s="8">
-        <v>46118.49560084491</v>
+        <v>46118.66226751157</v>
       </c>
       <c r="C49" s="8">
-        <v>46184.52128453704</v>
+        <v>46184.687951203705</v>
       </c>
       <c r="D49" s="8">
-        <v>46208.04356131944</v>
+        <v>46208.210227986114</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>192</v>
@@ -4385,13 +4385,13 @@
         <v>196</v>
       </c>
       <c r="B50" s="5">
-        <v>46118.49560603009</v>
+        <v>46118.66227269676</v>
       </c>
       <c r="C50" s="5">
-        <v>46193.39524637732</v>
+        <v>46193.56191304398</v>
       </c>
       <c r="D50" s="5">
-        <v>46208.04359453704</v>
+        <v>46208.210261203705</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>197</v>
@@ -4450,13 +4450,13 @@
         <v>200</v>
       </c>
       <c r="B51" s="8">
-        <v>46184.52131372685</v>
+        <v>46184.687980393515</v>
       </c>
       <c r="C51" s="8">
-        <v>46184.52255061343</v>
+        <v>46184.68921728009</v>
       </c>
       <c r="D51" s="8">
-        <v>46191.52051372685</v>
+        <v>46191.68718039352</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>201</v>
@@ -4505,13 +4505,13 @@
         <v>202</v>
       </c>
       <c r="B52" s="5">
-        <v>46184.52142638889</v>
+        <v>46184.688093055556</v>
       </c>
       <c r="C52" s="5">
-        <v>46195.53587391204</v>
+        <v>46195.7025405787</v>
       </c>
       <c r="D52" s="5">
-        <v>46195.53587571759</v>
+        <v>46195.70254238426</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>203</v>
@@ -4560,13 +4560,13 @@
         <v>204</v>
       </c>
       <c r="B53" s="8">
-        <v>46184.52150136574</v>
+        <v>46184.68816803241</v>
       </c>
       <c r="C53" s="8">
-        <v>46184.523340844906</v>
+        <v>46184.69000751157</v>
       </c>
       <c r="D53" s="8">
-        <v>46191.52050717593</v>
+        <v>46191.6871738426</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>205</v>
@@ -4615,13 +4615,13 @@
         <v>206</v>
       </c>
       <c r="B54" s="5">
-        <v>46184.52160033565</v>
+        <v>46184.68826700232</v>
       </c>
       <c r="C54" s="5">
-        <v>46184.52365296296</v>
+        <v>46184.69031962963</v>
       </c>
       <c r="D54" s="5">
-        <v>46191.520502326384</v>
+        <v>46191.687168993056</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>207</v>
@@ -4670,13 +4670,13 @@
         <v>208</v>
       </c>
       <c r="B55" s="8">
-        <v>46118.49561196759</v>
+        <v>46118.66227863426</v>
       </c>
       <c r="C55" s="8">
-        <v>46193.39573376157</v>
+        <v>46193.56240042824</v>
       </c>
       <c r="D55" s="8">
-        <v>46210.0316203588</v>
+        <v>46210.19828702546</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>209</v>
@@ -4735,13 +4735,13 @@
         <v>212</v>
       </c>
       <c r="B56" s="5">
-        <v>46118.495618217596</v>
+        <v>46118.66228488426</v>
       </c>
       <c r="C56" s="5">
-        <v>46193.889654548606</v>
+        <v>46194.05632121528</v>
       </c>
       <c r="D56" s="5">
-        <v>46193.88965658565</v>
+        <v>46194.05632325231</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>177</v>
@@ -4784,13 +4784,13 @@
         <v>214</v>
       </c>
       <c r="B57" s="8">
-        <v>46118.49562136574</v>
+        <v>46118.66228803241</v>
       </c>
       <c r="C57" s="8">
-        <v>46193.3956787037</v>
+        <v>46193.562345370374</v>
       </c>
       <c r="D57" s="8">
-        <v>46208.04370011574</v>
+        <v>46208.21036678241</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>215</v>
@@ -4849,13 +4849,13 @@
         <v>217</v>
       </c>
       <c r="B58" s="5">
-        <v>46118.49562685185</v>
+        <v>46118.662293518515</v>
       </c>
       <c r="C58" s="5">
-        <v>46193.39530791667</v>
+        <v>46193.56197458333</v>
       </c>
       <c r="D58" s="5">
-        <v>46208.04380561343</v>
+        <v>46208.210472280094</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>58</v>
@@ -4914,13 +4914,13 @@
         <v>219</v>
       </c>
       <c r="B59" s="8">
-        <v>46118.49563322916</v>
+        <v>46118.662299895834</v>
       </c>
       <c r="C59" s="8">
-        <v>46193.39531820602</v>
+        <v>46193.561984872686</v>
       </c>
       <c r="D59" s="8">
-        <v>46208.04380609954</v>
+        <v>46208.21047276621</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>220</v>
@@ -4979,13 +4979,13 @@
         <v>222</v>
       </c>
       <c r="B60" s="5">
-        <v>46118.495688842595</v>
+        <v>46118.66235550926</v>
       </c>
       <c r="C60" s="5">
-        <v>46193.3953305787</v>
+        <v>46193.56199724537</v>
       </c>
       <c r="D60" s="5">
-        <v>46208.04380655092</v>
+        <v>46208.210473217594</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>223</v>
@@ -5044,13 +5044,13 @@
         <v>225</v>
       </c>
       <c r="B61" s="8">
-        <v>46118.49569628472</v>
+        <v>46118.66236295139</v>
       </c>
       <c r="C61" s="8">
-        <v>46193.598368692124</v>
+        <v>46193.765035358796</v>
       </c>
       <c r="D61" s="8">
-        <v>46204.73348703704</v>
+        <v>46204.900153703704</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>226</v>
@@ -5093,13 +5093,13 @@
         <v>228</v>
       </c>
       <c r="B62" s="5">
-        <v>46118.495702071756</v>
+        <v>46118.66236873843</v>
       </c>
       <c r="C62" s="5">
-        <v>46193.445946782405</v>
+        <v>46193.61261344908</v>
       </c>
       <c r="D62" s="5">
-        <v>46208.04396326389</v>
+        <v>46208.21062993056</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>229</v>
@@ -5158,13 +5158,13 @@
         <v>231</v>
       </c>
       <c r="B63" s="8">
-        <v>46118.49570939815</v>
+        <v>46118.662376064814</v>
       </c>
       <c r="C63" s="8">
-        <v>46193.445992037035</v>
+        <v>46193.6126587037</v>
       </c>
       <c r="D63" s="8">
-        <v>46208.04396278935</v>
+        <v>46208.21062945602</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>224</v>
@@ -5223,13 +5223,13 @@
         <v>234</v>
       </c>
       <c r="B64" s="5">
-        <v>46118.4957208912</v>
+        <v>46118.662387557866</v>
       </c>
       <c r="C64" s="5">
-        <v>46193.44601277778</v>
+        <v>46193.61267944444</v>
       </c>
       <c r="D64" s="5">
-        <v>46208.043963703705</v>
+        <v>46208.21063037037</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>235</v>
@@ -5288,13 +5288,13 @@
         <v>237</v>
       </c>
       <c r="B65" s="8">
-        <v>46118.495732129624</v>
+        <v>46118.662398796296</v>
       </c>
       <c r="C65" s="8">
-        <v>46193.44607049768</v>
+        <v>46193.61273716435</v>
       </c>
       <c r="D65" s="8">
-        <v>46208.04396222222</v>
+        <v>46208.21062888889</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>238</v>
@@ -5353,13 +5353,13 @@
         <v>240</v>
       </c>
       <c r="B66" s="5">
-        <v>46118.495743182866</v>
+        <v>46118.66240984954</v>
       </c>
       <c r="C66" s="5">
-        <v>46193.59884520833</v>
+        <v>46193.765511875</v>
       </c>
       <c r="D66" s="5">
-        <v>46208.04396173611</v>
+        <v>46208.21062840278</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>174</v>
@@ -5416,13 +5416,13 @@
         <v>243</v>
       </c>
       <c r="B67" s="8">
-        <v>46118.49575346065</v>
+        <v>46118.662420127315</v>
       </c>
       <c r="C67" s="8">
-        <v>46196.75679758102</v>
+        <v>46196.92346424768</v>
       </c>
       <c r="D67" s="8">
-        <v>46208.043961250005</v>
+        <v>46208.21062791666</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>244</v>
@@ -5481,13 +5481,13 @@
         <v>246</v>
       </c>
       <c r="B68" s="5">
-        <v>46118.49576103009</v>
+        <v>46118.66242769676</v>
       </c>
       <c r="C68" s="5">
-        <v>46210.474296608794</v>
+        <v>46210.640963275466</v>
       </c>
       <c r="D68" s="5">
-        <v>46210.47431240741</v>
+        <v>46210.64097907407</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>247</v>
@@ -5534,13 +5534,13 @@
         <v>249</v>
       </c>
       <c r="B69" s="8">
-        <v>46118.49576510416</v>
+        <v>46118.662431770834</v>
       </c>
       <c r="C69" s="8">
-        <v>46203.64897710648</v>
+        <v>46203.81564377315</v>
       </c>
       <c r="D69" s="8">
-        <v>46208.04405054398</v>
+        <v>46208.21071721065</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>250</v>
@@ -5597,13 +5597,13 @@
         <v>254</v>
       </c>
       <c r="B70" s="5">
-        <v>46118.49577158564</v>
+        <v>46118.662438252315</v>
       </c>
       <c r="C70" s="5">
-        <v>46204.73111260417</v>
+        <v>46204.89777927083</v>
       </c>
       <c r="D70" s="5">
-        <v>46208.04405099537</v>
+        <v>46211.698982268514</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>255</v>
@@ -5660,13 +5660,13 @@
         <v>258</v>
       </c>
       <c r="B71" s="8">
-        <v>46118.49578482639</v>
+        <v>46118.66245149306</v>
       </c>
       <c r="C71" s="8">
-        <v>46196.75639109954</v>
+        <v>46196.9230577662</v>
       </c>
       <c r="D71" s="8">
-        <v>46208.04405145833</v>
+        <v>46208.210718125</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>259</v>
@@ -5723,13 +5723,13 @@
         <v>263</v>
       </c>
       <c r="B72" s="5">
-        <v>46118.49579103009</v>
+        <v>46118.66245769676</v>
       </c>
       <c r="C72" s="5">
-        <v>46210.47427461806</v>
+        <v>46210.64094128472</v>
       </c>
       <c r="D72" s="5">
-        <v>46210.47614521991</v>
+        <v>46210.64281188657</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>264</v>
@@ -5786,11 +5786,11 @@
         <v>266</v>
       </c>
       <c r="B73" s="8">
-        <v>46118.49579800926</v>
+        <v>46118.66246467593</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46118.5961819213</v>
+        <v>46118.76284858796</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>267</v>
@@ -5833,11 +5833,11 @@
         <v>269</v>
       </c>
       <c r="B74" s="5">
-        <v>46118.495801296296</v>
+        <v>46118.66246796296</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46210.47430541667</v>
+        <v>46210.64097208333</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>270</v>
@@ -5896,11 +5896,11 @@
         <v>273</v>
       </c>
       <c r="B75" s="8">
-        <v>46118.49584592592</v>
+        <v>46118.66251259259</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46210.47430590278</v>
+        <v>46210.64097256944</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>274</v>
@@ -5959,11 +5959,11 @@
         <v>275</v>
       </c>
       <c r="B76" s="5">
-        <v>46118.49585471065</v>
+        <v>46118.662521377315</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46118.59695680556</v>
+        <v>46118.76362347222</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>276</v>
@@ -6006,11 +6006,11 @@
         <v>278</v>
       </c>
       <c r="B77" s="8">
-        <v>46118.495858993054</v>
+        <v>46118.66252565972</v>
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46210.474303842595</v>
+        <v>46210.64097050926</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>279</v>
@@ -6069,11 +6069,11 @@
         <v>281</v>
       </c>
       <c r="B78" s="5">
-        <v>46118.49586534723</v>
+        <v>46118.662532013885</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46118.601592962965</v>
+        <v>46118.76825962963</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>282</v>

--- a/data/50001533 - GESVIAL.xlsx
+++ b/data/50001533 - GESVIAL.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="948" uniqueCount="283">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="939" uniqueCount="280">
   <si>
     <t xml:space="preserve"> 50001533 - GESVIAL</t>
   </si>
@@ -377,9 +377,6 @@
     <t>propuesta nucleo rodete</t>
   </si>
   <si>
-    <t>benjamin.bustos@zitron.com</t>
-  </si>
-  <si>
     <t>Propuesta compras:,Generación OC Rodete - OT4285</t>
   </si>
   <si>
@@ -390,12 +387,6 @@
   </si>
   <si>
     <t>propuesta compras a codigo // aprovisionamiento</t>
-  </si>
-  <si>
-    <t>hugo isla martinez</t>
-  </si>
-  <si>
-    <t>hugo.isla@zitron.com</t>
   </si>
   <si>
     <t xml:space="preserve">Check planos </t>
@@ -2633,11 +2624,9 @@
         <v>26</v>
       </c>
       <c r="G21" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="H21" s="9" t="s">
-        <v>91</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H21" s="9"/>
       <c r="I21" s="8">
         <v>46115</v>
       </c>
@@ -2660,7 +2649,7 @@
         <v>68</v>
       </c>
       <c r="P21" s="9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="Q21" s="8">
         <v>46118</v>
@@ -2675,12 +2664,12 @@
         <v>55</v>
       </c>
       <c r="U21" s="12" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B22" s="5">
         <v>46118.662087523146</v>
@@ -2692,17 +2681,15 @@
         <v>46208.21011525463</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="H22" s="6" t="s">
-        <v>97</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H22" s="6"/>
       <c r="I22" s="5">
         <v>46150</v>
       </c>
@@ -2722,10 +2709,10 @@
         <v>76</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="Q22" s="5">
         <v>46153</v>
@@ -2740,12 +2727,12 @@
         <v>32</v>
       </c>
       <c r="U22" s="12" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B23" s="8">
         <v>46118.66187195602</v>
@@ -2757,7 +2744,7 @@
         <v>46184.686248067126</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>25</v>
@@ -2781,7 +2768,7 @@
         <v>26</v>
       </c>
       <c r="O23" s="9" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="P23" s="9" t="s">
         <v>26</v>
@@ -2794,7 +2781,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B24" s="5">
         <v>46118.662093692124</v>
@@ -2806,16 +2793,16 @@
         <v>46208.21003241898</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="I24" s="5">
         <v>46119</v>
@@ -2833,13 +2820,13 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="Q24" s="5">
         <v>46232</v>
@@ -2854,12 +2841,12 @@
         <v>32</v>
       </c>
       <c r="U24" s="11" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B25" s="8">
         <v>46118.66209846065</v>
@@ -2871,16 +2858,16 @@
         <v>46208.21094784723</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="I25" s="8">
         <v>46119</v>
@@ -2898,13 +2885,13 @@
         <v>26</v>
       </c>
       <c r="N25" s="9" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="O25" s="9" t="s">
         <v>79</v>
       </c>
       <c r="P25" s="9" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="Q25" s="9"/>
       <c r="R25" s="9"/>
@@ -2916,7 +2903,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="B26" s="5">
         <v>46118.66210270833</v>
@@ -2928,16 +2915,16 @@
         <v>46208.21109037037</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="I26" s="5">
         <v>46121</v>
@@ -2955,13 +2942,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="Q26" s="6"/>
       <c r="R26" s="6"/>
@@ -2973,7 +2960,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B27" s="8">
         <v>46118.662106979165</v>
@@ -2985,16 +2972,16 @@
         <v>46208.209962824076</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="I27" s="8">
         <v>46111</v>
@@ -3012,13 +2999,13 @@
         <v>26</v>
       </c>
       <c r="N27" s="9" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="O27" s="9" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="P27" s="9" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="Q27" s="8">
         <v>46188</v>
@@ -3033,12 +3020,12 @@
         <v>32</v>
       </c>
       <c r="U27" s="11" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B28" s="5">
         <v>46118.662112094906</v>
@@ -3050,16 +3037,16 @@
         <v>46208.21118949074</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="I28" s="5">
         <v>46111</v>
@@ -3077,13 +3064,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="O28" s="6" t="s">
         <v>86</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
@@ -3094,12 +3081,12 @@
         <v>32</v>
       </c>
       <c r="U28" s="11" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="B29" s="8">
         <v>46118.66211693287</v>
@@ -3111,16 +3098,16 @@
         <v>46208.21130763889</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="I29" s="8">
         <v>46120</v>
@@ -3138,13 +3125,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="O29" s="9" t="s">
         <v>116</v>
       </c>
-      <c r="O29" s="9" t="s">
-        <v>119</v>
-      </c>
       <c r="P29" s="9" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="Q29" s="9"/>
       <c r="R29" s="9"/>
@@ -3155,12 +3142,12 @@
         <v>32</v>
       </c>
       <c r="U29" s="11" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B30" s="5">
         <v>46118.66212202546</v>
@@ -3172,16 +3159,16 @@
         <v>46208.20888993055</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="I30" s="5">
         <v>46119</v>
@@ -3199,13 +3186,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="Q30" s="5">
         <v>46167</v>
@@ -3220,12 +3207,12 @@
         <v>32</v>
       </c>
       <c r="U30" s="11" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B31" s="8">
         <v>46118.662126678246</v>
@@ -3237,16 +3224,16 @@
         <v>46208.211394502316</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="I31" s="8">
         <v>46119</v>
@@ -3264,13 +3251,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="9" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="O31" s="9" t="s">
         <v>90</v>
       </c>
       <c r="P31" s="9" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="Q31" s="9"/>
       <c r="R31" s="9"/>
@@ -3281,12 +3268,12 @@
         <v>32</v>
       </c>
       <c r="U31" s="11" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B32" s="5">
         <v>46118.662131261575</v>
@@ -3298,16 +3285,16 @@
         <v>46208.21147013889</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="I32" s="5">
         <v>46121</v>
@@ -3325,13 +3312,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="O32" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="O32" s="6" t="s">
-        <v>128</v>
-      </c>
       <c r="P32" s="6" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
@@ -3342,12 +3329,12 @@
         <v>32</v>
       </c>
       <c r="U32" s="11" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B33" s="8">
         <v>46118.66218372685</v>
@@ -3359,16 +3346,16 @@
         <v>46169.82398277777</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="I33" s="8">
         <v>46112</v>
@@ -3386,13 +3373,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="O33" s="9" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="P33" s="9" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="Q33" s="8">
         <v>46254</v>
@@ -3407,12 +3394,12 @@
         <v>32</v>
       </c>
       <c r="U33" s="11" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="B34" s="5">
         <v>46118.662190104165</v>
@@ -3424,16 +3411,16 @@
         <v>46208.211555636575</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="I34" s="5">
         <v>46112</v>
@@ -3451,13 +3438,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="O34" s="6" t="s">
         <v>83</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3468,12 +3455,12 @@
         <v>32</v>
       </c>
       <c r="U34" s="11" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="B35" s="8">
         <v>46118.662195694444</v>
@@ -3485,16 +3472,16 @@
         <v>46208.21164188658</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="I35" s="8">
         <v>46133</v>
@@ -3512,13 +3499,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="O35" s="9" t="s">
         <v>134</v>
       </c>
-      <c r="O35" s="9" t="s">
-        <v>137</v>
-      </c>
       <c r="P35" s="9" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="Q35" s="9"/>
       <c r="R35" s="9"/>
@@ -3529,12 +3516,12 @@
         <v>32</v>
       </c>
       <c r="U35" s="11" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B36" s="5">
         <v>46118.66220082176</v>
@@ -3546,16 +3533,16 @@
         <v>46208.211714791665</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="I36" s="5">
         <v>46133</v>
@@ -3573,13 +3560,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="O36" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="O36" s="6" t="s">
-        <v>137</v>
-      </c>
       <c r="P36" s="6" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
@@ -3590,12 +3577,12 @@
         <v>32</v>
       </c>
       <c r="U36" s="11" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="B37" s="8">
         <v>46118.66220634259</v>
@@ -3607,16 +3594,16 @@
         <v>46208.208834942125</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="I37" s="8">
         <v>46154</v>
@@ -3634,13 +3621,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="O37" s="9" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="Q37" s="8">
         <v>46170</v>
@@ -3655,12 +3642,12 @@
         <v>32</v>
       </c>
       <c r="U37" s="11" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="B38" s="5">
         <v>46118.66221234953</v>
@@ -3672,16 +3659,16 @@
         <v>46208.21179649305</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="I38" s="5">
         <v>46154</v>
@@ -3699,13 +3686,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -3716,12 +3703,12 @@
         <v>32</v>
       </c>
       <c r="U38" s="11" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="B39" s="8">
         <v>46118.66221657407</v>
@@ -3733,16 +3720,16 @@
         <v>46208.211892453706</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="I39" s="8">
         <v>46162</v>
@@ -3760,13 +3747,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="9" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="O39" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="P39" s="9" t="s">
         <v>150</v>
-      </c>
-      <c r="P39" s="9" t="s">
-        <v>153</v>
       </c>
       <c r="Q39" s="9"/>
       <c r="R39" s="9"/>
@@ -3777,12 +3764,12 @@
         <v>32</v>
       </c>
       <c r="U39" s="11" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B40" s="5">
         <v>46118.662220972226</v>
@@ -3794,7 +3781,7 @@
         <v>46204.652183645834</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>25</v>
@@ -3818,7 +3805,7 @@
         <v>26</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="P40" s="6" t="s">
         <v>26</v>
@@ -3831,7 +3818,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="B41" s="8">
         <v>46118.66222521991</v>
@@ -3843,16 +3830,16 @@
         <v>46129.57417895833</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="I41" s="8">
         <v>46115</v>
@@ -3870,13 +3857,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="O41" s="9" t="s">
         <v>72</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="Q41" s="8">
         <v>46121</v>
@@ -3896,7 +3883,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="B42" s="5">
         <v>46118.66223170139</v>
@@ -3908,16 +3895,16 @@
         <v>46134.80028269676</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="I42" s="5">
         <v>46142</v>
@@ -3935,13 +3922,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="Q42" s="5">
         <v>46148</v>
@@ -3961,7 +3948,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="B43" s="8">
         <v>46118.662239375</v>
@@ -3973,16 +3960,16 @@
         <v>46134.80040836806</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="I43" s="9"/>
       <c r="J43" s="8">
@@ -3998,13 +3985,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="P43" s="9" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="Q43" s="8">
         <v>46149</v>
@@ -4024,7 +4011,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B44" s="5">
         <v>46118.662245300926</v>
@@ -4036,16 +4023,16 @@
         <v>46208.20879145833</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="I44" s="5">
         <v>46268</v>
@@ -4063,13 +4050,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="Q44" s="5">
         <v>46268</v>
@@ -4084,12 +4071,12 @@
         <v>32</v>
       </c>
       <c r="U44" s="11" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="B45" s="8">
         <v>46118.66224984954</v>
@@ -4101,7 +4088,7 @@
         <v>46184.68718828703</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>25</v>
@@ -4125,7 +4112,7 @@
         <v>26</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="P45" s="9" t="s">
         <v>26</v>
@@ -4138,7 +4125,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="B46" s="5">
         <v>46118.66225350695</v>
@@ -4150,16 +4137,16 @@
         <v>46208.20988328704</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="I46" s="5">
         <v>46171</v>
@@ -4177,13 +4164,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="Q46" s="5">
         <v>46174</v>
@@ -4198,12 +4185,12 @@
         <v>32</v>
       </c>
       <c r="U46" s="11" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="B47" s="8">
         <v>46118.66225863426</v>
@@ -4215,16 +4202,16 @@
         <v>46208.20991337963</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="I47" s="8">
         <v>46175</v>
@@ -4242,13 +4229,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="Q47" s="8">
         <v>46176</v>
@@ -4263,12 +4250,12 @@
         <v>32</v>
       </c>
       <c r="U47" s="11" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="B48" s="5">
         <v>46118.662263819446</v>
@@ -4280,7 +4267,7 @@
         <v>46194.05633912037</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>25</v>
@@ -4304,7 +4291,7 @@
         <v>26</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="P48" s="6" t="s">
         <v>26</v>
@@ -4317,7 +4304,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="B49" s="8">
         <v>46118.66226751157</v>
@@ -4329,16 +4316,16 @@
         <v>46208.210227986114</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="I49" s="8">
         <v>46177</v>
@@ -4356,13 +4343,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="Q49" s="8">
         <v>46185</v>
@@ -4377,12 +4364,12 @@
         <v>32</v>
       </c>
       <c r="U49" s="11" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="B50" s="5">
         <v>46118.66227269676</v>
@@ -4394,16 +4381,16 @@
         <v>46208.210261203705</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="I50" s="5">
         <v>46188</v>
@@ -4421,13 +4408,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="Q50" s="5">
         <v>46205</v>
@@ -4442,12 +4429,12 @@
         <v>32</v>
       </c>
       <c r="U50" s="11" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="B51" s="8">
         <v>46184.687980393515</v>
@@ -4459,16 +4446,16 @@
         <v>46191.68718039352</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="I51" s="8">
         <v>46188</v>
@@ -4486,7 +4473,7 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="O51" s="9" t="s">
         <v>26</v>
@@ -4502,7 +4489,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="B52" s="5">
         <v>46184.688093055556</v>
@@ -4514,16 +4501,16 @@
         <v>46195.70254238426</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="I52" s="5">
         <v>46188</v>
@@ -4541,7 +4528,7 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="O52" s="6" t="s">
         <v>26</v>
@@ -4557,7 +4544,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="B53" s="8">
         <v>46184.68816803241</v>
@@ -4569,16 +4556,16 @@
         <v>46191.6871738426</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="H53" s="9" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="I53" s="8">
         <v>46188</v>
@@ -4596,7 +4583,7 @@
         <v>26</v>
       </c>
       <c r="N53" s="9" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="O53" s="9" t="s">
         <v>26</v>
@@ -4612,7 +4599,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="B54" s="5">
         <v>46184.68826700232</v>
@@ -4624,16 +4611,16 @@
         <v>46191.687168993056</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="I54" s="5">
         <v>46188</v>
@@ -4651,7 +4638,7 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="O54" s="6" t="s">
         <v>26</v>
@@ -4667,7 +4654,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="B55" s="8">
         <v>46118.66227863426</v>
@@ -4679,16 +4666,16 @@
         <v>46210.19828702546</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="I55" s="8">
         <v>46206</v>
@@ -4706,13 +4693,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="P55" s="9" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="Q55" s="8">
         <v>46209</v>
@@ -4727,12 +4714,12 @@
         <v>55</v>
       </c>
       <c r="U55" s="11" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="B56" s="5">
         <v>46118.66228488426</v>
@@ -4744,7 +4731,7 @@
         <v>46194.05632325231</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>25</v>
@@ -4768,7 +4755,7 @@
         <v>26</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="P56" s="6" t="s">
         <v>26</v>
@@ -4781,7 +4768,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="B57" s="8">
         <v>46118.66228803241</v>
@@ -4793,16 +4780,16 @@
         <v>46208.21036678241</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="I57" s="8">
         <v>46168</v>
@@ -4820,13 +4807,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="P57" s="9" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="Q57" s="8">
         <v>46169</v>
@@ -4841,12 +4828,12 @@
         <v>32</v>
       </c>
       <c r="U57" s="11" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="B58" s="5">
         <v>46118.662293518515</v>
@@ -4864,10 +4851,10 @@
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="I58" s="5">
         <v>46189</v>
@@ -4885,13 +4872,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="Q58" s="5">
         <v>46190</v>
@@ -4906,12 +4893,12 @@
         <v>32</v>
       </c>
       <c r="U58" s="11" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="B59" s="8">
         <v>46118.662299895834</v>
@@ -4923,16 +4910,16 @@
         <v>46208.21047276621</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="I59" s="8">
         <v>46233</v>
@@ -4950,13 +4937,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="Q59" s="8">
         <v>46234</v>
@@ -4971,12 +4958,12 @@
         <v>32</v>
       </c>
       <c r="U59" s="11" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B60" s="5">
         <v>46118.66235550926</v>
@@ -4988,16 +4975,16 @@
         <v>46208.210473217594</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="I60" s="5">
         <v>46255</v>
@@ -5015,13 +5002,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="Q60" s="5">
         <v>46258</v>
@@ -5036,12 +5023,12 @@
         <v>32</v>
       </c>
       <c r="U60" s="11" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="B61" s="8">
         <v>46118.66236295139</v>
@@ -5053,7 +5040,7 @@
         <v>46204.900153703704</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>25</v>
@@ -5077,7 +5064,7 @@
         <v>26</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="P61" s="9" t="s">
         <v>26</v>
@@ -5090,7 +5077,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="B62" s="5">
         <v>46118.66236873843</v>
@@ -5102,17 +5089,15 @@
         <v>46208.21062993056</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="H62" s="6" t="s">
-        <v>91</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H62" s="6"/>
       <c r="I62" s="5">
         <v>46210</v>
       </c>
@@ -5129,13 +5114,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="Q62" s="5">
         <v>46227</v>
@@ -5150,12 +5135,12 @@
         <v>32</v>
       </c>
       <c r="U62" s="11" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="B63" s="8">
         <v>46118.662376064814</v>
@@ -5167,17 +5152,15 @@
         <v>46208.21062945602</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="H63" s="9" t="s">
-        <v>91</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H63" s="9"/>
       <c r="I63" s="8">
         <v>46259</v>
       </c>
@@ -5194,13 +5177,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="P63" s="9" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="Q63" s="8">
         <v>46260</v>
@@ -5215,12 +5198,12 @@
         <v>32</v>
       </c>
       <c r="U63" s="11" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="B64" s="5">
         <v>46118.662387557866</v>
@@ -5232,17 +5215,15 @@
         <v>46208.21063037037</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="H64" s="6" t="s">
-        <v>91</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H64" s="6"/>
       <c r="I64" s="5">
         <v>46261</v>
       </c>
@@ -5259,13 +5240,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="Q64" s="5">
         <v>46262</v>
@@ -5280,12 +5261,12 @@
         <v>32</v>
       </c>
       <c r="U64" s="11" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="B65" s="8">
         <v>46118.662398796296</v>
@@ -5297,17 +5278,15 @@
         <v>46208.21062888889</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="H65" s="9" t="s">
-        <v>91</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H65" s="9"/>
       <c r="I65" s="8">
         <v>46265</v>
       </c>
@@ -5324,13 +5303,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="P65" s="9" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="Q65" s="8">
         <v>46266</v>
@@ -5345,12 +5324,12 @@
         <v>32</v>
       </c>
       <c r="U65" s="11" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="B66" s="5">
         <v>46118.66240984954</v>
@@ -5362,17 +5341,15 @@
         <v>46208.21062840278</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="H66" s="6" t="s">
-        <v>91</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H66" s="6"/>
       <c r="I66" s="6"/>
       <c r="J66" s="5">
         <v>46267</v>
@@ -5387,13 +5364,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="Q66" s="5">
         <v>46267</v>
@@ -5408,12 +5385,12 @@
         <v>32</v>
       </c>
       <c r="U66" s="11" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="B67" s="8">
         <v>46118.662420127315</v>
@@ -5425,17 +5402,15 @@
         <v>46208.21062791666</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="H67" s="9" t="s">
-        <v>91</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H67" s="9"/>
       <c r="I67" s="8">
         <v>46269</v>
       </c>
@@ -5452,13 +5427,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="P67" s="9" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="Q67" s="8">
         <v>46269</v>
@@ -5473,12 +5448,12 @@
         <v>32</v>
       </c>
       <c r="U67" s="11" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="B68" s="5">
         <v>46118.66242769676</v>
@@ -5490,7 +5465,7 @@
         <v>46210.64097907407</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>25</v>
@@ -5514,7 +5489,7 @@
         <v>26</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="P68" s="6" t="s">
         <v>26</v>
@@ -5531,7 +5506,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="B69" s="8">
         <v>46118.662431770834</v>
@@ -5543,16 +5518,16 @@
         <v>46208.21071721065</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="9" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="H69" s="9" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="I69" s="9"/>
       <c r="J69" s="8">
@@ -5568,13 +5543,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="P69" s="9" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="Q69" s="8">
         <v>46272</v>
@@ -5594,7 +5569,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="B70" s="5">
         <v>46118.662438252315</v>
@@ -5606,17 +5581,15 @@
         <v>46211.698982268514</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="H70" s="6" t="s">
-        <v>91</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H70" s="6"/>
       <c r="I70" s="6"/>
       <c r="J70" s="5">
         <v>46273</v>
@@ -5631,13 +5604,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="Q70" s="5">
         <v>46273</v>
@@ -5657,7 +5630,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="B71" s="8">
         <v>46118.66245149306</v>
@@ -5669,16 +5642,16 @@
         <v>46208.210718125</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="9" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="H71" s="9" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="I71" s="9"/>
       <c r="J71" s="8">
@@ -5694,13 +5667,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="P71" s="9" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="Q71" s="8">
         <v>46274</v>
@@ -5720,7 +5693,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="B72" s="5">
         <v>46118.66245769676</v>
@@ -5732,16 +5705,16 @@
         <v>46210.64281188657</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="I72" s="6"/>
       <c r="J72" s="5">
@@ -5757,13 +5730,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="Q72" s="5">
         <v>46275</v>
@@ -5783,7 +5756,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="B73" s="8">
         <v>46118.66246467593</v>
@@ -5793,7 +5766,7 @@
         <v>46118.76284858796</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>25</v>
@@ -5817,7 +5790,7 @@
         <v>26</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="P73" s="9" t="s">
         <v>26</v>
@@ -5830,7 +5803,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="B74" s="5">
         <v>46118.66246796296</v>
@@ -5840,16 +5813,16 @@
         <v>46210.64097208333</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="I74" s="5">
         <v>46276</v>
@@ -5867,13 +5840,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="O74" s="6" t="s">
+        <v>261</v>
+      </c>
+      <c r="P74" s="6" t="s">
         <v>264</v>
-      </c>
-      <c r="P74" s="6" t="s">
-        <v>267</v>
       </c>
       <c r="Q74" s="5">
         <v>46286</v>
@@ -5888,12 +5861,12 @@
         <v>32</v>
       </c>
       <c r="U74" s="12" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="B75" s="8">
         <v>46118.66251259259</v>
@@ -5903,16 +5876,16 @@
         <v>46210.64097256944</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="9" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="H75" s="9" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="I75" s="8">
         <v>46276</v>
@@ -5930,13 +5903,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="O75" s="9" t="s">
+        <v>261</v>
+      </c>
+      <c r="P75" s="9" t="s">
         <v>264</v>
-      </c>
-      <c r="P75" s="9" t="s">
-        <v>267</v>
       </c>
       <c r="Q75" s="8">
         <v>46286</v>
@@ -5951,12 +5924,12 @@
         <v>32</v>
       </c>
       <c r="U75" s="12" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="B76" s="5">
         <v>46118.662521377315</v>
@@ -5966,7 +5939,7 @@
         <v>46118.76362347222</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>25</v>
@@ -5990,7 +5963,7 @@
         <v>26</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="P76" s="6" t="s">
         <v>26</v>
@@ -6003,7 +5976,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="B77" s="8">
         <v>46118.66252565972</v>
@@ -6013,7 +5986,7 @@
         <v>46210.64097050926</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>26</v>
@@ -6040,13 +6013,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="9" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="P77" s="9" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="Q77" s="8">
         <v>46286</v>
@@ -6061,12 +6034,12 @@
         <v>32</v>
       </c>
       <c r="U77" s="12" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="B78" s="5">
         <v>46118.662532013885</v>
@@ -6076,7 +6049,7 @@
         <v>46118.76825962963</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
@@ -6103,13 +6076,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="O78" s="6" t="s">
         <v>276</v>
       </c>
-      <c r="O78" s="6" t="s">
-        <v>279</v>
-      </c>
       <c r="P78" s="6" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="Q78" s="5">
         <v>46295</v>
@@ -6124,7 +6097,7 @@
         <v>32</v>
       </c>
       <c r="U78" s="11" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001533 - GESVIAL.xlsx
+++ b/data/50001533 - GESVIAL.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="939" uniqueCount="280">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="939" uniqueCount="281">
   <si>
     <t xml:space="preserve"> 50001533 - GESVIAL</t>
   </si>
@@ -786,6 +786,9 @@
   </si>
   <si>
     <t>Montaje:,Montaje Alabe,Montaje Rodete,Montaje motor</t>
+  </si>
+  <si>
+    <t>Media</t>
   </si>
   <si>
     <t>1213955269755950</t>
@@ -5086,7 +5089,7 @@
         <v>46193.61261344908</v>
       </c>
       <c r="D62" s="5">
-        <v>46208.21062993056</v>
+        <v>46220.19222408565</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>226</v>
@@ -5131,8 +5134,8 @@
       <c r="S62" s="6">
         <v>1</v>
       </c>
-      <c r="T62" s="10" t="s">
-        <v>32</v>
+      <c r="T62" s="12" t="s">
+        <v>228</v>
       </c>
       <c r="U62" s="11" t="s">
         <v>105</v>
@@ -5140,7 +5143,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B63" s="8">
         <v>46118.662376064814</v>
@@ -5180,10 +5183,10 @@
         <v>223</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="P63" s="9" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q63" s="8">
         <v>46260</v>
@@ -5203,7 +5206,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B64" s="5">
         <v>46118.662387557866</v>
@@ -5215,7 +5218,7 @@
         <v>46208.21063037037</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
@@ -5243,10 +5246,10 @@
         <v>223</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q64" s="5">
         <v>46262</v>
@@ -5266,7 +5269,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B65" s="8">
         <v>46118.662398796296</v>
@@ -5278,7 +5281,7 @@
         <v>46208.21062888889</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
@@ -5306,10 +5309,10 @@
         <v>223</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="P65" s="9" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q65" s="8">
         <v>46266</v>
@@ -5329,7 +5332,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B66" s="5">
         <v>46118.66240984954</v>
@@ -5367,10 +5370,10 @@
         <v>223</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q66" s="5">
         <v>46267</v>
@@ -5390,7 +5393,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B67" s="8">
         <v>46118.662420127315</v>
@@ -5402,7 +5405,7 @@
         <v>46208.21062791666</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
@@ -5433,7 +5436,7 @@
         <v>168</v>
       </c>
       <c r="P67" s="9" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q67" s="8">
         <v>46269</v>
@@ -5453,7 +5456,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B68" s="5">
         <v>46118.66242769676</v>
@@ -5465,7 +5468,7 @@
         <v>46210.64097907407</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>25</v>
@@ -5489,7 +5492,7 @@
         <v>26</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="P68" s="6" t="s">
         <v>26</v>
@@ -5506,7 +5509,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B69" s="8">
         <v>46118.662431770834</v>
@@ -5518,16 +5521,16 @@
         <v>46208.21071721065</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="9" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H69" s="9" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="I69" s="9"/>
       <c r="J69" s="8">
@@ -5543,13 +5546,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="P69" s="9" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q69" s="8">
         <v>46272</v>
@@ -5569,7 +5572,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B70" s="5">
         <v>46118.662438252315</v>
@@ -5581,7 +5584,7 @@
         <v>46211.698982268514</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
@@ -5604,13 +5607,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q70" s="5">
         <v>46273</v>
@@ -5630,7 +5633,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B71" s="8">
         <v>46118.66245149306</v>
@@ -5642,16 +5645,16 @@
         <v>46208.210718125</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="9" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H71" s="9" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="I71" s="9"/>
       <c r="J71" s="8">
@@ -5667,13 +5670,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="P71" s="9" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q71" s="8">
         <v>46274</v>
@@ -5693,7 +5696,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B72" s="5">
         <v>46118.66245769676</v>
@@ -5705,16 +5708,16 @@
         <v>46210.64281188657</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="I72" s="6"/>
       <c r="J72" s="5">
@@ -5730,13 +5733,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q72" s="5">
         <v>46275</v>
@@ -5756,7 +5759,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B73" s="8">
         <v>46118.66246467593</v>
@@ -5766,7 +5769,7 @@
         <v>46118.76284858796</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>25</v>
@@ -5790,7 +5793,7 @@
         <v>26</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P73" s="9" t="s">
         <v>26</v>
@@ -5803,7 +5806,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B74" s="5">
         <v>46118.66246796296</v>
@@ -5813,16 +5816,16 @@
         <v>46210.64097208333</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="I74" s="5">
         <v>46276</v>
@@ -5840,13 +5843,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q74" s="5">
         <v>46286</v>
@@ -5866,7 +5869,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B75" s="8">
         <v>46118.66251259259</v>
@@ -5876,16 +5879,16 @@
         <v>46210.64097256944</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H75" s="9" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="I75" s="8">
         <v>46276</v>
@@ -5903,13 +5906,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q75" s="8">
         <v>46286</v>
@@ -5929,7 +5932,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B76" s="5">
         <v>46118.662521377315</v>
@@ -5939,7 +5942,7 @@
         <v>46118.76362347222</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>25</v>
@@ -5963,7 +5966,7 @@
         <v>26</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="P76" s="6" t="s">
         <v>26</v>
@@ -5976,7 +5979,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B77" s="8">
         <v>46118.66252565972</v>
@@ -5986,7 +5989,7 @@
         <v>46210.64097050926</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>26</v>
@@ -6013,13 +6016,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="9" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="P77" s="9" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q77" s="8">
         <v>46286</v>
@@ -6039,7 +6042,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B78" s="5">
         <v>46118.662532013885</v>
@@ -6049,7 +6052,7 @@
         <v>46118.76825962963</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
@@ -6076,13 +6079,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q78" s="5">
         <v>46295</v>

--- a/data/50001533 - GESVIAL.xlsx
+++ b/data/50001533 - GESVIAL.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="939" uniqueCount="281">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="948" uniqueCount="282">
   <si>
     <t xml:space="preserve"> 50001533 - GESVIAL</t>
   </si>
@@ -375,6 +375,9 @@
   </si>
   <si>
     <t>propuesta nucleo rodete</t>
+  </si>
+  <si>
+    <t>nespinoza@zitron.com</t>
   </si>
   <si>
     <t>Propuesta compras:,Generación OC Rodete - OT4285</t>
@@ -2618,7 +2621,7 @@
         <v>46183.88010105324</v>
       </c>
       <c r="D21" s="8">
-        <v>46208.21006932871</v>
+        <v>46223.807138668984</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>90</v>
@@ -2627,9 +2630,11 @@
         <v>26</v>
       </c>
       <c r="G21" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H21" s="9"/>
+        <v>91</v>
+      </c>
+      <c r="H21" s="9" t="s">
+        <v>91</v>
+      </c>
       <c r="I21" s="8">
         <v>46115</v>
       </c>
@@ -2652,7 +2657,7 @@
         <v>68</v>
       </c>
       <c r="P21" s="9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Q21" s="8">
         <v>46118</v>
@@ -2667,12 +2672,12 @@
         <v>55</v>
       </c>
       <c r="U21" s="12" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B22" s="5">
         <v>46118.662087523146</v>
@@ -2681,18 +2686,20 @@
         <v>46183.888051863425</v>
       </c>
       <c r="D22" s="5">
-        <v>46208.21011525463</v>
+        <v>46223.807134884264</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H22" s="6"/>
+        <v>91</v>
+      </c>
+      <c r="H22" s="6" t="s">
+        <v>91</v>
+      </c>
       <c r="I22" s="5">
         <v>46150</v>
       </c>
@@ -2712,10 +2719,10 @@
         <v>76</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="Q22" s="5">
         <v>46153</v>
@@ -2730,12 +2737,12 @@
         <v>32</v>
       </c>
       <c r="U22" s="12" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B23" s="8">
         <v>46118.66187195602</v>
@@ -2747,7 +2754,7 @@
         <v>46184.686248067126</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>25</v>
@@ -2771,7 +2778,7 @@
         <v>26</v>
       </c>
       <c r="O23" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="P23" s="9" t="s">
         <v>26</v>
@@ -2784,7 +2791,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B24" s="5">
         <v>46118.662093692124</v>
@@ -2796,16 +2803,16 @@
         <v>46208.21003241898</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I24" s="5">
         <v>46119</v>
@@ -2823,13 +2830,13 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Q24" s="5">
         <v>46232</v>
@@ -2844,12 +2851,12 @@
         <v>32</v>
       </c>
       <c r="U24" s="11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B25" s="8">
         <v>46118.66209846065</v>
@@ -2861,16 +2868,16 @@
         <v>46208.21094784723</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I25" s="8">
         <v>46119</v>
@@ -2888,13 +2895,13 @@
         <v>26</v>
       </c>
       <c r="N25" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="O25" s="9" t="s">
         <v>79</v>
       </c>
       <c r="P25" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Q25" s="9"/>
       <c r="R25" s="9"/>
@@ -2906,7 +2913,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B26" s="5">
         <v>46118.66210270833</v>
@@ -2918,16 +2925,16 @@
         <v>46208.21109037037</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I26" s="5">
         <v>46121</v>
@@ -2945,13 +2952,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Q26" s="6"/>
       <c r="R26" s="6"/>
@@ -2963,7 +2970,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B27" s="8">
         <v>46118.662106979165</v>
@@ -2975,16 +2982,16 @@
         <v>46208.209962824076</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I27" s="8">
         <v>46111</v>
@@ -3002,13 +3009,13 @@
         <v>26</v>
       </c>
       <c r="N27" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="O27" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="P27" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Q27" s="8">
         <v>46188</v>
@@ -3023,12 +3030,12 @@
         <v>32</v>
       </c>
       <c r="U27" s="11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B28" s="5">
         <v>46118.662112094906</v>
@@ -3040,16 +3047,16 @@
         <v>46208.21118949074</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I28" s="5">
         <v>46111</v>
@@ -3067,13 +3074,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O28" s="6" t="s">
         <v>86</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
@@ -3084,12 +3091,12 @@
         <v>32</v>
       </c>
       <c r="U28" s="11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B29" s="8">
         <v>46118.66211693287</v>
@@ -3101,16 +3108,16 @@
         <v>46208.21130763889</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I29" s="8">
         <v>46120</v>
@@ -3128,13 +3135,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O29" s="9" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="P29" s="9" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="Q29" s="9"/>
       <c r="R29" s="9"/>
@@ -3145,12 +3152,12 @@
         <v>32</v>
       </c>
       <c r="U29" s="11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B30" s="5">
         <v>46118.66212202546</v>
@@ -3162,16 +3169,16 @@
         <v>46208.20888993055</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I30" s="5">
         <v>46119</v>
@@ -3189,13 +3196,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Q30" s="5">
         <v>46167</v>
@@ -3210,12 +3217,12 @@
         <v>32</v>
       </c>
       <c r="U30" s="11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B31" s="8">
         <v>46118.662126678246</v>
@@ -3227,16 +3234,16 @@
         <v>46208.211394502316</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I31" s="8">
         <v>46119</v>
@@ -3254,13 +3261,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="O31" s="9" t="s">
         <v>90</v>
       </c>
       <c r="P31" s="9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="Q31" s="9"/>
       <c r="R31" s="9"/>
@@ -3271,12 +3278,12 @@
         <v>32</v>
       </c>
       <c r="U31" s="11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B32" s="5">
         <v>46118.662131261575</v>
@@ -3288,16 +3295,16 @@
         <v>46208.21147013889</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I32" s="5">
         <v>46121</v>
@@ -3315,13 +3322,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
@@ -3332,12 +3339,12 @@
         <v>32</v>
       </c>
       <c r="U32" s="11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B33" s="8">
         <v>46118.66218372685</v>
@@ -3349,16 +3356,16 @@
         <v>46169.82398277777</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I33" s="8">
         <v>46112</v>
@@ -3376,13 +3383,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="O33" s="9" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="P33" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Q33" s="8">
         <v>46254</v>
@@ -3397,12 +3404,12 @@
         <v>32</v>
       </c>
       <c r="U33" s="11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B34" s="5">
         <v>46118.662190104165</v>
@@ -3414,16 +3421,16 @@
         <v>46208.211555636575</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I34" s="5">
         <v>46112</v>
@@ -3441,13 +3448,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="O34" s="6" t="s">
         <v>83</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3458,12 +3465,12 @@
         <v>32</v>
       </c>
       <c r="U34" s="11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B35" s="8">
         <v>46118.662195694444</v>
@@ -3475,16 +3482,16 @@
         <v>46208.21164188658</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I35" s="8">
         <v>46133</v>
@@ -3502,13 +3509,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="P35" s="9" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="Q35" s="9"/>
       <c r="R35" s="9"/>
@@ -3519,12 +3526,12 @@
         <v>32</v>
       </c>
       <c r="U35" s="11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B36" s="5">
         <v>46118.66220082176</v>
@@ -3536,16 +3543,16 @@
         <v>46208.211714791665</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I36" s="5">
         <v>46133</v>
@@ -3563,13 +3570,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
@@ -3580,12 +3587,12 @@
         <v>32</v>
       </c>
       <c r="U36" s="11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B37" s="8">
         <v>46118.66220634259</v>
@@ -3597,16 +3604,16 @@
         <v>46208.208834942125</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I37" s="8">
         <v>46154</v>
@@ -3624,13 +3631,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="O37" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Q37" s="8">
         <v>46170</v>
@@ -3645,12 +3652,12 @@
         <v>32</v>
       </c>
       <c r="U37" s="11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B38" s="5">
         <v>46118.66221234953</v>
@@ -3662,16 +3669,16 @@
         <v>46208.21179649305</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I38" s="5">
         <v>46154</v>
@@ -3689,13 +3696,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -3706,12 +3713,12 @@
         <v>32</v>
       </c>
       <c r="U38" s="11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B39" s="8">
         <v>46118.66221657407</v>
@@ -3723,16 +3730,16 @@
         <v>46208.211892453706</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I39" s="8">
         <v>46162</v>
@@ -3750,13 +3757,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="9" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="P39" s="9" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q39" s="9"/>
       <c r="R39" s="9"/>
@@ -3767,12 +3774,12 @@
         <v>32</v>
       </c>
       <c r="U39" s="11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B40" s="5">
         <v>46118.662220972226</v>
@@ -3784,7 +3791,7 @@
         <v>46204.652183645834</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>25</v>
@@ -3808,7 +3815,7 @@
         <v>26</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="P40" s="6" t="s">
         <v>26</v>
@@ -3821,7 +3828,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B41" s="8">
         <v>46118.66222521991</v>
@@ -3833,16 +3840,16 @@
         <v>46129.57417895833</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I41" s="8">
         <v>46115</v>
@@ -3860,13 +3867,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="O41" s="9" t="s">
         <v>72</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q41" s="8">
         <v>46121</v>
@@ -3886,7 +3893,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B42" s="5">
         <v>46118.66223170139</v>
@@ -3898,16 +3905,16 @@
         <v>46134.80028269676</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I42" s="5">
         <v>46142</v>
@@ -3925,13 +3932,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q42" s="5">
         <v>46148</v>
@@ -3951,7 +3958,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B43" s="8">
         <v>46118.662239375</v>
@@ -3963,16 +3970,16 @@
         <v>46134.80040836806</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I43" s="9"/>
       <c r="J43" s="8">
@@ -3988,13 +3995,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="P43" s="9" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q43" s="8">
         <v>46149</v>
@@ -4014,7 +4021,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B44" s="5">
         <v>46118.662245300926</v>
@@ -4026,16 +4033,16 @@
         <v>46208.20879145833</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="I44" s="5">
         <v>46268</v>
@@ -4053,13 +4060,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q44" s="5">
         <v>46268</v>
@@ -4074,12 +4081,12 @@
         <v>32</v>
       </c>
       <c r="U44" s="11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B45" s="8">
         <v>46118.66224984954</v>
@@ -4091,7 +4098,7 @@
         <v>46184.68718828703</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>25</v>
@@ -4115,7 +4122,7 @@
         <v>26</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P45" s="9" t="s">
         <v>26</v>
@@ -4128,7 +4135,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B46" s="5">
         <v>46118.66225350695</v>
@@ -4140,16 +4147,16 @@
         <v>46208.20988328704</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I46" s="5">
         <v>46171</v>
@@ -4167,13 +4174,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q46" s="5">
         <v>46174</v>
@@ -4188,12 +4195,12 @@
         <v>32</v>
       </c>
       <c r="U46" s="11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B47" s="8">
         <v>46118.66225863426</v>
@@ -4205,16 +4212,16 @@
         <v>46208.20991337963</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I47" s="8">
         <v>46175</v>
@@ -4232,13 +4239,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q47" s="8">
         <v>46176</v>
@@ -4253,12 +4260,12 @@
         <v>32</v>
       </c>
       <c r="U47" s="11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B48" s="5">
         <v>46118.662263819446</v>
@@ -4270,7 +4277,7 @@
         <v>46194.05633912037</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>25</v>
@@ -4294,7 +4301,7 @@
         <v>26</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="P48" s="6" t="s">
         <v>26</v>
@@ -4307,7 +4314,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B49" s="8">
         <v>46118.66226751157</v>
@@ -4319,16 +4326,16 @@
         <v>46208.210227986114</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I49" s="8">
         <v>46177</v>
@@ -4346,13 +4353,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q49" s="8">
         <v>46185</v>
@@ -4367,12 +4374,12 @@
         <v>32</v>
       </c>
       <c r="U49" s="11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B50" s="5">
         <v>46118.66227269676</v>
@@ -4384,16 +4391,16 @@
         <v>46208.210261203705</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I50" s="5">
         <v>46188</v>
@@ -4411,13 +4418,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q50" s="5">
         <v>46205</v>
@@ -4432,12 +4439,12 @@
         <v>32</v>
       </c>
       <c r="U50" s="11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B51" s="8">
         <v>46184.687980393515</v>
@@ -4449,16 +4456,16 @@
         <v>46191.68718039352</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I51" s="8">
         <v>46188</v>
@@ -4476,7 +4483,7 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O51" s="9" t="s">
         <v>26</v>
@@ -4492,7 +4499,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B52" s="5">
         <v>46184.688093055556</v>
@@ -4504,16 +4511,16 @@
         <v>46195.70254238426</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I52" s="5">
         <v>46188</v>
@@ -4531,7 +4538,7 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O52" s="6" t="s">
         <v>26</v>
@@ -4547,7 +4554,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B53" s="8">
         <v>46184.68816803241</v>
@@ -4559,16 +4566,16 @@
         <v>46191.6871738426</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H53" s="9" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I53" s="8">
         <v>46188</v>
@@ -4586,7 +4593,7 @@
         <v>26</v>
       </c>
       <c r="N53" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O53" s="9" t="s">
         <v>26</v>
@@ -4602,7 +4609,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B54" s="5">
         <v>46184.68826700232</v>
@@ -4614,16 +4621,16 @@
         <v>46191.687168993056</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I54" s="5">
         <v>46188</v>
@@ -4641,7 +4648,7 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O54" s="6" t="s">
         <v>26</v>
@@ -4657,7 +4664,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B55" s="8">
         <v>46118.66227863426</v>
@@ -4669,16 +4676,16 @@
         <v>46210.19828702546</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I55" s="8">
         <v>46206</v>
@@ -4696,13 +4703,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P55" s="9" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q55" s="8">
         <v>46209</v>
@@ -4717,12 +4724,12 @@
         <v>55</v>
       </c>
       <c r="U55" s="11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B56" s="5">
         <v>46118.66228488426</v>
@@ -4734,7 +4741,7 @@
         <v>46194.05632325231</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>25</v>
@@ -4758,7 +4765,7 @@
         <v>26</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P56" s="6" t="s">
         <v>26</v>
@@ -4771,7 +4778,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B57" s="8">
         <v>46118.66228803241</v>
@@ -4783,16 +4790,16 @@
         <v>46208.21036678241</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I57" s="8">
         <v>46168</v>
@@ -4810,13 +4817,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="P57" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q57" s="8">
         <v>46169</v>
@@ -4831,12 +4838,12 @@
         <v>32</v>
       </c>
       <c r="U57" s="11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B58" s="5">
         <v>46118.662293518515</v>
@@ -4854,10 +4861,10 @@
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I58" s="5">
         <v>46189</v>
@@ -4875,13 +4882,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q58" s="5">
         <v>46190</v>
@@ -4896,12 +4903,12 @@
         <v>32</v>
       </c>
       <c r="U58" s="11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B59" s="8">
         <v>46118.662299895834</v>
@@ -4913,16 +4920,16 @@
         <v>46208.21047276621</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I59" s="8">
         <v>46233</v>
@@ -4940,13 +4947,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q59" s="8">
         <v>46234</v>
@@ -4961,12 +4968,12 @@
         <v>32</v>
       </c>
       <c r="U59" s="11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B60" s="5">
         <v>46118.66235550926</v>
@@ -4978,16 +4985,16 @@
         <v>46208.210473217594</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I60" s="5">
         <v>46255</v>
@@ -5005,13 +5012,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q60" s="5">
         <v>46258</v>
@@ -5026,12 +5033,12 @@
         <v>32</v>
       </c>
       <c r="U60" s="11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B61" s="8">
         <v>46118.66236295139</v>
@@ -5043,7 +5050,7 @@
         <v>46204.900153703704</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>25</v>
@@ -5067,7 +5074,7 @@
         <v>26</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="P61" s="9" t="s">
         <v>26</v>
@@ -5080,7 +5087,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B62" s="5">
         <v>46118.66236873843</v>
@@ -5089,18 +5096,20 @@
         <v>46193.61261344908</v>
       </c>
       <c r="D62" s="5">
-        <v>46220.19222408565</v>
+        <v>46223.80726836805</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H62" s="6"/>
+        <v>91</v>
+      </c>
+      <c r="H62" s="6" t="s">
+        <v>91</v>
+      </c>
       <c r="I62" s="5">
         <v>46210</v>
       </c>
@@ -5117,13 +5126,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q62" s="5">
         <v>46227</v>
@@ -5135,15 +5144,15 @@
         <v>1</v>
       </c>
       <c r="T62" s="12" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="U62" s="11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B63" s="8">
         <v>46118.662376064814</v>
@@ -5152,18 +5161,20 @@
         <v>46193.6126587037</v>
       </c>
       <c r="D63" s="8">
-        <v>46208.21062945602</v>
+        <v>46223.807264641204</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H63" s="9"/>
+        <v>91</v>
+      </c>
+      <c r="H63" s="9" t="s">
+        <v>91</v>
+      </c>
       <c r="I63" s="8">
         <v>46259</v>
       </c>
@@ -5180,13 +5191,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="P63" s="9" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q63" s="8">
         <v>46260</v>
@@ -5201,12 +5212,12 @@
         <v>32</v>
       </c>
       <c r="U63" s="11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B64" s="5">
         <v>46118.662387557866</v>
@@ -5215,18 +5226,20 @@
         <v>46193.61267944444</v>
       </c>
       <c r="D64" s="5">
-        <v>46208.21063037037</v>
+        <v>46223.80726166666</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H64" s="6"/>
+        <v>91</v>
+      </c>
+      <c r="H64" s="6" t="s">
+        <v>91</v>
+      </c>
       <c r="I64" s="5">
         <v>46261</v>
       </c>
@@ -5243,13 +5256,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q64" s="5">
         <v>46262</v>
@@ -5264,12 +5277,12 @@
         <v>32</v>
       </c>
       <c r="U64" s="11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B65" s="8">
         <v>46118.662398796296</v>
@@ -5278,18 +5291,20 @@
         <v>46193.61273716435</v>
       </c>
       <c r="D65" s="8">
-        <v>46208.21062888889</v>
+        <v>46223.807257754626</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H65" s="9"/>
+        <v>91</v>
+      </c>
+      <c r="H65" s="9" t="s">
+        <v>91</v>
+      </c>
       <c r="I65" s="8">
         <v>46265</v>
       </c>
@@ -5306,13 +5321,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="P65" s="9" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q65" s="8">
         <v>46266</v>
@@ -5327,12 +5342,12 @@
         <v>32</v>
       </c>
       <c r="U65" s="11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B66" s="5">
         <v>46118.66240984954</v>
@@ -5341,18 +5356,20 @@
         <v>46193.765511875</v>
       </c>
       <c r="D66" s="5">
-        <v>46208.21062840278</v>
+        <v>46223.80725450232</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H66" s="6"/>
+        <v>91</v>
+      </c>
+      <c r="H66" s="6" t="s">
+        <v>91</v>
+      </c>
       <c r="I66" s="6"/>
       <c r="J66" s="5">
         <v>46267</v>
@@ -5367,13 +5384,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q66" s="5">
         <v>46267</v>
@@ -5388,12 +5405,12 @@
         <v>32</v>
       </c>
       <c r="U66" s="11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B67" s="8">
         <v>46118.662420127315</v>
@@ -5402,18 +5419,20 @@
         <v>46196.92346424768</v>
       </c>
       <c r="D67" s="8">
-        <v>46208.21062791666</v>
+        <v>46223.807249398145</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H67" s="9"/>
+        <v>91</v>
+      </c>
+      <c r="H67" s="9" t="s">
+        <v>91</v>
+      </c>
       <c r="I67" s="8">
         <v>46269</v>
       </c>
@@ -5430,13 +5449,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="P67" s="9" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q67" s="8">
         <v>46269</v>
@@ -5451,12 +5470,12 @@
         <v>32</v>
       </c>
       <c r="U67" s="11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B68" s="5">
         <v>46118.66242769676</v>
@@ -5468,7 +5487,7 @@
         <v>46210.64097907407</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>25</v>
@@ -5492,7 +5511,7 @@
         <v>26</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="P68" s="6" t="s">
         <v>26</v>
@@ -5509,7 +5528,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B69" s="8">
         <v>46118.662431770834</v>
@@ -5521,16 +5540,16 @@
         <v>46208.21071721065</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="9" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H69" s="9" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="I69" s="9"/>
       <c r="J69" s="8">
@@ -5546,13 +5565,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="P69" s="9" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q69" s="8">
         <v>46272</v>
@@ -5572,7 +5591,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B70" s="5">
         <v>46118.662438252315</v>
@@ -5581,18 +5600,20 @@
         <v>46204.89777927083</v>
       </c>
       <c r="D70" s="5">
-        <v>46211.698982268514</v>
+        <v>46223.80733106482</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H70" s="6"/>
+        <v>91</v>
+      </c>
+      <c r="H70" s="6" t="s">
+        <v>91</v>
+      </c>
       <c r="I70" s="6"/>
       <c r="J70" s="5">
         <v>46273</v>
@@ -5607,13 +5628,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q70" s="5">
         <v>46273</v>
@@ -5633,7 +5654,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B71" s="8">
         <v>46118.66245149306</v>
@@ -5645,16 +5666,16 @@
         <v>46208.210718125</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="9" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H71" s="9" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="I71" s="9"/>
       <c r="J71" s="8">
@@ -5670,13 +5691,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="P71" s="9" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q71" s="8">
         <v>46274</v>
@@ -5696,7 +5717,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B72" s="5">
         <v>46118.66245769676</v>
@@ -5708,16 +5729,16 @@
         <v>46210.64281188657</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="I72" s="6"/>
       <c r="J72" s="5">
@@ -5733,13 +5754,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q72" s="5">
         <v>46275</v>
@@ -5759,7 +5780,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B73" s="8">
         <v>46118.66246467593</v>
@@ -5769,7 +5790,7 @@
         <v>46118.76284858796</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>25</v>
@@ -5793,7 +5814,7 @@
         <v>26</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P73" s="9" t="s">
         <v>26</v>
@@ -5806,7 +5827,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B74" s="5">
         <v>46118.66246796296</v>
@@ -5816,16 +5837,16 @@
         <v>46210.64097208333</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="I74" s="5">
         <v>46276</v>
@@ -5843,13 +5864,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q74" s="5">
         <v>46286</v>
@@ -5864,12 +5885,12 @@
         <v>32</v>
       </c>
       <c r="U74" s="12" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B75" s="8">
         <v>46118.66251259259</v>
@@ -5879,16 +5900,16 @@
         <v>46210.64097256944</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="9" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H75" s="9" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="I75" s="8">
         <v>46276</v>
@@ -5906,13 +5927,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q75" s="8">
         <v>46286</v>
@@ -5927,12 +5948,12 @@
         <v>32</v>
       </c>
       <c r="U75" s="12" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B76" s="5">
         <v>46118.662521377315</v>
@@ -5942,7 +5963,7 @@
         <v>46118.76362347222</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>25</v>
@@ -5966,7 +5987,7 @@
         <v>26</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="P76" s="6" t="s">
         <v>26</v>
@@ -5979,7 +6000,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B77" s="8">
         <v>46118.66252565972</v>
@@ -5989,7 +6010,7 @@
         <v>46210.64097050926</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>26</v>
@@ -6016,13 +6037,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="9" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="P77" s="9" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q77" s="8">
         <v>46286</v>
@@ -6037,12 +6058,12 @@
         <v>32</v>
       </c>
       <c r="U77" s="12" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B78" s="5">
         <v>46118.662532013885</v>
@@ -6052,7 +6073,7 @@
         <v>46118.76825962963</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
@@ -6079,13 +6100,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q78" s="5">
         <v>46295</v>
@@ -6100,7 +6121,7 @@
         <v>32</v>
       </c>
       <c r="U78" s="11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001533 - GESVIAL.xlsx
+++ b/data/50001533 - GESVIAL.xlsx
@@ -422,6 +422,9 @@
     <t>Fabricación Alabe - OT4285,Generación OC Alabe - OT4285</t>
   </si>
   <si>
+    <t>Media</t>
+  </si>
+  <si>
     <t>Tarea sin iniciar</t>
   </si>
   <si>
@@ -789,9 +792,6 @@
   </si>
   <si>
     <t>Montaje:,Montaje Alabe,Montaje Rodete,Montaje motor</t>
-  </si>
-  <si>
-    <t>Media</t>
   </si>
   <si>
     <t>1213955269755950</t>
@@ -2800,7 +2800,7 @@
         <v>46182.67644689815</v>
       </c>
       <c r="D24" s="5">
-        <v>46208.21003241898</v>
+        <v>46225.16781204861</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>102</v>
@@ -2847,16 +2847,16 @@
       <c r="S24" s="6">
         <v>1</v>
       </c>
-      <c r="T24" s="10" t="s">
-        <v>32</v>
+      <c r="T24" s="12" t="s">
+        <v>106</v>
       </c>
       <c r="U24" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B25" s="8">
         <v>46118.66209846065</v>
@@ -2868,7 +2868,7 @@
         <v>46208.21094784723</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>26</v>
@@ -2901,7 +2901,7 @@
         <v>79</v>
       </c>
       <c r="P25" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Q25" s="9"/>
       <c r="R25" s="9"/>
@@ -2913,7 +2913,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B26" s="5">
         <v>46118.66210270833</v>
@@ -2925,7 +2925,7 @@
         <v>46208.21109037037</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
@@ -2955,10 +2955,10 @@
         <v>102</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="Q26" s="6"/>
       <c r="R26" s="6"/>
@@ -2970,7 +2970,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B27" s="8">
         <v>46118.662106979165</v>
@@ -2982,7 +2982,7 @@
         <v>46208.209962824076</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>26</v>
@@ -3012,7 +3012,7 @@
         <v>99</v>
       </c>
       <c r="O27" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="P27" s="9" t="s">
         <v>99</v>
@@ -3030,12 +3030,12 @@
         <v>32</v>
       </c>
       <c r="U27" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B28" s="5">
         <v>46118.662112094906</v>
@@ -3047,7 +3047,7 @@
         <v>46208.21118949074</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
@@ -3074,13 +3074,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O28" s="6" t="s">
         <v>86</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
@@ -3091,12 +3091,12 @@
         <v>32</v>
       </c>
       <c r="U28" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B29" s="8">
         <v>46118.66211693287</v>
@@ -3108,7 +3108,7 @@
         <v>46208.21130763889</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>26</v>
@@ -3135,13 +3135,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O29" s="9" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="P29" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="Q29" s="9"/>
       <c r="R29" s="9"/>
@@ -3152,12 +3152,12 @@
         <v>32</v>
       </c>
       <c r="U29" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B30" s="5">
         <v>46118.66212202546</v>
@@ -3169,7 +3169,7 @@
         <v>46208.20888993055</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
@@ -3199,7 +3199,7 @@
         <v>99</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="P30" s="6" t="s">
         <v>99</v>
@@ -3217,12 +3217,12 @@
         <v>32</v>
       </c>
       <c r="U30" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B31" s="8">
         <v>46118.662126678246</v>
@@ -3234,7 +3234,7 @@
         <v>46208.211394502316</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>26</v>
@@ -3261,13 +3261,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="9" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="O31" s="9" t="s">
         <v>90</v>
       </c>
       <c r="P31" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="Q31" s="9"/>
       <c r="R31" s="9"/>
@@ -3278,12 +3278,12 @@
         <v>32</v>
       </c>
       <c r="U31" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B32" s="5">
         <v>46118.662131261575</v>
@@ -3295,7 +3295,7 @@
         <v>46208.21147013889</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
@@ -3322,13 +3322,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
@@ -3339,12 +3339,12 @@
         <v>32</v>
       </c>
       <c r="U32" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B33" s="8">
         <v>46118.66218372685</v>
@@ -3356,7 +3356,7 @@
         <v>46169.82398277777</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>26</v>
@@ -3386,7 +3386,7 @@
         <v>99</v>
       </c>
       <c r="O33" s="9" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="P33" s="9" t="s">
         <v>99</v>
@@ -3404,12 +3404,12 @@
         <v>32</v>
       </c>
       <c r="U33" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B34" s="5">
         <v>46118.662190104165</v>
@@ -3421,7 +3421,7 @@
         <v>46208.211555636575</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
@@ -3448,13 +3448,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="O34" s="6" t="s">
         <v>83</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3465,12 +3465,12 @@
         <v>32</v>
       </c>
       <c r="U34" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B35" s="8">
         <v>46118.662195694444</v>
@@ -3482,7 +3482,7 @@
         <v>46208.21164188658</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
@@ -3509,13 +3509,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P35" s="9" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="Q35" s="9"/>
       <c r="R35" s="9"/>
@@ -3526,12 +3526,12 @@
         <v>32</v>
       </c>
       <c r="U35" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B36" s="5">
         <v>46118.66220082176</v>
@@ -3543,7 +3543,7 @@
         <v>46208.211714791665</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
@@ -3570,13 +3570,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
@@ -3587,12 +3587,12 @@
         <v>32</v>
       </c>
       <c r="U36" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B37" s="8">
         <v>46118.66220634259</v>
@@ -3604,16 +3604,16 @@
         <v>46208.208834942125</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I37" s="8">
         <v>46154</v>
@@ -3634,7 +3634,7 @@
         <v>99</v>
       </c>
       <c r="O37" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="P37" s="9" t="s">
         <v>99</v>
@@ -3652,12 +3652,12 @@
         <v>32</v>
       </c>
       <c r="U37" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B38" s="5">
         <v>46118.66221234953</v>
@@ -3669,16 +3669,16 @@
         <v>46208.21179649305</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I38" s="5">
         <v>46154</v>
@@ -3696,13 +3696,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O38" s="6" t="s">
         <v>95</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -3713,12 +3713,12 @@
         <v>32</v>
       </c>
       <c r="U38" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B39" s="8">
         <v>46118.66221657407</v>
@@ -3730,16 +3730,16 @@
         <v>46208.211892453706</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I39" s="8">
         <v>46162</v>
@@ -3757,13 +3757,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P39" s="9" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Q39" s="9"/>
       <c r="R39" s="9"/>
@@ -3774,12 +3774,12 @@
         <v>32</v>
       </c>
       <c r="U39" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B40" s="5">
         <v>46118.662220972226</v>
@@ -3791,7 +3791,7 @@
         <v>46204.652183645834</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>25</v>
@@ -3815,7 +3815,7 @@
         <v>26</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="P40" s="6" t="s">
         <v>26</v>
@@ -3828,7 +3828,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B41" s="8">
         <v>46118.66222521991</v>
@@ -3840,16 +3840,16 @@
         <v>46129.57417895833</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I41" s="8">
         <v>46115</v>
@@ -3867,13 +3867,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O41" s="9" t="s">
         <v>72</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q41" s="8">
         <v>46121</v>
@@ -3893,7 +3893,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B42" s="5">
         <v>46118.66223170139</v>
@@ -3905,16 +3905,16 @@
         <v>46134.80028269676</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I42" s="5">
         <v>46142</v>
@@ -3932,13 +3932,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q42" s="5">
         <v>46148</v>
@@ -3958,7 +3958,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B43" s="8">
         <v>46118.662239375</v>
@@ -3976,10 +3976,10 @@
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I43" s="9"/>
       <c r="J43" s="8">
@@ -3995,13 +3995,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="P43" s="9" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q43" s="8">
         <v>46149</v>
@@ -4021,7 +4021,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B44" s="5">
         <v>46118.662245300926</v>
@@ -4033,16 +4033,16 @@
         <v>46208.20879145833</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="I44" s="5">
         <v>46268</v>
@@ -4060,13 +4060,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q44" s="5">
         <v>46268</v>
@@ -4081,12 +4081,12 @@
         <v>32</v>
       </c>
       <c r="U44" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B45" s="8">
         <v>46118.66224984954</v>
@@ -4098,7 +4098,7 @@
         <v>46184.68718828703</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>25</v>
@@ -4122,7 +4122,7 @@
         <v>26</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P45" s="9" t="s">
         <v>26</v>
@@ -4135,7 +4135,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B46" s="5">
         <v>46118.66225350695</v>
@@ -4147,16 +4147,16 @@
         <v>46208.20988328704</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="I46" s="5">
         <v>46171</v>
@@ -4174,13 +4174,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q46" s="5">
         <v>46174</v>
@@ -4195,12 +4195,12 @@
         <v>32</v>
       </c>
       <c r="U46" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B47" s="8">
         <v>46118.66225863426</v>
@@ -4212,16 +4212,16 @@
         <v>46208.20991337963</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I47" s="8">
         <v>46175</v>
@@ -4239,13 +4239,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q47" s="8">
         <v>46176</v>
@@ -4260,12 +4260,12 @@
         <v>32</v>
       </c>
       <c r="U47" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B48" s="5">
         <v>46118.662263819446</v>
@@ -4277,7 +4277,7 @@
         <v>46194.05633912037</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>25</v>
@@ -4301,7 +4301,7 @@
         <v>26</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P48" s="6" t="s">
         <v>26</v>
@@ -4314,7 +4314,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B49" s="8">
         <v>46118.66226751157</v>
@@ -4326,16 +4326,16 @@
         <v>46208.210227986114</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I49" s="8">
         <v>46177</v>
@@ -4353,13 +4353,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q49" s="8">
         <v>46185</v>
@@ -4374,12 +4374,12 @@
         <v>32</v>
       </c>
       <c r="U49" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B50" s="5">
         <v>46118.66227269676</v>
@@ -4391,16 +4391,16 @@
         <v>46208.210261203705</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I50" s="5">
         <v>46188</v>
@@ -4418,13 +4418,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q50" s="5">
         <v>46205</v>
@@ -4439,12 +4439,12 @@
         <v>32</v>
       </c>
       <c r="U50" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B51" s="8">
         <v>46184.687980393515</v>
@@ -4456,16 +4456,16 @@
         <v>46191.68718039352</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I51" s="8">
         <v>46188</v>
@@ -4483,7 +4483,7 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="O51" s="9" t="s">
         <v>26</v>
@@ -4499,7 +4499,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B52" s="5">
         <v>46184.688093055556</v>
@@ -4511,16 +4511,16 @@
         <v>46195.70254238426</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I52" s="5">
         <v>46188</v>
@@ -4538,7 +4538,7 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="O52" s="6" t="s">
         <v>26</v>
@@ -4554,7 +4554,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B53" s="8">
         <v>46184.68816803241</v>
@@ -4566,16 +4566,16 @@
         <v>46191.6871738426</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H53" s="9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I53" s="8">
         <v>46188</v>
@@ -4593,7 +4593,7 @@
         <v>26</v>
       </c>
       <c r="N53" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="O53" s="9" t="s">
         <v>26</v>
@@ -4609,7 +4609,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B54" s="5">
         <v>46184.68826700232</v>
@@ -4621,16 +4621,16 @@
         <v>46191.687168993056</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I54" s="5">
         <v>46188</v>
@@ -4648,7 +4648,7 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="O54" s="6" t="s">
         <v>26</v>
@@ -4664,7 +4664,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B55" s="8">
         <v>46118.66227863426</v>
@@ -4676,16 +4676,16 @@
         <v>46210.19828702546</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I55" s="8">
         <v>46206</v>
@@ -4703,13 +4703,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="P55" s="9" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q55" s="8">
         <v>46209</v>
@@ -4724,12 +4724,12 @@
         <v>55</v>
       </c>
       <c r="U55" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B56" s="5">
         <v>46118.66228488426</v>
@@ -4741,7 +4741,7 @@
         <v>46194.05632325231</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>25</v>
@@ -4765,7 +4765,7 @@
         <v>26</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P56" s="6" t="s">
         <v>26</v>
@@ -4778,7 +4778,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B57" s="8">
         <v>46118.66228803241</v>
@@ -4790,16 +4790,16 @@
         <v>46208.21036678241</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="I57" s="8">
         <v>46168</v>
@@ -4817,13 +4817,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="P57" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q57" s="8">
         <v>46169</v>
@@ -4838,12 +4838,12 @@
         <v>32</v>
       </c>
       <c r="U57" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B58" s="5">
         <v>46118.662293518515</v>
@@ -4861,10 +4861,10 @@
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="I58" s="5">
         <v>46189</v>
@@ -4882,13 +4882,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q58" s="5">
         <v>46190</v>
@@ -4903,12 +4903,12 @@
         <v>32</v>
       </c>
       <c r="U58" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B59" s="8">
         <v>46118.662299895834</v>
@@ -4920,16 +4920,16 @@
         <v>46208.21047276621</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="I59" s="8">
         <v>46233</v>
@@ -4947,13 +4947,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q59" s="8">
         <v>46234</v>
@@ -4968,12 +4968,12 @@
         <v>32</v>
       </c>
       <c r="U59" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B60" s="5">
         <v>46118.66235550926</v>
@@ -4985,16 +4985,16 @@
         <v>46208.210473217594</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="I60" s="5">
         <v>46255</v>
@@ -5012,13 +5012,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q60" s="5">
         <v>46258</v>
@@ -5033,12 +5033,12 @@
         <v>32</v>
       </c>
       <c r="U60" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B61" s="8">
         <v>46118.66236295139</v>
@@ -5050,7 +5050,7 @@
         <v>46204.900153703704</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>25</v>
@@ -5074,7 +5074,7 @@
         <v>26</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="P61" s="9" t="s">
         <v>26</v>
@@ -5087,7 +5087,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B62" s="5">
         <v>46118.66236873843</v>
@@ -5099,7 +5099,7 @@
         <v>46223.80726836805</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
@@ -5126,13 +5126,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q62" s="5">
         <v>46227</v>
@@ -5144,10 +5144,10 @@
         <v>1</v>
       </c>
       <c r="T62" s="12" t="s">
-        <v>229</v>
+        <v>106</v>
       </c>
       <c r="U62" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
@@ -5164,7 +5164,7 @@
         <v>46223.807264641204</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>26</v>
@@ -5191,7 +5191,7 @@
         <v>26</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O63" s="9" t="s">
         <v>231</v>
@@ -5212,7 +5212,7 @@
         <v>32</v>
       </c>
       <c r="U63" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
@@ -5256,7 +5256,7 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O64" s="6" t="s">
         <v>235</v>
@@ -5277,7 +5277,7 @@
         <v>32</v>
       </c>
       <c r="U64" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
@@ -5321,7 +5321,7 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O65" s="9" t="s">
         <v>238</v>
@@ -5342,7 +5342,7 @@
         <v>32</v>
       </c>
       <c r="U65" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
@@ -5359,7 +5359,7 @@
         <v>46223.80725450232</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
@@ -5384,7 +5384,7 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O66" s="6" t="s">
         <v>240</v>
@@ -5405,7 +5405,7 @@
         <v>32</v>
       </c>
       <c r="U66" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
@@ -5449,10 +5449,10 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P67" s="9" t="s">
         <v>244</v>
@@ -5470,7 +5470,7 @@
         <v>32</v>
       </c>
       <c r="U67" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
@@ -6121,7 +6121,7 @@
         <v>32</v>
       </c>
       <c r="U78" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001533 - GESVIAL.xlsx
+++ b/data/50001533 - GESVIAL.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="948" uniqueCount="282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="948" uniqueCount="283">
   <si>
     <t xml:space="preserve"> 50001533 - GESVIAL</t>
   </si>
@@ -375,6 +375,9 @@
   </si>
   <si>
     <t>propuesta nucleo rodete</t>
+  </si>
+  <si>
+    <t>NATALYA ESPINOZA</t>
   </si>
   <si>
     <t>nespinoza@zitron.com</t>
@@ -2633,7 +2636,7 @@
         <v>91</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I21" s="8">
         <v>46115</v>
@@ -2657,7 +2660,7 @@
         <v>68</v>
       </c>
       <c r="P21" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="Q21" s="8">
         <v>46118</v>
@@ -2672,12 +2675,12 @@
         <v>55</v>
       </c>
       <c r="U21" s="12" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B22" s="5">
         <v>46118.662087523146</v>
@@ -2689,7 +2692,7 @@
         <v>46223.807134884264</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>26</v>
@@ -2698,7 +2701,7 @@
         <v>91</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I22" s="5">
         <v>46150</v>
@@ -2719,10 +2722,10 @@
         <v>76</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="Q22" s="5">
         <v>46153</v>
@@ -2737,12 +2740,12 @@
         <v>32</v>
       </c>
       <c r="U22" s="12" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B23" s="8">
         <v>46118.66187195602</v>
@@ -2754,7 +2757,7 @@
         <v>46184.686248067126</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>25</v>
@@ -2778,7 +2781,7 @@
         <v>26</v>
       </c>
       <c r="O23" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="P23" s="9" t="s">
         <v>26</v>
@@ -2791,7 +2794,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B24" s="5">
         <v>46118.662093692124</v>
@@ -2803,16 +2806,16 @@
         <v>46225.16781204861</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I24" s="5">
         <v>46119</v>
@@ -2830,13 +2833,13 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="Q24" s="5">
         <v>46232</v>
@@ -2848,15 +2851,15 @@
         <v>1</v>
       </c>
       <c r="T24" s="12" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="U24" s="11" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B25" s="8">
         <v>46118.66209846065</v>
@@ -2868,16 +2871,16 @@
         <v>46208.21094784723</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I25" s="8">
         <v>46119</v>
@@ -2895,13 +2898,13 @@
         <v>26</v>
       </c>
       <c r="N25" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="O25" s="9" t="s">
         <v>79</v>
       </c>
       <c r="P25" s="9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Q25" s="9"/>
       <c r="R25" s="9"/>
@@ -2913,7 +2916,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B26" s="5">
         <v>46118.66210270833</v>
@@ -2925,16 +2928,16 @@
         <v>46208.21109037037</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I26" s="5">
         <v>46121</v>
@@ -2952,13 +2955,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="Q26" s="6"/>
       <c r="R26" s="6"/>
@@ -2970,7 +2973,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B27" s="8">
         <v>46118.662106979165</v>
@@ -2982,16 +2985,16 @@
         <v>46208.209962824076</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I27" s="8">
         <v>46111</v>
@@ -3009,13 +3012,13 @@
         <v>26</v>
       </c>
       <c r="N27" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="O27" s="9" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="P27" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="Q27" s="8">
         <v>46188</v>
@@ -3030,12 +3033,12 @@
         <v>32</v>
       </c>
       <c r="U27" s="11" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B28" s="5">
         <v>46118.662112094906</v>
@@ -3047,16 +3050,16 @@
         <v>46208.21118949074</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I28" s="5">
         <v>46111</v>
@@ -3074,13 +3077,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="O28" s="6" t="s">
         <v>86</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
@@ -3091,12 +3094,12 @@
         <v>32</v>
       </c>
       <c r="U28" s="11" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B29" s="8">
         <v>46118.66211693287</v>
@@ -3108,16 +3111,16 @@
         <v>46208.21130763889</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I29" s="8">
         <v>46120</v>
@@ -3135,13 +3138,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="O29" s="9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="P29" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="Q29" s="9"/>
       <c r="R29" s="9"/>
@@ -3152,12 +3155,12 @@
         <v>32</v>
       </c>
       <c r="U29" s="11" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B30" s="5">
         <v>46118.66212202546</v>
@@ -3169,16 +3172,16 @@
         <v>46208.20888993055</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I30" s="5">
         <v>46119</v>
@@ -3196,13 +3199,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="Q30" s="5">
         <v>46167</v>
@@ -3217,12 +3220,12 @@
         <v>32</v>
       </c>
       <c r="U30" s="11" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B31" s="8">
         <v>46118.662126678246</v>
@@ -3234,16 +3237,16 @@
         <v>46208.211394502316</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I31" s="8">
         <v>46119</v>
@@ -3261,13 +3264,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="9" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="O31" s="9" t="s">
         <v>90</v>
       </c>
       <c r="P31" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="Q31" s="9"/>
       <c r="R31" s="9"/>
@@ -3278,12 +3281,12 @@
         <v>32</v>
       </c>
       <c r="U31" s="11" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B32" s="5">
         <v>46118.662131261575</v>
@@ -3295,16 +3298,16 @@
         <v>46208.21147013889</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I32" s="5">
         <v>46121</v>
@@ -3322,13 +3325,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
@@ -3339,12 +3342,12 @@
         <v>32</v>
       </c>
       <c r="U32" s="11" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B33" s="8">
         <v>46118.66218372685</v>
@@ -3356,16 +3359,16 @@
         <v>46169.82398277777</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I33" s="8">
         <v>46112</v>
@@ -3383,13 +3386,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="O33" s="9" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="P33" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="Q33" s="8">
         <v>46254</v>
@@ -3404,12 +3407,12 @@
         <v>32</v>
       </c>
       <c r="U33" s="11" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B34" s="5">
         <v>46118.662190104165</v>
@@ -3421,16 +3424,16 @@
         <v>46208.211555636575</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I34" s="5">
         <v>46112</v>
@@ -3448,13 +3451,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="O34" s="6" t="s">
         <v>83</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3465,12 +3468,12 @@
         <v>32</v>
       </c>
       <c r="U34" s="11" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B35" s="8">
         <v>46118.662195694444</v>
@@ -3482,16 +3485,16 @@
         <v>46208.21164188658</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I35" s="8">
         <v>46133</v>
@@ -3509,13 +3512,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="P35" s="9" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="Q35" s="9"/>
       <c r="R35" s="9"/>
@@ -3526,12 +3529,12 @@
         <v>32</v>
       </c>
       <c r="U35" s="11" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B36" s="5">
         <v>46118.66220082176</v>
@@ -3543,16 +3546,16 @@
         <v>46208.211714791665</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I36" s="5">
         <v>46133</v>
@@ -3570,13 +3573,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
@@ -3587,12 +3590,12 @@
         <v>32</v>
       </c>
       <c r="U36" s="11" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B37" s="8">
         <v>46118.66220634259</v>
@@ -3604,16 +3607,16 @@
         <v>46208.208834942125</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I37" s="8">
         <v>46154</v>
@@ -3631,13 +3634,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="O37" s="9" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="Q37" s="8">
         <v>46170</v>
@@ -3652,12 +3655,12 @@
         <v>32</v>
       </c>
       <c r="U37" s="11" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B38" s="5">
         <v>46118.66221234953</v>
@@ -3669,16 +3672,16 @@
         <v>46208.21179649305</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I38" s="5">
         <v>46154</v>
@@ -3696,13 +3699,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -3713,12 +3716,12 @@
         <v>32</v>
       </c>
       <c r="U38" s="11" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B39" s="8">
         <v>46118.66221657407</v>
@@ -3730,16 +3733,16 @@
         <v>46208.211892453706</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I39" s="8">
         <v>46162</v>
@@ -3757,13 +3760,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P39" s="9" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q39" s="9"/>
       <c r="R39" s="9"/>
@@ -3774,12 +3777,12 @@
         <v>32</v>
       </c>
       <c r="U39" s="11" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B40" s="5">
         <v>46118.662220972226</v>
@@ -3791,7 +3794,7 @@
         <v>46204.652183645834</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>25</v>
@@ -3815,7 +3818,7 @@
         <v>26</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="P40" s="6" t="s">
         <v>26</v>
@@ -3828,7 +3831,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B41" s="8">
         <v>46118.66222521991</v>
@@ -3840,16 +3843,16 @@
         <v>46129.57417895833</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I41" s="8">
         <v>46115</v>
@@ -3867,13 +3870,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="O41" s="9" t="s">
         <v>72</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q41" s="8">
         <v>46121</v>
@@ -3893,7 +3896,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B42" s="5">
         <v>46118.66223170139</v>
@@ -3905,16 +3908,16 @@
         <v>46134.80028269676</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I42" s="5">
         <v>46142</v>
@@ -3932,13 +3935,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q42" s="5">
         <v>46148</v>
@@ -3958,7 +3961,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B43" s="8">
         <v>46118.662239375</v>
@@ -3970,16 +3973,16 @@
         <v>46134.80040836806</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I43" s="9"/>
       <c r="J43" s="8">
@@ -3995,13 +3998,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="P43" s="9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q43" s="8">
         <v>46149</v>
@@ -4021,7 +4024,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B44" s="5">
         <v>46118.662245300926</v>
@@ -4033,16 +4036,16 @@
         <v>46208.20879145833</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I44" s="5">
         <v>46268</v>
@@ -4060,13 +4063,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q44" s="5">
         <v>46268</v>
@@ -4081,12 +4084,12 @@
         <v>32</v>
       </c>
       <c r="U44" s="11" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B45" s="8">
         <v>46118.66224984954</v>
@@ -4098,7 +4101,7 @@
         <v>46184.68718828703</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>25</v>
@@ -4122,7 +4125,7 @@
         <v>26</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="P45" s="9" t="s">
         <v>26</v>
@@ -4135,7 +4138,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B46" s="5">
         <v>46118.66225350695</v>
@@ -4147,16 +4150,16 @@
         <v>46208.20988328704</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="I46" s="5">
         <v>46171</v>
@@ -4174,13 +4177,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q46" s="5">
         <v>46174</v>
@@ -4195,12 +4198,12 @@
         <v>32</v>
       </c>
       <c r="U46" s="11" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B47" s="8">
         <v>46118.66225863426</v>
@@ -4212,16 +4215,16 @@
         <v>46208.20991337963</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I47" s="8">
         <v>46175</v>
@@ -4239,13 +4242,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q47" s="8">
         <v>46176</v>
@@ -4260,12 +4263,12 @@
         <v>32</v>
       </c>
       <c r="U47" s="11" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B48" s="5">
         <v>46118.662263819446</v>
@@ -4277,7 +4280,7 @@
         <v>46194.05633912037</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>25</v>
@@ -4301,7 +4304,7 @@
         <v>26</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P48" s="6" t="s">
         <v>26</v>
@@ -4314,7 +4317,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B49" s="8">
         <v>46118.66226751157</v>
@@ -4326,16 +4329,16 @@
         <v>46208.210227986114</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I49" s="8">
         <v>46177</v>
@@ -4353,13 +4356,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q49" s="8">
         <v>46185</v>
@@ -4374,12 +4377,12 @@
         <v>32</v>
       </c>
       <c r="U49" s="11" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B50" s="5">
         <v>46118.66227269676</v>
@@ -4391,16 +4394,16 @@
         <v>46208.210261203705</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I50" s="5">
         <v>46188</v>
@@ -4418,13 +4421,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q50" s="5">
         <v>46205</v>
@@ -4439,12 +4442,12 @@
         <v>32</v>
       </c>
       <c r="U50" s="11" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B51" s="8">
         <v>46184.687980393515</v>
@@ -4456,16 +4459,16 @@
         <v>46191.68718039352</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I51" s="8">
         <v>46188</v>
@@ -4483,7 +4486,7 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O51" s="9" t="s">
         <v>26</v>
@@ -4499,7 +4502,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B52" s="5">
         <v>46184.688093055556</v>
@@ -4511,16 +4514,16 @@
         <v>46195.70254238426</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I52" s="5">
         <v>46188</v>
@@ -4538,7 +4541,7 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O52" s="6" t="s">
         <v>26</v>
@@ -4554,7 +4557,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B53" s="8">
         <v>46184.68816803241</v>
@@ -4566,16 +4569,16 @@
         <v>46191.6871738426</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H53" s="9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I53" s="8">
         <v>46188</v>
@@ -4593,7 +4596,7 @@
         <v>26</v>
       </c>
       <c r="N53" s="9" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O53" s="9" t="s">
         <v>26</v>
@@ -4609,7 +4612,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B54" s="5">
         <v>46184.68826700232</v>
@@ -4621,16 +4624,16 @@
         <v>46191.687168993056</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I54" s="5">
         <v>46188</v>
@@ -4648,7 +4651,7 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O54" s="6" t="s">
         <v>26</v>
@@ -4664,7 +4667,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B55" s="8">
         <v>46118.66227863426</v>
@@ -4676,16 +4679,16 @@
         <v>46210.19828702546</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I55" s="8">
         <v>46206</v>
@@ -4703,13 +4706,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="P55" s="9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q55" s="8">
         <v>46209</v>
@@ -4724,12 +4727,12 @@
         <v>55</v>
       </c>
       <c r="U55" s="11" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B56" s="5">
         <v>46118.66228488426</v>
@@ -4741,7 +4744,7 @@
         <v>46194.05632325231</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>25</v>
@@ -4765,7 +4768,7 @@
         <v>26</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P56" s="6" t="s">
         <v>26</v>
@@ -4778,7 +4781,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B57" s="8">
         <v>46118.66228803241</v>
@@ -4790,16 +4793,16 @@
         <v>46208.21036678241</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="I57" s="8">
         <v>46168</v>
@@ -4817,13 +4820,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="P57" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q57" s="8">
         <v>46169</v>
@@ -4838,12 +4841,12 @@
         <v>32</v>
       </c>
       <c r="U57" s="11" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B58" s="5">
         <v>46118.662293518515</v>
@@ -4861,10 +4864,10 @@
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="I58" s="5">
         <v>46189</v>
@@ -4882,13 +4885,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q58" s="5">
         <v>46190</v>
@@ -4903,12 +4906,12 @@
         <v>32</v>
       </c>
       <c r="U58" s="11" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B59" s="8">
         <v>46118.662299895834</v>
@@ -4920,16 +4923,16 @@
         <v>46208.21047276621</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="I59" s="8">
         <v>46233</v>
@@ -4947,13 +4950,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q59" s="8">
         <v>46234</v>
@@ -4968,12 +4971,12 @@
         <v>32</v>
       </c>
       <c r="U59" s="11" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B60" s="5">
         <v>46118.66235550926</v>
@@ -4985,16 +4988,16 @@
         <v>46208.210473217594</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="I60" s="5">
         <v>46255</v>
@@ -5012,13 +5015,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q60" s="5">
         <v>46258</v>
@@ -5033,12 +5036,12 @@
         <v>32</v>
       </c>
       <c r="U60" s="11" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B61" s="8">
         <v>46118.66236295139</v>
@@ -5050,7 +5053,7 @@
         <v>46204.900153703704</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>25</v>
@@ -5074,7 +5077,7 @@
         <v>26</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="P61" s="9" t="s">
         <v>26</v>
@@ -5087,7 +5090,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B62" s="5">
         <v>46118.66236873843</v>
@@ -5099,7 +5102,7 @@
         <v>46223.80726836805</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
@@ -5108,7 +5111,7 @@
         <v>91</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I62" s="5">
         <v>46210</v>
@@ -5126,13 +5129,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q62" s="5">
         <v>46227</v>
@@ -5144,15 +5147,15 @@
         <v>1</v>
       </c>
       <c r="T62" s="12" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="U62" s="11" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B63" s="8">
         <v>46118.662376064814</v>
@@ -5164,7 +5167,7 @@
         <v>46223.807264641204</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>26</v>
@@ -5173,7 +5176,7 @@
         <v>91</v>
       </c>
       <c r="H63" s="9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I63" s="8">
         <v>46259</v>
@@ -5191,13 +5194,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="P63" s="9" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q63" s="8">
         <v>46260</v>
@@ -5212,12 +5215,12 @@
         <v>32</v>
       </c>
       <c r="U63" s="11" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B64" s="5">
         <v>46118.662387557866</v>
@@ -5229,7 +5232,7 @@
         <v>46223.80726166666</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
@@ -5238,7 +5241,7 @@
         <v>91</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I64" s="5">
         <v>46261</v>
@@ -5256,13 +5259,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q64" s="5">
         <v>46262</v>
@@ -5277,12 +5280,12 @@
         <v>32</v>
       </c>
       <c r="U64" s="11" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B65" s="8">
         <v>46118.662398796296</v>
@@ -5294,7 +5297,7 @@
         <v>46223.807257754626</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
@@ -5303,7 +5306,7 @@
         <v>91</v>
       </c>
       <c r="H65" s="9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I65" s="8">
         <v>46265</v>
@@ -5321,13 +5324,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="P65" s="9" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q65" s="8">
         <v>46266</v>
@@ -5342,12 +5345,12 @@
         <v>32</v>
       </c>
       <c r="U65" s="11" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B66" s="5">
         <v>46118.66240984954</v>
@@ -5359,7 +5362,7 @@
         <v>46223.80725450232</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
@@ -5368,7 +5371,7 @@
         <v>91</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I66" s="6"/>
       <c r="J66" s="5">
@@ -5384,13 +5387,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q66" s="5">
         <v>46267</v>
@@ -5405,12 +5408,12 @@
         <v>32</v>
       </c>
       <c r="U66" s="11" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B67" s="8">
         <v>46118.662420127315</v>
@@ -5422,7 +5425,7 @@
         <v>46223.807249398145</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
@@ -5431,7 +5434,7 @@
         <v>91</v>
       </c>
       <c r="H67" s="9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I67" s="8">
         <v>46269</v>
@@ -5449,13 +5452,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P67" s="9" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q67" s="8">
         <v>46269</v>
@@ -5470,12 +5473,12 @@
         <v>32</v>
       </c>
       <c r="U67" s="11" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B68" s="5">
         <v>46118.66242769676</v>
@@ -5487,7 +5490,7 @@
         <v>46210.64097907407</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>25</v>
@@ -5511,7 +5514,7 @@
         <v>26</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P68" s="6" t="s">
         <v>26</v>
@@ -5528,7 +5531,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B69" s="8">
         <v>46118.662431770834</v>
@@ -5540,16 +5543,16 @@
         <v>46208.21071721065</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="9" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H69" s="9" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I69" s="9"/>
       <c r="J69" s="8">
@@ -5565,13 +5568,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="P69" s="9" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q69" s="8">
         <v>46272</v>
@@ -5591,7 +5594,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B70" s="5">
         <v>46118.662438252315</v>
@@ -5603,7 +5606,7 @@
         <v>46223.80733106482</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
@@ -5612,7 +5615,7 @@
         <v>91</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I70" s="6"/>
       <c r="J70" s="5">
@@ -5628,13 +5631,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q70" s="5">
         <v>46273</v>
@@ -5654,7 +5657,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B71" s="8">
         <v>46118.66245149306</v>
@@ -5666,16 +5669,16 @@
         <v>46208.210718125</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="9" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H71" s="9" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="I71" s="9"/>
       <c r="J71" s="8">
@@ -5691,13 +5694,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="P71" s="9" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q71" s="8">
         <v>46274</v>
@@ -5717,7 +5720,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B72" s="5">
         <v>46118.66245769676</v>
@@ -5729,16 +5732,16 @@
         <v>46210.64281188657</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="I72" s="6"/>
       <c r="J72" s="5">
@@ -5754,13 +5757,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q72" s="5">
         <v>46275</v>
@@ -5780,7 +5783,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B73" s="8">
         <v>46118.66246467593</v>
@@ -5790,7 +5793,7 @@
         <v>46118.76284858796</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>25</v>
@@ -5814,7 +5817,7 @@
         <v>26</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="P73" s="9" t="s">
         <v>26</v>
@@ -5827,7 +5830,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B74" s="5">
         <v>46118.66246796296</v>
@@ -5837,16 +5840,16 @@
         <v>46210.64097208333</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="I74" s="5">
         <v>46276</v>
@@ -5864,13 +5867,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q74" s="5">
         <v>46286</v>
@@ -5885,12 +5888,12 @@
         <v>32</v>
       </c>
       <c r="U74" s="12" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B75" s="8">
         <v>46118.66251259259</v>
@@ -5900,16 +5903,16 @@
         <v>46210.64097256944</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="9" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H75" s="9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="I75" s="8">
         <v>46276</v>
@@ -5927,13 +5930,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q75" s="8">
         <v>46286</v>
@@ -5948,12 +5951,12 @@
         <v>32</v>
       </c>
       <c r="U75" s="12" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B76" s="5">
         <v>46118.662521377315</v>
@@ -5963,7 +5966,7 @@
         <v>46118.76362347222</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>25</v>
@@ -5987,7 +5990,7 @@
         <v>26</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="P76" s="6" t="s">
         <v>26</v>
@@ -6000,7 +6003,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B77" s="8">
         <v>46118.66252565972</v>
@@ -6010,7 +6013,7 @@
         <v>46210.64097050926</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>26</v>
@@ -6037,13 +6040,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="9" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="P77" s="9" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q77" s="8">
         <v>46286</v>
@@ -6058,12 +6061,12 @@
         <v>32</v>
       </c>
       <c r="U77" s="12" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B78" s="5">
         <v>46118.662532013885</v>
@@ -6073,7 +6076,7 @@
         <v>46118.76825962963</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
@@ -6100,13 +6103,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q78" s="5">
         <v>46295</v>
@@ -6121,7 +6124,7 @@
         <v>32</v>
       </c>
       <c r="U78" s="11" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001533 - GESVIAL.xlsx
+++ b/data/50001533 - GESVIAL.xlsx
@@ -4920,7 +4920,7 @@
         <v>46193.561984872686</v>
       </c>
       <c r="D59" s="8">
-        <v>46208.21047276621</v>
+        <v>46227.19815074074</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>220</v>
@@ -4967,8 +4967,8 @@
       <c r="S59" s="9">
         <v>1</v>
       </c>
-      <c r="T59" s="10" t="s">
-        <v>32</v>
+      <c r="T59" s="12" t="s">
+        <v>107</v>
       </c>
       <c r="U59" s="11" t="s">
         <v>108</v>
@@ -5099,7 +5099,7 @@
         <v>46193.61261344908</v>
       </c>
       <c r="D62" s="5">
-        <v>46223.80726836805</v>
+        <v>46228.2021169213</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>229</v>
@@ -5146,8 +5146,8 @@
       <c r="S62" s="6">
         <v>1</v>
       </c>
-      <c r="T62" s="12" t="s">
-        <v>107</v>
+      <c r="T62" s="11" t="s">
+        <v>55</v>
       </c>
       <c r="U62" s="11" t="s">
         <v>108</v>

--- a/data/50001533 - GESVIAL.xlsx
+++ b/data/50001533 - GESVIAL.xlsx
@@ -425,349 +425,349 @@
     <t>Fabricación Alabe - OT4285,Generación OC Alabe - OT4285</t>
   </si>
   <si>
+    <t>Tarea sin iniciar</t>
+  </si>
+  <si>
+    <t>1213973327836153</t>
+  </si>
+  <si>
+    <t>Generación OC Alabe - OT4285</t>
+  </si>
+  <si>
+    <t>Fabricación Alabe - OT4285,Alabe - OT4285</t>
+  </si>
+  <si>
+    <t>1213963069147532</t>
+  </si>
+  <si>
+    <t>Fabricación Alabe - OT4285</t>
+  </si>
+  <si>
+    <t>Recepcion Alabe,Alabe - OT4285</t>
+  </si>
+  <si>
+    <t>1213963069147547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tablero y componentes electricos - OT 4286  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generación OC Tableros OT 4286 ,Fabricación Tablero OT 4286 </t>
+  </si>
+  <si>
+    <t>1213963069147562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generación OC Tableros OT 4286 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tablero y componentes electricos - OT 4286  ,Fabricación Tablero OT 4286 </t>
+  </si>
+  <si>
+    <t>1213962383658793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabricación Tablero OT 4286 </t>
+  </si>
+  <si>
+    <t>Tablero y componentes electricos - OT 4286  ,Recepcion Tableros y componentes electricos</t>
+  </si>
+  <si>
+    <t>1213964538755145</t>
+  </si>
+  <si>
+    <t>rodete- OT4285</t>
+  </si>
+  <si>
+    <t>Fabricación Rodete - OT4285,Generación OC Rodete - OT4285</t>
+  </si>
+  <si>
+    <t>1213964538755160</t>
+  </si>
+  <si>
+    <t>Generación OC Rodete - OT4285</t>
+  </si>
+  <si>
+    <t>Fabricación Rodete - OT4285,rodete- OT4285</t>
+  </si>
+  <si>
+    <t>1213963069155882</t>
+  </si>
+  <si>
+    <t>Fabricación Rodete - OT4285</t>
+  </si>
+  <si>
+    <t>Recepcion Rodete,Materiales a codigo // compras locales aprovisionamientomiento: - OT4285,rodete- OT4285</t>
+  </si>
+  <si>
+    <t>1213962383635366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Motor - OT4285 </t>
+  </si>
+  <si>
+    <t>Generación OC motor - OT4285,Fabricación motor  - OT4285,Planos motor proveedor - OT4285</t>
+  </si>
+  <si>
+    <t>1213962383670236</t>
+  </si>
+  <si>
+    <t>Generación OC motor - OT4285</t>
+  </si>
+  <si>
+    <t>Motor - OT4285 ,Fabricación motor  - OT4285,Planos motor proveedor - OT4285</t>
+  </si>
+  <si>
+    <t>1213962383670254</t>
+  </si>
+  <si>
+    <t>Fabricación motor  - OT4285</t>
+  </si>
+  <si>
+    <t>Motor - OT4285 ,Recepcion motor</t>
+  </si>
+  <si>
+    <t>1213962383670374</t>
+  </si>
+  <si>
+    <t>Planos motor proveedor - OT4285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Planos definitivo,Motor - OT4285 </t>
+  </si>
+  <si>
+    <t>1213962383670392</t>
+  </si>
+  <si>
+    <t>Materiales a codigo // compras locales aprovisionamientomiento: - OT4285</t>
+  </si>
+  <si>
+    <t>Yerlia Ayleen Castillo Diaz</t>
+  </si>
+  <si>
+    <t>yerlia.castillo@zitron.com</t>
+  </si>
+  <si>
+    <t>1213962383671823</t>
+  </si>
+  <si>
+    <t>Generación OC materiales - OT4285</t>
+  </si>
+  <si>
+    <t>Fabricacion a codigo y compras locales - OT4285</t>
+  </si>
+  <si>
+    <t>1213962383671836</t>
+  </si>
+  <si>
+    <t>Recepcion materiales a codigos // compras locales aprovisionamiento</t>
+  </si>
+  <si>
+    <t>1213963540650358</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseño:</t>
+  </si>
+  <si>
+    <t>Planos definitivo,Check planos ,Check Pruebas fat,Planos Preliminar</t>
+  </si>
+  <si>
+    <t>1213963540650370</t>
+  </si>
+  <si>
+    <t>Planos Preliminar</t>
+  </si>
+  <si>
+    <t>Gonzalo Javier Dávila Bade</t>
+  </si>
+  <si>
+    <t>gonzalo.davila@zitron.com</t>
+  </si>
+  <si>
+    <t>Planos definitivo,Ingenieria y diseño:</t>
+  </si>
+  <si>
+    <t>1213955269721772</t>
+  </si>
+  <si>
+    <t>Planos definitivo</t>
+  </si>
+  <si>
+    <t>Hernan Roberto Gutierrez Barrientos</t>
+  </si>
+  <si>
+    <t>hgutierrez@zitron.com</t>
+  </si>
+  <si>
+    <t>Ingenieria Basica Motor,Planos motor proveedor - OT4285,Planos Preliminar</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseño:,Check planos ,Montaje Rodete</t>
+  </si>
+  <si>
+    <t>1213962383672603</t>
+  </si>
+  <si>
+    <t>Fabricacion,Control de calidad ,Montaje Alabe,Ingenieria y diseño:,propuesta compras a codigo // aprovisionamiento,Montaje Rodete,Montaje motor</t>
+  </si>
+  <si>
+    <t>1213962383672623</t>
+  </si>
+  <si>
+    <t>Check Pruebas fat</t>
+  </si>
+  <si>
+    <t>Francisca González Cornejo</t>
+  </si>
+  <si>
+    <t>francisca.gonzalez@zitron.com</t>
+  </si>
+  <si>
+    <t>Pruebas FAT</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseño:,RE-PINTADO</t>
+  </si>
+  <si>
+    <t>1213962383676938</t>
+  </si>
+  <si>
+    <t>Bodega:</t>
+  </si>
+  <si>
+    <t>Recepcion materiales a codigos // compras locales aprovisionamiento,Control de calidad compras materiales a codigo // compras locale aprovisionamiento</t>
+  </si>
+  <si>
+    <t>1213962383676950</t>
+  </si>
+  <si>
+    <t>Victor Muñoz</t>
+  </si>
+  <si>
+    <t>victor.munoz@zitron.com</t>
+  </si>
+  <si>
+    <t>Bodega:,Control de calidad compras materiales a codigo // compras locale aprovisionamiento</t>
+  </si>
+  <si>
+    <t>1213962383680132</t>
+  </si>
+  <si>
+    <t>Control de calidad compras materiales a codigo // compras locale aprovisionamiento</t>
+  </si>
+  <si>
+    <t>Nicolás López</t>
+  </si>
+  <si>
+    <t>nicolas.lopez@zitron.com</t>
+  </si>
+  <si>
+    <t>Generacion oc ,Bodega:</t>
+  </si>
+  <si>
+    <t>1213962383680152</t>
+  </si>
+  <si>
+    <t>Fabricacion externa :</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generacion oc ,Fabricacion,Control de calidad </t>
+  </si>
+  <si>
+    <t>1213955269732491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generacion oc </t>
+  </si>
+  <si>
+    <t>Rosemary Singh</t>
+  </si>
+  <si>
+    <t>rosemary.singh@zitron.com</t>
+  </si>
+  <si>
+    <t>Fabricacion externa :,Fabricacion</t>
+  </si>
+  <si>
+    <t>1213955269732511</t>
+  </si>
+  <si>
+    <t>Fabricacion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generacion oc ,Check planos </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabricacion externa :,Control de calidad </t>
+  </si>
+  <si>
+    <t>1215632916059321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carcasa </t>
+  </si>
+  <si>
+    <t>1215632916059322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Silenciador </t>
+  </si>
+  <si>
+    <t>1215632916059323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pieza de adaptacion </t>
+  </si>
+  <si>
+    <t>1215632916059324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rejilla </t>
+  </si>
+  <si>
+    <t>1213955269733641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabricacion,Check planos </t>
+  </si>
+  <si>
+    <t>Fabricacion externa :,Revestimiento</t>
+  </si>
+  <si>
+    <t>1213955269734786</t>
+  </si>
+  <si>
+    <t>Recepcion Alabe,Recepcion Rodete,Recepcion Tableros y componentes electricos</t>
+  </si>
+  <si>
+    <t>1213955269734796</t>
+  </si>
+  <si>
+    <t>Recepcion Rodete</t>
+  </si>
+  <si>
+    <t>Montaje Rodete,Bodega:</t>
+  </si>
+  <si>
+    <t>1213964538786219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bodega:,Revisión tableros pruebas y componentes eléctricos </t>
+  </si>
+  <si>
+    <t>1213955269739200</t>
+  </si>
+  <si>
+    <t>Recepcion Alabe</t>
+  </si>
+  <si>
+    <t>Bodega:,Montaje Alabe</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>Tarea sin iniciar</t>
-  </si>
-  <si>
-    <t>1213973327836153</t>
-  </si>
-  <si>
-    <t>Generación OC Alabe - OT4285</t>
-  </si>
-  <si>
-    <t>Fabricación Alabe - OT4285,Alabe - OT4285</t>
-  </si>
-  <si>
-    <t>1213963069147532</t>
-  </si>
-  <si>
-    <t>Fabricación Alabe - OT4285</t>
-  </si>
-  <si>
-    <t>Recepcion Alabe,Alabe - OT4285</t>
-  </si>
-  <si>
-    <t>1213963069147547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tablero y componentes electricos - OT 4286  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generación OC Tableros OT 4286 ,Fabricación Tablero OT 4286 </t>
-  </si>
-  <si>
-    <t>1213963069147562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generación OC Tableros OT 4286 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tablero y componentes electricos - OT 4286  ,Fabricación Tablero OT 4286 </t>
-  </si>
-  <si>
-    <t>1213962383658793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fabricación Tablero OT 4286 </t>
-  </si>
-  <si>
-    <t>Tablero y componentes electricos - OT 4286  ,Recepcion Tableros y componentes electricos</t>
-  </si>
-  <si>
-    <t>1213964538755145</t>
-  </si>
-  <si>
-    <t>rodete- OT4285</t>
-  </si>
-  <si>
-    <t>Fabricación Rodete - OT4285,Generación OC Rodete - OT4285</t>
-  </si>
-  <si>
-    <t>1213964538755160</t>
-  </si>
-  <si>
-    <t>Generación OC Rodete - OT4285</t>
-  </si>
-  <si>
-    <t>Fabricación Rodete - OT4285,rodete- OT4285</t>
-  </si>
-  <si>
-    <t>1213963069155882</t>
-  </si>
-  <si>
-    <t>Fabricación Rodete - OT4285</t>
-  </si>
-  <si>
-    <t>Recepcion Rodete,Materiales a codigo // compras locales aprovisionamientomiento: - OT4285,rodete- OT4285</t>
-  </si>
-  <si>
-    <t>1213962383635366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Motor - OT4285 </t>
-  </si>
-  <si>
-    <t>Generación OC motor - OT4285,Fabricación motor  - OT4285,Planos motor proveedor - OT4285</t>
-  </si>
-  <si>
-    <t>1213962383670236</t>
-  </si>
-  <si>
-    <t>Generación OC motor - OT4285</t>
-  </si>
-  <si>
-    <t>Motor - OT4285 ,Fabricación motor  - OT4285,Planos motor proveedor - OT4285</t>
-  </si>
-  <si>
-    <t>1213962383670254</t>
-  </si>
-  <si>
-    <t>Fabricación motor  - OT4285</t>
-  </si>
-  <si>
-    <t>Motor - OT4285 ,Recepcion motor</t>
-  </si>
-  <si>
-    <t>1213962383670374</t>
-  </si>
-  <si>
-    <t>Planos motor proveedor - OT4285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Planos definitivo,Motor - OT4285 </t>
-  </si>
-  <si>
-    <t>1213962383670392</t>
-  </si>
-  <si>
-    <t>Materiales a codigo // compras locales aprovisionamientomiento: - OT4285</t>
-  </si>
-  <si>
-    <t>Yerlia Ayleen Castillo Diaz</t>
-  </si>
-  <si>
-    <t>yerlia.castillo@zitron.com</t>
-  </si>
-  <si>
-    <t>1213962383671823</t>
-  </si>
-  <si>
-    <t>Generación OC materiales - OT4285</t>
-  </si>
-  <si>
-    <t>Fabricacion a codigo y compras locales - OT4285</t>
-  </si>
-  <si>
-    <t>1213962383671836</t>
-  </si>
-  <si>
-    <t>Recepcion materiales a codigos // compras locales aprovisionamiento</t>
-  </si>
-  <si>
-    <t>1213963540650358</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseño:</t>
-  </si>
-  <si>
-    <t>Planos definitivo,Check planos ,Check Pruebas fat,Planos Preliminar</t>
-  </si>
-  <si>
-    <t>1213963540650370</t>
-  </si>
-  <si>
-    <t>Planos Preliminar</t>
-  </si>
-  <si>
-    <t>Gonzalo Javier Dávila Bade</t>
-  </si>
-  <si>
-    <t>gonzalo.davila@zitron.com</t>
-  </si>
-  <si>
-    <t>Planos definitivo,Ingenieria y diseño:</t>
-  </si>
-  <si>
-    <t>1213955269721772</t>
-  </si>
-  <si>
-    <t>Planos definitivo</t>
-  </si>
-  <si>
-    <t>Hernan Roberto Gutierrez Barrientos</t>
-  </si>
-  <si>
-    <t>hgutierrez@zitron.com</t>
-  </si>
-  <si>
-    <t>Ingenieria Basica Motor,Planos motor proveedor - OT4285,Planos Preliminar</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseño:,Check planos ,Montaje Rodete</t>
-  </si>
-  <si>
-    <t>1213962383672603</t>
-  </si>
-  <si>
-    <t>Fabricacion,Control de calidad ,Montaje Alabe,Ingenieria y diseño:,propuesta compras a codigo // aprovisionamiento,Montaje Rodete,Montaje motor</t>
-  </si>
-  <si>
-    <t>1213962383672623</t>
-  </si>
-  <si>
-    <t>Check Pruebas fat</t>
-  </si>
-  <si>
-    <t>Francisca González Cornejo</t>
-  </si>
-  <si>
-    <t>francisca.gonzalez@zitron.com</t>
-  </si>
-  <si>
-    <t>Pruebas FAT</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseño:,RE-PINTADO</t>
-  </si>
-  <si>
-    <t>1213962383676938</t>
-  </si>
-  <si>
-    <t>Bodega:</t>
-  </si>
-  <si>
-    <t>Recepcion materiales a codigos // compras locales aprovisionamiento,Control de calidad compras materiales a codigo // compras locale aprovisionamiento</t>
-  </si>
-  <si>
-    <t>1213962383676950</t>
-  </si>
-  <si>
-    <t>Victor Muñoz</t>
-  </si>
-  <si>
-    <t>victor.munoz@zitron.com</t>
-  </si>
-  <si>
-    <t>Bodega:,Control de calidad compras materiales a codigo // compras locale aprovisionamiento</t>
-  </si>
-  <si>
-    <t>1213962383680132</t>
-  </si>
-  <si>
-    <t>Control de calidad compras materiales a codigo // compras locale aprovisionamiento</t>
-  </si>
-  <si>
-    <t>Nicolás López</t>
-  </si>
-  <si>
-    <t>nicolas.lopez@zitron.com</t>
-  </si>
-  <si>
-    <t>Generacion oc ,Bodega:</t>
-  </si>
-  <si>
-    <t>1213962383680152</t>
-  </si>
-  <si>
-    <t>Fabricacion externa :</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generacion oc ,Fabricacion,Control de calidad </t>
-  </si>
-  <si>
-    <t>1213955269732491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generacion oc </t>
-  </si>
-  <si>
-    <t>Rosemary Singh</t>
-  </si>
-  <si>
-    <t>rosemary.singh@zitron.com</t>
-  </si>
-  <si>
-    <t>Fabricacion externa :,Fabricacion</t>
-  </si>
-  <si>
-    <t>1213955269732511</t>
-  </si>
-  <si>
-    <t>Fabricacion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generacion oc ,Check planos </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fabricacion externa :,Control de calidad </t>
-  </si>
-  <si>
-    <t>1215632916059321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Carcasa </t>
-  </si>
-  <si>
-    <t>1215632916059322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Silenciador </t>
-  </si>
-  <si>
-    <t>1215632916059323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pieza de adaptacion </t>
-  </si>
-  <si>
-    <t>1215632916059324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rejilla </t>
-  </si>
-  <si>
-    <t>1213955269733641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fabricacion,Check planos </t>
-  </si>
-  <si>
-    <t>Fabricacion externa :,Revestimiento</t>
-  </si>
-  <si>
-    <t>1213955269734786</t>
-  </si>
-  <si>
-    <t>Recepcion Alabe,Recepcion Rodete,Recepcion Tableros y componentes electricos</t>
-  </si>
-  <si>
-    <t>1213955269734796</t>
-  </si>
-  <si>
-    <t>Recepcion Rodete</t>
-  </si>
-  <si>
-    <t>Montaje Rodete,Bodega:</t>
-  </si>
-  <si>
-    <t>1213964538786219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bodega:,Revisión tableros pruebas y componentes eléctricos </t>
-  </si>
-  <si>
-    <t>1213955269739200</t>
-  </si>
-  <si>
-    <t>Recepcion Alabe</t>
-  </si>
-  <si>
-    <t>Bodega:,Montaje Alabe</t>
   </si>
   <si>
     <t>1213964538772984</t>
@@ -2803,7 +2803,7 @@
         <v>46182.67644689815</v>
       </c>
       <c r="D24" s="5">
-        <v>46225.16781204861</v>
+        <v>46233.20105234954</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>103</v>
@@ -2850,16 +2850,16 @@
       <c r="S24" s="6">
         <v>1</v>
       </c>
-      <c r="T24" s="12" t="s">
+      <c r="T24" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="U24" s="11" t="s">
         <v>107</v>
-      </c>
-      <c r="U24" s="11" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B25" s="8">
         <v>46118.66209846065</v>
@@ -2871,7 +2871,7 @@
         <v>46208.21094784723</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>26</v>
@@ -2904,7 +2904,7 @@
         <v>79</v>
       </c>
       <c r="P25" s="9" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="Q25" s="9"/>
       <c r="R25" s="9"/>
@@ -2916,7 +2916,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B26" s="5">
         <v>46118.66210270833</v>
@@ -2928,7 +2928,7 @@
         <v>46208.21109037037</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
@@ -2958,10 +2958,10 @@
         <v>103</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Q26" s="6"/>
       <c r="R26" s="6"/>
@@ -2973,7 +2973,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B27" s="8">
         <v>46118.662106979165</v>
@@ -2985,7 +2985,7 @@
         <v>46208.209962824076</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>26</v>
@@ -3015,7 +3015,7 @@
         <v>100</v>
       </c>
       <c r="O27" s="9" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="P27" s="9" t="s">
         <v>100</v>
@@ -3033,12 +3033,12 @@
         <v>32</v>
       </c>
       <c r="U27" s="11" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B28" s="5">
         <v>46118.662112094906</v>
@@ -3050,7 +3050,7 @@
         <v>46208.21118949074</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
@@ -3077,13 +3077,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="O28" s="6" t="s">
         <v>86</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
@@ -3094,12 +3094,12 @@
         <v>32</v>
       </c>
       <c r="U28" s="11" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B29" s="8">
         <v>46118.66211693287</v>
@@ -3111,7 +3111,7 @@
         <v>46208.21130763889</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>26</v>
@@ -3138,13 +3138,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="9" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="O29" s="9" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="P29" s="9" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Q29" s="9"/>
       <c r="R29" s="9"/>
@@ -3155,12 +3155,12 @@
         <v>32</v>
       </c>
       <c r="U29" s="11" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B30" s="5">
         <v>46118.66212202546</v>
@@ -3172,7 +3172,7 @@
         <v>46208.20888993055</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
@@ -3202,7 +3202,7 @@
         <v>100</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="P30" s="6" t="s">
         <v>100</v>
@@ -3220,12 +3220,12 @@
         <v>32</v>
       </c>
       <c r="U30" s="11" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B31" s="8">
         <v>46118.662126678246</v>
@@ -3237,7 +3237,7 @@
         <v>46208.211394502316</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>26</v>
@@ -3264,13 +3264,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="O31" s="9" t="s">
         <v>90</v>
       </c>
       <c r="P31" s="9" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="Q31" s="9"/>
       <c r="R31" s="9"/>
@@ -3281,12 +3281,12 @@
         <v>32</v>
       </c>
       <c r="U31" s="11" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B32" s="5">
         <v>46118.662131261575</v>
@@ -3298,7 +3298,7 @@
         <v>46208.21147013889</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
@@ -3325,13 +3325,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
@@ -3342,12 +3342,12 @@
         <v>32</v>
       </c>
       <c r="U32" s="11" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B33" s="8">
         <v>46118.66218372685</v>
@@ -3359,7 +3359,7 @@
         <v>46169.82398277777</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>26</v>
@@ -3389,7 +3389,7 @@
         <v>100</v>
       </c>
       <c r="O33" s="9" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P33" s="9" t="s">
         <v>100</v>
@@ -3407,12 +3407,12 @@
         <v>32</v>
       </c>
       <c r="U33" s="11" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B34" s="5">
         <v>46118.662190104165</v>
@@ -3424,7 +3424,7 @@
         <v>46208.211555636575</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
@@ -3451,13 +3451,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="O34" s="6" t="s">
         <v>83</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3468,12 +3468,12 @@
         <v>32</v>
       </c>
       <c r="U34" s="11" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B35" s="8">
         <v>46118.662195694444</v>
@@ -3485,7 +3485,7 @@
         <v>46208.21164188658</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
@@ -3512,13 +3512,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="P35" s="9" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="Q35" s="9"/>
       <c r="R35" s="9"/>
@@ -3529,12 +3529,12 @@
         <v>32</v>
       </c>
       <c r="U35" s="11" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B36" s="5">
         <v>46118.66220082176</v>
@@ -3546,7 +3546,7 @@
         <v>46208.211714791665</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
@@ -3573,13 +3573,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
@@ -3590,12 +3590,12 @@
         <v>32</v>
       </c>
       <c r="U36" s="11" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B37" s="8">
         <v>46118.66220634259</v>
@@ -3607,16 +3607,16 @@
         <v>46208.208834942125</v>
       </c>
       <c r="E37" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="F37" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G37" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="F37" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G37" s="9" t="s">
+      <c r="H37" s="9" t="s">
         <v>147</v>
-      </c>
-      <c r="H37" s="9" t="s">
-        <v>148</v>
       </c>
       <c r="I37" s="8">
         <v>46154</v>
@@ -3637,7 +3637,7 @@
         <v>100</v>
       </c>
       <c r="O37" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="P37" s="9" t="s">
         <v>100</v>
@@ -3655,12 +3655,12 @@
         <v>32</v>
       </c>
       <c r="U37" s="11" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B38" s="5">
         <v>46118.66221234953</v>
@@ -3672,16 +3672,16 @@
         <v>46208.21179649305</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="H38" s="6" t="s">
         <v>147</v>
-      </c>
-      <c r="H38" s="6" t="s">
-        <v>148</v>
       </c>
       <c r="I38" s="5">
         <v>46154</v>
@@ -3699,13 +3699,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="O38" s="6" t="s">
         <v>96</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -3716,12 +3716,12 @@
         <v>32</v>
       </c>
       <c r="U38" s="11" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B39" s="8">
         <v>46118.66221657407</v>
@@ -3733,16 +3733,16 @@
         <v>46208.211892453706</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="H39" s="9" t="s">
         <v>147</v>
-      </c>
-      <c r="H39" s="9" t="s">
-        <v>148</v>
       </c>
       <c r="I39" s="8">
         <v>46162</v>
@@ -3760,13 +3760,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P39" s="9" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="Q39" s="9"/>
       <c r="R39" s="9"/>
@@ -3777,12 +3777,12 @@
         <v>32</v>
       </c>
       <c r="U39" s="11" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B40" s="5">
         <v>46118.662220972226</v>
@@ -3794,7 +3794,7 @@
         <v>46204.652183645834</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>25</v>
@@ -3818,7 +3818,7 @@
         <v>26</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="P40" s="6" t="s">
         <v>26</v>
@@ -3831,7 +3831,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B41" s="8">
         <v>46118.66222521991</v>
@@ -3843,16 +3843,16 @@
         <v>46129.57417895833</v>
       </c>
       <c r="E41" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="F41" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G41" s="9" t="s">
         <v>158</v>
       </c>
-      <c r="F41" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G41" s="9" t="s">
+      <c r="H41" s="9" t="s">
         <v>159</v>
-      </c>
-      <c r="H41" s="9" t="s">
-        <v>160</v>
       </c>
       <c r="I41" s="8">
         <v>46115</v>
@@ -3870,13 +3870,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="O41" s="9" t="s">
         <v>72</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="Q41" s="8">
         <v>46121</v>
@@ -3896,7 +3896,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B42" s="5">
         <v>46118.66223170139</v>
@@ -3908,16 +3908,16 @@
         <v>46134.80028269676</v>
       </c>
       <c r="E42" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="F42" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G42" s="6" t="s">
         <v>163</v>
       </c>
-      <c r="F42" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G42" s="6" t="s">
+      <c r="H42" s="6" t="s">
         <v>164</v>
-      </c>
-      <c r="H42" s="6" t="s">
-        <v>165</v>
       </c>
       <c r="I42" s="5">
         <v>46142</v>
@@ -3935,13 +3935,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="O42" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="P42" s="6" t="s">
         <v>166</v>
-      </c>
-      <c r="P42" s="6" t="s">
-        <v>167</v>
       </c>
       <c r="Q42" s="5">
         <v>46148</v>
@@ -3961,7 +3961,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B43" s="8">
         <v>46118.662239375</v>
@@ -3979,10 +3979,10 @@
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="H43" s="9" t="s">
         <v>164</v>
-      </c>
-      <c r="H43" s="9" t="s">
-        <v>165</v>
       </c>
       <c r="I43" s="9"/>
       <c r="J43" s="8">
@@ -3998,13 +3998,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="P43" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="Q43" s="8">
         <v>46149</v>
@@ -4024,7 +4024,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B44" s="5">
         <v>46118.662245300926</v>
@@ -4036,16 +4036,16 @@
         <v>46208.20879145833</v>
       </c>
       <c r="E44" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="F44" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G44" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="F44" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G44" s="6" t="s">
+      <c r="H44" s="6" t="s">
         <v>172</v>
-      </c>
-      <c r="H44" s="6" t="s">
-        <v>173</v>
       </c>
       <c r="I44" s="5">
         <v>46268</v>
@@ -4063,13 +4063,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="O44" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="P44" s="6" t="s">
         <v>174</v>
-      </c>
-      <c r="P44" s="6" t="s">
-        <v>175</v>
       </c>
       <c r="Q44" s="5">
         <v>46268</v>
@@ -4084,12 +4084,12 @@
         <v>32</v>
       </c>
       <c r="U44" s="11" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B45" s="8">
         <v>46118.66224984954</v>
@@ -4101,7 +4101,7 @@
         <v>46184.68718828703</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>25</v>
@@ -4125,7 +4125,7 @@
         <v>26</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="P45" s="9" t="s">
         <v>26</v>
@@ -4138,7 +4138,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B46" s="5">
         <v>46118.66225350695</v>
@@ -4150,16 +4150,16 @@
         <v>46208.20988328704</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="H46" s="6" t="s">
         <v>180</v>
-      </c>
-      <c r="H46" s="6" t="s">
-        <v>181</v>
       </c>
       <c r="I46" s="5">
         <v>46171</v>
@@ -4177,13 +4177,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q46" s="5">
         <v>46174</v>
@@ -4198,12 +4198,12 @@
         <v>32</v>
       </c>
       <c r="U46" s="11" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B47" s="8">
         <v>46118.66225863426</v>
@@ -4215,16 +4215,16 @@
         <v>46208.20991337963</v>
       </c>
       <c r="E47" s="9" t="s">
+        <v>183</v>
+      </c>
+      <c r="F47" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G47" s="9" t="s">
         <v>184</v>
       </c>
-      <c r="F47" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G47" s="9" t="s">
+      <c r="H47" s="9" t="s">
         <v>185</v>
-      </c>
-      <c r="H47" s="9" t="s">
-        <v>186</v>
       </c>
       <c r="I47" s="8">
         <v>46175</v>
@@ -4242,13 +4242,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="Q47" s="8">
         <v>46176</v>
@@ -4263,12 +4263,12 @@
         <v>32</v>
       </c>
       <c r="U47" s="11" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B48" s="5">
         <v>46118.662263819446</v>
@@ -4280,7 +4280,7 @@
         <v>46194.05633912037</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>25</v>
@@ -4304,7 +4304,7 @@
         <v>26</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P48" s="6" t="s">
         <v>26</v>
@@ -4317,7 +4317,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B49" s="8">
         <v>46118.66226751157</v>
@@ -4329,16 +4329,16 @@
         <v>46208.210227986114</v>
       </c>
       <c r="E49" s="9" t="s">
+        <v>191</v>
+      </c>
+      <c r="F49" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G49" s="9" t="s">
         <v>192</v>
       </c>
-      <c r="F49" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G49" s="9" t="s">
+      <c r="H49" s="9" t="s">
         <v>193</v>
-      </c>
-      <c r="H49" s="9" t="s">
-        <v>194</v>
       </c>
       <c r="I49" s="8">
         <v>46177</v>
@@ -4356,13 +4356,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="Q49" s="8">
         <v>46185</v>
@@ -4377,12 +4377,12 @@
         <v>32</v>
       </c>
       <c r="U49" s="11" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B50" s="5">
         <v>46118.66227269676</v>
@@ -4394,16 +4394,16 @@
         <v>46208.210261203705</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="H50" s="6" t="s">
         <v>193</v>
-      </c>
-      <c r="H50" s="6" t="s">
-        <v>194</v>
       </c>
       <c r="I50" s="5">
         <v>46188</v>
@@ -4421,13 +4421,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="O50" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="P50" s="6" t="s">
         <v>198</v>
-      </c>
-      <c r="P50" s="6" t="s">
-        <v>199</v>
       </c>
       <c r="Q50" s="5">
         <v>46205</v>
@@ -4442,12 +4442,12 @@
         <v>32</v>
       </c>
       <c r="U50" s="11" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B51" s="8">
         <v>46184.687980393515</v>
@@ -4459,16 +4459,16 @@
         <v>46191.68718039352</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="H51" s="9" t="s">
         <v>193</v>
-      </c>
-      <c r="H51" s="9" t="s">
-        <v>194</v>
       </c>
       <c r="I51" s="8">
         <v>46188</v>
@@ -4486,7 +4486,7 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="O51" s="9" t="s">
         <v>26</v>
@@ -4502,7 +4502,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B52" s="5">
         <v>46184.688093055556</v>
@@ -4514,16 +4514,16 @@
         <v>46195.70254238426</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="H52" s="6" t="s">
         <v>193</v>
-      </c>
-      <c r="H52" s="6" t="s">
-        <v>194</v>
       </c>
       <c r="I52" s="5">
         <v>46188</v>
@@ -4541,7 +4541,7 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="O52" s="6" t="s">
         <v>26</v>
@@ -4557,7 +4557,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B53" s="8">
         <v>46184.68816803241</v>
@@ -4569,16 +4569,16 @@
         <v>46191.6871738426</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="H53" s="9" t="s">
         <v>193</v>
-      </c>
-      <c r="H53" s="9" t="s">
-        <v>194</v>
       </c>
       <c r="I53" s="8">
         <v>46188</v>
@@ -4596,7 +4596,7 @@
         <v>26</v>
       </c>
       <c r="N53" s="9" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="O53" s="9" t="s">
         <v>26</v>
@@ -4612,7 +4612,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B54" s="5">
         <v>46184.68826700232</v>
@@ -4624,16 +4624,16 @@
         <v>46191.687168993056</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="H54" s="6" t="s">
         <v>193</v>
-      </c>
-      <c r="H54" s="6" t="s">
-        <v>194</v>
       </c>
       <c r="I54" s="5">
         <v>46188</v>
@@ -4651,7 +4651,7 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="O54" s="6" t="s">
         <v>26</v>
@@ -4667,7 +4667,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B55" s="8">
         <v>46118.66227863426</v>
@@ -4679,16 +4679,16 @@
         <v>46210.19828702546</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="H55" s="9" t="s">
         <v>185</v>
-      </c>
-      <c r="H55" s="9" t="s">
-        <v>186</v>
       </c>
       <c r="I55" s="8">
         <v>46206</v>
@@ -4706,13 +4706,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="O55" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="P55" s="9" t="s">
         <v>210</v>
-      </c>
-      <c r="P55" s="9" t="s">
-        <v>211</v>
       </c>
       <c r="Q55" s="8">
         <v>46209</v>
@@ -4727,12 +4727,12 @@
         <v>55</v>
       </c>
       <c r="U55" s="11" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B56" s="5">
         <v>46118.66228488426</v>
@@ -4744,7 +4744,7 @@
         <v>46194.05632325231</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>25</v>
@@ -4768,7 +4768,7 @@
         <v>26</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P56" s="6" t="s">
         <v>26</v>
@@ -4781,7 +4781,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B57" s="8">
         <v>46118.66228803241</v>
@@ -4793,16 +4793,16 @@
         <v>46208.21036678241</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="H57" s="9" t="s">
         <v>180</v>
-      </c>
-      <c r="H57" s="9" t="s">
-        <v>181</v>
       </c>
       <c r="I57" s="8">
         <v>46168</v>
@@ -4820,13 +4820,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="P57" s="9" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="Q57" s="8">
         <v>46169</v>
@@ -4841,12 +4841,12 @@
         <v>32</v>
       </c>
       <c r="U57" s="11" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B58" s="5">
         <v>46118.662293518515</v>
@@ -4864,10 +4864,10 @@
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="H58" s="6" t="s">
         <v>180</v>
-      </c>
-      <c r="H58" s="6" t="s">
-        <v>181</v>
       </c>
       <c r="I58" s="5">
         <v>46189</v>
@@ -4885,13 +4885,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="Q58" s="5">
         <v>46190</v>
@@ -4906,12 +4906,12 @@
         <v>32</v>
       </c>
       <c r="U58" s="11" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B59" s="8">
         <v>46118.662299895834</v>
@@ -4923,16 +4923,16 @@
         <v>46227.19815074074</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="H59" s="9" t="s">
         <v>180</v>
-      </c>
-      <c r="H59" s="9" t="s">
-        <v>181</v>
       </c>
       <c r="I59" s="8">
         <v>46233</v>
@@ -4950,13 +4950,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="Q59" s="8">
         <v>46234</v>
@@ -4968,10 +4968,10 @@
         <v>1</v>
       </c>
       <c r="T59" s="12" t="s">
+        <v>221</v>
+      </c>
+      <c r="U59" s="11" t="s">
         <v>107</v>
-      </c>
-      <c r="U59" s="11" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
@@ -4994,10 +4994,10 @@
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="H60" s="6" t="s">
         <v>180</v>
-      </c>
-      <c r="H60" s="6" t="s">
-        <v>181</v>
       </c>
       <c r="I60" s="5">
         <v>46255</v>
@@ -5015,10 +5015,10 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P60" s="6" t="s">
         <v>224</v>
@@ -5036,7 +5036,7 @@
         <v>32</v>
       </c>
       <c r="U60" s="11" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
@@ -5132,7 +5132,7 @@
         <v>226</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="P62" s="6" t="s">
         <v>230</v>
@@ -5150,7 +5150,7 @@
         <v>55</v>
       </c>
       <c r="U62" s="11" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
@@ -5215,7 +5215,7 @@
         <v>32</v>
       </c>
       <c r="U63" s="11" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
@@ -5280,7 +5280,7 @@
         <v>32</v>
       </c>
       <c r="U64" s="11" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
@@ -5345,7 +5345,7 @@
         <v>32</v>
       </c>
       <c r="U65" s="11" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
@@ -5362,7 +5362,7 @@
         <v>46223.80725450232</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
@@ -5408,7 +5408,7 @@
         <v>32</v>
       </c>
       <c r="U66" s="11" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
@@ -5455,7 +5455,7 @@
         <v>226</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P67" s="9" t="s">
         <v>245</v>
@@ -5473,7 +5473,7 @@
         <v>32</v>
       </c>
       <c r="U67" s="11" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
@@ -6124,7 +6124,7 @@
         <v>32</v>
       </c>
       <c r="U78" s="11" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001533 - GESVIAL.xlsx
+++ b/data/50001533 - GESVIAL.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="948" uniqueCount="283">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="948" uniqueCount="282">
   <si>
     <t xml:space="preserve"> 50001533 - GESVIAL</t>
   </si>
@@ -765,9 +765,6 @@
   </si>
   <si>
     <t>Bodega:,Montaje Alabe</t>
-  </si>
-  <si>
-    <t>Media</t>
   </si>
   <si>
     <t>1213964538772984</t>
@@ -4920,7 +4917,7 @@
         <v>46193.561984872686</v>
       </c>
       <c r="D59" s="8">
-        <v>46227.19815074074</v>
+        <v>46235.186337858795</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>219</v>
@@ -4967,8 +4964,8 @@
       <c r="S59" s="9">
         <v>1</v>
       </c>
-      <c r="T59" s="12" t="s">
-        <v>221</v>
+      <c r="T59" s="11" t="s">
+        <v>55</v>
       </c>
       <c r="U59" s="11" t="s">
         <v>107</v>
@@ -4976,7 +4973,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B60" s="5">
         <v>46118.66235550926</v>
@@ -4988,7 +4985,7 @@
         <v>46208.210473217594</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
@@ -5021,7 +5018,7 @@
         <v>139</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="Q60" s="5">
         <v>46258</v>
@@ -5041,7 +5038,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B61" s="8">
         <v>46118.66236295139</v>
@@ -5053,7 +5050,7 @@
         <v>46204.900153703704</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>25</v>
@@ -5077,7 +5074,7 @@
         <v>26</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="P61" s="9" t="s">
         <v>26</v>
@@ -5090,7 +5087,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B62" s="5">
         <v>46118.66236873843</v>
@@ -5102,7 +5099,7 @@
         <v>46228.2021169213</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
@@ -5129,13 +5126,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="O62" s="6" t="s">
         <v>208</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="Q62" s="5">
         <v>46227</v>
@@ -5155,7 +5152,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B63" s="8">
         <v>46118.662376064814</v>
@@ -5167,7 +5164,7 @@
         <v>46223.807264641204</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>26</v>
@@ -5194,13 +5191,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="O63" s="9" t="s">
+        <v>231</v>
+      </c>
+      <c r="P63" s="9" t="s">
         <v>232</v>
-      </c>
-      <c r="P63" s="9" t="s">
-        <v>233</v>
       </c>
       <c r="Q63" s="8">
         <v>46260</v>
@@ -5220,7 +5217,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B64" s="5">
         <v>46118.662387557866</v>
@@ -5232,7 +5229,7 @@
         <v>46223.80726166666</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
@@ -5259,13 +5256,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q64" s="5">
         <v>46262</v>
@@ -5285,7 +5282,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B65" s="8">
         <v>46118.662398796296</v>
@@ -5297,7 +5294,7 @@
         <v>46223.807257754626</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
@@ -5324,13 +5321,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="P65" s="9" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q65" s="8">
         <v>46266</v>
@@ -5350,7 +5347,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B66" s="5">
         <v>46118.66240984954</v>
@@ -5387,13 +5384,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="O66" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="P66" s="6" t="s">
         <v>241</v>
-      </c>
-      <c r="P66" s="6" t="s">
-        <v>242</v>
       </c>
       <c r="Q66" s="5">
         <v>46267</v>
@@ -5413,7 +5410,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B67" s="8">
         <v>46118.662420127315</v>
@@ -5425,7 +5422,7 @@
         <v>46223.807249398145</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
@@ -5452,13 +5449,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="O67" s="9" t="s">
         <v>170</v>
       </c>
       <c r="P67" s="9" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="Q67" s="8">
         <v>46269</v>
@@ -5478,7 +5475,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B68" s="5">
         <v>46118.66242769676</v>
@@ -5490,7 +5487,7 @@
         <v>46210.64097907407</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>25</v>
@@ -5514,7 +5511,7 @@
         <v>26</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="P68" s="6" t="s">
         <v>26</v>
@@ -5531,7 +5528,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B69" s="8">
         <v>46118.662431770834</v>
@@ -5543,16 +5540,16 @@
         <v>46208.21071721065</v>
       </c>
       <c r="E69" s="9" t="s">
+        <v>249</v>
+      </c>
+      <c r="F69" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G69" s="9" t="s">
         <v>250</v>
       </c>
-      <c r="F69" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G69" s="9" t="s">
+      <c r="H69" s="9" t="s">
         <v>251</v>
-      </c>
-      <c r="H69" s="9" t="s">
-        <v>252</v>
       </c>
       <c r="I69" s="9"/>
       <c r="J69" s="8">
@@ -5568,13 +5565,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="P69" s="9" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Q69" s="8">
         <v>46272</v>
@@ -5594,7 +5591,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B70" s="5">
         <v>46118.662438252315</v>
@@ -5606,7 +5603,7 @@
         <v>46223.80733106482</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
@@ -5631,13 +5628,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="O70" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="P70" s="6" t="s">
         <v>256</v>
-      </c>
-      <c r="P70" s="6" t="s">
-        <v>257</v>
       </c>
       <c r="Q70" s="5">
         <v>46273</v>
@@ -5657,7 +5654,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B71" s="8">
         <v>46118.66245149306</v>
@@ -5669,16 +5666,16 @@
         <v>46208.210718125</v>
       </c>
       <c r="E71" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="F71" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G71" s="9" t="s">
         <v>259</v>
       </c>
-      <c r="F71" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G71" s="9" t="s">
+      <c r="H71" s="9" t="s">
         <v>260</v>
-      </c>
-      <c r="H71" s="9" t="s">
-        <v>261</v>
       </c>
       <c r="I71" s="9"/>
       <c r="J71" s="8">
@@ -5694,13 +5691,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="P71" s="9" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="Q71" s="8">
         <v>46274</v>
@@ -5720,7 +5717,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B72" s="5">
         <v>46118.66245769676</v>
@@ -5732,16 +5729,16 @@
         <v>46210.64281188657</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="H72" s="6" t="s">
         <v>260</v>
-      </c>
-      <c r="H72" s="6" t="s">
-        <v>261</v>
       </c>
       <c r="I72" s="6"/>
       <c r="J72" s="5">
@@ -5757,13 +5754,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="Q72" s="5">
         <v>46275</v>
@@ -5783,7 +5780,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B73" s="8">
         <v>46118.66246467593</v>
@@ -5793,7 +5790,7 @@
         <v>46118.76284858796</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>25</v>
@@ -5817,7 +5814,7 @@
         <v>26</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="P73" s="9" t="s">
         <v>26</v>
@@ -5830,7 +5827,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B74" s="5">
         <v>46118.66246796296</v>
@@ -5840,16 +5837,16 @@
         <v>46210.64097208333</v>
       </c>
       <c r="E74" s="6" t="s">
+        <v>269</v>
+      </c>
+      <c r="F74" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G74" s="6" t="s">
         <v>270</v>
       </c>
-      <c r="F74" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G74" s="6" t="s">
+      <c r="H74" s="6" t="s">
         <v>271</v>
-      </c>
-      <c r="H74" s="6" t="s">
-        <v>272</v>
       </c>
       <c r="I74" s="5">
         <v>46276</v>
@@ -5867,13 +5864,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="Q74" s="5">
         <v>46286</v>
@@ -5893,7 +5890,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B75" s="8">
         <v>46118.66251259259</v>
@@ -5903,16 +5900,16 @@
         <v>46210.64097256944</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="H75" s="9" t="s">
         <v>271</v>
-      </c>
-      <c r="H75" s="9" t="s">
-        <v>272</v>
       </c>
       <c r="I75" s="8">
         <v>46276</v>
@@ -5930,13 +5927,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="Q75" s="8">
         <v>46286</v>
@@ -5956,7 +5953,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B76" s="5">
         <v>46118.662521377315</v>
@@ -5966,7 +5963,7 @@
         <v>46118.76362347222</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>25</v>
@@ -5990,7 +5987,7 @@
         <v>26</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="P76" s="6" t="s">
         <v>26</v>
@@ -6003,7 +6000,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B77" s="8">
         <v>46118.66252565972</v>
@@ -6013,7 +6010,7 @@
         <v>46210.64097050926</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>26</v>
@@ -6040,13 +6037,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="9" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="P77" s="9" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="Q77" s="8">
         <v>46286</v>
@@ -6066,7 +6063,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B78" s="5">
         <v>46118.662532013885</v>
@@ -6076,7 +6073,7 @@
         <v>46118.76825962963</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
@@ -6103,13 +6100,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="Q78" s="5">
         <v>46295</v>

--- a/data/50001533 - GESVIAL.xlsx
+++ b/data/50001533 - GESVIAL.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="948" uniqueCount="282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="912" uniqueCount="274">
   <si>
     <t xml:space="preserve"> 50001533 - GESVIAL</t>
   </si>
@@ -896,7 +896,7 @@
     <t>Despacho</t>
   </si>
   <si>
-    <t>Gestion,Instalacion de componentes ,Costos,Logistica:</t>
+    <t>Gestion,Costos,Logistica:</t>
   </si>
   <si>
     <t>1213964538819755</t>
@@ -924,30 +924,6 @@
   </si>
   <si>
     <t>Costos</t>
-  </si>
-  <si>
-    <t>1213962383736711</t>
-  </si>
-  <si>
-    <t>Puesta en marcha Servicios</t>
-  </si>
-  <si>
-    <t>Instalacion de componentes ,Pruebas de instalacion componentes</t>
-  </si>
-  <si>
-    <t>1213962383736721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Instalacion de componentes </t>
-  </si>
-  <si>
-    <t>Puesta en marcha Servicios,Pruebas de instalacion componentes</t>
-  </si>
-  <si>
-    <t>1213963069243810</t>
-  </si>
-  <si>
-    <t>Pruebas de instalacion componentes</t>
   </si>
 </sst>
 </file>
@@ -1471,7 +1447,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:U78"/>
+  <dimension ref="A1:U75"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10.4" customWidth="1"/>
@@ -5726,7 +5702,7 @@
         <v>46210.64094128472</v>
       </c>
       <c r="D72" s="5">
-        <v>46210.64281188657</v>
+        <v>46240.71876092593</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>263</v>
@@ -5949,179 +5925,6 @@
       </c>
       <c r="U75" s="12" t="s">
         <v>94</v>
-      </c>
-    </row>
-    <row r="76" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A76" s="4" t="s">
-        <v>274</v>
-      </c>
-      <c r="B76" s="5">
-        <v>46118.662521377315</v>
-      </c>
-      <c r="C76" s="6"/>
-      <c r="D76" s="5">
-        <v>46118.76362347222</v>
-      </c>
-      <c r="E76" s="6" t="s">
-        <v>275</v>
-      </c>
-      <c r="F76" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G76" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H76" s="6"/>
-      <c r="I76" s="6"/>
-      <c r="J76" s="6"/>
-      <c r="K76" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L76" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M76" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="N76" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="O76" s="6" t="s">
-        <v>276</v>
-      </c>
-      <c r="P76" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q76" s="6"/>
-      <c r="R76" s="6"/>
-      <c r="S76" s="6"/>
-      <c r="T76" s="6"/>
-      <c r="U76" s="6"/>
-    </row>
-    <row r="77" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A77" s="7" t="s">
-        <v>277</v>
-      </c>
-      <c r="B77" s="8">
-        <v>46118.66252565972</v>
-      </c>
-      <c r="C77" s="9"/>
-      <c r="D77" s="8">
-        <v>46210.64097050926</v>
-      </c>
-      <c r="E77" s="9" t="s">
-        <v>278</v>
-      </c>
-      <c r="F77" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G77" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="H77" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="I77" s="8">
-        <v>46276</v>
-      </c>
-      <c r="J77" s="8">
-        <v>46286</v>
-      </c>
-      <c r="K77" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L77" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M77" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N77" s="9" t="s">
-        <v>275</v>
-      </c>
-      <c r="O77" s="9" t="s">
-        <v>263</v>
-      </c>
-      <c r="P77" s="9" t="s">
-        <v>279</v>
-      </c>
-      <c r="Q77" s="8">
-        <v>46286</v>
-      </c>
-      <c r="R77" s="8">
-        <v>46276</v>
-      </c>
-      <c r="S77" s="9">
-        <v>0</v>
-      </c>
-      <c r="T77" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="U77" s="12" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="78" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A78" s="4" t="s">
-        <v>280</v>
-      </c>
-      <c r="B78" s="5">
-        <v>46118.662532013885</v>
-      </c>
-      <c r="C78" s="6"/>
-      <c r="D78" s="5">
-        <v>46118.76825962963</v>
-      </c>
-      <c r="E78" s="6" t="s">
-        <v>281</v>
-      </c>
-      <c r="F78" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G78" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="H78" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="I78" s="5">
-        <v>46287</v>
-      </c>
-      <c r="J78" s="5">
-        <v>46295</v>
-      </c>
-      <c r="K78" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L78" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M78" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N78" s="6" t="s">
-        <v>275</v>
-      </c>
-      <c r="O78" s="6" t="s">
-        <v>278</v>
-      </c>
-      <c r="P78" s="6" t="s">
-        <v>275</v>
-      </c>
-      <c r="Q78" s="5">
-        <v>46295</v>
-      </c>
-      <c r="R78" s="5">
-        <v>46287</v>
-      </c>
-      <c r="S78" s="6">
-        <v>0</v>
-      </c>
-      <c r="T78" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="U78" s="11" t="s">
-        <v>107</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001533 - GESVIAL.xlsx
+++ b/data/50001533 - GESVIAL.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="912" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="912" uniqueCount="275">
   <si>
     <t xml:space="preserve"> 50001533 - GESVIAL</t>
   </si>
@@ -507,6 +507,9 @@
   </si>
   <si>
     <t>Generación OC motor - OT4285,Fabricación motor  - OT4285,Planos motor proveedor - OT4285</t>
+  </si>
+  <si>
+    <t>Media</t>
   </si>
   <si>
     <t>1213962383670236</t>
@@ -3329,7 +3332,7 @@
         <v>46156.821339988426</v>
       </c>
       <c r="D33" s="8">
-        <v>46169.82398277777</v>
+        <v>46247.17789337963</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>133</v>
@@ -3376,8 +3379,8 @@
       <c r="S33" s="9">
         <v>1</v>
       </c>
-      <c r="T33" s="10" t="s">
-        <v>32</v>
+      <c r="T33" s="12" t="s">
+        <v>135</v>
       </c>
       <c r="U33" s="11" t="s">
         <v>107</v>
@@ -3385,7 +3388,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B34" s="5">
         <v>46118.662190104165</v>
@@ -3397,7 +3400,7 @@
         <v>46208.211555636575</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
@@ -3430,7 +3433,7 @@
         <v>83</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3446,7 +3449,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B35" s="8">
         <v>46118.662195694444</v>
@@ -3458,7 +3461,7 @@
         <v>46208.21164188658</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
@@ -3488,10 +3491,10 @@
         <v>133</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="P35" s="9" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="Q35" s="9"/>
       <c r="R35" s="9"/>
@@ -3507,7 +3510,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B36" s="5">
         <v>46118.66220082176</v>
@@ -3519,7 +3522,7 @@
         <v>46208.211714791665</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
@@ -3549,10 +3552,10 @@
         <v>133</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
@@ -3568,7 +3571,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B37" s="8">
         <v>46118.66220634259</v>
@@ -3580,16 +3583,16 @@
         <v>46208.208834942125</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I37" s="8">
         <v>46154</v>
@@ -3633,7 +3636,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B38" s="5">
         <v>46118.66221234953</v>
@@ -3645,16 +3648,16 @@
         <v>46208.21179649305</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I38" s="5">
         <v>46154</v>
@@ -3672,13 +3675,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="O38" s="6" t="s">
         <v>96</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -3694,7 +3697,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B39" s="8">
         <v>46118.66221657407</v>
@@ -3706,16 +3709,16 @@
         <v>46208.211892453706</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I39" s="8">
         <v>46162</v>
@@ -3733,13 +3736,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P39" s="9" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q39" s="9"/>
       <c r="R39" s="9"/>
@@ -3755,7 +3758,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B40" s="5">
         <v>46118.662220972226</v>
@@ -3767,7 +3770,7 @@
         <v>46204.652183645834</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>25</v>
@@ -3791,7 +3794,7 @@
         <v>26</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="P40" s="6" t="s">
         <v>26</v>
@@ -3804,7 +3807,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B41" s="8">
         <v>46118.66222521991</v>
@@ -3816,16 +3819,16 @@
         <v>46129.57417895833</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I41" s="8">
         <v>46115</v>
@@ -3843,13 +3846,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="O41" s="9" t="s">
         <v>72</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q41" s="8">
         <v>46121</v>
@@ -3869,7 +3872,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B42" s="5">
         <v>46118.66223170139</v>
@@ -3881,16 +3884,16 @@
         <v>46134.80028269676</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I42" s="5">
         <v>46142</v>
@@ -3908,13 +3911,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q42" s="5">
         <v>46148</v>
@@ -3934,7 +3937,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B43" s="8">
         <v>46118.662239375</v>
@@ -3952,10 +3955,10 @@
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I43" s="9"/>
       <c r="J43" s="8">
@@ -3971,13 +3974,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="P43" s="9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q43" s="8">
         <v>46149</v>
@@ -3997,7 +4000,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B44" s="5">
         <v>46118.662245300926</v>
@@ -4009,16 +4012,16 @@
         <v>46208.20879145833</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I44" s="5">
         <v>46268</v>
@@ -4036,13 +4039,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q44" s="5">
         <v>46268</v>
@@ -4062,7 +4065,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B45" s="8">
         <v>46118.66224984954</v>
@@ -4074,7 +4077,7 @@
         <v>46184.68718828703</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>25</v>
@@ -4098,7 +4101,7 @@
         <v>26</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="P45" s="9" t="s">
         <v>26</v>
@@ -4111,7 +4114,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B46" s="5">
         <v>46118.66225350695</v>
@@ -4123,16 +4126,16 @@
         <v>46208.20988328704</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="I46" s="5">
         <v>46171</v>
@@ -4150,13 +4153,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q46" s="5">
         <v>46174</v>
@@ -4176,7 +4179,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B47" s="8">
         <v>46118.66225863426</v>
@@ -4188,16 +4191,16 @@
         <v>46208.20991337963</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I47" s="8">
         <v>46175</v>
@@ -4215,13 +4218,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q47" s="8">
         <v>46176</v>
@@ -4241,7 +4244,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B48" s="5">
         <v>46118.662263819446</v>
@@ -4253,7 +4256,7 @@
         <v>46194.05633912037</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>25</v>
@@ -4277,7 +4280,7 @@
         <v>26</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P48" s="6" t="s">
         <v>26</v>
@@ -4290,7 +4293,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B49" s="8">
         <v>46118.66226751157</v>
@@ -4302,16 +4305,16 @@
         <v>46208.210227986114</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I49" s="8">
         <v>46177</v>
@@ -4329,13 +4332,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q49" s="8">
         <v>46185</v>
@@ -4355,7 +4358,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B50" s="5">
         <v>46118.66227269676</v>
@@ -4367,16 +4370,16 @@
         <v>46208.210261203705</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I50" s="5">
         <v>46188</v>
@@ -4394,13 +4397,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q50" s="5">
         <v>46205</v>
@@ -4420,7 +4423,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B51" s="8">
         <v>46184.687980393515</v>
@@ -4432,16 +4435,16 @@
         <v>46191.68718039352</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I51" s="8">
         <v>46188</v>
@@ -4459,7 +4462,7 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O51" s="9" t="s">
         <v>26</v>
@@ -4475,7 +4478,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B52" s="5">
         <v>46184.688093055556</v>
@@ -4487,16 +4490,16 @@
         <v>46195.70254238426</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I52" s="5">
         <v>46188</v>
@@ -4514,7 +4517,7 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O52" s="6" t="s">
         <v>26</v>
@@ -4530,7 +4533,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B53" s="8">
         <v>46184.68816803241</v>
@@ -4542,16 +4545,16 @@
         <v>46191.6871738426</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H53" s="9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I53" s="8">
         <v>46188</v>
@@ -4569,7 +4572,7 @@
         <v>26</v>
       </c>
       <c r="N53" s="9" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O53" s="9" t="s">
         <v>26</v>
@@ -4585,7 +4588,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B54" s="5">
         <v>46184.68826700232</v>
@@ -4597,16 +4600,16 @@
         <v>46191.687168993056</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I54" s="5">
         <v>46188</v>
@@ -4624,7 +4627,7 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O54" s="6" t="s">
         <v>26</v>
@@ -4640,7 +4643,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B55" s="8">
         <v>46118.66227863426</v>
@@ -4652,16 +4655,16 @@
         <v>46210.19828702546</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I55" s="8">
         <v>46206</v>
@@ -4679,13 +4682,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="P55" s="9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q55" s="8">
         <v>46209</v>
@@ -4705,7 +4708,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B56" s="5">
         <v>46118.66228488426</v>
@@ -4717,7 +4720,7 @@
         <v>46194.05632325231</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>25</v>
@@ -4741,7 +4744,7 @@
         <v>26</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P56" s="6" t="s">
         <v>26</v>
@@ -4754,7 +4757,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B57" s="8">
         <v>46118.66228803241</v>
@@ -4766,16 +4769,16 @@
         <v>46208.21036678241</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="I57" s="8">
         <v>46168</v>
@@ -4793,13 +4796,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="O57" s="9" t="s">
         <v>130</v>
       </c>
       <c r="P57" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q57" s="8">
         <v>46169</v>
@@ -4819,7 +4822,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B58" s="5">
         <v>46118.662293518515</v>
@@ -4837,10 +4840,10 @@
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="I58" s="5">
         <v>46189</v>
@@ -4858,13 +4861,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="O58" s="6" t="s">
         <v>121</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q58" s="5">
         <v>46190</v>
@@ -4884,7 +4887,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B59" s="8">
         <v>46118.662299895834</v>
@@ -4896,16 +4899,16 @@
         <v>46235.186337858795</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="I59" s="8">
         <v>46233</v>
@@ -4923,13 +4926,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="O59" s="9" t="s">
         <v>112</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q59" s="8">
         <v>46234</v>
@@ -4949,7 +4952,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B60" s="5">
         <v>46118.66235550926</v>
@@ -4961,16 +4964,16 @@
         <v>46208.210473217594</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="I60" s="5">
         <v>46255</v>
@@ -4988,13 +4991,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q60" s="5">
         <v>46258</v>
@@ -5014,7 +5017,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B61" s="8">
         <v>46118.66236295139</v>
@@ -5026,7 +5029,7 @@
         <v>46204.900153703704</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>25</v>
@@ -5050,7 +5053,7 @@
         <v>26</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="P61" s="9" t="s">
         <v>26</v>
@@ -5063,7 +5066,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B62" s="5">
         <v>46118.66236873843</v>
@@ -5075,7 +5078,7 @@
         <v>46228.2021169213</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
@@ -5102,13 +5105,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q62" s="5">
         <v>46227</v>
@@ -5128,7 +5131,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B63" s="8">
         <v>46118.662376064814</v>
@@ -5140,7 +5143,7 @@
         <v>46223.807264641204</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>26</v>
@@ -5167,13 +5170,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="P63" s="9" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q63" s="8">
         <v>46260</v>
@@ -5193,7 +5196,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B64" s="5">
         <v>46118.662387557866</v>
@@ -5205,7 +5208,7 @@
         <v>46223.80726166666</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
@@ -5232,13 +5235,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q64" s="5">
         <v>46262</v>
@@ -5258,7 +5261,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B65" s="8">
         <v>46118.662398796296</v>
@@ -5270,7 +5273,7 @@
         <v>46223.807257754626</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
@@ -5297,13 +5300,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="P65" s="9" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q65" s="8">
         <v>46266</v>
@@ -5323,7 +5326,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B66" s="5">
         <v>46118.66240984954</v>
@@ -5335,7 +5338,7 @@
         <v>46223.80725450232</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
@@ -5360,13 +5363,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q66" s="5">
         <v>46267</v>
@@ -5386,7 +5389,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B67" s="8">
         <v>46118.662420127315</v>
@@ -5398,7 +5401,7 @@
         <v>46223.807249398145</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
@@ -5425,13 +5428,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P67" s="9" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q67" s="8">
         <v>46269</v>
@@ -5451,7 +5454,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B68" s="5">
         <v>46118.66242769676</v>
@@ -5463,7 +5466,7 @@
         <v>46210.64097907407</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>25</v>
@@ -5487,7 +5490,7 @@
         <v>26</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P68" s="6" t="s">
         <v>26</v>
@@ -5504,7 +5507,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B69" s="8">
         <v>46118.662431770834</v>
@@ -5516,16 +5519,16 @@
         <v>46208.21071721065</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="9" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H69" s="9" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I69" s="9"/>
       <c r="J69" s="8">
@@ -5541,13 +5544,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="P69" s="9" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q69" s="8">
         <v>46272</v>
@@ -5567,7 +5570,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B70" s="5">
         <v>46118.662438252315</v>
@@ -5579,7 +5582,7 @@
         <v>46223.80733106482</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
@@ -5604,13 +5607,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q70" s="5">
         <v>46273</v>
@@ -5630,7 +5633,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B71" s="8">
         <v>46118.66245149306</v>
@@ -5642,16 +5645,16 @@
         <v>46208.210718125</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="9" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H71" s="9" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="I71" s="9"/>
       <c r="J71" s="8">
@@ -5667,13 +5670,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="P71" s="9" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q71" s="8">
         <v>46274</v>
@@ -5693,7 +5696,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B72" s="5">
         <v>46118.66245769676</v>
@@ -5705,16 +5708,16 @@
         <v>46240.71876092593</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="I72" s="6"/>
       <c r="J72" s="5">
@@ -5730,13 +5733,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q72" s="5">
         <v>46275</v>
@@ -5756,7 +5759,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B73" s="8">
         <v>46118.66246467593</v>
@@ -5766,7 +5769,7 @@
         <v>46118.76284858796</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>25</v>
@@ -5790,7 +5793,7 @@
         <v>26</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="P73" s="9" t="s">
         <v>26</v>
@@ -5803,7 +5806,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B74" s="5">
         <v>46118.66246796296</v>
@@ -5813,16 +5816,16 @@
         <v>46210.64097208333</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="I74" s="5">
         <v>46276</v>
@@ -5840,13 +5843,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q74" s="5">
         <v>46286</v>
@@ -5866,7 +5869,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B75" s="8">
         <v>46118.66251259259</v>
@@ -5876,16 +5879,16 @@
         <v>46210.64097256944</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="9" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H75" s="9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="I75" s="8">
         <v>46276</v>
@@ -5903,13 +5906,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q75" s="8">
         <v>46286</v>

--- a/data/50001533 - GESVIAL.xlsx
+++ b/data/50001533 - GESVIAL.xlsx
@@ -4961,7 +4961,7 @@
         <v>46193.56199724537</v>
       </c>
       <c r="D60" s="5">
-        <v>46208.210473217594</v>
+        <v>46251.18919104167</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>223</v>
@@ -5008,8 +5008,8 @@
       <c r="S60" s="6">
         <v>1</v>
       </c>
-      <c r="T60" s="10" t="s">
-        <v>32</v>
+      <c r="T60" s="12" t="s">
+        <v>135</v>
       </c>
       <c r="U60" s="11" t="s">
         <v>107</v>

--- a/data/50001533 - GESVIAL.xlsx
+++ b/data/50001533 - GESVIAL.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="912" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="913" uniqueCount="275">
   <si>
     <t xml:space="preserve"> 50001533 - GESVIAL</t>
   </si>
@@ -5764,9 +5764,11 @@
       <c r="B73" s="8">
         <v>46118.66246467593</v>
       </c>
-      <c r="C73" s="9"/>
+      <c r="C73" s="8">
+        <v>46251.952283819446</v>
+      </c>
       <c r="D73" s="8">
-        <v>46118.76284858796</v>
+        <v>46251.952298206015</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>267</v>
@@ -5800,9 +5802,13 @@
       </c>
       <c r="Q73" s="9"/>
       <c r="R73" s="9"/>
-      <c r="S73" s="9"/>
+      <c r="S73" s="9">
+        <v>1</v>
+      </c>
       <c r="T73" s="9"/>
-      <c r="U73" s="9"/>
+      <c r="U73" s="10" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
@@ -5811,9 +5817,11 @@
       <c r="B74" s="5">
         <v>46118.66246796296</v>
       </c>
-      <c r="C74" s="6"/>
+      <c r="C74" s="5">
+        <v>46251.95225530093</v>
+      </c>
       <c r="D74" s="5">
-        <v>46210.64097208333</v>
+        <v>46251.95227454861</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>270</v>
@@ -5858,13 +5866,13 @@
         <v>46276</v>
       </c>
       <c r="S74" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T74" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="U74" s="12" t="s">
-        <v>94</v>
+      <c r="U74" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
@@ -5874,9 +5882,11 @@
       <c r="B75" s="8">
         <v>46118.66251259259</v>
       </c>
-      <c r="C75" s="9"/>
+      <c r="C75" s="8">
+        <v>46251.952265555556</v>
+      </c>
       <c r="D75" s="8">
-        <v>46210.64097256944</v>
+        <v>46251.95228457176</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>274</v>
@@ -5921,13 +5931,13 @@
         <v>46276</v>
       </c>
       <c r="S75" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T75" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="U75" s="12" t="s">
-        <v>94</v>
+      <c r="U75" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001533 - GESVIAL.xlsx
+++ b/data/50001533 - GESVIAL.xlsx
@@ -5140,7 +5140,7 @@
         <v>46193.6126587037</v>
       </c>
       <c r="D63" s="8">
-        <v>46223.807264641204</v>
+        <v>46253.20344491898</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>224</v>
@@ -5187,8 +5187,8 @@
       <c r="S63" s="9">
         <v>1</v>
       </c>
-      <c r="T63" s="10" t="s">
-        <v>32</v>
+      <c r="T63" s="12" t="s">
+        <v>135</v>
       </c>
       <c r="U63" s="11" t="s">
         <v>107</v>

--- a/data/50001533 - GESVIAL.xlsx
+++ b/data/50001533 - GESVIAL.xlsx
@@ -509,274 +509,274 @@
     <t>Generación OC motor - OT4285,Fabricación motor  - OT4285,Planos motor proveedor - OT4285</t>
   </si>
   <si>
+    <t>1213962383670236</t>
+  </si>
+  <si>
+    <t>Generación OC motor - OT4285</t>
+  </si>
+  <si>
+    <t>Motor - OT4285 ,Fabricación motor  - OT4285,Planos motor proveedor - OT4285</t>
+  </si>
+  <si>
+    <t>1213962383670254</t>
+  </si>
+  <si>
+    <t>Fabricación motor  - OT4285</t>
+  </si>
+  <si>
+    <t>Motor - OT4285 ,Recepcion motor</t>
+  </si>
+  <si>
+    <t>1213962383670374</t>
+  </si>
+  <si>
+    <t>Planos motor proveedor - OT4285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Planos definitivo,Motor - OT4285 </t>
+  </si>
+  <si>
+    <t>1213962383670392</t>
+  </si>
+  <si>
+    <t>Materiales a codigo // compras locales aprovisionamientomiento: - OT4285</t>
+  </si>
+  <si>
+    <t>Yerlia Ayleen Castillo Diaz</t>
+  </si>
+  <si>
+    <t>yerlia.castillo@zitron.com</t>
+  </si>
+  <si>
+    <t>1213962383671823</t>
+  </si>
+  <si>
+    <t>Generación OC materiales - OT4285</t>
+  </si>
+  <si>
+    <t>Fabricacion a codigo y compras locales - OT4285</t>
+  </si>
+  <si>
+    <t>1213962383671836</t>
+  </si>
+  <si>
+    <t>Recepcion materiales a codigos // compras locales aprovisionamiento</t>
+  </si>
+  <si>
+    <t>1213963540650358</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseño:</t>
+  </si>
+  <si>
+    <t>Planos definitivo,Check planos ,Check Pruebas fat,Planos Preliminar</t>
+  </si>
+  <si>
+    <t>1213963540650370</t>
+  </si>
+  <si>
+    <t>Planos Preliminar</t>
+  </si>
+  <si>
+    <t>Gonzalo Javier Dávila Bade</t>
+  </si>
+  <si>
+    <t>gonzalo.davila@zitron.com</t>
+  </si>
+  <si>
+    <t>Planos definitivo,Ingenieria y diseño:</t>
+  </si>
+  <si>
+    <t>1213955269721772</t>
+  </si>
+  <si>
+    <t>Planos definitivo</t>
+  </si>
+  <si>
+    <t>Hernan Roberto Gutierrez Barrientos</t>
+  </si>
+  <si>
+    <t>hgutierrez@zitron.com</t>
+  </si>
+  <si>
+    <t>Ingenieria Basica Motor,Planos motor proveedor - OT4285,Planos Preliminar</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseño:,Check planos ,Montaje Rodete</t>
+  </si>
+  <si>
+    <t>1213962383672603</t>
+  </si>
+  <si>
+    <t>Fabricacion,Control de calidad ,Montaje Alabe,Ingenieria y diseño:,propuesta compras a codigo // aprovisionamiento,Montaje Rodete,Montaje motor</t>
+  </si>
+  <si>
+    <t>1213962383672623</t>
+  </si>
+  <si>
+    <t>Check Pruebas fat</t>
+  </si>
+  <si>
+    <t>Francisca González Cornejo</t>
+  </si>
+  <si>
+    <t>francisca.gonzalez@zitron.com</t>
+  </si>
+  <si>
+    <t>Pruebas FAT</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseño:,RE-PINTADO</t>
+  </si>
+  <si>
+    <t>1213962383676938</t>
+  </si>
+  <si>
+    <t>Bodega:</t>
+  </si>
+  <si>
+    <t>Recepcion materiales a codigos // compras locales aprovisionamiento,Control de calidad compras materiales a codigo // compras locale aprovisionamiento</t>
+  </si>
+  <si>
+    <t>1213962383676950</t>
+  </si>
+  <si>
+    <t>Victor Muñoz</t>
+  </si>
+  <si>
+    <t>victor.munoz@zitron.com</t>
+  </si>
+  <si>
+    <t>Bodega:,Control de calidad compras materiales a codigo // compras locale aprovisionamiento</t>
+  </si>
+  <si>
+    <t>1213962383680132</t>
+  </si>
+  <si>
+    <t>Control de calidad compras materiales a codigo // compras locale aprovisionamiento</t>
+  </si>
+  <si>
+    <t>Nicolás López</t>
+  </si>
+  <si>
+    <t>nicolas.lopez@zitron.com</t>
+  </si>
+  <si>
+    <t>Generacion oc ,Bodega:</t>
+  </si>
+  <si>
+    <t>1213962383680152</t>
+  </si>
+  <si>
+    <t>Fabricacion externa :</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generacion oc ,Fabricacion,Control de calidad </t>
+  </si>
+  <si>
+    <t>1213955269732491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generacion oc </t>
+  </si>
+  <si>
+    <t>Rosemary Singh</t>
+  </si>
+  <si>
+    <t>rosemary.singh@zitron.com</t>
+  </si>
+  <si>
+    <t>Fabricacion externa :,Fabricacion</t>
+  </si>
+  <si>
+    <t>1213955269732511</t>
+  </si>
+  <si>
+    <t>Fabricacion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generacion oc ,Check planos </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabricacion externa :,Control de calidad </t>
+  </si>
+  <si>
+    <t>1215632916059321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carcasa </t>
+  </si>
+  <si>
+    <t>1215632916059322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Silenciador </t>
+  </si>
+  <si>
+    <t>1215632916059323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pieza de adaptacion </t>
+  </si>
+  <si>
+    <t>1215632916059324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rejilla </t>
+  </si>
+  <si>
+    <t>1213955269733641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabricacion,Check planos </t>
+  </si>
+  <si>
+    <t>Fabricacion externa :,Revestimiento</t>
+  </si>
+  <si>
+    <t>1213955269734786</t>
+  </si>
+  <si>
+    <t>Recepcion Alabe,Recepcion Rodete,Recepcion Tableros y componentes electricos</t>
+  </si>
+  <si>
+    <t>1213955269734796</t>
+  </si>
+  <si>
+    <t>Recepcion Rodete</t>
+  </si>
+  <si>
+    <t>Montaje Rodete,Bodega:</t>
+  </si>
+  <si>
+    <t>1213964538786219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bodega:,Revisión tableros pruebas y componentes eléctricos </t>
+  </si>
+  <si>
+    <t>1213955269739200</t>
+  </si>
+  <si>
+    <t>Recepcion Alabe</t>
+  </si>
+  <si>
+    <t>Bodega:,Montaje Alabe</t>
+  </si>
+  <si>
+    <t>1213964538772984</t>
+  </si>
+  <si>
+    <t>Recepcion motor</t>
+  </si>
+  <si>
+    <t>Montaje motor</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1213962383670236</t>
-  </si>
-  <si>
-    <t>Generación OC motor - OT4285</t>
-  </si>
-  <si>
-    <t>Motor - OT4285 ,Fabricación motor  - OT4285,Planos motor proveedor - OT4285</t>
-  </si>
-  <si>
-    <t>1213962383670254</t>
-  </si>
-  <si>
-    <t>Fabricación motor  - OT4285</t>
-  </si>
-  <si>
-    <t>Motor - OT4285 ,Recepcion motor</t>
-  </si>
-  <si>
-    <t>1213962383670374</t>
-  </si>
-  <si>
-    <t>Planos motor proveedor - OT4285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Planos definitivo,Motor - OT4285 </t>
-  </si>
-  <si>
-    <t>1213962383670392</t>
-  </si>
-  <si>
-    <t>Materiales a codigo // compras locales aprovisionamientomiento: - OT4285</t>
-  </si>
-  <si>
-    <t>Yerlia Ayleen Castillo Diaz</t>
-  </si>
-  <si>
-    <t>yerlia.castillo@zitron.com</t>
-  </si>
-  <si>
-    <t>1213962383671823</t>
-  </si>
-  <si>
-    <t>Generación OC materiales - OT4285</t>
-  </si>
-  <si>
-    <t>Fabricacion a codigo y compras locales - OT4285</t>
-  </si>
-  <si>
-    <t>1213962383671836</t>
-  </si>
-  <si>
-    <t>Recepcion materiales a codigos // compras locales aprovisionamiento</t>
-  </si>
-  <si>
-    <t>1213963540650358</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseño:</t>
-  </si>
-  <si>
-    <t>Planos definitivo,Check planos ,Check Pruebas fat,Planos Preliminar</t>
-  </si>
-  <si>
-    <t>1213963540650370</t>
-  </si>
-  <si>
-    <t>Planos Preliminar</t>
-  </si>
-  <si>
-    <t>Gonzalo Javier Dávila Bade</t>
-  </si>
-  <si>
-    <t>gonzalo.davila@zitron.com</t>
-  </si>
-  <si>
-    <t>Planos definitivo,Ingenieria y diseño:</t>
-  </si>
-  <si>
-    <t>1213955269721772</t>
-  </si>
-  <si>
-    <t>Planos definitivo</t>
-  </si>
-  <si>
-    <t>Hernan Roberto Gutierrez Barrientos</t>
-  </si>
-  <si>
-    <t>hgutierrez@zitron.com</t>
-  </si>
-  <si>
-    <t>Ingenieria Basica Motor,Planos motor proveedor - OT4285,Planos Preliminar</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseño:,Check planos ,Montaje Rodete</t>
-  </si>
-  <si>
-    <t>1213962383672603</t>
-  </si>
-  <si>
-    <t>Fabricacion,Control de calidad ,Montaje Alabe,Ingenieria y diseño:,propuesta compras a codigo // aprovisionamiento,Montaje Rodete,Montaje motor</t>
-  </si>
-  <si>
-    <t>1213962383672623</t>
-  </si>
-  <si>
-    <t>Check Pruebas fat</t>
-  </si>
-  <si>
-    <t>Francisca González Cornejo</t>
-  </si>
-  <si>
-    <t>francisca.gonzalez@zitron.com</t>
-  </si>
-  <si>
-    <t>Pruebas FAT</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseño:,RE-PINTADO</t>
-  </si>
-  <si>
-    <t>1213962383676938</t>
-  </si>
-  <si>
-    <t>Bodega:</t>
-  </si>
-  <si>
-    <t>Recepcion materiales a codigos // compras locales aprovisionamiento,Control de calidad compras materiales a codigo // compras locale aprovisionamiento</t>
-  </si>
-  <si>
-    <t>1213962383676950</t>
-  </si>
-  <si>
-    <t>Victor Muñoz</t>
-  </si>
-  <si>
-    <t>victor.munoz@zitron.com</t>
-  </si>
-  <si>
-    <t>Bodega:,Control de calidad compras materiales a codigo // compras locale aprovisionamiento</t>
-  </si>
-  <si>
-    <t>1213962383680132</t>
-  </si>
-  <si>
-    <t>Control de calidad compras materiales a codigo // compras locale aprovisionamiento</t>
-  </si>
-  <si>
-    <t>Nicolás López</t>
-  </si>
-  <si>
-    <t>nicolas.lopez@zitron.com</t>
-  </si>
-  <si>
-    <t>Generacion oc ,Bodega:</t>
-  </si>
-  <si>
-    <t>1213962383680152</t>
-  </si>
-  <si>
-    <t>Fabricacion externa :</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generacion oc ,Fabricacion,Control de calidad </t>
-  </si>
-  <si>
-    <t>1213955269732491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generacion oc </t>
-  </si>
-  <si>
-    <t>Rosemary Singh</t>
-  </si>
-  <si>
-    <t>rosemary.singh@zitron.com</t>
-  </si>
-  <si>
-    <t>Fabricacion externa :,Fabricacion</t>
-  </si>
-  <si>
-    <t>1213955269732511</t>
-  </si>
-  <si>
-    <t>Fabricacion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generacion oc ,Check planos </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fabricacion externa :,Control de calidad </t>
-  </si>
-  <si>
-    <t>1215632916059321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Carcasa </t>
-  </si>
-  <si>
-    <t>1215632916059322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Silenciador </t>
-  </si>
-  <si>
-    <t>1215632916059323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pieza de adaptacion </t>
-  </si>
-  <si>
-    <t>1215632916059324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rejilla </t>
-  </si>
-  <si>
-    <t>1213955269733641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fabricacion,Check planos </t>
-  </si>
-  <si>
-    <t>Fabricacion externa :,Revestimiento</t>
-  </si>
-  <si>
-    <t>1213955269734786</t>
-  </si>
-  <si>
-    <t>Recepcion Alabe,Recepcion Rodete,Recepcion Tableros y componentes electricos</t>
-  </si>
-  <si>
-    <t>1213955269734796</t>
-  </si>
-  <si>
-    <t>Recepcion Rodete</t>
-  </si>
-  <si>
-    <t>Montaje Rodete,Bodega:</t>
-  </si>
-  <si>
-    <t>1213964538786219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bodega:,Revisión tableros pruebas y componentes eléctricos </t>
-  </si>
-  <si>
-    <t>1213955269739200</t>
-  </si>
-  <si>
-    <t>Recepcion Alabe</t>
-  </si>
-  <si>
-    <t>Bodega:,Montaje Alabe</t>
-  </si>
-  <si>
-    <t>1213964538772984</t>
-  </si>
-  <si>
-    <t>Recepcion motor</t>
-  </si>
-  <si>
-    <t>Montaje motor</t>
   </si>
   <si>
     <t>1213964538772999</t>
@@ -3332,7 +3332,7 @@
         <v>46156.821339988426</v>
       </c>
       <c r="D33" s="8">
-        <v>46247.17789337963</v>
+        <v>46255.2038697338</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>133</v>
@@ -3379,8 +3379,8 @@
       <c r="S33" s="9">
         <v>1</v>
       </c>
-      <c r="T33" s="12" t="s">
-        <v>135</v>
+      <c r="T33" s="11" t="s">
+        <v>55</v>
       </c>
       <c r="U33" s="11" t="s">
         <v>107</v>
@@ -3388,7 +3388,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B34" s="5">
         <v>46118.662190104165</v>
@@ -3400,7 +3400,7 @@
         <v>46208.211555636575</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
@@ -3433,7 +3433,7 @@
         <v>83</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3449,7 +3449,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B35" s="8">
         <v>46118.662195694444</v>
@@ -3461,7 +3461,7 @@
         <v>46208.21164188658</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
@@ -3491,10 +3491,10 @@
         <v>133</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="P35" s="9" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="Q35" s="9"/>
       <c r="R35" s="9"/>
@@ -3510,7 +3510,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B36" s="5">
         <v>46118.66220082176</v>
@@ -3522,7 +3522,7 @@
         <v>46208.211714791665</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
@@ -3552,10 +3552,10 @@
         <v>133</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
@@ -3571,7 +3571,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B37" s="8">
         <v>46118.66220634259</v>
@@ -3583,16 +3583,16 @@
         <v>46208.208834942125</v>
       </c>
       <c r="E37" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="F37" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G37" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="F37" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G37" s="9" t="s">
+      <c r="H37" s="9" t="s">
         <v>147</v>
-      </c>
-      <c r="H37" s="9" t="s">
-        <v>148</v>
       </c>
       <c r="I37" s="8">
         <v>46154</v>
@@ -3636,7 +3636,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B38" s="5">
         <v>46118.66221234953</v>
@@ -3648,16 +3648,16 @@
         <v>46208.21179649305</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="H38" s="6" t="s">
         <v>147</v>
-      </c>
-      <c r="H38" s="6" t="s">
-        <v>148</v>
       </c>
       <c r="I38" s="5">
         <v>46154</v>
@@ -3675,13 +3675,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="O38" s="6" t="s">
         <v>96</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -3697,7 +3697,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B39" s="8">
         <v>46118.66221657407</v>
@@ -3709,16 +3709,16 @@
         <v>46208.211892453706</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="H39" s="9" t="s">
         <v>147</v>
-      </c>
-      <c r="H39" s="9" t="s">
-        <v>148</v>
       </c>
       <c r="I39" s="8">
         <v>46162</v>
@@ -3736,13 +3736,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P39" s="9" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="Q39" s="9"/>
       <c r="R39" s="9"/>
@@ -3758,7 +3758,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B40" s="5">
         <v>46118.662220972226</v>
@@ -3770,7 +3770,7 @@
         <v>46204.652183645834</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>25</v>
@@ -3794,7 +3794,7 @@
         <v>26</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="P40" s="6" t="s">
         <v>26</v>
@@ -3807,7 +3807,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B41" s="8">
         <v>46118.66222521991</v>
@@ -3819,16 +3819,16 @@
         <v>46129.57417895833</v>
       </c>
       <c r="E41" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="F41" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G41" s="9" t="s">
         <v>158</v>
       </c>
-      <c r="F41" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G41" s="9" t="s">
+      <c r="H41" s="9" t="s">
         <v>159</v>
-      </c>
-      <c r="H41" s="9" t="s">
-        <v>160</v>
       </c>
       <c r="I41" s="8">
         <v>46115</v>
@@ -3846,13 +3846,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="O41" s="9" t="s">
         <v>72</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="Q41" s="8">
         <v>46121</v>
@@ -3872,7 +3872,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B42" s="5">
         <v>46118.66223170139</v>
@@ -3884,16 +3884,16 @@
         <v>46134.80028269676</v>
       </c>
       <c r="E42" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="F42" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G42" s="6" t="s">
         <v>163</v>
       </c>
-      <c r="F42" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G42" s="6" t="s">
+      <c r="H42" s="6" t="s">
         <v>164</v>
-      </c>
-      <c r="H42" s="6" t="s">
-        <v>165</v>
       </c>
       <c r="I42" s="5">
         <v>46142</v>
@@ -3911,13 +3911,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="O42" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="P42" s="6" t="s">
         <v>166</v>
-      </c>
-      <c r="P42" s="6" t="s">
-        <v>167</v>
       </c>
       <c r="Q42" s="5">
         <v>46148</v>
@@ -3937,7 +3937,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B43" s="8">
         <v>46118.662239375</v>
@@ -3955,10 +3955,10 @@
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="H43" s="9" t="s">
         <v>164</v>
-      </c>
-      <c r="H43" s="9" t="s">
-        <v>165</v>
       </c>
       <c r="I43" s="9"/>
       <c r="J43" s="8">
@@ -3974,13 +3974,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="P43" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="Q43" s="8">
         <v>46149</v>
@@ -4000,7 +4000,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B44" s="5">
         <v>46118.662245300926</v>
@@ -4012,16 +4012,16 @@
         <v>46208.20879145833</v>
       </c>
       <c r="E44" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="F44" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G44" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="F44" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G44" s="6" t="s">
+      <c r="H44" s="6" t="s">
         <v>172</v>
-      </c>
-      <c r="H44" s="6" t="s">
-        <v>173</v>
       </c>
       <c r="I44" s="5">
         <v>46268</v>
@@ -4039,13 +4039,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="O44" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="P44" s="6" t="s">
         <v>174</v>
-      </c>
-      <c r="P44" s="6" t="s">
-        <v>175</v>
       </c>
       <c r="Q44" s="5">
         <v>46268</v>
@@ -4065,7 +4065,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B45" s="8">
         <v>46118.66224984954</v>
@@ -4077,7 +4077,7 @@
         <v>46184.68718828703</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>25</v>
@@ -4101,7 +4101,7 @@
         <v>26</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="P45" s="9" t="s">
         <v>26</v>
@@ -4114,7 +4114,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B46" s="5">
         <v>46118.66225350695</v>
@@ -4126,16 +4126,16 @@
         <v>46208.20988328704</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="H46" s="6" t="s">
         <v>180</v>
-      </c>
-      <c r="H46" s="6" t="s">
-        <v>181</v>
       </c>
       <c r="I46" s="5">
         <v>46171</v>
@@ -4153,13 +4153,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q46" s="5">
         <v>46174</v>
@@ -4179,7 +4179,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B47" s="8">
         <v>46118.66225863426</v>
@@ -4191,16 +4191,16 @@
         <v>46208.20991337963</v>
       </c>
       <c r="E47" s="9" t="s">
+        <v>183</v>
+      </c>
+      <c r="F47" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G47" s="9" t="s">
         <v>184</v>
       </c>
-      <c r="F47" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G47" s="9" t="s">
+      <c r="H47" s="9" t="s">
         <v>185</v>
-      </c>
-      <c r="H47" s="9" t="s">
-        <v>186</v>
       </c>
       <c r="I47" s="8">
         <v>46175</v>
@@ -4218,13 +4218,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="Q47" s="8">
         <v>46176</v>
@@ -4244,7 +4244,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B48" s="5">
         <v>46118.662263819446</v>
@@ -4256,7 +4256,7 @@
         <v>46194.05633912037</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>25</v>
@@ -4280,7 +4280,7 @@
         <v>26</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P48" s="6" t="s">
         <v>26</v>
@@ -4293,7 +4293,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B49" s="8">
         <v>46118.66226751157</v>
@@ -4305,16 +4305,16 @@
         <v>46208.210227986114</v>
       </c>
       <c r="E49" s="9" t="s">
+        <v>191</v>
+      </c>
+      <c r="F49" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G49" s="9" t="s">
         <v>192</v>
       </c>
-      <c r="F49" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G49" s="9" t="s">
+      <c r="H49" s="9" t="s">
         <v>193</v>
-      </c>
-      <c r="H49" s="9" t="s">
-        <v>194</v>
       </c>
       <c r="I49" s="8">
         <v>46177</v>
@@ -4332,13 +4332,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="Q49" s="8">
         <v>46185</v>
@@ -4358,7 +4358,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B50" s="5">
         <v>46118.66227269676</v>
@@ -4370,16 +4370,16 @@
         <v>46208.210261203705</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="H50" s="6" t="s">
         <v>193</v>
-      </c>
-      <c r="H50" s="6" t="s">
-        <v>194</v>
       </c>
       <c r="I50" s="5">
         <v>46188</v>
@@ -4397,13 +4397,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="O50" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="P50" s="6" t="s">
         <v>198</v>
-      </c>
-      <c r="P50" s="6" t="s">
-        <v>199</v>
       </c>
       <c r="Q50" s="5">
         <v>46205</v>
@@ -4423,7 +4423,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B51" s="8">
         <v>46184.687980393515</v>
@@ -4435,16 +4435,16 @@
         <v>46191.68718039352</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="H51" s="9" t="s">
         <v>193</v>
-      </c>
-      <c r="H51" s="9" t="s">
-        <v>194</v>
       </c>
       <c r="I51" s="8">
         <v>46188</v>
@@ -4462,7 +4462,7 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="O51" s="9" t="s">
         <v>26</v>
@@ -4478,7 +4478,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B52" s="5">
         <v>46184.688093055556</v>
@@ -4490,16 +4490,16 @@
         <v>46195.70254238426</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="H52" s="6" t="s">
         <v>193</v>
-      </c>
-      <c r="H52" s="6" t="s">
-        <v>194</v>
       </c>
       <c r="I52" s="5">
         <v>46188</v>
@@ -4517,7 +4517,7 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="O52" s="6" t="s">
         <v>26</v>
@@ -4533,7 +4533,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B53" s="8">
         <v>46184.68816803241</v>
@@ -4545,16 +4545,16 @@
         <v>46191.6871738426</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="H53" s="9" t="s">
         <v>193</v>
-      </c>
-      <c r="H53" s="9" t="s">
-        <v>194</v>
       </c>
       <c r="I53" s="8">
         <v>46188</v>
@@ -4572,7 +4572,7 @@
         <v>26</v>
       </c>
       <c r="N53" s="9" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="O53" s="9" t="s">
         <v>26</v>
@@ -4588,7 +4588,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B54" s="5">
         <v>46184.68826700232</v>
@@ -4600,16 +4600,16 @@
         <v>46191.687168993056</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="H54" s="6" t="s">
         <v>193</v>
-      </c>
-      <c r="H54" s="6" t="s">
-        <v>194</v>
       </c>
       <c r="I54" s="5">
         <v>46188</v>
@@ -4627,7 +4627,7 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="O54" s="6" t="s">
         <v>26</v>
@@ -4643,7 +4643,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B55" s="8">
         <v>46118.66227863426</v>
@@ -4655,16 +4655,16 @@
         <v>46210.19828702546</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="H55" s="9" t="s">
         <v>185</v>
-      </c>
-      <c r="H55" s="9" t="s">
-        <v>186</v>
       </c>
       <c r="I55" s="8">
         <v>46206</v>
@@ -4682,13 +4682,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="O55" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="P55" s="9" t="s">
         <v>210</v>
-      </c>
-      <c r="P55" s="9" t="s">
-        <v>211</v>
       </c>
       <c r="Q55" s="8">
         <v>46209</v>
@@ -4708,7 +4708,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B56" s="5">
         <v>46118.66228488426</v>
@@ -4720,7 +4720,7 @@
         <v>46194.05632325231</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>25</v>
@@ -4744,7 +4744,7 @@
         <v>26</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P56" s="6" t="s">
         <v>26</v>
@@ -4757,7 +4757,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B57" s="8">
         <v>46118.66228803241</v>
@@ -4769,16 +4769,16 @@
         <v>46208.21036678241</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="H57" s="9" t="s">
         <v>180</v>
-      </c>
-      <c r="H57" s="9" t="s">
-        <v>181</v>
       </c>
       <c r="I57" s="8">
         <v>46168</v>
@@ -4796,13 +4796,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="O57" s="9" t="s">
         <v>130</v>
       </c>
       <c r="P57" s="9" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="Q57" s="8">
         <v>46169</v>
@@ -4822,7 +4822,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B58" s="5">
         <v>46118.662293518515</v>
@@ -4840,10 +4840,10 @@
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="H58" s="6" t="s">
         <v>180</v>
-      </c>
-      <c r="H58" s="6" t="s">
-        <v>181</v>
       </c>
       <c r="I58" s="5">
         <v>46189</v>
@@ -4861,13 +4861,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="O58" s="6" t="s">
         <v>121</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="Q58" s="5">
         <v>46190</v>
@@ -4887,7 +4887,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B59" s="8">
         <v>46118.662299895834</v>
@@ -4899,16 +4899,16 @@
         <v>46235.186337858795</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="H59" s="9" t="s">
         <v>180</v>
-      </c>
-      <c r="H59" s="9" t="s">
-        <v>181</v>
       </c>
       <c r="I59" s="8">
         <v>46233</v>
@@ -4926,13 +4926,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="O59" s="9" t="s">
         <v>112</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="Q59" s="8">
         <v>46234</v>
@@ -4952,7 +4952,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B60" s="5">
         <v>46118.66235550926</v>
@@ -4964,16 +4964,16 @@
         <v>46251.18919104167</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="H60" s="6" t="s">
         <v>180</v>
-      </c>
-      <c r="H60" s="6" t="s">
-        <v>181</v>
       </c>
       <c r="I60" s="5">
         <v>46255</v>
@@ -4991,13 +4991,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="Q60" s="5">
         <v>46258</v>
@@ -5009,7 +5009,7 @@
         <v>1</v>
       </c>
       <c r="T60" s="12" t="s">
-        <v>135</v>
+        <v>224</v>
       </c>
       <c r="U60" s="11" t="s">
         <v>107</v>
@@ -5108,7 +5108,7 @@
         <v>226</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="P62" s="6" t="s">
         <v>230</v>
@@ -5143,7 +5143,7 @@
         <v>46253.20344491898</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>26</v>
@@ -5188,7 +5188,7 @@
         <v>1</v>
       </c>
       <c r="T63" s="12" t="s">
-        <v>135</v>
+        <v>224</v>
       </c>
       <c r="U63" s="11" t="s">
         <v>107</v>
@@ -5205,7 +5205,7 @@
         <v>46193.61267944444</v>
       </c>
       <c r="D64" s="5">
-        <v>46223.80726166666</v>
+        <v>46255.187699664355</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>235</v>
@@ -5252,8 +5252,8 @@
       <c r="S64" s="6">
         <v>1</v>
       </c>
-      <c r="T64" s="10" t="s">
-        <v>32</v>
+      <c r="T64" s="12" t="s">
+        <v>224</v>
       </c>
       <c r="U64" s="11" t="s">
         <v>107</v>
@@ -5338,7 +5338,7 @@
         <v>46223.80725450232</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
@@ -5431,7 +5431,7 @@
         <v>226</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P67" s="9" t="s">
         <v>245</v>

--- a/data/50001533 - GESVIAL.xlsx
+++ b/data/50001533 - GESVIAL.xlsx
@@ -4367,7 +4367,7 @@
         <v>46193.56191304398</v>
       </c>
       <c r="D50" s="5">
-        <v>46208.210261203705</v>
+        <v>46257.57684141204</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>196</v>

--- a/data/50001533 - GESVIAL.xlsx
+++ b/data/50001533 - GESVIAL.xlsx
@@ -776,34 +776,34 @@
     <t>Montaje motor</t>
   </si>
   <si>
+    <t>1213964538772999</t>
+  </si>
+  <si>
+    <t>Montaje:</t>
+  </si>
+  <si>
+    <t>Revestimiento,RE-PINTADO,Montaje motor,Montaje Alabe,Montaje Rodete,Pruebas FAT</t>
+  </si>
+  <si>
+    <t>1213955269755930</t>
+  </si>
+  <si>
+    <t>Revestimiento</t>
+  </si>
+  <si>
+    <t>Montaje:,Montaje Alabe,Montaje Rodete,Montaje motor</t>
+  </si>
+  <si>
+    <t>1213955269755950</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revestimiento,Recepcion motor,Check planos </t>
+  </si>
+  <si>
+    <t>Montaje:,Pruebas FAT</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1213964538772999</t>
-  </si>
-  <si>
-    <t>Montaje:</t>
-  </si>
-  <si>
-    <t>Revestimiento,RE-PINTADO,Montaje motor,Montaje Alabe,Montaje Rodete,Pruebas FAT</t>
-  </si>
-  <si>
-    <t>1213955269755930</t>
-  </si>
-  <si>
-    <t>Revestimiento</t>
-  </si>
-  <si>
-    <t>Montaje:,Montaje Alabe,Montaje Rodete,Montaje motor</t>
-  </si>
-  <si>
-    <t>1213955269755950</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Revestimiento,Recepcion motor,Check planos </t>
-  </si>
-  <si>
-    <t>Montaje:,Pruebas FAT</t>
   </si>
   <si>
     <t>1213963540685278</t>
@@ -4961,7 +4961,7 @@
         <v>46193.56199724537</v>
       </c>
       <c r="D60" s="5">
-        <v>46251.18919104167</v>
+        <v>46259.20590515046</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>222</v>
@@ -5008,8 +5008,8 @@
       <c r="S60" s="6">
         <v>1</v>
       </c>
-      <c r="T60" s="12" t="s">
-        <v>224</v>
+      <c r="T60" s="11" t="s">
+        <v>55</v>
       </c>
       <c r="U60" s="11" t="s">
         <v>107</v>
@@ -5017,7 +5017,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B61" s="8">
         <v>46118.66236295139</v>
@@ -5029,7 +5029,7 @@
         <v>46204.900153703704</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>25</v>
@@ -5053,7 +5053,7 @@
         <v>26</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="P61" s="9" t="s">
         <v>26</v>
@@ -5066,7 +5066,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B62" s="5">
         <v>46118.66236873843</v>
@@ -5078,7 +5078,7 @@
         <v>46228.2021169213</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
@@ -5105,13 +5105,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="O62" s="6" t="s">
         <v>208</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="Q62" s="5">
         <v>46227</v>
@@ -5131,7 +5131,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B63" s="8">
         <v>46118.662376064814</v>
@@ -5170,13 +5170,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="O63" s="9" t="s">
+        <v>231</v>
+      </c>
+      <c r="P63" s="9" t="s">
         <v>232</v>
-      </c>
-      <c r="P63" s="9" t="s">
-        <v>233</v>
       </c>
       <c r="Q63" s="8">
         <v>46260</v>
@@ -5188,7 +5188,7 @@
         <v>1</v>
       </c>
       <c r="T63" s="12" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="U63" s="11" t="s">
         <v>107</v>
@@ -5235,13 +5235,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="O64" s="6" t="s">
         <v>236</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q64" s="5">
         <v>46262</v>
@@ -5253,7 +5253,7 @@
         <v>1</v>
       </c>
       <c r="T64" s="12" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="U64" s="11" t="s">
         <v>107</v>
@@ -5270,7 +5270,7 @@
         <v>46193.61273716435</v>
       </c>
       <c r="D65" s="8">
-        <v>46223.807257754626</v>
+        <v>46259.1828917824</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>238</v>
@@ -5300,13 +5300,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="O65" s="9" t="s">
         <v>239</v>
       </c>
       <c r="P65" s="9" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q65" s="8">
         <v>46266</v>
@@ -5317,8 +5317,8 @@
       <c r="S65" s="9">
         <v>1</v>
       </c>
-      <c r="T65" s="10" t="s">
-        <v>32</v>
+      <c r="T65" s="12" t="s">
+        <v>233</v>
       </c>
       <c r="U65" s="11" t="s">
         <v>107</v>
@@ -5363,7 +5363,7 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="O66" s="6" t="s">
         <v>241</v>
@@ -5428,7 +5428,7 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="O67" s="9" t="s">
         <v>170</v>

--- a/data/50001533 - GESVIAL.xlsx
+++ b/data/50001533 - GESVIAL.xlsx
@@ -5335,7 +5335,7 @@
         <v>46193.765511875</v>
       </c>
       <c r="D66" s="5">
-        <v>46223.80725450232</v>
+        <v>46260.199299942135</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>173</v>
@@ -5380,8 +5380,8 @@
       <c r="S66" s="6">
         <v>1</v>
       </c>
-      <c r="T66" s="10" t="s">
-        <v>32</v>
+      <c r="T66" s="12" t="s">
+        <v>233</v>
       </c>
       <c r="U66" s="11" t="s">
         <v>107</v>

--- a/data/50001533 - GESVIAL.xlsx
+++ b/data/50001533 - GESVIAL.xlsx
@@ -629,6 +629,9 @@
     <t>Ingenieria y diseño:,RE-PINTADO</t>
   </si>
   <si>
+    <t>Media</t>
+  </si>
+  <si>
     <t>1213962383676938</t>
   </si>
   <si>
@@ -801,9 +804,6 @@
   </si>
   <si>
     <t>Montaje:,Pruebas FAT</t>
-  </si>
-  <si>
-    <t>Media</t>
   </si>
   <si>
     <t>1213963540685278</t>
@@ -4009,7 +4009,7 @@
         <v>46198.5694571412</v>
       </c>
       <c r="D44" s="5">
-        <v>46208.20879145833</v>
+        <v>46261.16791466435</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>170</v>
@@ -4056,8 +4056,8 @@
       <c r="S44" s="6">
         <v>1</v>
       </c>
-      <c r="T44" s="10" t="s">
-        <v>32</v>
+      <c r="T44" s="12" t="s">
+        <v>175</v>
       </c>
       <c r="U44" s="11" t="s">
         <v>107</v>
@@ -4065,7 +4065,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B45" s="8">
         <v>46118.66224984954</v>
@@ -4077,7 +4077,7 @@
         <v>46184.68718828703</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>25</v>
@@ -4101,7 +4101,7 @@
         <v>26</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="P45" s="9" t="s">
         <v>26</v>
@@ -4114,7 +4114,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B46" s="5">
         <v>46118.66225350695</v>
@@ -4132,10 +4132,10 @@
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="I46" s="5">
         <v>46171</v>
@@ -4153,13 +4153,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="O46" s="6" t="s">
         <v>150</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q46" s="5">
         <v>46174</v>
@@ -4179,7 +4179,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B47" s="8">
         <v>46118.66225863426</v>
@@ -4191,16 +4191,16 @@
         <v>46208.20991337963</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I47" s="8">
         <v>46175</v>
@@ -4218,13 +4218,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="O47" s="9" t="s">
         <v>152</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q47" s="8">
         <v>46176</v>
@@ -4244,7 +4244,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B48" s="5">
         <v>46118.662263819446</v>
@@ -4256,7 +4256,7 @@
         <v>46194.05633912037</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>25</v>
@@ -4280,7 +4280,7 @@
         <v>26</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P48" s="6" t="s">
         <v>26</v>
@@ -4293,7 +4293,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B49" s="8">
         <v>46118.66226751157</v>
@@ -4305,16 +4305,16 @@
         <v>46208.210227986114</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I49" s="8">
         <v>46177</v>
@@ -4332,13 +4332,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q49" s="8">
         <v>46185</v>
@@ -4358,7 +4358,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B50" s="5">
         <v>46118.66227269676</v>
@@ -4370,16 +4370,16 @@
         <v>46257.57684141204</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I50" s="5">
         <v>46188</v>
@@ -4397,13 +4397,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q50" s="5">
         <v>46205</v>
@@ -4423,7 +4423,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B51" s="8">
         <v>46184.687980393515</v>
@@ -4435,16 +4435,16 @@
         <v>46191.68718039352</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I51" s="8">
         <v>46188</v>
@@ -4462,7 +4462,7 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O51" s="9" t="s">
         <v>26</v>
@@ -4478,7 +4478,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B52" s="5">
         <v>46184.688093055556</v>
@@ -4490,16 +4490,16 @@
         <v>46195.70254238426</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I52" s="5">
         <v>46188</v>
@@ -4517,7 +4517,7 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O52" s="6" t="s">
         <v>26</v>
@@ -4533,7 +4533,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B53" s="8">
         <v>46184.68816803241</v>
@@ -4545,16 +4545,16 @@
         <v>46191.6871738426</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H53" s="9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I53" s="8">
         <v>46188</v>
@@ -4572,7 +4572,7 @@
         <v>26</v>
       </c>
       <c r="N53" s="9" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O53" s="9" t="s">
         <v>26</v>
@@ -4588,7 +4588,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B54" s="5">
         <v>46184.68826700232</v>
@@ -4600,16 +4600,16 @@
         <v>46191.687168993056</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I54" s="5">
         <v>46188</v>
@@ -4627,7 +4627,7 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O54" s="6" t="s">
         <v>26</v>
@@ -4643,7 +4643,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B55" s="8">
         <v>46118.66227863426</v>
@@ -4655,16 +4655,16 @@
         <v>46210.19828702546</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I55" s="8">
         <v>46206</v>
@@ -4682,13 +4682,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="P55" s="9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q55" s="8">
         <v>46209</v>
@@ -4708,7 +4708,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B56" s="5">
         <v>46118.66228488426</v>
@@ -4720,7 +4720,7 @@
         <v>46194.05632325231</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>25</v>
@@ -4744,7 +4744,7 @@
         <v>26</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P56" s="6" t="s">
         <v>26</v>
@@ -4757,7 +4757,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B57" s="8">
         <v>46118.66228803241</v>
@@ -4769,16 +4769,16 @@
         <v>46208.21036678241</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="I57" s="8">
         <v>46168</v>
@@ -4796,13 +4796,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="O57" s="9" t="s">
         <v>130</v>
       </c>
       <c r="P57" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q57" s="8">
         <v>46169</v>
@@ -4822,7 +4822,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B58" s="5">
         <v>46118.662293518515</v>
@@ -4840,10 +4840,10 @@
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="I58" s="5">
         <v>46189</v>
@@ -4861,13 +4861,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="O58" s="6" t="s">
         <v>121</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q58" s="5">
         <v>46190</v>
@@ -4887,7 +4887,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B59" s="8">
         <v>46118.662299895834</v>
@@ -4899,16 +4899,16 @@
         <v>46235.186337858795</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="I59" s="8">
         <v>46233</v>
@@ -4926,13 +4926,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="O59" s="9" t="s">
         <v>112</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q59" s="8">
         <v>46234</v>
@@ -4952,7 +4952,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B60" s="5">
         <v>46118.66235550926</v>
@@ -4964,16 +4964,16 @@
         <v>46259.20590515046</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="I60" s="5">
         <v>46255</v>
@@ -4991,13 +4991,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="O60" s="6" t="s">
         <v>139</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q60" s="5">
         <v>46258</v>
@@ -5017,7 +5017,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B61" s="8">
         <v>46118.66236295139</v>
@@ -5029,7 +5029,7 @@
         <v>46204.900153703704</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>25</v>
@@ -5053,7 +5053,7 @@
         <v>26</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="P61" s="9" t="s">
         <v>26</v>
@@ -5066,7 +5066,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B62" s="5">
         <v>46118.66236873843</v>
@@ -5078,7 +5078,7 @@
         <v>46228.2021169213</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
@@ -5105,13 +5105,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q62" s="5">
         <v>46227</v>
@@ -5131,7 +5131,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B63" s="8">
         <v>46118.662376064814</v>
@@ -5140,10 +5140,10 @@
         <v>46193.6126587037</v>
       </c>
       <c r="D63" s="8">
-        <v>46253.20344491898</v>
+        <v>46261.18259065972</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>26</v>
@@ -5170,13 +5170,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="P63" s="9" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q63" s="8">
         <v>46260</v>
@@ -5187,8 +5187,8 @@
       <c r="S63" s="9">
         <v>1</v>
       </c>
-      <c r="T63" s="12" t="s">
-        <v>233</v>
+      <c r="T63" s="11" t="s">
+        <v>55</v>
       </c>
       <c r="U63" s="11" t="s">
         <v>107</v>
@@ -5235,13 +5235,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="O64" s="6" t="s">
         <v>236</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q64" s="5">
         <v>46262</v>
@@ -5253,7 +5253,7 @@
         <v>1</v>
       </c>
       <c r="T64" s="12" t="s">
-        <v>233</v>
+        <v>175</v>
       </c>
       <c r="U64" s="11" t="s">
         <v>107</v>
@@ -5300,13 +5300,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="O65" s="9" t="s">
         <v>239</v>
       </c>
       <c r="P65" s="9" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q65" s="8">
         <v>46266</v>
@@ -5318,7 +5318,7 @@
         <v>1</v>
       </c>
       <c r="T65" s="12" t="s">
-        <v>233</v>
+        <v>175</v>
       </c>
       <c r="U65" s="11" t="s">
         <v>107</v>
@@ -5363,7 +5363,7 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="O66" s="6" t="s">
         <v>241</v>
@@ -5381,7 +5381,7 @@
         <v>1</v>
       </c>
       <c r="T66" s="12" t="s">
-        <v>233</v>
+        <v>175</v>
       </c>
       <c r="U66" s="11" t="s">
         <v>107</v>
@@ -5428,7 +5428,7 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="O67" s="9" t="s">
         <v>170</v>

--- a/data/50001533 - GESVIAL.xlsx
+++ b/data/50001533 - GESVIAL.xlsx
@@ -5398,7 +5398,7 @@
         <v>46196.92346424768</v>
       </c>
       <c r="D67" s="8">
-        <v>46223.807249398145</v>
+        <v>46262.17054369213</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>244</v>
@@ -5445,8 +5445,8 @@
       <c r="S67" s="9">
         <v>1</v>
       </c>
-      <c r="T67" s="10" t="s">
-        <v>32</v>
+      <c r="T67" s="12" t="s">
+        <v>175</v>
       </c>
       <c r="U67" s="11" t="s">
         <v>107</v>

--- a/data/50001533 - GESVIAL.xlsx
+++ b/data/50001533 - GESVIAL.xlsx
@@ -2112,7 +2112,7 @@
         <v>46193.56179229167</v>
       </c>
       <c r="D13" s="8">
-        <v>46193.561794629626</v>
+        <v>46263.3584521875</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>61</v>
@@ -5205,7 +5205,7 @@
         <v>46193.61267944444</v>
       </c>
       <c r="D64" s="5">
-        <v>46255.187699664355</v>
+        <v>46263.200463692134</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>235</v>
@@ -5252,8 +5252,8 @@
       <c r="S64" s="6">
         <v>1</v>
       </c>
-      <c r="T64" s="12" t="s">
-        <v>175</v>
+      <c r="T64" s="11" t="s">
+        <v>55</v>
       </c>
       <c r="U64" s="11" t="s">
         <v>107</v>

--- a/data/50001533 - GESVIAL.xlsx
+++ b/data/50001533 - GESVIAL.xlsx
@@ -5516,7 +5516,7 @@
         <v>46203.81564377315</v>
       </c>
       <c r="D69" s="8">
-        <v>46208.21071721065</v>
+        <v>46265.183787766204</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>250</v>
@@ -5561,8 +5561,8 @@
       <c r="S69" s="9">
         <v>1</v>
       </c>
-      <c r="T69" s="10" t="s">
-        <v>32</v>
+      <c r="T69" s="12" t="s">
+        <v>175</v>
       </c>
       <c r="U69" s="10" t="s">
         <v>33</v>

--- a/data/50001533 - GESVIAL.xlsx
+++ b/data/50001533 - GESVIAL.xlsx
@@ -5579,7 +5579,7 @@
         <v>46204.89777927083</v>
       </c>
       <c r="D70" s="5">
-        <v>46223.80733106482</v>
+        <v>46266.19055326389</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>255</v>
@@ -5624,8 +5624,8 @@
       <c r="S70" s="6">
         <v>1</v>
       </c>
-      <c r="T70" s="10" t="s">
-        <v>32</v>
+      <c r="T70" s="12" t="s">
+        <v>175</v>
       </c>
       <c r="U70" s="10" t="s">
         <v>33</v>

--- a/data/50001533 - GESVIAL.xlsx
+++ b/data/50001533 - GESVIAL.xlsx
@@ -5270,7 +5270,7 @@
         <v>46193.61273716435</v>
       </c>
       <c r="D65" s="8">
-        <v>46259.1828917824</v>
+        <v>46267.18259930555</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>238</v>
@@ -5317,8 +5317,8 @@
       <c r="S65" s="9">
         <v>1</v>
       </c>
-      <c r="T65" s="12" t="s">
-        <v>175</v>
+      <c r="T65" s="11" t="s">
+        <v>55</v>
       </c>
       <c r="U65" s="11" t="s">
         <v>107</v>
@@ -5642,7 +5642,7 @@
         <v>46196.9230577662</v>
       </c>
       <c r="D71" s="8">
-        <v>46208.210718125</v>
+        <v>46267.1821840162</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>259</v>
@@ -5687,8 +5687,8 @@
       <c r="S71" s="9">
         <v>1</v>
       </c>
-      <c r="T71" s="10" t="s">
-        <v>32</v>
+      <c r="T71" s="12" t="s">
+        <v>175</v>
       </c>
       <c r="U71" s="10" t="s">
         <v>33</v>

--- a/data/50001533 - GESVIAL.xlsx
+++ b/data/50001533 - GESVIAL.xlsx
@@ -5335,7 +5335,7 @@
         <v>46193.765511875</v>
       </c>
       <c r="D66" s="5">
-        <v>46260.199299942135</v>
+        <v>46268.19471135417</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>173</v>
@@ -5380,8 +5380,8 @@
       <c r="S66" s="6">
         <v>1</v>
       </c>
-      <c r="T66" s="12" t="s">
-        <v>175</v>
+      <c r="T66" s="11" t="s">
+        <v>55</v>
       </c>
       <c r="U66" s="11" t="s">
         <v>107</v>
@@ -5705,7 +5705,7 @@
         <v>46210.64094128472</v>
       </c>
       <c r="D72" s="5">
-        <v>46240.71876092593</v>
+        <v>46268.17928672454</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>264</v>
@@ -5750,8 +5750,8 @@
       <c r="S72" s="6">
         <v>1</v>
       </c>
-      <c r="T72" s="10" t="s">
-        <v>32</v>
+      <c r="T72" s="12" t="s">
+        <v>175</v>
       </c>
       <c r="U72" s="10" t="s">
         <v>33</v>

--- a/data/50001533 - GESVIAL.xlsx
+++ b/data/50001533 - GESVIAL.xlsx
@@ -629,217 +629,217 @@
     <t>Ingenieria y diseño:,RE-PINTADO</t>
   </si>
   <si>
+    <t>1213962383676938</t>
+  </si>
+  <si>
+    <t>Bodega:</t>
+  </si>
+  <si>
+    <t>Recepcion materiales a codigos // compras locales aprovisionamiento,Control de calidad compras materiales a codigo // compras locale aprovisionamiento</t>
+  </si>
+  <si>
+    <t>1213962383676950</t>
+  </si>
+  <si>
+    <t>Victor Muñoz</t>
+  </si>
+  <si>
+    <t>victor.munoz@zitron.com</t>
+  </si>
+  <si>
+    <t>Bodega:,Control de calidad compras materiales a codigo // compras locale aprovisionamiento</t>
+  </si>
+  <si>
+    <t>1213962383680132</t>
+  </si>
+  <si>
+    <t>Control de calidad compras materiales a codigo // compras locale aprovisionamiento</t>
+  </si>
+  <si>
+    <t>Nicolás López</t>
+  </si>
+  <si>
+    <t>nicolas.lopez@zitron.com</t>
+  </si>
+  <si>
+    <t>Generacion oc ,Bodega:</t>
+  </si>
+  <si>
+    <t>1213962383680152</t>
+  </si>
+  <si>
+    <t>Fabricacion externa :</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generacion oc ,Fabricacion,Control de calidad </t>
+  </si>
+  <si>
+    <t>1213955269732491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generacion oc </t>
+  </si>
+  <si>
+    <t>Rosemary Singh</t>
+  </si>
+  <si>
+    <t>rosemary.singh@zitron.com</t>
+  </si>
+  <si>
+    <t>Fabricacion externa :,Fabricacion</t>
+  </si>
+  <si>
+    <t>1213955269732511</t>
+  </si>
+  <si>
+    <t>Fabricacion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generacion oc ,Check planos </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabricacion externa :,Control de calidad </t>
+  </si>
+  <si>
+    <t>1215632916059321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carcasa </t>
+  </si>
+  <si>
+    <t>1215632916059322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Silenciador </t>
+  </si>
+  <si>
+    <t>1215632916059323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pieza de adaptacion </t>
+  </si>
+  <si>
+    <t>1215632916059324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rejilla </t>
+  </si>
+  <si>
+    <t>1213955269733641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabricacion,Check planos </t>
+  </si>
+  <si>
+    <t>Fabricacion externa :,Revestimiento</t>
+  </si>
+  <si>
+    <t>1213955269734786</t>
+  </si>
+  <si>
+    <t>Recepcion Alabe,Recepcion Rodete,Recepcion Tableros y componentes electricos</t>
+  </si>
+  <si>
+    <t>1213955269734796</t>
+  </si>
+  <si>
+    <t>Recepcion Rodete</t>
+  </si>
+  <si>
+    <t>Montaje Rodete,Bodega:</t>
+  </si>
+  <si>
+    <t>1213964538786219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bodega:,Revisión tableros pruebas y componentes eléctricos </t>
+  </si>
+  <si>
+    <t>1213955269739200</t>
+  </si>
+  <si>
+    <t>Recepcion Alabe</t>
+  </si>
+  <si>
+    <t>Bodega:,Montaje Alabe</t>
+  </si>
+  <si>
+    <t>1213964538772984</t>
+  </si>
+  <si>
+    <t>Recepcion motor</t>
+  </si>
+  <si>
+    <t>Montaje motor</t>
+  </si>
+  <si>
+    <t>1213964538772999</t>
+  </si>
+  <si>
+    <t>Montaje:</t>
+  </si>
+  <si>
+    <t>Revestimiento,RE-PINTADO,Montaje motor,Montaje Alabe,Montaje Rodete,Pruebas FAT</t>
+  </si>
+  <si>
+    <t>1213955269755930</t>
+  </si>
+  <si>
+    <t>Revestimiento</t>
+  </si>
+  <si>
+    <t>Montaje:,Montaje Alabe,Montaje Rodete,Montaje motor</t>
+  </si>
+  <si>
+    <t>1213955269755950</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revestimiento,Recepcion motor,Check planos </t>
+  </si>
+  <si>
+    <t>Montaje:,Pruebas FAT</t>
+  </si>
+  <si>
+    <t>1213963540685278</t>
+  </si>
+  <si>
+    <t>Montaje Alabe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recepcion Alabe,Revestimiento,Check planos </t>
+  </si>
+  <si>
+    <t>1213963540686923</t>
+  </si>
+  <si>
+    <t>Montaje Rodete</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recepcion Rodete,Planos definitivo,Revestimiento,Check planos </t>
+  </si>
+  <si>
+    <t>1213963540687227</t>
+  </si>
+  <si>
+    <t>Montaje motor,Montaje Alabe,Montaje Rodete</t>
+  </si>
+  <si>
+    <t>Check Pruebas fat,Montaje:</t>
+  </si>
+  <si>
+    <t>1213962383715526</t>
+  </si>
+  <si>
+    <t>RE-PINTADO</t>
+  </si>
+  <si>
+    <t>Montaje:,Coordinacion Entrega con Cliente</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1213962383676938</t>
-  </si>
-  <si>
-    <t>Bodega:</t>
-  </si>
-  <si>
-    <t>Recepcion materiales a codigos // compras locales aprovisionamiento,Control de calidad compras materiales a codigo // compras locale aprovisionamiento</t>
-  </si>
-  <si>
-    <t>1213962383676950</t>
-  </si>
-  <si>
-    <t>Victor Muñoz</t>
-  </si>
-  <si>
-    <t>victor.munoz@zitron.com</t>
-  </si>
-  <si>
-    <t>Bodega:,Control de calidad compras materiales a codigo // compras locale aprovisionamiento</t>
-  </si>
-  <si>
-    <t>1213962383680132</t>
-  </si>
-  <si>
-    <t>Control de calidad compras materiales a codigo // compras locale aprovisionamiento</t>
-  </si>
-  <si>
-    <t>Nicolás López</t>
-  </si>
-  <si>
-    <t>nicolas.lopez@zitron.com</t>
-  </si>
-  <si>
-    <t>Generacion oc ,Bodega:</t>
-  </si>
-  <si>
-    <t>1213962383680152</t>
-  </si>
-  <si>
-    <t>Fabricacion externa :</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generacion oc ,Fabricacion,Control de calidad </t>
-  </si>
-  <si>
-    <t>1213955269732491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generacion oc </t>
-  </si>
-  <si>
-    <t>Rosemary Singh</t>
-  </si>
-  <si>
-    <t>rosemary.singh@zitron.com</t>
-  </si>
-  <si>
-    <t>Fabricacion externa :,Fabricacion</t>
-  </si>
-  <si>
-    <t>1213955269732511</t>
-  </si>
-  <si>
-    <t>Fabricacion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generacion oc ,Check planos </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fabricacion externa :,Control de calidad </t>
-  </si>
-  <si>
-    <t>1215632916059321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Carcasa </t>
-  </si>
-  <si>
-    <t>1215632916059322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Silenciador </t>
-  </si>
-  <si>
-    <t>1215632916059323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pieza de adaptacion </t>
-  </si>
-  <si>
-    <t>1215632916059324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rejilla </t>
-  </si>
-  <si>
-    <t>1213955269733641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fabricacion,Check planos </t>
-  </si>
-  <si>
-    <t>Fabricacion externa :,Revestimiento</t>
-  </si>
-  <si>
-    <t>1213955269734786</t>
-  </si>
-  <si>
-    <t>Recepcion Alabe,Recepcion Rodete,Recepcion Tableros y componentes electricos</t>
-  </si>
-  <si>
-    <t>1213955269734796</t>
-  </si>
-  <si>
-    <t>Recepcion Rodete</t>
-  </si>
-  <si>
-    <t>Montaje Rodete,Bodega:</t>
-  </si>
-  <si>
-    <t>1213964538786219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bodega:,Revisión tableros pruebas y componentes eléctricos </t>
-  </si>
-  <si>
-    <t>1213955269739200</t>
-  </si>
-  <si>
-    <t>Recepcion Alabe</t>
-  </si>
-  <si>
-    <t>Bodega:,Montaje Alabe</t>
-  </si>
-  <si>
-    <t>1213964538772984</t>
-  </si>
-  <si>
-    <t>Recepcion motor</t>
-  </si>
-  <si>
-    <t>Montaje motor</t>
-  </si>
-  <si>
-    <t>1213964538772999</t>
-  </si>
-  <si>
-    <t>Montaje:</t>
-  </si>
-  <si>
-    <t>Revestimiento,RE-PINTADO,Montaje motor,Montaje Alabe,Montaje Rodete,Pruebas FAT</t>
-  </si>
-  <si>
-    <t>1213955269755930</t>
-  </si>
-  <si>
-    <t>Revestimiento</t>
-  </si>
-  <si>
-    <t>Montaje:,Montaje Alabe,Montaje Rodete,Montaje motor</t>
-  </si>
-  <si>
-    <t>1213955269755950</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Revestimiento,Recepcion motor,Check planos </t>
-  </si>
-  <si>
-    <t>Montaje:,Pruebas FAT</t>
-  </si>
-  <si>
-    <t>1213963540685278</t>
-  </si>
-  <si>
-    <t>Montaje Alabe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recepcion Alabe,Revestimiento,Check planos </t>
-  </si>
-  <si>
-    <t>1213963540686923</t>
-  </si>
-  <si>
-    <t>Montaje Rodete</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recepcion Rodete,Planos definitivo,Revestimiento,Check planos </t>
-  </si>
-  <si>
-    <t>1213963540687227</t>
-  </si>
-  <si>
-    <t>Montaje motor,Montaje Alabe,Montaje Rodete</t>
-  </si>
-  <si>
-    <t>Check Pruebas fat,Montaje:</t>
-  </si>
-  <si>
-    <t>1213962383715526</t>
-  </si>
-  <si>
-    <t>RE-PINTADO</t>
-  </si>
-  <si>
-    <t>Montaje:,Coordinacion Entrega con Cliente</t>
   </si>
   <si>
     <t>1213962383715546</t>
@@ -4009,7 +4009,7 @@
         <v>46198.5694571412</v>
       </c>
       <c r="D44" s="5">
-        <v>46261.16791466435</v>
+        <v>46269.187862569444</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>170</v>
@@ -4056,8 +4056,8 @@
       <c r="S44" s="6">
         <v>1</v>
       </c>
-      <c r="T44" s="12" t="s">
-        <v>175</v>
+      <c r="T44" s="11" t="s">
+        <v>55</v>
       </c>
       <c r="U44" s="11" t="s">
         <v>107</v>
@@ -4065,7 +4065,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B45" s="8">
         <v>46118.66224984954</v>
@@ -4077,7 +4077,7 @@
         <v>46184.68718828703</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>25</v>
@@ -4101,7 +4101,7 @@
         <v>26</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="P45" s="9" t="s">
         <v>26</v>
@@ -4114,7 +4114,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B46" s="5">
         <v>46118.66225350695</v>
@@ -4132,10 +4132,10 @@
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="H46" s="6" t="s">
         <v>180</v>
-      </c>
-      <c r="H46" s="6" t="s">
-        <v>181</v>
       </c>
       <c r="I46" s="5">
         <v>46171</v>
@@ -4153,13 +4153,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="O46" s="6" t="s">
         <v>150</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q46" s="5">
         <v>46174</v>
@@ -4179,7 +4179,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B47" s="8">
         <v>46118.66225863426</v>
@@ -4191,16 +4191,16 @@
         <v>46208.20991337963</v>
       </c>
       <c r="E47" s="9" t="s">
+        <v>183</v>
+      </c>
+      <c r="F47" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G47" s="9" t="s">
         <v>184</v>
       </c>
-      <c r="F47" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G47" s="9" t="s">
+      <c r="H47" s="9" t="s">
         <v>185</v>
-      </c>
-      <c r="H47" s="9" t="s">
-        <v>186</v>
       </c>
       <c r="I47" s="8">
         <v>46175</v>
@@ -4218,13 +4218,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="O47" s="9" t="s">
         <v>152</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="Q47" s="8">
         <v>46176</v>
@@ -4244,7 +4244,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B48" s="5">
         <v>46118.662263819446</v>
@@ -4256,7 +4256,7 @@
         <v>46194.05633912037</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>25</v>
@@ -4280,7 +4280,7 @@
         <v>26</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P48" s="6" t="s">
         <v>26</v>
@@ -4293,7 +4293,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B49" s="8">
         <v>46118.66226751157</v>
@@ -4305,16 +4305,16 @@
         <v>46208.210227986114</v>
       </c>
       <c r="E49" s="9" t="s">
+        <v>191</v>
+      </c>
+      <c r="F49" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G49" s="9" t="s">
         <v>192</v>
       </c>
-      <c r="F49" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G49" s="9" t="s">
+      <c r="H49" s="9" t="s">
         <v>193</v>
-      </c>
-      <c r="H49" s="9" t="s">
-        <v>194</v>
       </c>
       <c r="I49" s="8">
         <v>46177</v>
@@ -4332,13 +4332,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="Q49" s="8">
         <v>46185</v>
@@ -4358,7 +4358,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B50" s="5">
         <v>46118.66227269676</v>
@@ -4370,16 +4370,16 @@
         <v>46257.57684141204</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="H50" s="6" t="s">
         <v>193</v>
-      </c>
-      <c r="H50" s="6" t="s">
-        <v>194</v>
       </c>
       <c r="I50" s="5">
         <v>46188</v>
@@ -4397,13 +4397,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="O50" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="P50" s="6" t="s">
         <v>198</v>
-      </c>
-      <c r="P50" s="6" t="s">
-        <v>199</v>
       </c>
       <c r="Q50" s="5">
         <v>46205</v>
@@ -4423,7 +4423,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B51" s="8">
         <v>46184.687980393515</v>
@@ -4435,16 +4435,16 @@
         <v>46191.68718039352</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="H51" s="9" t="s">
         <v>193</v>
-      </c>
-      <c r="H51" s="9" t="s">
-        <v>194</v>
       </c>
       <c r="I51" s="8">
         <v>46188</v>
@@ -4462,7 +4462,7 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="O51" s="9" t="s">
         <v>26</v>
@@ -4478,7 +4478,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B52" s="5">
         <v>46184.688093055556</v>
@@ -4490,16 +4490,16 @@
         <v>46195.70254238426</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="H52" s="6" t="s">
         <v>193</v>
-      </c>
-      <c r="H52" s="6" t="s">
-        <v>194</v>
       </c>
       <c r="I52" s="5">
         <v>46188</v>
@@ -4517,7 +4517,7 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="O52" s="6" t="s">
         <v>26</v>
@@ -4533,7 +4533,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B53" s="8">
         <v>46184.68816803241</v>
@@ -4545,16 +4545,16 @@
         <v>46191.6871738426</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="H53" s="9" t="s">
         <v>193</v>
-      </c>
-      <c r="H53" s="9" t="s">
-        <v>194</v>
       </c>
       <c r="I53" s="8">
         <v>46188</v>
@@ -4572,7 +4572,7 @@
         <v>26</v>
       </c>
       <c r="N53" s="9" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="O53" s="9" t="s">
         <v>26</v>
@@ -4588,7 +4588,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B54" s="5">
         <v>46184.68826700232</v>
@@ -4600,16 +4600,16 @@
         <v>46191.687168993056</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="H54" s="6" t="s">
         <v>193</v>
-      </c>
-      <c r="H54" s="6" t="s">
-        <v>194</v>
       </c>
       <c r="I54" s="5">
         <v>46188</v>
@@ -4627,7 +4627,7 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="O54" s="6" t="s">
         <v>26</v>
@@ -4643,7 +4643,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B55" s="8">
         <v>46118.66227863426</v>
@@ -4655,16 +4655,16 @@
         <v>46210.19828702546</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="H55" s="9" t="s">
         <v>185</v>
-      </c>
-      <c r="H55" s="9" t="s">
-        <v>186</v>
       </c>
       <c r="I55" s="8">
         <v>46206</v>
@@ -4682,13 +4682,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="O55" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="P55" s="9" t="s">
         <v>210</v>
-      </c>
-      <c r="P55" s="9" t="s">
-        <v>211</v>
       </c>
       <c r="Q55" s="8">
         <v>46209</v>
@@ -4708,7 +4708,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B56" s="5">
         <v>46118.66228488426</v>
@@ -4720,7 +4720,7 @@
         <v>46194.05632325231</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>25</v>
@@ -4744,7 +4744,7 @@
         <v>26</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P56" s="6" t="s">
         <v>26</v>
@@ -4757,7 +4757,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B57" s="8">
         <v>46118.66228803241</v>
@@ -4769,16 +4769,16 @@
         <v>46208.21036678241</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="H57" s="9" t="s">
         <v>180</v>
-      </c>
-      <c r="H57" s="9" t="s">
-        <v>181</v>
       </c>
       <c r="I57" s="8">
         <v>46168</v>
@@ -4796,13 +4796,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="O57" s="9" t="s">
         <v>130</v>
       </c>
       <c r="P57" s="9" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="Q57" s="8">
         <v>46169</v>
@@ -4822,7 +4822,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B58" s="5">
         <v>46118.662293518515</v>
@@ -4840,10 +4840,10 @@
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="H58" s="6" t="s">
         <v>180</v>
-      </c>
-      <c r="H58" s="6" t="s">
-        <v>181</v>
       </c>
       <c r="I58" s="5">
         <v>46189</v>
@@ -4861,13 +4861,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="O58" s="6" t="s">
         <v>121</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="Q58" s="5">
         <v>46190</v>
@@ -4887,7 +4887,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B59" s="8">
         <v>46118.662299895834</v>
@@ -4899,16 +4899,16 @@
         <v>46235.186337858795</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="H59" s="9" t="s">
         <v>180</v>
-      </c>
-      <c r="H59" s="9" t="s">
-        <v>181</v>
       </c>
       <c r="I59" s="8">
         <v>46233</v>
@@ -4926,13 +4926,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="O59" s="9" t="s">
         <v>112</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="Q59" s="8">
         <v>46234</v>
@@ -4952,7 +4952,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B60" s="5">
         <v>46118.66235550926</v>
@@ -4964,16 +4964,16 @@
         <v>46259.20590515046</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="H60" s="6" t="s">
         <v>180</v>
-      </c>
-      <c r="H60" s="6" t="s">
-        <v>181</v>
       </c>
       <c r="I60" s="5">
         <v>46255</v>
@@ -4991,13 +4991,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="O60" s="6" t="s">
         <v>139</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="Q60" s="5">
         <v>46258</v>
@@ -5017,7 +5017,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B61" s="8">
         <v>46118.66236295139</v>
@@ -5029,7 +5029,7 @@
         <v>46204.900153703704</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>25</v>
@@ -5053,7 +5053,7 @@
         <v>26</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="P61" s="9" t="s">
         <v>26</v>
@@ -5066,7 +5066,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B62" s="5">
         <v>46118.66236873843</v>
@@ -5078,7 +5078,7 @@
         <v>46228.2021169213</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
@@ -5105,13 +5105,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="Q62" s="5">
         <v>46227</v>
@@ -5131,7 +5131,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B63" s="8">
         <v>46118.662376064814</v>
@@ -5143,7 +5143,7 @@
         <v>46261.18259065972</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>26</v>
@@ -5170,13 +5170,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="O63" s="9" t="s">
+        <v>231</v>
+      </c>
+      <c r="P63" s="9" t="s">
         <v>232</v>
-      </c>
-      <c r="P63" s="9" t="s">
-        <v>233</v>
       </c>
       <c r="Q63" s="8">
         <v>46260</v>
@@ -5196,7 +5196,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B64" s="5">
         <v>46118.662387557866</v>
@@ -5208,7 +5208,7 @@
         <v>46263.200463692134</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
@@ -5235,13 +5235,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q64" s="5">
         <v>46262</v>
@@ -5261,7 +5261,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B65" s="8">
         <v>46118.662398796296</v>
@@ -5273,7 +5273,7 @@
         <v>46267.18259930555</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
@@ -5300,13 +5300,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="P65" s="9" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q65" s="8">
         <v>46266</v>
@@ -5326,7 +5326,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B66" s="5">
         <v>46118.66240984954</v>
@@ -5363,13 +5363,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="O66" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="P66" s="6" t="s">
         <v>241</v>
-      </c>
-      <c r="P66" s="6" t="s">
-        <v>242</v>
       </c>
       <c r="Q66" s="5">
         <v>46267</v>
@@ -5389,7 +5389,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B67" s="8">
         <v>46118.662420127315</v>
@@ -5401,7 +5401,7 @@
         <v>46262.17054369213</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
@@ -5428,13 +5428,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="O67" s="9" t="s">
         <v>170</v>
       </c>
       <c r="P67" s="9" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="Q67" s="8">
         <v>46269</v>
@@ -5446,7 +5446,7 @@
         <v>1</v>
       </c>
       <c r="T67" s="12" t="s">
-        <v>175</v>
+        <v>245</v>
       </c>
       <c r="U67" s="11" t="s">
         <v>107</v>
@@ -5547,7 +5547,7 @@
         <v>247</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="P69" s="9" t="s">
         <v>253</v>
@@ -5562,7 +5562,7 @@
         <v>1</v>
       </c>
       <c r="T69" s="12" t="s">
-        <v>175</v>
+        <v>245</v>
       </c>
       <c r="U69" s="10" t="s">
         <v>33</v>
@@ -5625,7 +5625,7 @@
         <v>1</v>
       </c>
       <c r="T70" s="12" t="s">
-        <v>175</v>
+        <v>245</v>
       </c>
       <c r="U70" s="10" t="s">
         <v>33</v>
@@ -5688,7 +5688,7 @@
         <v>1</v>
       </c>
       <c r="T71" s="12" t="s">
-        <v>175</v>
+        <v>245</v>
       </c>
       <c r="U71" s="10" t="s">
         <v>33</v>
@@ -5751,7 +5751,7 @@
         <v>1</v>
       </c>
       <c r="T72" s="12" t="s">
-        <v>175</v>
+        <v>245</v>
       </c>
       <c r="U72" s="10" t="s">
         <v>33</v>

--- a/data/50001533 - GESVIAL.xlsx
+++ b/data/50001533 - GESVIAL.xlsx
@@ -839,31 +839,31 @@
     <t>Montaje:,Coordinacion Entrega con Cliente</t>
   </si>
   <si>
+    <t>1213962383715546</t>
+  </si>
+  <si>
+    <t>Logistica:</t>
+  </si>
+  <si>
+    <t>Coordinacion Entrega con Cliente,Embalaje,PACKING LIST,Despacho</t>
+  </si>
+  <si>
+    <t>1213962383719851</t>
+  </si>
+  <si>
+    <t>Coordinacion Entrega con Cliente</t>
+  </si>
+  <si>
+    <t>Karin Pinto</t>
+  </si>
+  <si>
+    <t>kpinto@zitron.com</t>
+  </si>
+  <si>
+    <t>Logistica:,Embalaje</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1213962383715546</t>
-  </si>
-  <si>
-    <t>Logistica:</t>
-  </si>
-  <si>
-    <t>Coordinacion Entrega con Cliente,Embalaje,PACKING LIST,Despacho</t>
-  </si>
-  <si>
-    <t>1213962383719851</t>
-  </si>
-  <si>
-    <t>Coordinacion Entrega con Cliente</t>
-  </si>
-  <si>
-    <t>Karin Pinto</t>
-  </si>
-  <si>
-    <t>kpinto@zitron.com</t>
-  </si>
-  <si>
-    <t>Logistica:,Embalaje</t>
   </si>
   <si>
     <t>1213962383719871</t>
@@ -5398,7 +5398,7 @@
         <v>46196.92346424768</v>
       </c>
       <c r="D67" s="8">
-        <v>46262.17054369213</v>
+        <v>46270.186431967595</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>243</v>
@@ -5445,8 +5445,8 @@
       <c r="S67" s="9">
         <v>1</v>
       </c>
-      <c r="T67" s="12" t="s">
-        <v>245</v>
+      <c r="T67" s="11" t="s">
+        <v>55</v>
       </c>
       <c r="U67" s="11" t="s">
         <v>107</v>
@@ -5454,7 +5454,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B68" s="5">
         <v>46118.66242769676</v>
@@ -5466,7 +5466,7 @@
         <v>46210.64097907407</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>25</v>
@@ -5490,7 +5490,7 @@
         <v>26</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="P68" s="6" t="s">
         <v>26</v>
@@ -5507,7 +5507,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B69" s="8">
         <v>46118.662431770834</v>
@@ -5519,16 +5519,16 @@
         <v>46265.183787766204</v>
       </c>
       <c r="E69" s="9" t="s">
+        <v>249</v>
+      </c>
+      <c r="F69" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G69" s="9" t="s">
         <v>250</v>
       </c>
-      <c r="F69" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G69" s="9" t="s">
+      <c r="H69" s="9" t="s">
         <v>251</v>
-      </c>
-      <c r="H69" s="9" t="s">
-        <v>252</v>
       </c>
       <c r="I69" s="9"/>
       <c r="J69" s="8">
@@ -5544,13 +5544,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="O69" s="9" t="s">
         <v>243</v>
       </c>
       <c r="P69" s="9" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Q69" s="8">
         <v>46272</v>
@@ -5562,7 +5562,7 @@
         <v>1</v>
       </c>
       <c r="T69" s="12" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="U69" s="10" t="s">
         <v>33</v>
@@ -5607,7 +5607,7 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="O70" s="6" t="s">
         <v>256</v>
@@ -5625,7 +5625,7 @@
         <v>1</v>
       </c>
       <c r="T70" s="12" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="U70" s="10" t="s">
         <v>33</v>
@@ -5670,7 +5670,7 @@
         <v>26</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="O71" s="9" t="s">
         <v>255</v>
@@ -5688,7 +5688,7 @@
         <v>1</v>
       </c>
       <c r="T71" s="12" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="U71" s="10" t="s">
         <v>33</v>
@@ -5733,7 +5733,7 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="O72" s="6" t="s">
         <v>259</v>
@@ -5751,7 +5751,7 @@
         <v>1</v>
       </c>
       <c r="T72" s="12" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="U72" s="10" t="s">
         <v>33</v>

--- a/data/50001533 - GESVIAL.xlsx
+++ b/data/50001533 - GESVIAL.xlsx
@@ -5026,7 +5026,7 @@
         <v>46193.765035358796</v>
       </c>
       <c r="D61" s="8">
-        <v>46204.900153703704</v>
+        <v>46270.937854965276</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>225</v>

--- a/data/50001533 - GESVIAL.xlsx
+++ b/data/50001533 - GESVIAL.xlsx
@@ -863,19 +863,19 @@
     <t>Logistica:,Embalaje</t>
   </si>
   <si>
+    <t>1213962383719871</t>
+  </si>
+  <si>
+    <t>Embalaje</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coordinacion Entrega con Cliente,Revisión tableros pruebas y componentes eléctricos </t>
+  </si>
+  <si>
+    <t>Logistica:,PACKING LIST</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1213962383719871</t>
-  </si>
-  <si>
-    <t>Embalaje</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coordinacion Entrega con Cliente,Revisión tableros pruebas y componentes eléctricos </t>
-  </si>
-  <si>
-    <t>Logistica:,PACKING LIST</t>
   </si>
   <si>
     <t>1213962383721160</t>
@@ -5516,7 +5516,7 @@
         <v>46203.81564377315</v>
       </c>
       <c r="D69" s="8">
-        <v>46265.183787766204</v>
+        <v>46273.13226677083</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>249</v>
@@ -5561,8 +5561,8 @@
       <c r="S69" s="9">
         <v>1</v>
       </c>
-      <c r="T69" s="12" t="s">
-        <v>253</v>
+      <c r="T69" s="11" t="s">
+        <v>55</v>
       </c>
       <c r="U69" s="10" t="s">
         <v>33</v>
@@ -5570,7 +5570,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B70" s="5">
         <v>46118.662438252315</v>
@@ -5582,7 +5582,7 @@
         <v>46266.19055326389</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
@@ -5610,10 +5610,10 @@
         <v>246</v>
       </c>
       <c r="O70" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="P70" s="6" t="s">
         <v>256</v>
-      </c>
-      <c r="P70" s="6" t="s">
-        <v>257</v>
       </c>
       <c r="Q70" s="5">
         <v>46273</v>
@@ -5625,7 +5625,7 @@
         <v>1</v>
       </c>
       <c r="T70" s="12" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="U70" s="10" t="s">
         <v>33</v>
@@ -5673,7 +5673,7 @@
         <v>246</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="P71" s="9" t="s">
         <v>262</v>
@@ -5688,7 +5688,7 @@
         <v>1</v>
       </c>
       <c r="T71" s="12" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="U71" s="10" t="s">
         <v>33</v>
@@ -5751,7 +5751,7 @@
         <v>1</v>
       </c>
       <c r="T72" s="12" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="U72" s="10" t="s">
         <v>33</v>

--- a/data/50001533 - GESVIAL.xlsx
+++ b/data/50001533 - GESVIAL.xlsx
@@ -875,22 +875,22 @@
     <t>Logistica:,PACKING LIST</t>
   </si>
   <si>
+    <t>1213962383721160</t>
+  </si>
+  <si>
+    <t>PACKING LIST</t>
+  </si>
+  <si>
+    <t>Nicolás Mol</t>
+  </si>
+  <si>
+    <t>nicolas.mol@zitron.com</t>
+  </si>
+  <si>
+    <t>Logistica:,Despacho</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1213962383721160</t>
-  </si>
-  <si>
-    <t>PACKING LIST</t>
-  </si>
-  <si>
-    <t>Nicolás Mol</t>
-  </si>
-  <si>
-    <t>nicolas.mol@zitron.com</t>
-  </si>
-  <si>
-    <t>Logistica:,Despacho</t>
   </si>
   <si>
     <t>1213964538819735</t>
@@ -5579,7 +5579,7 @@
         <v>46204.89777927083</v>
       </c>
       <c r="D70" s="5">
-        <v>46266.19055326389</v>
+        <v>46274.13525070602</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>254</v>
@@ -5624,8 +5624,8 @@
       <c r="S70" s="6">
         <v>1</v>
       </c>
-      <c r="T70" s="12" t="s">
-        <v>257</v>
+      <c r="T70" s="11" t="s">
+        <v>55</v>
       </c>
       <c r="U70" s="10" t="s">
         <v>33</v>
@@ -5633,7 +5633,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B71" s="8">
         <v>46118.66245149306</v>
@@ -5645,16 +5645,16 @@
         <v>46267.1821840162</v>
       </c>
       <c r="E71" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="F71" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G71" s="9" t="s">
         <v>259</v>
       </c>
-      <c r="F71" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G71" s="9" t="s">
+      <c r="H71" s="9" t="s">
         <v>260</v>
-      </c>
-      <c r="H71" s="9" t="s">
-        <v>261</v>
       </c>
       <c r="I71" s="9"/>
       <c r="J71" s="8">
@@ -5676,7 +5676,7 @@
         <v>254</v>
       </c>
       <c r="P71" s="9" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="Q71" s="8">
         <v>46274</v>
@@ -5688,7 +5688,7 @@
         <v>1</v>
       </c>
       <c r="T71" s="12" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="U71" s="10" t="s">
         <v>33</v>
@@ -5714,10 +5714,10 @@
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="H72" s="6" t="s">
         <v>260</v>
-      </c>
-      <c r="H72" s="6" t="s">
-        <v>261</v>
       </c>
       <c r="I72" s="6"/>
       <c r="J72" s="5">
@@ -5736,7 +5736,7 @@
         <v>246</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="P72" s="6" t="s">
         <v>265</v>
@@ -5751,7 +5751,7 @@
         <v>1</v>
       </c>
       <c r="T72" s="12" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="U72" s="10" t="s">
         <v>33</v>

--- a/data/50001533 - GESVIAL.xlsx
+++ b/data/50001533 - GESVIAL.xlsx
@@ -890,16 +890,16 @@
     <t>Logistica:,Despacho</t>
   </si>
   <si>
+    <t>1213964538819735</t>
+  </si>
+  <si>
+    <t>Despacho</t>
+  </si>
+  <si>
+    <t>Gestion,Costos,Logistica:</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1213964538819735</t>
-  </si>
-  <si>
-    <t>Despacho</t>
-  </si>
-  <si>
-    <t>Gestion,Costos,Logistica:</t>
   </si>
   <si>
     <t>1213964538819755</t>
@@ -5642,7 +5642,7 @@
         <v>46196.9230577662</v>
       </c>
       <c r="D71" s="8">
-        <v>46267.1821840162</v>
+        <v>46275.154988229166</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>258</v>
@@ -5687,8 +5687,8 @@
       <c r="S71" s="9">
         <v>1</v>
       </c>
-      <c r="T71" s="12" t="s">
-        <v>262</v>
+      <c r="T71" s="11" t="s">
+        <v>55</v>
       </c>
       <c r="U71" s="10" t="s">
         <v>33</v>
@@ -5696,7 +5696,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B72" s="5">
         <v>46118.66245769676</v>
@@ -5708,7 +5708,7 @@
         <v>46268.17928672454</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
@@ -5739,7 +5739,7 @@
         <v>258</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="Q72" s="5">
         <v>46275</v>
@@ -5751,7 +5751,7 @@
         <v>1</v>
       </c>
       <c r="T72" s="12" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="U72" s="10" t="s">
         <v>33</v>
@@ -5854,7 +5854,7 @@
         <v>267</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="P74" s="6" t="s">
         <v>267</v>
@@ -5919,7 +5919,7 @@
         <v>267</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="P75" s="9" t="s">
         <v>267</v>

--- a/data/50001533 - GESVIAL.xlsx
+++ b/data/50001533 - GESVIAL.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="913" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="913" uniqueCount="274">
   <si>
     <t xml:space="preserve"> 50001533 - GESVIAL</t>
   </si>
@@ -897,9 +897,6 @@
   </si>
   <si>
     <t>Gestion,Costos,Logistica:</t>
-  </si>
-  <si>
-    <t>Media</t>
   </si>
   <si>
     <t>1213964538819755</t>
@@ -5705,7 +5702,7 @@
         <v>46210.64094128472</v>
       </c>
       <c r="D72" s="5">
-        <v>46268.17928672454</v>
+        <v>46276.15991097222</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>263</v>
@@ -5750,8 +5747,8 @@
       <c r="S72" s="6">
         <v>1</v>
       </c>
-      <c r="T72" s="12" t="s">
-        <v>265</v>
+      <c r="T72" s="11" t="s">
+        <v>55</v>
       </c>
       <c r="U72" s="10" t="s">
         <v>33</v>
@@ -5759,7 +5756,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B73" s="8">
         <v>46118.66246467593</v>
@@ -5771,7 +5768,7 @@
         <v>46251.952298206015</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>25</v>
@@ -5795,7 +5792,7 @@
         <v>26</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="P73" s="9" t="s">
         <v>26</v>
@@ -5812,7 +5809,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B74" s="5">
         <v>46118.66246796296</v>
@@ -5824,16 +5821,16 @@
         <v>46251.95227454861</v>
       </c>
       <c r="E74" s="6" t="s">
+        <v>269</v>
+      </c>
+      <c r="F74" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G74" s="6" t="s">
         <v>270</v>
       </c>
-      <c r="F74" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G74" s="6" t="s">
+      <c r="H74" s="6" t="s">
         <v>271</v>
-      </c>
-      <c r="H74" s="6" t="s">
-        <v>272</v>
       </c>
       <c r="I74" s="5">
         <v>46276</v>
@@ -5851,13 +5848,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="O74" s="6" t="s">
         <v>263</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="Q74" s="5">
         <v>46286</v>
@@ -5877,7 +5874,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B75" s="8">
         <v>46118.66251259259</v>
@@ -5889,16 +5886,16 @@
         <v>46251.95228457176</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="H75" s="9" t="s">
         <v>271</v>
-      </c>
-      <c r="H75" s="9" t="s">
-        <v>272</v>
       </c>
       <c r="I75" s="8">
         <v>46276</v>
@@ -5916,13 +5913,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="O75" s="9" t="s">
         <v>263</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="Q75" s="8">
         <v>46286</v>
